--- a/Quotation_Comparative.xlsx
+++ b/Quotation_Comparative.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Titles" vbProcedure="false">Comparative!$4:$5</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Comparative!$A$5:$U$129</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Comparative!$A$5:$W$129</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="787" uniqueCount="595">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="605">
   <si>
     <t xml:space="preserve">COMPARATIVE STATEMENT OF QUOTATIONS – RFQ (MEDICINES)</t>
   </si>
@@ -66,6 +66,9 @@
     <t xml:space="preserve">NMMC</t>
   </si>
   <si>
+    <t xml:space="preserve">Platinum</t>
+  </si>
+  <si>
     <t xml:space="preserve">No. of Quotes</t>
   </si>
   <si>
@@ -483,6 +486,9 @@
     <t xml:space="preserve">REVOMAT PLUS GEL(KAIZEN)</t>
   </si>
   <si>
+    <t xml:space="preserve">Revomet Plus Gel</t>
+  </si>
+  <si>
     <t xml:space="preserve">99-98-9120027-27-000-000</t>
   </si>
   <si>
@@ -666,6 +672,9 @@
     <t xml:space="preserve">FROBE 100MG TAB</t>
   </si>
   <si>
+    <t xml:space="preserve">Synalgo</t>
+  </si>
+  <si>
     <t xml:space="preserve">99-98-9120013-85-000-000</t>
   </si>
   <si>
@@ -1077,6 +1086,9 @@
     <t xml:space="preserve">SYNFLEX 500MG TABLET</t>
   </si>
   <si>
+    <t xml:space="preserve">Dolonap</t>
+  </si>
+  <si>
     <t xml:space="preserve">99-98-9120019-01-000-000</t>
   </si>
   <si>
@@ -1203,6 +1215,9 @@
     <t xml:space="preserve">LIPIREX 10MG TABLET</t>
   </si>
   <si>
+    <t xml:space="preserve">Statin</t>
+  </si>
+  <si>
     <t xml:space="preserve">99-98-9120018-06-000-000</t>
   </si>
   <si>
@@ -1305,6 +1320,9 @@
     <t xml:space="preserve">FLAGYL (HOECHST/ SANOFI), KLINT (SAMI), METROZINE (SEARLE),GRAMEX (PLATINUM)</t>
   </si>
   <si>
+    <t xml:space="preserve">Gramex</t>
+  </si>
+  <si>
     <t xml:space="preserve">99-98-9120018-01-000-000</t>
   </si>
   <si>
@@ -1377,6 +1395,9 @@
     <t xml:space="preserve">OSNATE-D (OBS/AGP)</t>
   </si>
   <si>
+    <t xml:space="preserve">Ossobon-D</t>
+  </si>
+  <si>
     <t xml:space="preserve">99-98-9120015-49-000-000</t>
   </si>
   <si>
@@ -1464,6 +1485,9 @@
     <t xml:space="preserve">MOTILLIUM (ASPIN)</t>
   </si>
   <si>
+    <t xml:space="preserve">Emiset</t>
+  </si>
+  <si>
     <t xml:space="preserve">99-98-9120015-28-000-000</t>
   </si>
   <si>
@@ -1725,6 +1749,9 @@
     <t xml:space="preserve">MUSCORIL (HOECHST/ SANOFI), COLRIL (SEARLE), MUCOGIN (HORIZON), BRUSPAZ (MCOLSON), RECLINE (PLATINUM)</t>
   </si>
   <si>
+    <t xml:space="preserve">Recline</t>
+  </si>
+  <si>
     <t xml:space="preserve">99-98-9120011-21-000-000</t>
   </si>
   <si>
@@ -1806,10 +1833,13 @@
     <t xml:space="preserve">3. Some vendors stated pack sizes in remarks (e.g. Aslam "6's", "14's") – confirm pack size matches the UOM before award.</t>
   </si>
   <si>
-    <t xml:space="preserve">4. NMMC "NIL" entries are treated as not quoted.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5. Source: vendor RFQ files Ahsan.xls, Aslam.xls, Jamil.xls, Muller.xls, NMMC.xls (rates entered as received).</t>
+    <t xml:space="preserve">4. NMMC "NIL" and Platinum "NA" entries are treated as not quoted.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. Source: vendor RFQ files Ahsan.xls, Aslam.xls, Jamil.xls, Muller.xls, NMMC.xls, Platinum.xls (rates entered as received).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6. Aslam_2.xls was checked cell by cell and is identical to Aslam.xls (same rates, brands, remarks), so it is not shown as a separate vendor.</t>
   </si>
 </sst>
 </file>
@@ -2366,7 +2396,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:U130"/>
+  <dimension ref="A1:W130"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -2384,11 +2414,13 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="30"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2443,17 +2475,21 @@
       <c r="Q4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="R4" s="3" t="s">
+      <c r="R4" s="3"/>
+      <c r="S4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="S4" s="3" t="s">
+      <c r="T4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="T4" s="3" t="s">
+      <c r="U4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U4" s="3" t="s">
+      <c r="V4" s="3" t="s">
         <v>17</v>
+      </c>
+      <c r="W4" s="3" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2464,56 +2500,62 @@
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="I5" s="4" t="s">
-        <v>18</v>
-      </c>
       <c r="J5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="K5" s="4" t="s">
-        <v>18</v>
-      </c>
       <c r="L5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="M5" s="4" t="s">
-        <v>18</v>
-      </c>
       <c r="N5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="O5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="O5" s="4" t="s">
-        <v>18</v>
-      </c>
       <c r="P5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="3"/>
+      <c r="R5" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="S5" s="3"/>
       <c r="T5" s="3"/>
       <c r="U5" s="3"/>
+      <c r="V5" s="3"/>
+      <c r="W5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="n">
         <v>1</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>200</v>
@@ -2528,43 +2570,45 @@
         <v>5525</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O6" s="7"/>
       <c r="P6" s="6"/>
-      <c r="Q6" s="5" t="n">
-        <f aca="false">COUNT(G6,I6,K6,M6,O6)</f>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="6"/>
+      <c r="S6" s="5" t="n">
+        <f aca="false">COUNT(G6,I6,K6,M6,O6,Q6)</f>
         <v>1</v>
       </c>
-      <c r="R6" s="8" t="n">
-        <f aca="false">IF(Q6=0,"",MIN(G6,I6,K6,M6,O6))</f>
+      <c r="T6" s="8" t="n">
+        <f aca="false">IF(S6=0,"",MIN(G6,I6,K6,M6,O6,Q6))</f>
         <v>5525</v>
       </c>
-      <c r="S6" s="9" t="str">
-        <f aca="false">IF(Q6=0,"No quote",LEFT(IF(AND(ISNUMBER(G6),G6=R6),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I6),I6=R6),"Aslam, ","")&amp;IF(AND(ISNUMBER(K6),K6=R6),"Jamil, ","")&amp;IF(AND(ISNUMBER(M6),M6=R6),"Muller, ","")&amp;IF(AND(ISNUMBER(O6),O6=R6),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G6),G6=R6),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I6),I6=R6),"Aslam, ","")&amp;IF(AND(ISNUMBER(K6),K6=R6),"Jamil, ","")&amp;IF(AND(ISNUMBER(M6),M6=R6),"Muller, ","")&amp;IF(AND(ISNUMBER(O6),O6=R6),"NMMC, ",""))-2))</f>
+      <c r="U6" s="9" t="str">
+        <f aca="false">IF(S6=0,"No quote",LEFT(IF(AND(ISNUMBER(G6),G6=T6),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I6),I6=T6),"Aslam, ","")&amp;IF(AND(ISNUMBER(K6),K6=T6),"Jamil, ","")&amp;IF(AND(ISNUMBER(M6),M6=T6),"Muller, ","")&amp;IF(AND(ISNUMBER(O6),O6=T6),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q6),Q6=T6),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G6),G6=T6),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I6),I6=T6),"Aslam, ","")&amp;IF(AND(ISNUMBER(K6),K6=T6),"Jamil, ","")&amp;IF(AND(ISNUMBER(M6),M6=T6),"Muller, ","")&amp;IF(AND(ISNUMBER(O6),O6=T6),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q6),Q6=T6),"Platinum, ",""))-2))</f>
         <v>Muller</v>
       </c>
-      <c r="T6" s="10" t="n">
-        <f aca="false">IF(Q6=0,"",R6*F6)</f>
+      <c r="V6" s="10" t="n">
+        <f aca="false">IF(S6=0,"",T6*F6)</f>
         <v>1105000</v>
       </c>
-      <c r="U6" s="6"/>
+      <c r="W6" s="6"/>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="n">
         <v>2</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>200</v>
@@ -2579,43 +2623,45 @@
         <v>4207.5</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O7" s="7"/>
       <c r="P7" s="6"/>
-      <c r="Q7" s="5" t="n">
-        <f aca="false">COUNT(G7,I7,K7,M7,O7)</f>
+      <c r="Q7" s="7"/>
+      <c r="R7" s="6"/>
+      <c r="S7" s="5" t="n">
+        <f aca="false">COUNT(G7,I7,K7,M7,O7,Q7)</f>
         <v>1</v>
       </c>
-      <c r="R7" s="8" t="n">
-        <f aca="false">IF(Q7=0,"",MIN(G7,I7,K7,M7,O7))</f>
+      <c r="T7" s="8" t="n">
+        <f aca="false">IF(S7=0,"",MIN(G7,I7,K7,M7,O7,Q7))</f>
         <v>4207.5</v>
       </c>
-      <c r="S7" s="9" t="str">
-        <f aca="false">IF(Q7=0,"No quote",LEFT(IF(AND(ISNUMBER(G7),G7=R7),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I7),I7=R7),"Aslam, ","")&amp;IF(AND(ISNUMBER(K7),K7=R7),"Jamil, ","")&amp;IF(AND(ISNUMBER(M7),M7=R7),"Muller, ","")&amp;IF(AND(ISNUMBER(O7),O7=R7),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G7),G7=R7),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I7),I7=R7),"Aslam, ","")&amp;IF(AND(ISNUMBER(K7),K7=R7),"Jamil, ","")&amp;IF(AND(ISNUMBER(M7),M7=R7),"Muller, ","")&amp;IF(AND(ISNUMBER(O7),O7=R7),"NMMC, ",""))-2))</f>
+      <c r="U7" s="9" t="str">
+        <f aca="false">IF(S7=0,"No quote",LEFT(IF(AND(ISNUMBER(G7),G7=T7),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I7),I7=T7),"Aslam, ","")&amp;IF(AND(ISNUMBER(K7),K7=T7),"Jamil, ","")&amp;IF(AND(ISNUMBER(M7),M7=T7),"Muller, ","")&amp;IF(AND(ISNUMBER(O7),O7=T7),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q7),Q7=T7),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G7),G7=T7),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I7),I7=T7),"Aslam, ","")&amp;IF(AND(ISNUMBER(K7),K7=T7),"Jamil, ","")&amp;IF(AND(ISNUMBER(M7),M7=T7),"Muller, ","")&amp;IF(AND(ISNUMBER(O7),O7=T7),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q7),Q7=T7),"Platinum, ",""))-2))</f>
         <v>Muller</v>
       </c>
-      <c r="T7" s="10" t="n">
-        <f aca="false">IF(Q7=0,"",R7*F7)</f>
+      <c r="V7" s="10" t="n">
+        <f aca="false">IF(S7=0,"",T7*F7)</f>
         <v>841500</v>
       </c>
-      <c r="U7" s="6"/>
+      <c r="W7" s="6"/>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="n">
         <v>3</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F8" s="5" t="n">
         <v>100</v>
@@ -2630,43 +2676,45 @@
         <v>3357.5</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O8" s="7"/>
       <c r="P8" s="6"/>
-      <c r="Q8" s="5" t="n">
-        <f aca="false">COUNT(G8,I8,K8,M8,O8)</f>
+      <c r="Q8" s="7"/>
+      <c r="R8" s="6"/>
+      <c r="S8" s="5" t="n">
+        <f aca="false">COUNT(G8,I8,K8,M8,O8,Q8)</f>
         <v>1</v>
       </c>
-      <c r="R8" s="8" t="n">
-        <f aca="false">IF(Q8=0,"",MIN(G8,I8,K8,M8,O8))</f>
+      <c r="T8" s="8" t="n">
+        <f aca="false">IF(S8=0,"",MIN(G8,I8,K8,M8,O8,Q8))</f>
         <v>3357.5</v>
       </c>
-      <c r="S8" s="9" t="str">
-        <f aca="false">IF(Q8=0,"No quote",LEFT(IF(AND(ISNUMBER(G8),G8=R8),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I8),I8=R8),"Aslam, ","")&amp;IF(AND(ISNUMBER(K8),K8=R8),"Jamil, ","")&amp;IF(AND(ISNUMBER(M8),M8=R8),"Muller, ","")&amp;IF(AND(ISNUMBER(O8),O8=R8),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G8),G8=R8),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I8),I8=R8),"Aslam, ","")&amp;IF(AND(ISNUMBER(K8),K8=R8),"Jamil, ","")&amp;IF(AND(ISNUMBER(M8),M8=R8),"Muller, ","")&amp;IF(AND(ISNUMBER(O8),O8=R8),"NMMC, ",""))-2))</f>
+      <c r="U8" s="9" t="str">
+        <f aca="false">IF(S8=0,"No quote",LEFT(IF(AND(ISNUMBER(G8),G8=T8),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I8),I8=T8),"Aslam, ","")&amp;IF(AND(ISNUMBER(K8),K8=T8),"Jamil, ","")&amp;IF(AND(ISNUMBER(M8),M8=T8),"Muller, ","")&amp;IF(AND(ISNUMBER(O8),O8=T8),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q8),Q8=T8),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G8),G8=T8),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I8),I8=T8),"Aslam, ","")&amp;IF(AND(ISNUMBER(K8),K8=T8),"Jamil, ","")&amp;IF(AND(ISNUMBER(M8),M8=T8),"Muller, ","")&amp;IF(AND(ISNUMBER(O8),O8=T8),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q8),Q8=T8),"Platinum, ",""))-2))</f>
         <v>Muller</v>
       </c>
-      <c r="T8" s="10" t="n">
-        <f aca="false">IF(Q8=0,"",R8*F8)</f>
+      <c r="V8" s="10" t="n">
+        <f aca="false">IF(S8=0,"",T8*F8)</f>
         <v>335750</v>
       </c>
-      <c r="U8" s="6"/>
+      <c r="W8" s="6"/>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="n">
         <v>4</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F9" s="5" t="n">
         <v>100</v>
@@ -2681,43 +2729,45 @@
         <v>2507.5</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O9" s="7"/>
       <c r="P9" s="6"/>
-      <c r="Q9" s="5" t="n">
-        <f aca="false">COUNT(G9,I9,K9,M9,O9)</f>
+      <c r="Q9" s="7"/>
+      <c r="R9" s="6"/>
+      <c r="S9" s="5" t="n">
+        <f aca="false">COUNT(G9,I9,K9,M9,O9,Q9)</f>
         <v>1</v>
       </c>
-      <c r="R9" s="8" t="n">
-        <f aca="false">IF(Q9=0,"",MIN(G9,I9,K9,M9,O9))</f>
+      <c r="T9" s="8" t="n">
+        <f aca="false">IF(S9=0,"",MIN(G9,I9,K9,M9,O9,Q9))</f>
         <v>2507.5</v>
       </c>
-      <c r="S9" s="9" t="str">
-        <f aca="false">IF(Q9=0,"No quote",LEFT(IF(AND(ISNUMBER(G9),G9=R9),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I9),I9=R9),"Aslam, ","")&amp;IF(AND(ISNUMBER(K9),K9=R9),"Jamil, ","")&amp;IF(AND(ISNUMBER(M9),M9=R9),"Muller, ","")&amp;IF(AND(ISNUMBER(O9),O9=R9),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G9),G9=R9),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I9),I9=R9),"Aslam, ","")&amp;IF(AND(ISNUMBER(K9),K9=R9),"Jamil, ","")&amp;IF(AND(ISNUMBER(M9),M9=R9),"Muller, ","")&amp;IF(AND(ISNUMBER(O9),O9=R9),"NMMC, ",""))-2))</f>
+      <c r="U9" s="9" t="str">
+        <f aca="false">IF(S9=0,"No quote",LEFT(IF(AND(ISNUMBER(G9),G9=T9),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I9),I9=T9),"Aslam, ","")&amp;IF(AND(ISNUMBER(K9),K9=T9),"Jamil, ","")&amp;IF(AND(ISNUMBER(M9),M9=T9),"Muller, ","")&amp;IF(AND(ISNUMBER(O9),O9=T9),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q9),Q9=T9),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G9),G9=T9),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I9),I9=T9),"Aslam, ","")&amp;IF(AND(ISNUMBER(K9),K9=T9),"Jamil, ","")&amp;IF(AND(ISNUMBER(M9),M9=T9),"Muller, ","")&amp;IF(AND(ISNUMBER(O9),O9=T9),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q9),Q9=T9),"Platinum, ",""))-2))</f>
         <v>Muller</v>
       </c>
-      <c r="T9" s="10" t="n">
-        <f aca="false">IF(Q9=0,"",R9*F9)</f>
+      <c r="V9" s="10" t="n">
+        <f aca="false">IF(S9=0,"",T9*F9)</f>
         <v>250750</v>
       </c>
-      <c r="U9" s="6"/>
+      <c r="W9" s="6"/>
     </row>
     <row r="10" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="n">
         <v>5</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>100</v>
@@ -2726,65 +2776,67 @@
         <v>368.9</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I10" s="7" t="n">
         <v>348.5</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K10" s="7" t="n">
         <v>371.28</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M10" s="7" t="n">
         <v>403.55</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O10" s="7" t="n">
         <v>326.4</v>
       </c>
       <c r="P10" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q10" s="5" t="n">
-        <f aca="false">COUNT(G10,I10,K10,M10,O10)</f>
+        <v>42</v>
+      </c>
+      <c r="Q10" s="7"/>
+      <c r="R10" s="6"/>
+      <c r="S10" s="5" t="n">
+        <f aca="false">COUNT(G10,I10,K10,M10,O10,Q10)</f>
         <v>5</v>
       </c>
-      <c r="R10" s="8" t="n">
-        <f aca="false">IF(Q10=0,"",MIN(G10,I10,K10,M10,O10))</f>
+      <c r="T10" s="8" t="n">
+        <f aca="false">IF(S10=0,"",MIN(G10,I10,K10,M10,O10,Q10))</f>
         <v>326.4</v>
       </c>
-      <c r="S10" s="9" t="str">
-        <f aca="false">IF(Q10=0,"No quote",LEFT(IF(AND(ISNUMBER(G10),G10=R10),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I10),I10=R10),"Aslam, ","")&amp;IF(AND(ISNUMBER(K10),K10=R10),"Jamil, ","")&amp;IF(AND(ISNUMBER(M10),M10=R10),"Muller, ","")&amp;IF(AND(ISNUMBER(O10),O10=R10),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G10),G10=R10),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I10),I10=R10),"Aslam, ","")&amp;IF(AND(ISNUMBER(K10),K10=R10),"Jamil, ","")&amp;IF(AND(ISNUMBER(M10),M10=R10),"Muller, ","")&amp;IF(AND(ISNUMBER(O10),O10=R10),"NMMC, ",""))-2))</f>
+      <c r="U10" s="9" t="str">
+        <f aca="false">IF(S10=0,"No quote",LEFT(IF(AND(ISNUMBER(G10),G10=T10),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I10),I10=T10),"Aslam, ","")&amp;IF(AND(ISNUMBER(K10),K10=T10),"Jamil, ","")&amp;IF(AND(ISNUMBER(M10),M10=T10),"Muller, ","")&amp;IF(AND(ISNUMBER(O10),O10=T10),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q10),Q10=T10),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G10),G10=T10),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I10),I10=T10),"Aslam, ","")&amp;IF(AND(ISNUMBER(K10),K10=T10),"Jamil, ","")&amp;IF(AND(ISNUMBER(M10),M10=T10),"Muller, ","")&amp;IF(AND(ISNUMBER(O10),O10=T10),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q10),Q10=T10),"Platinum, ",""))-2))</f>
         <v>NMMC</v>
       </c>
-      <c r="T10" s="10" t="n">
-        <f aca="false">IF(Q10=0,"",R10*F10)</f>
+      <c r="V10" s="10" t="n">
+        <f aca="false">IF(S10=0,"",T10*F10)</f>
         <v>32640</v>
       </c>
-      <c r="U10" s="6"/>
+      <c r="W10" s="6"/>
     </row>
     <row r="11" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="n">
         <v>6</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F11" s="5" t="n">
         <v>100</v>
@@ -2795,7 +2847,7 @@
         <v>786.25</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K11" s="7"/>
       <c r="L11" s="6"/>
@@ -2803,28 +2855,30 @@
         <v>212.5</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O11" s="7"/>
       <c r="P11" s="6"/>
-      <c r="Q11" s="5" t="n">
-        <f aca="false">COUNT(G11,I11,K11,M11,O11)</f>
+      <c r="Q11" s="7"/>
+      <c r="R11" s="6"/>
+      <c r="S11" s="5" t="n">
+        <f aca="false">COUNT(G11,I11,K11,M11,O11,Q11)</f>
         <v>2</v>
       </c>
-      <c r="R11" s="8" t="n">
-        <f aca="false">IF(Q11=0,"",MIN(G11,I11,K11,M11,O11))</f>
+      <c r="T11" s="8" t="n">
+        <f aca="false">IF(S11=0,"",MIN(G11,I11,K11,M11,O11,Q11))</f>
         <v>212.5</v>
       </c>
-      <c r="S11" s="9" t="str">
-        <f aca="false">IF(Q11=0,"No quote",LEFT(IF(AND(ISNUMBER(G11),G11=R11),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I11),I11=R11),"Aslam, ","")&amp;IF(AND(ISNUMBER(K11),K11=R11),"Jamil, ","")&amp;IF(AND(ISNUMBER(M11),M11=R11),"Muller, ","")&amp;IF(AND(ISNUMBER(O11),O11=R11),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G11),G11=R11),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I11),I11=R11),"Aslam, ","")&amp;IF(AND(ISNUMBER(K11),K11=R11),"Jamil, ","")&amp;IF(AND(ISNUMBER(M11),M11=R11),"Muller, ","")&amp;IF(AND(ISNUMBER(O11),O11=R11),"NMMC, ",""))-2))</f>
+      <c r="U11" s="9" t="str">
+        <f aca="false">IF(S11=0,"No quote",LEFT(IF(AND(ISNUMBER(G11),G11=T11),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I11),I11=T11),"Aslam, ","")&amp;IF(AND(ISNUMBER(K11),K11=T11),"Jamil, ","")&amp;IF(AND(ISNUMBER(M11),M11=T11),"Muller, ","")&amp;IF(AND(ISNUMBER(O11),O11=T11),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q11),Q11=T11),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G11),G11=T11),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I11),I11=T11),"Aslam, ","")&amp;IF(AND(ISNUMBER(K11),K11=T11),"Jamil, ","")&amp;IF(AND(ISNUMBER(M11),M11=T11),"Muller, ","")&amp;IF(AND(ISNUMBER(O11),O11=T11),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q11),Q11=T11),"Platinum, ",""))-2))</f>
         <v>Muller</v>
       </c>
-      <c r="T11" s="10" t="n">
-        <f aca="false">IF(Q11=0,"",R11*F11)</f>
+      <c r="V11" s="10" t="n">
+        <f aca="false">IF(S11=0,"",T11*F11)</f>
         <v>21250</v>
       </c>
-      <c r="U11" s="6" t="s">
-        <v>47</v>
+      <c r="W11" s="6" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2832,16 +2886,16 @@
         <v>7</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F12" s="5" t="n">
         <v>30</v>
@@ -2858,41 +2912,43 @@
         <v>345.02</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q12" s="5" t="n">
-        <f aca="false">COUNT(G12,I12,K12,M12,O12)</f>
+        <v>52</v>
+      </c>
+      <c r="Q12" s="7"/>
+      <c r="R12" s="6"/>
+      <c r="S12" s="5" t="n">
+        <f aca="false">COUNT(G12,I12,K12,M12,O12,Q12)</f>
         <v>1</v>
       </c>
-      <c r="R12" s="8" t="n">
-        <f aca="false">IF(Q12=0,"",MIN(G12,I12,K12,M12,O12))</f>
+      <c r="T12" s="8" t="n">
+        <f aca="false">IF(S12=0,"",MIN(G12,I12,K12,M12,O12,Q12))</f>
         <v>345.02</v>
       </c>
-      <c r="S12" s="9" t="str">
-        <f aca="false">IF(Q12=0,"No quote",LEFT(IF(AND(ISNUMBER(G12),G12=R12),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I12),I12=R12),"Aslam, ","")&amp;IF(AND(ISNUMBER(K12),K12=R12),"Jamil, ","")&amp;IF(AND(ISNUMBER(M12),M12=R12),"Muller, ","")&amp;IF(AND(ISNUMBER(O12),O12=R12),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G12),G12=R12),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I12),I12=R12),"Aslam, ","")&amp;IF(AND(ISNUMBER(K12),K12=R12),"Jamil, ","")&amp;IF(AND(ISNUMBER(M12),M12=R12),"Muller, ","")&amp;IF(AND(ISNUMBER(O12),O12=R12),"NMMC, ",""))-2))</f>
+      <c r="U12" s="9" t="str">
+        <f aca="false">IF(S12=0,"No quote",LEFT(IF(AND(ISNUMBER(G12),G12=T12),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I12),I12=T12),"Aslam, ","")&amp;IF(AND(ISNUMBER(K12),K12=T12),"Jamil, ","")&amp;IF(AND(ISNUMBER(M12),M12=T12),"Muller, ","")&amp;IF(AND(ISNUMBER(O12),O12=T12),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q12),Q12=T12),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G12),G12=T12),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I12),I12=T12),"Aslam, ","")&amp;IF(AND(ISNUMBER(K12),K12=T12),"Jamil, ","")&amp;IF(AND(ISNUMBER(M12),M12=T12),"Muller, ","")&amp;IF(AND(ISNUMBER(O12),O12=T12),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q12),Q12=T12),"Platinum, ",""))-2))</f>
         <v>NMMC</v>
       </c>
-      <c r="T12" s="10" t="n">
-        <f aca="false">IF(Q12=0,"",R12*F12)</f>
+      <c r="V12" s="10" t="n">
+        <f aca="false">IF(S12=0,"",T12*F12)</f>
         <v>10350.6</v>
       </c>
-      <c r="U12" s="6"/>
+      <c r="W12" s="6"/>
     </row>
     <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="n">
         <v>8</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F13" s="5" t="n">
         <v>100</v>
@@ -2901,19 +2957,19 @@
         <v>80.7</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I13" s="7" t="n">
         <v>115.38</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K13" s="7" t="n">
         <v>101.48</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M13" s="7"/>
       <c r="N13" s="6"/>
@@ -2921,41 +2977,43 @@
         <v>124.45</v>
       </c>
       <c r="P13" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q13" s="5" t="n">
-        <f aca="false">COUNT(G13,I13,K13,M13,O13)</f>
+        <v>59</v>
+      </c>
+      <c r="Q13" s="7"/>
+      <c r="R13" s="6"/>
+      <c r="S13" s="5" t="n">
+        <f aca="false">COUNT(G13,I13,K13,M13,O13,Q13)</f>
         <v>4</v>
       </c>
-      <c r="R13" s="8" t="n">
-        <f aca="false">IF(Q13=0,"",MIN(G13,I13,K13,M13,O13))</f>
+      <c r="T13" s="8" t="n">
+        <f aca="false">IF(S13=0,"",MIN(G13,I13,K13,M13,O13,Q13))</f>
         <v>80.7</v>
       </c>
-      <c r="S13" s="9" t="str">
-        <f aca="false">IF(Q13=0,"No quote",LEFT(IF(AND(ISNUMBER(G13),G13=R13),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I13),I13=R13),"Aslam, ","")&amp;IF(AND(ISNUMBER(K13),K13=R13),"Jamil, ","")&amp;IF(AND(ISNUMBER(M13),M13=R13),"Muller, ","")&amp;IF(AND(ISNUMBER(O13),O13=R13),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G13),G13=R13),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I13),I13=R13),"Aslam, ","")&amp;IF(AND(ISNUMBER(K13),K13=R13),"Jamil, ","")&amp;IF(AND(ISNUMBER(M13),M13=R13),"Muller, ","")&amp;IF(AND(ISNUMBER(O13),O13=R13),"NMMC, ",""))-2))</f>
+      <c r="U13" s="9" t="str">
+        <f aca="false">IF(S13=0,"No quote",LEFT(IF(AND(ISNUMBER(G13),G13=T13),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I13),I13=T13),"Aslam, ","")&amp;IF(AND(ISNUMBER(K13),K13=T13),"Jamil, ","")&amp;IF(AND(ISNUMBER(M13),M13=T13),"Muller, ","")&amp;IF(AND(ISNUMBER(O13),O13=T13),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q13),Q13=T13),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G13),G13=T13),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I13),I13=T13),"Aslam, ","")&amp;IF(AND(ISNUMBER(K13),K13=T13),"Jamil, ","")&amp;IF(AND(ISNUMBER(M13),M13=T13),"Muller, ","")&amp;IF(AND(ISNUMBER(O13),O13=T13),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q13),Q13=T13),"Platinum, ",""))-2))</f>
         <v>Ahsan</v>
       </c>
-      <c r="T13" s="10" t="n">
-        <f aca="false">IF(Q13=0,"",R13*F13)</f>
+      <c r="V13" s="10" t="n">
+        <f aca="false">IF(S13=0,"",T13*F13)</f>
         <v>8070</v>
       </c>
-      <c r="U13" s="6"/>
+      <c r="W13" s="6"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="n">
         <v>9</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F14" s="5" t="n">
         <v>100</v>
@@ -2970,39 +3028,41 @@
       <c r="N14" s="6"/>
       <c r="O14" s="7"/>
       <c r="P14" s="6"/>
-      <c r="Q14" s="5" t="n">
-        <f aca="false">COUNT(G14,I14,K14,M14,O14)</f>
+      <c r="Q14" s="7"/>
+      <c r="R14" s="6"/>
+      <c r="S14" s="5" t="n">
+        <f aca="false">COUNT(G14,I14,K14,M14,O14,Q14)</f>
         <v>0</v>
       </c>
-      <c r="R14" s="8" t="str">
-        <f aca="false">IF(Q14=0,"",MIN(G14,I14,K14,M14,O14))</f>
+      <c r="T14" s="8" t="str">
+        <f aca="false">IF(S14=0,"",MIN(G14,I14,K14,M14,O14,Q14))</f>
         <v/>
       </c>
-      <c r="S14" s="9" t="str">
-        <f aca="false">IF(Q14=0,"No quote",LEFT(IF(AND(ISNUMBER(G14),G14=R14),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I14),I14=R14),"Aslam, ","")&amp;IF(AND(ISNUMBER(K14),K14=R14),"Jamil, ","")&amp;IF(AND(ISNUMBER(M14),M14=R14),"Muller, ","")&amp;IF(AND(ISNUMBER(O14),O14=R14),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G14),G14=R14),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I14),I14=R14),"Aslam, ","")&amp;IF(AND(ISNUMBER(K14),K14=R14),"Jamil, ","")&amp;IF(AND(ISNUMBER(M14),M14=R14),"Muller, ","")&amp;IF(AND(ISNUMBER(O14),O14=R14),"NMMC, ",""))-2))</f>
+      <c r="U14" s="9" t="str">
+        <f aca="false">IF(S14=0,"No quote",LEFT(IF(AND(ISNUMBER(G14),G14=T14),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I14),I14=T14),"Aslam, ","")&amp;IF(AND(ISNUMBER(K14),K14=T14),"Jamil, ","")&amp;IF(AND(ISNUMBER(M14),M14=T14),"Muller, ","")&amp;IF(AND(ISNUMBER(O14),O14=T14),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q14),Q14=T14),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G14),G14=T14),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I14),I14=T14),"Aslam, ","")&amp;IF(AND(ISNUMBER(K14),K14=T14),"Jamil, ","")&amp;IF(AND(ISNUMBER(M14),M14=T14),"Muller, ","")&amp;IF(AND(ISNUMBER(O14),O14=T14),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q14),Q14=T14),"Platinum, ",""))-2))</f>
         <v>No quote</v>
       </c>
-      <c r="T14" s="10" t="str">
-        <f aca="false">IF(Q14=0,"",R14*F14)</f>
+      <c r="V14" s="10" t="str">
+        <f aca="false">IF(S14=0,"",T14*F14)</f>
         <v/>
       </c>
-      <c r="U14" s="6"/>
+      <c r="W14" s="6"/>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="n">
         <v>10</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F15" s="5" t="n">
         <v>100</v>
@@ -3015,45 +3075,47 @@
         <v>301.55</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M15" s="7"/>
       <c r="N15" s="6"/>
       <c r="O15" s="7"/>
       <c r="P15" s="6"/>
-      <c r="Q15" s="5" t="n">
-        <f aca="false">COUNT(G15,I15,K15,M15,O15)</f>
+      <c r="Q15" s="7"/>
+      <c r="R15" s="6"/>
+      <c r="S15" s="5" t="n">
+        <f aca="false">COUNT(G15,I15,K15,M15,O15,Q15)</f>
         <v>1</v>
       </c>
-      <c r="R15" s="8" t="n">
-        <f aca="false">IF(Q15=0,"",MIN(G15,I15,K15,M15,O15))</f>
+      <c r="T15" s="8" t="n">
+        <f aca="false">IF(S15=0,"",MIN(G15,I15,K15,M15,O15,Q15))</f>
         <v>301.55</v>
       </c>
-      <c r="S15" s="9" t="str">
-        <f aca="false">IF(Q15=0,"No quote",LEFT(IF(AND(ISNUMBER(G15),G15=R15),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I15),I15=R15),"Aslam, ","")&amp;IF(AND(ISNUMBER(K15),K15=R15),"Jamil, ","")&amp;IF(AND(ISNUMBER(M15),M15=R15),"Muller, ","")&amp;IF(AND(ISNUMBER(O15),O15=R15),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G15),G15=R15),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I15),I15=R15),"Aslam, ","")&amp;IF(AND(ISNUMBER(K15),K15=R15),"Jamil, ","")&amp;IF(AND(ISNUMBER(M15),M15=R15),"Muller, ","")&amp;IF(AND(ISNUMBER(O15),O15=R15),"NMMC, ",""))-2))</f>
+      <c r="U15" s="9" t="str">
+        <f aca="false">IF(S15=0,"No quote",LEFT(IF(AND(ISNUMBER(G15),G15=T15),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I15),I15=T15),"Aslam, ","")&amp;IF(AND(ISNUMBER(K15),K15=T15),"Jamil, ","")&amp;IF(AND(ISNUMBER(M15),M15=T15),"Muller, ","")&amp;IF(AND(ISNUMBER(O15),O15=T15),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q15),Q15=T15),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G15),G15=T15),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I15),I15=T15),"Aslam, ","")&amp;IF(AND(ISNUMBER(K15),K15=T15),"Jamil, ","")&amp;IF(AND(ISNUMBER(M15),M15=T15),"Muller, ","")&amp;IF(AND(ISNUMBER(O15),O15=T15),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q15),Q15=T15),"Platinum, ",""))-2))</f>
         <v>Jamil</v>
       </c>
-      <c r="T15" s="10" t="n">
-        <f aca="false">IF(Q15=0,"",R15*F15)</f>
+      <c r="V15" s="10" t="n">
+        <f aca="false">IF(S15=0,"",T15*F15)</f>
         <v>30155</v>
       </c>
-      <c r="U15" s="6"/>
+      <c r="W15" s="6"/>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="n">
         <v>11</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F16" s="5" t="n">
         <v>200</v>
@@ -3062,13 +3124,13 @@
         <v>195.5</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I16" s="7" t="n">
         <v>212.5</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K16" s="7"/>
       <c r="L16" s="6"/>
@@ -3078,41 +3140,43 @@
         <v>135</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q16" s="5" t="n">
-        <f aca="false">COUNT(G16,I16,K16,M16,O16)</f>
+        <v>72</v>
+      </c>
+      <c r="Q16" s="7"/>
+      <c r="R16" s="6"/>
+      <c r="S16" s="5" t="n">
+        <f aca="false">COUNT(G16,I16,K16,M16,O16,Q16)</f>
         <v>3</v>
       </c>
-      <c r="R16" s="8" t="n">
-        <f aca="false">IF(Q16=0,"",MIN(G16,I16,K16,M16,O16))</f>
+      <c r="T16" s="8" t="n">
+        <f aca="false">IF(S16=0,"",MIN(G16,I16,K16,M16,O16,Q16))</f>
         <v>135</v>
       </c>
-      <c r="S16" s="9" t="str">
-        <f aca="false">IF(Q16=0,"No quote",LEFT(IF(AND(ISNUMBER(G16),G16=R16),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I16),I16=R16),"Aslam, ","")&amp;IF(AND(ISNUMBER(K16),K16=R16),"Jamil, ","")&amp;IF(AND(ISNUMBER(M16),M16=R16),"Muller, ","")&amp;IF(AND(ISNUMBER(O16),O16=R16),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G16),G16=R16),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I16),I16=R16),"Aslam, ","")&amp;IF(AND(ISNUMBER(K16),K16=R16),"Jamil, ","")&amp;IF(AND(ISNUMBER(M16),M16=R16),"Muller, ","")&amp;IF(AND(ISNUMBER(O16),O16=R16),"NMMC, ",""))-2))</f>
+      <c r="U16" s="9" t="str">
+        <f aca="false">IF(S16=0,"No quote",LEFT(IF(AND(ISNUMBER(G16),G16=T16),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I16),I16=T16),"Aslam, ","")&amp;IF(AND(ISNUMBER(K16),K16=T16),"Jamil, ","")&amp;IF(AND(ISNUMBER(M16),M16=T16),"Muller, ","")&amp;IF(AND(ISNUMBER(O16),O16=T16),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q16),Q16=T16),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G16),G16=T16),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I16),I16=T16),"Aslam, ","")&amp;IF(AND(ISNUMBER(K16),K16=T16),"Jamil, ","")&amp;IF(AND(ISNUMBER(M16),M16=T16),"Muller, ","")&amp;IF(AND(ISNUMBER(O16),O16=T16),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q16),Q16=T16),"Platinum, ",""))-2))</f>
         <v>NMMC</v>
       </c>
-      <c r="T16" s="10" t="n">
-        <f aca="false">IF(Q16=0,"",R16*F16)</f>
+      <c r="V16" s="10" t="n">
+        <f aca="false">IF(S16=0,"",T16*F16)</f>
         <v>27000</v>
       </c>
-      <c r="U16" s="6"/>
+      <c r="W16" s="6"/>
     </row>
     <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="n">
         <v>12</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F17" s="5" t="n">
         <v>200</v>
@@ -3125,7 +3189,7 @@
         <v>272</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M17" s="7"/>
       <c r="N17" s="6"/>
@@ -3133,41 +3197,43 @@
         <v>279.898</v>
       </c>
       <c r="P17" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q17" s="5" t="n">
-        <f aca="false">COUNT(G17,I17,K17,M17,O17)</f>
+        <v>77</v>
+      </c>
+      <c r="Q17" s="7"/>
+      <c r="R17" s="6"/>
+      <c r="S17" s="5" t="n">
+        <f aca="false">COUNT(G17,I17,K17,M17,O17,Q17)</f>
         <v>2</v>
       </c>
-      <c r="R17" s="8" t="n">
-        <f aca="false">IF(Q17=0,"",MIN(G17,I17,K17,M17,O17))</f>
+      <c r="T17" s="8" t="n">
+        <f aca="false">IF(S17=0,"",MIN(G17,I17,K17,M17,O17,Q17))</f>
         <v>272</v>
       </c>
-      <c r="S17" s="9" t="str">
-        <f aca="false">IF(Q17=0,"No quote",LEFT(IF(AND(ISNUMBER(G17),G17=R17),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I17),I17=R17),"Aslam, ","")&amp;IF(AND(ISNUMBER(K17),K17=R17),"Jamil, ","")&amp;IF(AND(ISNUMBER(M17),M17=R17),"Muller, ","")&amp;IF(AND(ISNUMBER(O17),O17=R17),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G17),G17=R17),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I17),I17=R17),"Aslam, ","")&amp;IF(AND(ISNUMBER(K17),K17=R17),"Jamil, ","")&amp;IF(AND(ISNUMBER(M17),M17=R17),"Muller, ","")&amp;IF(AND(ISNUMBER(O17),O17=R17),"NMMC, ",""))-2))</f>
+      <c r="U17" s="9" t="str">
+        <f aca="false">IF(S17=0,"No quote",LEFT(IF(AND(ISNUMBER(G17),G17=T17),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I17),I17=T17),"Aslam, ","")&amp;IF(AND(ISNUMBER(K17),K17=T17),"Jamil, ","")&amp;IF(AND(ISNUMBER(M17),M17=T17),"Muller, ","")&amp;IF(AND(ISNUMBER(O17),O17=T17),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q17),Q17=T17),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G17),G17=T17),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I17),I17=T17),"Aslam, ","")&amp;IF(AND(ISNUMBER(K17),K17=T17),"Jamil, ","")&amp;IF(AND(ISNUMBER(M17),M17=T17),"Muller, ","")&amp;IF(AND(ISNUMBER(O17),O17=T17),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q17),Q17=T17),"Platinum, ",""))-2))</f>
         <v>Jamil</v>
       </c>
-      <c r="T17" s="10" t="n">
-        <f aca="false">IF(Q17=0,"",R17*F17)</f>
+      <c r="V17" s="10" t="n">
+        <f aca="false">IF(S17=0,"",T17*F17)</f>
         <v>54400</v>
       </c>
-      <c r="U17" s="6"/>
+      <c r="W17" s="6"/>
     </row>
     <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="n">
         <v>13</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F18" s="5" t="n">
         <v>200</v>
@@ -3178,7 +3244,7 @@
         <v>175.95</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K18" s="7"/>
       <c r="L18" s="6"/>
@@ -3186,39 +3252,41 @@
       <c r="N18" s="6"/>
       <c r="O18" s="7"/>
       <c r="P18" s="6"/>
-      <c r="Q18" s="5" t="n">
-        <f aca="false">COUNT(G18,I18,K18,M18,O18)</f>
+      <c r="Q18" s="7"/>
+      <c r="R18" s="6"/>
+      <c r="S18" s="5" t="n">
+        <f aca="false">COUNT(G18,I18,K18,M18,O18,Q18)</f>
         <v>1</v>
       </c>
-      <c r="R18" s="8" t="n">
-        <f aca="false">IF(Q18=0,"",MIN(G18,I18,K18,M18,O18))</f>
+      <c r="T18" s="8" t="n">
+        <f aca="false">IF(S18=0,"",MIN(G18,I18,K18,M18,O18,Q18))</f>
         <v>175.95</v>
       </c>
-      <c r="S18" s="9" t="str">
-        <f aca="false">IF(Q18=0,"No quote",LEFT(IF(AND(ISNUMBER(G18),G18=R18),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I18),I18=R18),"Aslam, ","")&amp;IF(AND(ISNUMBER(K18),K18=R18),"Jamil, ","")&amp;IF(AND(ISNUMBER(M18),M18=R18),"Muller, ","")&amp;IF(AND(ISNUMBER(O18),O18=R18),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G18),G18=R18),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I18),I18=R18),"Aslam, ","")&amp;IF(AND(ISNUMBER(K18),K18=R18),"Jamil, ","")&amp;IF(AND(ISNUMBER(M18),M18=R18),"Muller, ","")&amp;IF(AND(ISNUMBER(O18),O18=R18),"NMMC, ",""))-2))</f>
+      <c r="U18" s="9" t="str">
+        <f aca="false">IF(S18=0,"No quote",LEFT(IF(AND(ISNUMBER(G18),G18=T18),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I18),I18=T18),"Aslam, ","")&amp;IF(AND(ISNUMBER(K18),K18=T18),"Jamil, ","")&amp;IF(AND(ISNUMBER(M18),M18=T18),"Muller, ","")&amp;IF(AND(ISNUMBER(O18),O18=T18),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q18),Q18=T18),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G18),G18=T18),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I18),I18=T18),"Aslam, ","")&amp;IF(AND(ISNUMBER(K18),K18=T18),"Jamil, ","")&amp;IF(AND(ISNUMBER(M18),M18=T18),"Muller, ","")&amp;IF(AND(ISNUMBER(O18),O18=T18),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q18),Q18=T18),"Platinum, ",""))-2))</f>
         <v>Aslam</v>
       </c>
-      <c r="T18" s="10" t="n">
-        <f aca="false">IF(Q18=0,"",R18*F18)</f>
+      <c r="V18" s="10" t="n">
+        <f aca="false">IF(S18=0,"",T18*F18)</f>
         <v>35190</v>
       </c>
-      <c r="U18" s="6"/>
+      <c r="W18" s="6"/>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="n">
         <v>14</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F19" s="5" t="n">
         <v>50</v>
@@ -3235,41 +3303,43 @@
         <v>316.2</v>
       </c>
       <c r="P19" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q19" s="5" t="n">
-        <f aca="false">COUNT(G19,I19,K19,M19,O19)</f>
+        <v>85</v>
+      </c>
+      <c r="Q19" s="7"/>
+      <c r="R19" s="6"/>
+      <c r="S19" s="5" t="n">
+        <f aca="false">COUNT(G19,I19,K19,M19,O19,Q19)</f>
         <v>1</v>
       </c>
-      <c r="R19" s="8" t="n">
-        <f aca="false">IF(Q19=0,"",MIN(G19,I19,K19,M19,O19))</f>
+      <c r="T19" s="8" t="n">
+        <f aca="false">IF(S19=0,"",MIN(G19,I19,K19,M19,O19,Q19))</f>
         <v>316.2</v>
       </c>
-      <c r="S19" s="9" t="str">
-        <f aca="false">IF(Q19=0,"No quote",LEFT(IF(AND(ISNUMBER(G19),G19=R19),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I19),I19=R19),"Aslam, ","")&amp;IF(AND(ISNUMBER(K19),K19=R19),"Jamil, ","")&amp;IF(AND(ISNUMBER(M19),M19=R19),"Muller, ","")&amp;IF(AND(ISNUMBER(O19),O19=R19),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G19),G19=R19),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I19),I19=R19),"Aslam, ","")&amp;IF(AND(ISNUMBER(K19),K19=R19),"Jamil, ","")&amp;IF(AND(ISNUMBER(M19),M19=R19),"Muller, ","")&amp;IF(AND(ISNUMBER(O19),O19=R19),"NMMC, ",""))-2))</f>
+      <c r="U19" s="9" t="str">
+        <f aca="false">IF(S19=0,"No quote",LEFT(IF(AND(ISNUMBER(G19),G19=T19),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I19),I19=T19),"Aslam, ","")&amp;IF(AND(ISNUMBER(K19),K19=T19),"Jamil, ","")&amp;IF(AND(ISNUMBER(M19),M19=T19),"Muller, ","")&amp;IF(AND(ISNUMBER(O19),O19=T19),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q19),Q19=T19),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G19),G19=T19),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I19),I19=T19),"Aslam, ","")&amp;IF(AND(ISNUMBER(K19),K19=T19),"Jamil, ","")&amp;IF(AND(ISNUMBER(M19),M19=T19),"Muller, ","")&amp;IF(AND(ISNUMBER(O19),O19=T19),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q19),Q19=T19),"Platinum, ",""))-2))</f>
         <v>NMMC</v>
       </c>
-      <c r="T19" s="10" t="n">
-        <f aca="false">IF(Q19=0,"",R19*F19)</f>
+      <c r="V19" s="10" t="n">
+        <f aca="false">IF(S19=0,"",T19*F19)</f>
         <v>15810</v>
       </c>
-      <c r="U19" s="6"/>
+      <c r="W19" s="6"/>
     </row>
     <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="n">
         <v>15</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F20" s="5" t="n">
         <v>300</v>
@@ -3278,7 +3348,7 @@
         <v>620.5</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I20" s="7"/>
       <c r="J20" s="6"/>
@@ -3288,47 +3358,49 @@
         <v>403.75</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O20" s="7" t="n">
         <v>355.536</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q20" s="5" t="n">
-        <f aca="false">COUNT(G20,I20,K20,M20,O20)</f>
+        <v>91</v>
+      </c>
+      <c r="Q20" s="7"/>
+      <c r="R20" s="6"/>
+      <c r="S20" s="5" t="n">
+        <f aca="false">COUNT(G20,I20,K20,M20,O20,Q20)</f>
         <v>3</v>
       </c>
-      <c r="R20" s="8" t="n">
-        <f aca="false">IF(Q20=0,"",MIN(G20,I20,K20,M20,O20))</f>
+      <c r="T20" s="8" t="n">
+        <f aca="false">IF(S20=0,"",MIN(G20,I20,K20,M20,O20,Q20))</f>
         <v>355.536</v>
       </c>
-      <c r="S20" s="9" t="str">
-        <f aca="false">IF(Q20=0,"No quote",LEFT(IF(AND(ISNUMBER(G20),G20=R20),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I20),I20=R20),"Aslam, ","")&amp;IF(AND(ISNUMBER(K20),K20=R20),"Jamil, ","")&amp;IF(AND(ISNUMBER(M20),M20=R20),"Muller, ","")&amp;IF(AND(ISNUMBER(O20),O20=R20),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G20),G20=R20),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I20),I20=R20),"Aslam, ","")&amp;IF(AND(ISNUMBER(K20),K20=R20),"Jamil, ","")&amp;IF(AND(ISNUMBER(M20),M20=R20),"Muller, ","")&amp;IF(AND(ISNUMBER(O20),O20=R20),"NMMC, ",""))-2))</f>
+      <c r="U20" s="9" t="str">
+        <f aca="false">IF(S20=0,"No quote",LEFT(IF(AND(ISNUMBER(G20),G20=T20),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I20),I20=T20),"Aslam, ","")&amp;IF(AND(ISNUMBER(K20),K20=T20),"Jamil, ","")&amp;IF(AND(ISNUMBER(M20),M20=T20),"Muller, ","")&amp;IF(AND(ISNUMBER(O20),O20=T20),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q20),Q20=T20),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G20),G20=T20),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I20),I20=T20),"Aslam, ","")&amp;IF(AND(ISNUMBER(K20),K20=T20),"Jamil, ","")&amp;IF(AND(ISNUMBER(M20),M20=T20),"Muller, ","")&amp;IF(AND(ISNUMBER(O20),O20=T20),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q20),Q20=T20),"Platinum, ",""))-2))</f>
         <v>NMMC</v>
       </c>
-      <c r="T20" s="10" t="n">
-        <f aca="false">IF(Q20=0,"",R20*F20)</f>
+      <c r="V20" s="10" t="n">
+        <f aca="false">IF(S20=0,"",T20*F20)</f>
         <v>106660.8</v>
       </c>
-      <c r="U20" s="6"/>
+      <c r="W20" s="6"/>
     </row>
     <row r="21" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="n">
         <v>16</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F21" s="5" t="n">
         <v>1000</v>
@@ -3337,7 +3409,7 @@
         <v>425.85</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I21" s="7"/>
       <c r="J21" s="6"/>
@@ -3347,47 +3419,49 @@
         <v>306</v>
       </c>
       <c r="N21" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O21" s="7" t="n">
         <v>287.81</v>
       </c>
       <c r="P21" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q21" s="5" t="n">
-        <f aca="false">COUNT(G21,I21,K21,M21,O21)</f>
+        <v>96</v>
+      </c>
+      <c r="Q21" s="7"/>
+      <c r="R21" s="6"/>
+      <c r="S21" s="5" t="n">
+        <f aca="false">COUNT(G21,I21,K21,M21,O21,Q21)</f>
         <v>3</v>
       </c>
-      <c r="R21" s="8" t="n">
-        <f aca="false">IF(Q21=0,"",MIN(G21,I21,K21,M21,O21))</f>
+      <c r="T21" s="8" t="n">
+        <f aca="false">IF(S21=0,"",MIN(G21,I21,K21,M21,O21,Q21))</f>
         <v>287.81</v>
       </c>
-      <c r="S21" s="9" t="str">
-        <f aca="false">IF(Q21=0,"No quote",LEFT(IF(AND(ISNUMBER(G21),G21=R21),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I21),I21=R21),"Aslam, ","")&amp;IF(AND(ISNUMBER(K21),K21=R21),"Jamil, ","")&amp;IF(AND(ISNUMBER(M21),M21=R21),"Muller, ","")&amp;IF(AND(ISNUMBER(O21),O21=R21),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G21),G21=R21),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I21),I21=R21),"Aslam, ","")&amp;IF(AND(ISNUMBER(K21),K21=R21),"Jamil, ","")&amp;IF(AND(ISNUMBER(M21),M21=R21),"Muller, ","")&amp;IF(AND(ISNUMBER(O21),O21=R21),"NMMC, ",""))-2))</f>
+      <c r="U21" s="9" t="str">
+        <f aca="false">IF(S21=0,"No quote",LEFT(IF(AND(ISNUMBER(G21),G21=T21),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I21),I21=T21),"Aslam, ","")&amp;IF(AND(ISNUMBER(K21),K21=T21),"Jamil, ","")&amp;IF(AND(ISNUMBER(M21),M21=T21),"Muller, ","")&amp;IF(AND(ISNUMBER(O21),O21=T21),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q21),Q21=T21),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G21),G21=T21),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I21),I21=T21),"Aslam, ","")&amp;IF(AND(ISNUMBER(K21),K21=T21),"Jamil, ","")&amp;IF(AND(ISNUMBER(M21),M21=T21),"Muller, ","")&amp;IF(AND(ISNUMBER(O21),O21=T21),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q21),Q21=T21),"Platinum, ",""))-2))</f>
         <v>NMMC</v>
       </c>
-      <c r="T21" s="10" t="n">
-        <f aca="false">IF(Q21=0,"",R21*F21)</f>
+      <c r="V21" s="10" t="n">
+        <f aca="false">IF(S21=0,"",T21*F21)</f>
         <v>287810</v>
       </c>
-      <c r="U21" s="6"/>
+      <c r="W21" s="6"/>
     </row>
     <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="n">
         <v>17</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F22" s="5" t="n">
         <v>100</v>
@@ -3396,7 +3470,7 @@
         <v>127.5</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I22" s="7"/>
       <c r="J22" s="6"/>
@@ -3406,47 +3480,49 @@
         <v>212.5</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O22" s="7" t="n">
         <v>115.6</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="Q22" s="5" t="n">
-        <f aca="false">COUNT(G22,I22,K22,M22,O22)</f>
+        <v>102</v>
+      </c>
+      <c r="Q22" s="7"/>
+      <c r="R22" s="6"/>
+      <c r="S22" s="5" t="n">
+        <f aca="false">COUNT(G22,I22,K22,M22,O22,Q22)</f>
         <v>3</v>
       </c>
-      <c r="R22" s="8" t="n">
-        <f aca="false">IF(Q22=0,"",MIN(G22,I22,K22,M22,O22))</f>
+      <c r="T22" s="8" t="n">
+        <f aca="false">IF(S22=0,"",MIN(G22,I22,K22,M22,O22,Q22))</f>
         <v>115.6</v>
       </c>
-      <c r="S22" s="9" t="str">
-        <f aca="false">IF(Q22=0,"No quote",LEFT(IF(AND(ISNUMBER(G22),G22=R22),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I22),I22=R22),"Aslam, ","")&amp;IF(AND(ISNUMBER(K22),K22=R22),"Jamil, ","")&amp;IF(AND(ISNUMBER(M22),M22=R22),"Muller, ","")&amp;IF(AND(ISNUMBER(O22),O22=R22),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G22),G22=R22),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I22),I22=R22),"Aslam, ","")&amp;IF(AND(ISNUMBER(K22),K22=R22),"Jamil, ","")&amp;IF(AND(ISNUMBER(M22),M22=R22),"Muller, ","")&amp;IF(AND(ISNUMBER(O22),O22=R22),"NMMC, ",""))-2))</f>
+      <c r="U22" s="9" t="str">
+        <f aca="false">IF(S22=0,"No quote",LEFT(IF(AND(ISNUMBER(G22),G22=T22),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I22),I22=T22),"Aslam, ","")&amp;IF(AND(ISNUMBER(K22),K22=T22),"Jamil, ","")&amp;IF(AND(ISNUMBER(M22),M22=T22),"Muller, ","")&amp;IF(AND(ISNUMBER(O22),O22=T22),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q22),Q22=T22),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G22),G22=T22),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I22),I22=T22),"Aslam, ","")&amp;IF(AND(ISNUMBER(K22),K22=T22),"Jamil, ","")&amp;IF(AND(ISNUMBER(M22),M22=T22),"Muller, ","")&amp;IF(AND(ISNUMBER(O22),O22=T22),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q22),Q22=T22),"Platinum, ",""))-2))</f>
         <v>NMMC</v>
       </c>
-      <c r="T22" s="10" t="n">
-        <f aca="false">IF(Q22=0,"",R22*F22)</f>
+      <c r="V22" s="10" t="n">
+        <f aca="false">IF(S22=0,"",T22*F22)</f>
         <v>11560</v>
       </c>
-      <c r="U22" s="6"/>
+      <c r="W22" s="6"/>
     </row>
     <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="n">
         <v>18</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F23" s="5" t="n">
         <v>500</v>
@@ -3463,47 +3539,49 @@
         <v>348.5</v>
       </c>
       <c r="N23" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O23" s="7" t="n">
         <v>164.543</v>
       </c>
       <c r="P23" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q23" s="5" t="n">
-        <f aca="false">COUNT(G23,I23,K23,M23,O23)</f>
+        <v>107</v>
+      </c>
+      <c r="Q23" s="7"/>
+      <c r="R23" s="6"/>
+      <c r="S23" s="5" t="n">
+        <f aca="false">COUNT(G23,I23,K23,M23,O23,Q23)</f>
         <v>3</v>
       </c>
-      <c r="R23" s="8" t="n">
-        <f aca="false">IF(Q23=0,"",MIN(G23,I23,K23,M23,O23))</f>
+      <c r="T23" s="8" t="n">
+        <f aca="false">IF(S23=0,"",MIN(G23,I23,K23,M23,O23,Q23))</f>
         <v>164.543</v>
       </c>
-      <c r="S23" s="9" t="str">
-        <f aca="false">IF(Q23=0,"No quote",LEFT(IF(AND(ISNUMBER(G23),G23=R23),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I23),I23=R23),"Aslam, ","")&amp;IF(AND(ISNUMBER(K23),K23=R23),"Jamil, ","")&amp;IF(AND(ISNUMBER(M23),M23=R23),"Muller, ","")&amp;IF(AND(ISNUMBER(O23),O23=R23),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G23),G23=R23),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I23),I23=R23),"Aslam, ","")&amp;IF(AND(ISNUMBER(K23),K23=R23),"Jamil, ","")&amp;IF(AND(ISNUMBER(M23),M23=R23),"Muller, ","")&amp;IF(AND(ISNUMBER(O23),O23=R23),"NMMC, ",""))-2))</f>
+      <c r="U23" s="9" t="str">
+        <f aca="false">IF(S23=0,"No quote",LEFT(IF(AND(ISNUMBER(G23),G23=T23),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I23),I23=T23),"Aslam, ","")&amp;IF(AND(ISNUMBER(K23),K23=T23),"Jamil, ","")&amp;IF(AND(ISNUMBER(M23),M23=T23),"Muller, ","")&amp;IF(AND(ISNUMBER(O23),O23=T23),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q23),Q23=T23),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G23),G23=T23),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I23),I23=T23),"Aslam, ","")&amp;IF(AND(ISNUMBER(K23),K23=T23),"Jamil, ","")&amp;IF(AND(ISNUMBER(M23),M23=T23),"Muller, ","")&amp;IF(AND(ISNUMBER(O23),O23=T23),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q23),Q23=T23),"Platinum, ",""))-2))</f>
         <v>NMMC</v>
       </c>
-      <c r="T23" s="10" t="n">
-        <f aca="false">IF(Q23=0,"",R23*F23)</f>
+      <c r="V23" s="10" t="n">
+        <f aca="false">IF(S23=0,"",T23*F23)</f>
         <v>82271.5</v>
       </c>
-      <c r="U23" s="6"/>
+      <c r="W23" s="6"/>
     </row>
     <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="n">
         <v>19</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F24" s="5" t="n">
         <v>100</v>
@@ -3512,7 +3590,7 @@
         <v>1015.75</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I24" s="7"/>
       <c r="J24" s="6"/>
@@ -3524,41 +3602,43 @@
         <v>294.53</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q24" s="5" t="n">
-        <f aca="false">COUNT(G24,I24,K24,M24,O24)</f>
+        <v>112</v>
+      </c>
+      <c r="Q24" s="7"/>
+      <c r="R24" s="6"/>
+      <c r="S24" s="5" t="n">
+        <f aca="false">COUNT(G24,I24,K24,M24,O24,Q24)</f>
         <v>2</v>
       </c>
-      <c r="R24" s="8" t="n">
-        <f aca="false">IF(Q24=0,"",MIN(G24,I24,K24,M24,O24))</f>
+      <c r="T24" s="8" t="n">
+        <f aca="false">IF(S24=0,"",MIN(G24,I24,K24,M24,O24,Q24))</f>
         <v>294.53</v>
       </c>
-      <c r="S24" s="9" t="str">
-        <f aca="false">IF(Q24=0,"No quote",LEFT(IF(AND(ISNUMBER(G24),G24=R24),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I24),I24=R24),"Aslam, ","")&amp;IF(AND(ISNUMBER(K24),K24=R24),"Jamil, ","")&amp;IF(AND(ISNUMBER(M24),M24=R24),"Muller, ","")&amp;IF(AND(ISNUMBER(O24),O24=R24),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G24),G24=R24),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I24),I24=R24),"Aslam, ","")&amp;IF(AND(ISNUMBER(K24),K24=R24),"Jamil, ","")&amp;IF(AND(ISNUMBER(M24),M24=R24),"Muller, ","")&amp;IF(AND(ISNUMBER(O24),O24=R24),"NMMC, ",""))-2))</f>
+      <c r="U24" s="9" t="str">
+        <f aca="false">IF(S24=0,"No quote",LEFT(IF(AND(ISNUMBER(G24),G24=T24),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I24),I24=T24),"Aslam, ","")&amp;IF(AND(ISNUMBER(K24),K24=T24),"Jamil, ","")&amp;IF(AND(ISNUMBER(M24),M24=T24),"Muller, ","")&amp;IF(AND(ISNUMBER(O24),O24=T24),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q24),Q24=T24),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G24),G24=T24),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I24),I24=T24),"Aslam, ","")&amp;IF(AND(ISNUMBER(K24),K24=T24),"Jamil, ","")&amp;IF(AND(ISNUMBER(M24),M24=T24),"Muller, ","")&amp;IF(AND(ISNUMBER(O24),O24=T24),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q24),Q24=T24),"Platinum, ",""))-2))</f>
         <v>NMMC</v>
       </c>
-      <c r="T24" s="10" t="n">
-        <f aca="false">IF(Q24=0,"",R24*F24)</f>
+      <c r="V24" s="10" t="n">
+        <f aca="false">IF(S24=0,"",T24*F24)</f>
         <v>29453</v>
       </c>
-      <c r="U24" s="6"/>
+      <c r="W24" s="6"/>
     </row>
     <row r="25" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="n">
         <v>20</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F25" s="5" t="n">
         <v>300</v>
@@ -3567,7 +3647,7 @@
         <v>348.5</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I25" s="7"/>
       <c r="J25" s="6"/>
@@ -3577,47 +3657,49 @@
         <v>291.04</v>
       </c>
       <c r="N25" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O25" s="7" t="n">
         <v>152.405</v>
       </c>
       <c r="P25" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q25" s="5" t="n">
-        <f aca="false">COUNT(G25,I25,K25,M25,O25)</f>
+        <v>118</v>
+      </c>
+      <c r="Q25" s="7"/>
+      <c r="R25" s="6"/>
+      <c r="S25" s="5" t="n">
+        <f aca="false">COUNT(G25,I25,K25,M25,O25,Q25)</f>
         <v>3</v>
       </c>
-      <c r="R25" s="8" t="n">
-        <f aca="false">IF(Q25=0,"",MIN(G25,I25,K25,M25,O25))</f>
+      <c r="T25" s="8" t="n">
+        <f aca="false">IF(S25=0,"",MIN(G25,I25,K25,M25,O25,Q25))</f>
         <v>152.405</v>
       </c>
-      <c r="S25" s="9" t="str">
-        <f aca="false">IF(Q25=0,"No quote",LEFT(IF(AND(ISNUMBER(G25),G25=R25),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I25),I25=R25),"Aslam, ","")&amp;IF(AND(ISNUMBER(K25),K25=R25),"Jamil, ","")&amp;IF(AND(ISNUMBER(M25),M25=R25),"Muller, ","")&amp;IF(AND(ISNUMBER(O25),O25=R25),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G25),G25=R25),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I25),I25=R25),"Aslam, ","")&amp;IF(AND(ISNUMBER(K25),K25=R25),"Jamil, ","")&amp;IF(AND(ISNUMBER(M25),M25=R25),"Muller, ","")&amp;IF(AND(ISNUMBER(O25),O25=R25),"NMMC, ",""))-2))</f>
+      <c r="U25" s="9" t="str">
+        <f aca="false">IF(S25=0,"No quote",LEFT(IF(AND(ISNUMBER(G25),G25=T25),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I25),I25=T25),"Aslam, ","")&amp;IF(AND(ISNUMBER(K25),K25=T25),"Jamil, ","")&amp;IF(AND(ISNUMBER(M25),M25=T25),"Muller, ","")&amp;IF(AND(ISNUMBER(O25),O25=T25),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q25),Q25=T25),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G25),G25=T25),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I25),I25=T25),"Aslam, ","")&amp;IF(AND(ISNUMBER(K25),K25=T25),"Jamil, ","")&amp;IF(AND(ISNUMBER(M25),M25=T25),"Muller, ","")&amp;IF(AND(ISNUMBER(O25),O25=T25),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q25),Q25=T25),"Platinum, ",""))-2))</f>
         <v>NMMC</v>
       </c>
-      <c r="T25" s="10" t="n">
-        <f aca="false">IF(Q25=0,"",R25*F25)</f>
+      <c r="V25" s="10" t="n">
+        <f aca="false">IF(S25=0,"",T25*F25)</f>
         <v>45721.5</v>
       </c>
-      <c r="U25" s="6"/>
+      <c r="W25" s="6"/>
     </row>
     <row r="26" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="n">
         <v>21</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F26" s="5" t="n">
         <v>35</v>
@@ -3628,7 +3710,7 @@
         <v>578</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K26" s="7"/>
       <c r="L26" s="6"/>
@@ -3636,47 +3718,49 @@
         <v>509.32</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O26" s="7" t="n">
         <v>387.6</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="Q26" s="5" t="n">
-        <f aca="false">COUNT(G26,I26,K26,M26,O26)</f>
+        <v>123</v>
+      </c>
+      <c r="Q26" s="7"/>
+      <c r="R26" s="6"/>
+      <c r="S26" s="5" t="n">
+        <f aca="false">COUNT(G26,I26,K26,M26,O26,Q26)</f>
         <v>3</v>
       </c>
-      <c r="R26" s="8" t="n">
-        <f aca="false">IF(Q26=0,"",MIN(G26,I26,K26,M26,O26))</f>
+      <c r="T26" s="8" t="n">
+        <f aca="false">IF(S26=0,"",MIN(G26,I26,K26,M26,O26,Q26))</f>
         <v>387.6</v>
       </c>
-      <c r="S26" s="9" t="str">
-        <f aca="false">IF(Q26=0,"No quote",LEFT(IF(AND(ISNUMBER(G26),G26=R26),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I26),I26=R26),"Aslam, ","")&amp;IF(AND(ISNUMBER(K26),K26=R26),"Jamil, ","")&amp;IF(AND(ISNUMBER(M26),M26=R26),"Muller, ","")&amp;IF(AND(ISNUMBER(O26),O26=R26),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G26),G26=R26),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I26),I26=R26),"Aslam, ","")&amp;IF(AND(ISNUMBER(K26),K26=R26),"Jamil, ","")&amp;IF(AND(ISNUMBER(M26),M26=R26),"Muller, ","")&amp;IF(AND(ISNUMBER(O26),O26=R26),"NMMC, ",""))-2))</f>
+      <c r="U26" s="9" t="str">
+        <f aca="false">IF(S26=0,"No quote",LEFT(IF(AND(ISNUMBER(G26),G26=T26),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I26),I26=T26),"Aslam, ","")&amp;IF(AND(ISNUMBER(K26),K26=T26),"Jamil, ","")&amp;IF(AND(ISNUMBER(M26),M26=T26),"Muller, ","")&amp;IF(AND(ISNUMBER(O26),O26=T26),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q26),Q26=T26),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G26),G26=T26),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I26),I26=T26),"Aslam, ","")&amp;IF(AND(ISNUMBER(K26),K26=T26),"Jamil, ","")&amp;IF(AND(ISNUMBER(M26),M26=T26),"Muller, ","")&amp;IF(AND(ISNUMBER(O26),O26=T26),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q26),Q26=T26),"Platinum, ",""))-2))</f>
         <v>NMMC</v>
       </c>
-      <c r="T26" s="10" t="n">
-        <f aca="false">IF(Q26=0,"",R26*F26)</f>
+      <c r="V26" s="10" t="n">
+        <f aca="false">IF(S26=0,"",T26*F26)</f>
         <v>13566</v>
       </c>
-      <c r="U26" s="6"/>
+      <c r="W26" s="6"/>
     </row>
     <row r="27" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="n">
         <v>22</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F27" s="5" t="n">
         <v>50</v>
@@ -3685,7 +3769,7 @@
         <v>403.75</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I27" s="7"/>
       <c r="J27" s="6"/>
@@ -3695,47 +3779,49 @@
         <v>516.757</v>
       </c>
       <c r="N27" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O27" s="7" t="n">
         <v>267.75</v>
       </c>
       <c r="P27" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="Q27" s="5" t="n">
-        <f aca="false">COUNT(G27,I27,K27,M27,O27)</f>
+        <v>129</v>
+      </c>
+      <c r="Q27" s="7"/>
+      <c r="R27" s="6"/>
+      <c r="S27" s="5" t="n">
+        <f aca="false">COUNT(G27,I27,K27,M27,O27,Q27)</f>
         <v>3</v>
       </c>
-      <c r="R27" s="8" t="n">
-        <f aca="false">IF(Q27=0,"",MIN(G27,I27,K27,M27,O27))</f>
+      <c r="T27" s="8" t="n">
+        <f aca="false">IF(S27=0,"",MIN(G27,I27,K27,M27,O27,Q27))</f>
         <v>267.75</v>
       </c>
-      <c r="S27" s="9" t="str">
-        <f aca="false">IF(Q27=0,"No quote",LEFT(IF(AND(ISNUMBER(G27),G27=R27),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I27),I27=R27),"Aslam, ","")&amp;IF(AND(ISNUMBER(K27),K27=R27),"Jamil, ","")&amp;IF(AND(ISNUMBER(M27),M27=R27),"Muller, ","")&amp;IF(AND(ISNUMBER(O27),O27=R27),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G27),G27=R27),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I27),I27=R27),"Aslam, ","")&amp;IF(AND(ISNUMBER(K27),K27=R27),"Jamil, ","")&amp;IF(AND(ISNUMBER(M27),M27=R27),"Muller, ","")&amp;IF(AND(ISNUMBER(O27),O27=R27),"NMMC, ",""))-2))</f>
+      <c r="U27" s="9" t="str">
+        <f aca="false">IF(S27=0,"No quote",LEFT(IF(AND(ISNUMBER(G27),G27=T27),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I27),I27=T27),"Aslam, ","")&amp;IF(AND(ISNUMBER(K27),K27=T27),"Jamil, ","")&amp;IF(AND(ISNUMBER(M27),M27=T27),"Muller, ","")&amp;IF(AND(ISNUMBER(O27),O27=T27),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q27),Q27=T27),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G27),G27=T27),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I27),I27=T27),"Aslam, ","")&amp;IF(AND(ISNUMBER(K27),K27=T27),"Jamil, ","")&amp;IF(AND(ISNUMBER(M27),M27=T27),"Muller, ","")&amp;IF(AND(ISNUMBER(O27),O27=T27),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q27),Q27=T27),"Platinum, ",""))-2))</f>
         <v>NMMC</v>
       </c>
-      <c r="T27" s="10" t="n">
-        <f aca="false">IF(Q27=0,"",R27*F27)</f>
+      <c r="V27" s="10" t="n">
+        <f aca="false">IF(S27=0,"",T27*F27)</f>
         <v>13387.5</v>
       </c>
-      <c r="U27" s="6"/>
+      <c r="W27" s="6"/>
     </row>
     <row r="28" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="n">
         <v>23</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F28" s="5" t="n">
         <v>1000</v>
@@ -3744,50 +3830,52 @@
         <v>408</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I28" s="7" t="n">
         <v>425</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K28" s="7" t="n">
         <v>333.2</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M28" s="7" t="n">
         <v>357</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O28" s="7" t="n">
         <v>306</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="Q28" s="5" t="n">
-        <f aca="false">COUNT(G28,I28,K28,M28,O28)</f>
+        <v>134</v>
+      </c>
+      <c r="Q28" s="7"/>
+      <c r="R28" s="6"/>
+      <c r="S28" s="5" t="n">
+        <f aca="false">COUNT(G28,I28,K28,M28,O28,Q28)</f>
         <v>5</v>
       </c>
-      <c r="R28" s="8" t="n">
-        <f aca="false">IF(Q28=0,"",MIN(G28,I28,K28,M28,O28))</f>
+      <c r="T28" s="8" t="n">
+        <f aca="false">IF(S28=0,"",MIN(G28,I28,K28,M28,O28,Q28))</f>
         <v>306</v>
       </c>
-      <c r="S28" s="9" t="str">
-        <f aca="false">IF(Q28=0,"No quote",LEFT(IF(AND(ISNUMBER(G28),G28=R28),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I28),I28=R28),"Aslam, ","")&amp;IF(AND(ISNUMBER(K28),K28=R28),"Jamil, ","")&amp;IF(AND(ISNUMBER(M28),M28=R28),"Muller, ","")&amp;IF(AND(ISNUMBER(O28),O28=R28),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G28),G28=R28),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I28),I28=R28),"Aslam, ","")&amp;IF(AND(ISNUMBER(K28),K28=R28),"Jamil, ","")&amp;IF(AND(ISNUMBER(M28),M28=R28),"Muller, ","")&amp;IF(AND(ISNUMBER(O28),O28=R28),"NMMC, ",""))-2))</f>
+      <c r="U28" s="9" t="str">
+        <f aca="false">IF(S28=0,"No quote",LEFT(IF(AND(ISNUMBER(G28),G28=T28),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I28),I28=T28),"Aslam, ","")&amp;IF(AND(ISNUMBER(K28),K28=T28),"Jamil, ","")&amp;IF(AND(ISNUMBER(M28),M28=T28),"Muller, ","")&amp;IF(AND(ISNUMBER(O28),O28=T28),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q28),Q28=T28),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G28),G28=T28),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I28),I28=T28),"Aslam, ","")&amp;IF(AND(ISNUMBER(K28),K28=T28),"Jamil, ","")&amp;IF(AND(ISNUMBER(M28),M28=T28),"Muller, ","")&amp;IF(AND(ISNUMBER(O28),O28=T28),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q28),Q28=T28),"Platinum, ",""))-2))</f>
         <v>NMMC</v>
       </c>
-      <c r="T28" s="10" t="n">
-        <f aca="false">IF(Q28=0,"",R28*F28)</f>
+      <c r="V28" s="10" t="n">
+        <f aca="false">IF(S28=0,"",T28*F28)</f>
         <v>306000</v>
       </c>
-      <c r="U28" s="6" t="s">
-        <v>134</v>
+      <c r="W28" s="6" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3795,16 +3883,16 @@
         <v>24</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F29" s="5" t="n">
         <v>300</v>
@@ -3817,53 +3905,55 @@
         <v>245.48</v>
       </c>
       <c r="L29" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M29" s="7" t="n">
         <v>261.8</v>
       </c>
       <c r="N29" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O29" s="7" t="n">
         <v>111.69</v>
       </c>
       <c r="P29" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="Q29" s="5" t="n">
-        <f aca="false">COUNT(G29,I29,K29,M29,O29)</f>
+        <v>141</v>
+      </c>
+      <c r="Q29" s="7"/>
+      <c r="R29" s="6"/>
+      <c r="S29" s="5" t="n">
+        <f aca="false">COUNT(G29,I29,K29,M29,O29,Q29)</f>
         <v>3</v>
       </c>
-      <c r="R29" s="8" t="n">
-        <f aca="false">IF(Q29=0,"",MIN(G29,I29,K29,M29,O29))</f>
+      <c r="T29" s="8" t="n">
+        <f aca="false">IF(S29=0,"",MIN(G29,I29,K29,M29,O29,Q29))</f>
         <v>111.69</v>
       </c>
-      <c r="S29" s="9" t="str">
-        <f aca="false">IF(Q29=0,"No quote",LEFT(IF(AND(ISNUMBER(G29),G29=R29),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I29),I29=R29),"Aslam, ","")&amp;IF(AND(ISNUMBER(K29),K29=R29),"Jamil, ","")&amp;IF(AND(ISNUMBER(M29),M29=R29),"Muller, ","")&amp;IF(AND(ISNUMBER(O29),O29=R29),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G29),G29=R29),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I29),I29=R29),"Aslam, ","")&amp;IF(AND(ISNUMBER(K29),K29=R29),"Jamil, ","")&amp;IF(AND(ISNUMBER(M29),M29=R29),"Muller, ","")&amp;IF(AND(ISNUMBER(O29),O29=R29),"NMMC, ",""))-2))</f>
+      <c r="U29" s="9" t="str">
+        <f aca="false">IF(S29=0,"No quote",LEFT(IF(AND(ISNUMBER(G29),G29=T29),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I29),I29=T29),"Aslam, ","")&amp;IF(AND(ISNUMBER(K29),K29=T29),"Jamil, ","")&amp;IF(AND(ISNUMBER(M29),M29=T29),"Muller, ","")&amp;IF(AND(ISNUMBER(O29),O29=T29),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q29),Q29=T29),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G29),G29=T29),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I29),I29=T29),"Aslam, ","")&amp;IF(AND(ISNUMBER(K29),K29=T29),"Jamil, ","")&amp;IF(AND(ISNUMBER(M29),M29=T29),"Muller, ","")&amp;IF(AND(ISNUMBER(O29),O29=T29),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q29),Q29=T29),"Platinum, ",""))-2))</f>
         <v>NMMC</v>
       </c>
-      <c r="T29" s="10" t="n">
-        <f aca="false">IF(Q29=0,"",R29*F29)</f>
+      <c r="V29" s="10" t="n">
+        <f aca="false">IF(S29=0,"",T29*F29)</f>
         <v>33507</v>
       </c>
-      <c r="U29" s="6"/>
+      <c r="W29" s="6"/>
     </row>
     <row r="30" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="n">
         <v>25</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F30" s="5" t="n">
         <v>100</v>
@@ -3876,45 +3966,47 @@
         <v>267.75</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M30" s="7"/>
       <c r="N30" s="6"/>
       <c r="O30" s="7"/>
       <c r="P30" s="6"/>
-      <c r="Q30" s="5" t="n">
-        <f aca="false">COUNT(G30,I30,K30,M30,O30)</f>
+      <c r="Q30" s="7"/>
+      <c r="R30" s="6"/>
+      <c r="S30" s="5" t="n">
+        <f aca="false">COUNT(G30,I30,K30,M30,O30,Q30)</f>
         <v>1</v>
       </c>
-      <c r="R30" s="8" t="n">
-        <f aca="false">IF(Q30=0,"",MIN(G30,I30,K30,M30,O30))</f>
+      <c r="T30" s="8" t="n">
+        <f aca="false">IF(S30=0,"",MIN(G30,I30,K30,M30,O30,Q30))</f>
         <v>267.75</v>
       </c>
-      <c r="S30" s="9" t="str">
-        <f aca="false">IF(Q30=0,"No quote",LEFT(IF(AND(ISNUMBER(G30),G30=R30),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I30),I30=R30),"Aslam, ","")&amp;IF(AND(ISNUMBER(K30),K30=R30),"Jamil, ","")&amp;IF(AND(ISNUMBER(M30),M30=R30),"Muller, ","")&amp;IF(AND(ISNUMBER(O30),O30=R30),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G30),G30=R30),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I30),I30=R30),"Aslam, ","")&amp;IF(AND(ISNUMBER(K30),K30=R30),"Jamil, ","")&amp;IF(AND(ISNUMBER(M30),M30=R30),"Muller, ","")&amp;IF(AND(ISNUMBER(O30),O30=R30),"NMMC, ",""))-2))</f>
+      <c r="U30" s="9" t="str">
+        <f aca="false">IF(S30=0,"No quote",LEFT(IF(AND(ISNUMBER(G30),G30=T30),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I30),I30=T30),"Aslam, ","")&amp;IF(AND(ISNUMBER(K30),K30=T30),"Jamil, ","")&amp;IF(AND(ISNUMBER(M30),M30=T30),"Muller, ","")&amp;IF(AND(ISNUMBER(O30),O30=T30),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q30),Q30=T30),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G30),G30=T30),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I30),I30=T30),"Aslam, ","")&amp;IF(AND(ISNUMBER(K30),K30=T30),"Jamil, ","")&amp;IF(AND(ISNUMBER(M30),M30=T30),"Muller, ","")&amp;IF(AND(ISNUMBER(O30),O30=T30),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q30),Q30=T30),"Platinum, ",""))-2))</f>
         <v>Jamil</v>
       </c>
-      <c r="T30" s="10" t="n">
-        <f aca="false">IF(Q30=0,"",R30*F30)</f>
+      <c r="V30" s="10" t="n">
+        <f aca="false">IF(S30=0,"",T30*F30)</f>
         <v>26775</v>
       </c>
-      <c r="U30" s="6"/>
+      <c r="W30" s="6"/>
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="n">
         <v>26</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F31" s="5" t="n">
         <v>100</v>
@@ -3931,41 +4023,43 @@
         <v>147.9</v>
       </c>
       <c r="P31" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="Q31" s="5" t="n">
-        <f aca="false">COUNT(G31,I31,K31,M31,O31)</f>
+        <v>149</v>
+      </c>
+      <c r="Q31" s="7"/>
+      <c r="R31" s="6"/>
+      <c r="S31" s="5" t="n">
+        <f aca="false">COUNT(G31,I31,K31,M31,O31,Q31)</f>
         <v>1</v>
       </c>
-      <c r="R31" s="8" t="n">
-        <f aca="false">IF(Q31=0,"",MIN(G31,I31,K31,M31,O31))</f>
+      <c r="T31" s="8" t="n">
+        <f aca="false">IF(S31=0,"",MIN(G31,I31,K31,M31,O31,Q31))</f>
         <v>147.9</v>
       </c>
-      <c r="S31" s="9" t="str">
-        <f aca="false">IF(Q31=0,"No quote",LEFT(IF(AND(ISNUMBER(G31),G31=R31),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I31),I31=R31),"Aslam, ","")&amp;IF(AND(ISNUMBER(K31),K31=R31),"Jamil, ","")&amp;IF(AND(ISNUMBER(M31),M31=R31),"Muller, ","")&amp;IF(AND(ISNUMBER(O31),O31=R31),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G31),G31=R31),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I31),I31=R31),"Aslam, ","")&amp;IF(AND(ISNUMBER(K31),K31=R31),"Jamil, ","")&amp;IF(AND(ISNUMBER(M31),M31=R31),"Muller, ","")&amp;IF(AND(ISNUMBER(O31),O31=R31),"NMMC, ",""))-2))</f>
+      <c r="U31" s="9" t="str">
+        <f aca="false">IF(S31=0,"No quote",LEFT(IF(AND(ISNUMBER(G31),G31=T31),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I31),I31=T31),"Aslam, ","")&amp;IF(AND(ISNUMBER(K31),K31=T31),"Jamil, ","")&amp;IF(AND(ISNUMBER(M31),M31=T31),"Muller, ","")&amp;IF(AND(ISNUMBER(O31),O31=T31),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q31),Q31=T31),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G31),G31=T31),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I31),I31=T31),"Aslam, ","")&amp;IF(AND(ISNUMBER(K31),K31=T31),"Jamil, ","")&amp;IF(AND(ISNUMBER(M31),M31=T31),"Muller, ","")&amp;IF(AND(ISNUMBER(O31),O31=T31),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q31),Q31=T31),"Platinum, ",""))-2))</f>
         <v>NMMC</v>
       </c>
-      <c r="T31" s="10" t="n">
-        <f aca="false">IF(Q31=0,"",R31*F31)</f>
+      <c r="V31" s="10" t="n">
+        <f aca="false">IF(S31=0,"",T31*F31)</f>
         <v>14790</v>
       </c>
-      <c r="U31" s="6"/>
+      <c r="W31" s="6"/>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="n">
         <v>27</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F32" s="5" t="n">
         <v>100</v>
@@ -3980,39 +4074,45 @@
       <c r="N32" s="6"/>
       <c r="O32" s="7"/>
       <c r="P32" s="6"/>
-      <c r="Q32" s="5" t="n">
-        <f aca="false">COUNT(G32,I32,K32,M32,O32)</f>
-        <v>0</v>
-      </c>
-      <c r="R32" s="8" t="str">
-        <f aca="false">IF(Q32=0,"",MIN(G32,I32,K32,M32,O32))</f>
-        <v/>
-      </c>
-      <c r="S32" s="9" t="str">
-        <f aca="false">IF(Q32=0,"No quote",LEFT(IF(AND(ISNUMBER(G32),G32=R32),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I32),I32=R32),"Aslam, ","")&amp;IF(AND(ISNUMBER(K32),K32=R32),"Jamil, ","")&amp;IF(AND(ISNUMBER(M32),M32=R32),"Muller, ","")&amp;IF(AND(ISNUMBER(O32),O32=R32),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G32),G32=R32),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I32),I32=R32),"Aslam, ","")&amp;IF(AND(ISNUMBER(K32),K32=R32),"Jamil, ","")&amp;IF(AND(ISNUMBER(M32),M32=R32),"Muller, ","")&amp;IF(AND(ISNUMBER(O32),O32=R32),"NMMC, ",""))-2))</f>
-        <v>No quote</v>
-      </c>
-      <c r="T32" s="10" t="str">
-        <f aca="false">IF(Q32=0,"",R32*F32)</f>
-        <v/>
-      </c>
-      <c r="U32" s="6"/>
+      <c r="Q32" s="7" t="n">
+        <v>343.19</v>
+      </c>
+      <c r="R32" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="S32" s="5" t="n">
+        <f aca="false">COUNT(G32,I32,K32,M32,O32,Q32)</f>
+        <v>1</v>
+      </c>
+      <c r="T32" s="8" t="n">
+        <f aca="false">IF(S32=0,"",MIN(G32,I32,K32,M32,O32,Q32))</f>
+        <v>343.19</v>
+      </c>
+      <c r="U32" s="9" t="str">
+        <f aca="false">IF(S32=0,"No quote",LEFT(IF(AND(ISNUMBER(G32),G32=T32),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I32),I32=T32),"Aslam, ","")&amp;IF(AND(ISNUMBER(K32),K32=T32),"Jamil, ","")&amp;IF(AND(ISNUMBER(M32),M32=T32),"Muller, ","")&amp;IF(AND(ISNUMBER(O32),O32=T32),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q32),Q32=T32),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G32),G32=T32),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I32),I32=T32),"Aslam, ","")&amp;IF(AND(ISNUMBER(K32),K32=T32),"Jamil, ","")&amp;IF(AND(ISNUMBER(M32),M32=T32),"Muller, ","")&amp;IF(AND(ISNUMBER(O32),O32=T32),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q32),Q32=T32),"Platinum, ",""))-2))</f>
+        <v>Platinum</v>
+      </c>
+      <c r="V32" s="10" t="n">
+        <f aca="false">IF(S32=0,"",T32*F32)</f>
+        <v>34319</v>
+      </c>
+      <c r="W32" s="6"/>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="n">
         <v>28</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F33" s="5" t="n">
         <v>2500</v>
@@ -4027,47 +4127,49 @@
         <v>743.4</v>
       </c>
       <c r="N33" s="6" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="O33" s="7" t="n">
         <v>329.73</v>
       </c>
       <c r="P33" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q33" s="5" t="n">
-        <f aca="false">COUNT(G33,I33,K33,M33,O33)</f>
+        <v>158</v>
+      </c>
+      <c r="Q33" s="7"/>
+      <c r="R33" s="6"/>
+      <c r="S33" s="5" t="n">
+        <f aca="false">COUNT(G33,I33,K33,M33,O33,Q33)</f>
         <v>2</v>
       </c>
-      <c r="R33" s="8" t="n">
-        <f aca="false">IF(Q33=0,"",MIN(G33,I33,K33,M33,O33))</f>
+      <c r="T33" s="8" t="n">
+        <f aca="false">IF(S33=0,"",MIN(G33,I33,K33,M33,O33,Q33))</f>
         <v>329.73</v>
       </c>
-      <c r="S33" s="9" t="str">
-        <f aca="false">IF(Q33=0,"No quote",LEFT(IF(AND(ISNUMBER(G33),G33=R33),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I33),I33=R33),"Aslam, ","")&amp;IF(AND(ISNUMBER(K33),K33=R33),"Jamil, ","")&amp;IF(AND(ISNUMBER(M33),M33=R33),"Muller, ","")&amp;IF(AND(ISNUMBER(O33),O33=R33),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G33),G33=R33),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I33),I33=R33),"Aslam, ","")&amp;IF(AND(ISNUMBER(K33),K33=R33),"Jamil, ","")&amp;IF(AND(ISNUMBER(M33),M33=R33),"Muller, ","")&amp;IF(AND(ISNUMBER(O33),O33=R33),"NMMC, ",""))-2))</f>
+      <c r="U33" s="9" t="str">
+        <f aca="false">IF(S33=0,"No quote",LEFT(IF(AND(ISNUMBER(G33),G33=T33),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I33),I33=T33),"Aslam, ","")&amp;IF(AND(ISNUMBER(K33),K33=T33),"Jamil, ","")&amp;IF(AND(ISNUMBER(M33),M33=T33),"Muller, ","")&amp;IF(AND(ISNUMBER(O33),O33=T33),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q33),Q33=T33),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G33),G33=T33),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I33),I33=T33),"Aslam, ","")&amp;IF(AND(ISNUMBER(K33),K33=T33),"Jamil, ","")&amp;IF(AND(ISNUMBER(M33),M33=T33),"Muller, ","")&amp;IF(AND(ISNUMBER(O33),O33=T33),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q33),Q33=T33),"Platinum, ",""))-2))</f>
         <v>NMMC</v>
       </c>
-      <c r="T33" s="10" t="n">
-        <f aca="false">IF(Q33=0,"",R33*F33)</f>
+      <c r="V33" s="10" t="n">
+        <f aca="false">IF(S33=0,"",T33*F33)</f>
         <v>824325</v>
       </c>
-      <c r="U33" s="6"/>
+      <c r="W33" s="6"/>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="n">
         <v>29</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F34" s="5" t="n">
         <v>50</v>
@@ -4080,7 +4182,7 @@
         <v>153.53</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="M34" s="7"/>
       <c r="N34" s="6"/>
@@ -4088,41 +4190,43 @@
         <v>102</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="Q34" s="5" t="n">
-        <f aca="false">COUNT(G34,I34,K34,M34,O34)</f>
+        <v>163</v>
+      </c>
+      <c r="Q34" s="7"/>
+      <c r="R34" s="6"/>
+      <c r="S34" s="5" t="n">
+        <f aca="false">COUNT(G34,I34,K34,M34,O34,Q34)</f>
         <v>2</v>
       </c>
-      <c r="R34" s="8" t="n">
-        <f aca="false">IF(Q34=0,"",MIN(G34,I34,K34,M34,O34))</f>
+      <c r="T34" s="8" t="n">
+        <f aca="false">IF(S34=0,"",MIN(G34,I34,K34,M34,O34,Q34))</f>
         <v>102</v>
       </c>
-      <c r="S34" s="9" t="str">
-        <f aca="false">IF(Q34=0,"No quote",LEFT(IF(AND(ISNUMBER(G34),G34=R34),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I34),I34=R34),"Aslam, ","")&amp;IF(AND(ISNUMBER(K34),K34=R34),"Jamil, ","")&amp;IF(AND(ISNUMBER(M34),M34=R34),"Muller, ","")&amp;IF(AND(ISNUMBER(O34),O34=R34),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G34),G34=R34),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I34),I34=R34),"Aslam, ","")&amp;IF(AND(ISNUMBER(K34),K34=R34),"Jamil, ","")&amp;IF(AND(ISNUMBER(M34),M34=R34),"Muller, ","")&amp;IF(AND(ISNUMBER(O34),O34=R34),"NMMC, ",""))-2))</f>
+      <c r="U34" s="9" t="str">
+        <f aca="false">IF(S34=0,"No quote",LEFT(IF(AND(ISNUMBER(G34),G34=T34),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I34),I34=T34),"Aslam, ","")&amp;IF(AND(ISNUMBER(K34),K34=T34),"Jamil, ","")&amp;IF(AND(ISNUMBER(M34),M34=T34),"Muller, ","")&amp;IF(AND(ISNUMBER(O34),O34=T34),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q34),Q34=T34),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G34),G34=T34),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I34),I34=T34),"Aslam, ","")&amp;IF(AND(ISNUMBER(K34),K34=T34),"Jamil, ","")&amp;IF(AND(ISNUMBER(M34),M34=T34),"Muller, ","")&amp;IF(AND(ISNUMBER(O34),O34=T34),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q34),Q34=T34),"Platinum, ",""))-2))</f>
         <v>NMMC</v>
       </c>
-      <c r="T34" s="10" t="n">
-        <f aca="false">IF(Q34=0,"",R34*F34)</f>
+      <c r="V34" s="10" t="n">
+        <f aca="false">IF(S34=0,"",T34*F34)</f>
         <v>5100</v>
       </c>
-      <c r="U34" s="6"/>
+      <c r="W34" s="6"/>
     </row>
     <row r="35" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="n">
         <v>30</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F35" s="5" t="n">
         <v>200</v>
@@ -4133,59 +4237,61 @@
         <v>254.27</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K35" s="7" t="n">
         <v>254.29</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="M35" s="7" t="n">
         <v>165.82</v>
       </c>
       <c r="N35" s="6" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="O35" s="7" t="n">
         <v>153.43</v>
       </c>
       <c r="P35" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="Q35" s="5" t="n">
-        <f aca="false">COUNT(G35,I35,K35,M35,O35)</f>
+        <v>169</v>
+      </c>
+      <c r="Q35" s="7"/>
+      <c r="R35" s="6"/>
+      <c r="S35" s="5" t="n">
+        <f aca="false">COUNT(G35,I35,K35,M35,O35,Q35)</f>
         <v>4</v>
       </c>
-      <c r="R35" s="8" t="n">
-        <f aca="false">IF(Q35=0,"",MIN(G35,I35,K35,M35,O35))</f>
+      <c r="T35" s="8" t="n">
+        <f aca="false">IF(S35=0,"",MIN(G35,I35,K35,M35,O35,Q35))</f>
         <v>153.43</v>
       </c>
-      <c r="S35" s="9" t="str">
-        <f aca="false">IF(Q35=0,"No quote",LEFT(IF(AND(ISNUMBER(G35),G35=R35),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I35),I35=R35),"Aslam, ","")&amp;IF(AND(ISNUMBER(K35),K35=R35),"Jamil, ","")&amp;IF(AND(ISNUMBER(M35),M35=R35),"Muller, ","")&amp;IF(AND(ISNUMBER(O35),O35=R35),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G35),G35=R35),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I35),I35=R35),"Aslam, ","")&amp;IF(AND(ISNUMBER(K35),K35=R35),"Jamil, ","")&amp;IF(AND(ISNUMBER(M35),M35=R35),"Muller, ","")&amp;IF(AND(ISNUMBER(O35),O35=R35),"NMMC, ",""))-2))</f>
+      <c r="U35" s="9" t="str">
+        <f aca="false">IF(S35=0,"No quote",LEFT(IF(AND(ISNUMBER(G35),G35=T35),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I35),I35=T35),"Aslam, ","")&amp;IF(AND(ISNUMBER(K35),K35=T35),"Jamil, ","")&amp;IF(AND(ISNUMBER(M35),M35=T35),"Muller, ","")&amp;IF(AND(ISNUMBER(O35),O35=T35),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q35),Q35=T35),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G35),G35=T35),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I35),I35=T35),"Aslam, ","")&amp;IF(AND(ISNUMBER(K35),K35=T35),"Jamil, ","")&amp;IF(AND(ISNUMBER(M35),M35=T35),"Muller, ","")&amp;IF(AND(ISNUMBER(O35),O35=T35),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q35),Q35=T35),"Platinum, ",""))-2))</f>
         <v>NMMC</v>
       </c>
-      <c r="T35" s="10" t="n">
-        <f aca="false">IF(Q35=0,"",R35*F35)</f>
+      <c r="V35" s="10" t="n">
+        <f aca="false">IF(S35=0,"",T35*F35)</f>
         <v>30686</v>
       </c>
-      <c r="U35" s="6"/>
+      <c r="W35" s="6"/>
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="n">
         <v>31</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F36" s="5" t="n">
         <v>200</v>
@@ -4198,45 +4304,47 @@
         <v>109.96</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M36" s="7"/>
       <c r="N36" s="6"/>
       <c r="O36" s="7"/>
       <c r="P36" s="6"/>
-      <c r="Q36" s="5" t="n">
-        <f aca="false">COUNT(G36,I36,K36,M36,O36)</f>
+      <c r="Q36" s="7"/>
+      <c r="R36" s="6"/>
+      <c r="S36" s="5" t="n">
+        <f aca="false">COUNT(G36,I36,K36,M36,O36,Q36)</f>
         <v>1</v>
       </c>
-      <c r="R36" s="8" t="n">
-        <f aca="false">IF(Q36=0,"",MIN(G36,I36,K36,M36,O36))</f>
+      <c r="T36" s="8" t="n">
+        <f aca="false">IF(S36=0,"",MIN(G36,I36,K36,M36,O36,Q36))</f>
         <v>109.96</v>
       </c>
-      <c r="S36" s="9" t="str">
-        <f aca="false">IF(Q36=0,"No quote",LEFT(IF(AND(ISNUMBER(G36),G36=R36),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I36),I36=R36),"Aslam, ","")&amp;IF(AND(ISNUMBER(K36),K36=R36),"Jamil, ","")&amp;IF(AND(ISNUMBER(M36),M36=R36),"Muller, ","")&amp;IF(AND(ISNUMBER(O36),O36=R36),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G36),G36=R36),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I36),I36=R36),"Aslam, ","")&amp;IF(AND(ISNUMBER(K36),K36=R36),"Jamil, ","")&amp;IF(AND(ISNUMBER(M36),M36=R36),"Muller, ","")&amp;IF(AND(ISNUMBER(O36),O36=R36),"NMMC, ",""))-2))</f>
+      <c r="U36" s="9" t="str">
+        <f aca="false">IF(S36=0,"No quote",LEFT(IF(AND(ISNUMBER(G36),G36=T36),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I36),I36=T36),"Aslam, ","")&amp;IF(AND(ISNUMBER(K36),K36=T36),"Jamil, ","")&amp;IF(AND(ISNUMBER(M36),M36=T36),"Muller, ","")&amp;IF(AND(ISNUMBER(O36),O36=T36),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q36),Q36=T36),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G36),G36=T36),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I36),I36=T36),"Aslam, ","")&amp;IF(AND(ISNUMBER(K36),K36=T36),"Jamil, ","")&amp;IF(AND(ISNUMBER(M36),M36=T36),"Muller, ","")&amp;IF(AND(ISNUMBER(O36),O36=T36),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q36),Q36=T36),"Platinum, ",""))-2))</f>
         <v>Jamil</v>
       </c>
-      <c r="T36" s="10" t="n">
-        <f aca="false">IF(Q36=0,"",R36*F36)</f>
+      <c r="V36" s="10" t="n">
+        <f aca="false">IF(S36=0,"",T36*F36)</f>
         <v>21992</v>
       </c>
-      <c r="U36" s="6"/>
+      <c r="W36" s="6"/>
     </row>
     <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="n">
         <v>32</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F37" s="5" t="n">
         <v>50</v>
@@ -4251,39 +4359,41 @@
       <c r="N37" s="6"/>
       <c r="O37" s="7"/>
       <c r="P37" s="6"/>
-      <c r="Q37" s="5" t="n">
-        <f aca="false">COUNT(G37,I37,K37,M37,O37)</f>
+      <c r="Q37" s="7"/>
+      <c r="R37" s="6"/>
+      <c r="S37" s="5" t="n">
+        <f aca="false">COUNT(G37,I37,K37,M37,O37,Q37)</f>
         <v>0</v>
       </c>
-      <c r="R37" s="8" t="str">
-        <f aca="false">IF(Q37=0,"",MIN(G37,I37,K37,M37,O37))</f>
+      <c r="T37" s="8" t="str">
+        <f aca="false">IF(S37=0,"",MIN(G37,I37,K37,M37,O37,Q37))</f>
         <v/>
       </c>
-      <c r="S37" s="9" t="str">
-        <f aca="false">IF(Q37=0,"No quote",LEFT(IF(AND(ISNUMBER(G37),G37=R37),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I37),I37=R37),"Aslam, ","")&amp;IF(AND(ISNUMBER(K37),K37=R37),"Jamil, ","")&amp;IF(AND(ISNUMBER(M37),M37=R37),"Muller, ","")&amp;IF(AND(ISNUMBER(O37),O37=R37),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G37),G37=R37),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I37),I37=R37),"Aslam, ","")&amp;IF(AND(ISNUMBER(K37),K37=R37),"Jamil, ","")&amp;IF(AND(ISNUMBER(M37),M37=R37),"Muller, ","")&amp;IF(AND(ISNUMBER(O37),O37=R37),"NMMC, ",""))-2))</f>
+      <c r="U37" s="9" t="str">
+        <f aca="false">IF(S37=0,"No quote",LEFT(IF(AND(ISNUMBER(G37),G37=T37),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I37),I37=T37),"Aslam, ","")&amp;IF(AND(ISNUMBER(K37),K37=T37),"Jamil, ","")&amp;IF(AND(ISNUMBER(M37),M37=T37),"Muller, ","")&amp;IF(AND(ISNUMBER(O37),O37=T37),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q37),Q37=T37),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G37),G37=T37),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I37),I37=T37),"Aslam, ","")&amp;IF(AND(ISNUMBER(K37),K37=T37),"Jamil, ","")&amp;IF(AND(ISNUMBER(M37),M37=T37),"Muller, ","")&amp;IF(AND(ISNUMBER(O37),O37=T37),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q37),Q37=T37),"Platinum, ",""))-2))</f>
         <v>No quote</v>
       </c>
-      <c r="T37" s="10" t="str">
-        <f aca="false">IF(Q37=0,"",R37*F37)</f>
+      <c r="V37" s="10" t="str">
+        <f aca="false">IF(S37=0,"",T37*F37)</f>
         <v/>
       </c>
-      <c r="U37" s="6"/>
+      <c r="W37" s="6"/>
     </row>
     <row r="38" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="n">
         <v>33</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F38" s="5" t="n">
         <v>50</v>
@@ -4292,13 +4402,13 @@
         <v>335.75</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I38" s="7" t="n">
         <v>382.5</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K38" s="7"/>
       <c r="L38" s="6"/>
@@ -4306,47 +4416,49 @@
         <v>552.5</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="O38" s="7" t="n">
         <v>251.6</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="Q38" s="5" t="n">
-        <f aca="false">COUNT(G38,I38,K38,M38,O38)</f>
+        <v>181</v>
+      </c>
+      <c r="Q38" s="7"/>
+      <c r="R38" s="6"/>
+      <c r="S38" s="5" t="n">
+        <f aca="false">COUNT(G38,I38,K38,M38,O38,Q38)</f>
         <v>4</v>
       </c>
-      <c r="R38" s="8" t="n">
-        <f aca="false">IF(Q38=0,"",MIN(G38,I38,K38,M38,O38))</f>
+      <c r="T38" s="8" t="n">
+        <f aca="false">IF(S38=0,"",MIN(G38,I38,K38,M38,O38,Q38))</f>
         <v>251.6</v>
       </c>
-      <c r="S38" s="9" t="str">
-        <f aca="false">IF(Q38=0,"No quote",LEFT(IF(AND(ISNUMBER(G38),G38=R38),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I38),I38=R38),"Aslam, ","")&amp;IF(AND(ISNUMBER(K38),K38=R38),"Jamil, ","")&amp;IF(AND(ISNUMBER(M38),M38=R38),"Muller, ","")&amp;IF(AND(ISNUMBER(O38),O38=R38),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G38),G38=R38),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I38),I38=R38),"Aslam, ","")&amp;IF(AND(ISNUMBER(K38),K38=R38),"Jamil, ","")&amp;IF(AND(ISNUMBER(M38),M38=R38),"Muller, ","")&amp;IF(AND(ISNUMBER(O38),O38=R38),"NMMC, ",""))-2))</f>
+      <c r="U38" s="9" t="str">
+        <f aca="false">IF(S38=0,"No quote",LEFT(IF(AND(ISNUMBER(G38),G38=T38),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I38),I38=T38),"Aslam, ","")&amp;IF(AND(ISNUMBER(K38),K38=T38),"Jamil, ","")&amp;IF(AND(ISNUMBER(M38),M38=T38),"Muller, ","")&amp;IF(AND(ISNUMBER(O38),O38=T38),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q38),Q38=T38),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G38),G38=T38),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I38),I38=T38),"Aslam, ","")&amp;IF(AND(ISNUMBER(K38),K38=T38),"Jamil, ","")&amp;IF(AND(ISNUMBER(M38),M38=T38),"Muller, ","")&amp;IF(AND(ISNUMBER(O38),O38=T38),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q38),Q38=T38),"Platinum, ",""))-2))</f>
         <v>NMMC</v>
       </c>
-      <c r="T38" s="10" t="n">
-        <f aca="false">IF(Q38=0,"",R38*F38)</f>
+      <c r="V38" s="10" t="n">
+        <f aca="false">IF(S38=0,"",T38*F38)</f>
         <v>12580</v>
       </c>
-      <c r="U38" s="6"/>
+      <c r="W38" s="6"/>
     </row>
     <row r="39" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="n">
         <v>34</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F39" s="5" t="n">
         <v>500</v>
@@ -4355,13 +4467,13 @@
         <v>187</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="I39" s="7" t="n">
         <v>170</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K39" s="7"/>
       <c r="L39" s="6"/>
@@ -4369,47 +4481,49 @@
         <v>262.65</v>
       </c>
       <c r="N39" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="O39" s="7" t="n">
         <v>144.5</v>
       </c>
       <c r="P39" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="Q39" s="5" t="n">
-        <f aca="false">COUNT(G39,I39,K39,M39,O39)</f>
+        <v>187</v>
+      </c>
+      <c r="Q39" s="7"/>
+      <c r="R39" s="6"/>
+      <c r="S39" s="5" t="n">
+        <f aca="false">COUNT(G39,I39,K39,M39,O39,Q39)</f>
         <v>4</v>
       </c>
-      <c r="R39" s="8" t="n">
-        <f aca="false">IF(Q39=0,"",MIN(G39,I39,K39,M39,O39))</f>
+      <c r="T39" s="8" t="n">
+        <f aca="false">IF(S39=0,"",MIN(G39,I39,K39,M39,O39,Q39))</f>
         <v>144.5</v>
       </c>
-      <c r="S39" s="9" t="str">
-        <f aca="false">IF(Q39=0,"No quote",LEFT(IF(AND(ISNUMBER(G39),G39=R39),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I39),I39=R39),"Aslam, ","")&amp;IF(AND(ISNUMBER(K39),K39=R39),"Jamil, ","")&amp;IF(AND(ISNUMBER(M39),M39=R39),"Muller, ","")&amp;IF(AND(ISNUMBER(O39),O39=R39),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G39),G39=R39),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I39),I39=R39),"Aslam, ","")&amp;IF(AND(ISNUMBER(K39),K39=R39),"Jamil, ","")&amp;IF(AND(ISNUMBER(M39),M39=R39),"Muller, ","")&amp;IF(AND(ISNUMBER(O39),O39=R39),"NMMC, ",""))-2))</f>
+      <c r="U39" s="9" t="str">
+        <f aca="false">IF(S39=0,"No quote",LEFT(IF(AND(ISNUMBER(G39),G39=T39),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I39),I39=T39),"Aslam, ","")&amp;IF(AND(ISNUMBER(K39),K39=T39),"Jamil, ","")&amp;IF(AND(ISNUMBER(M39),M39=T39),"Muller, ","")&amp;IF(AND(ISNUMBER(O39),O39=T39),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q39),Q39=T39),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G39),G39=T39),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I39),I39=T39),"Aslam, ","")&amp;IF(AND(ISNUMBER(K39),K39=T39),"Jamil, ","")&amp;IF(AND(ISNUMBER(M39),M39=T39),"Muller, ","")&amp;IF(AND(ISNUMBER(O39),O39=T39),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q39),Q39=T39),"Platinum, ",""))-2))</f>
         <v>NMMC</v>
       </c>
-      <c r="T39" s="10" t="n">
-        <f aca="false">IF(Q39=0,"",R39*F39)</f>
+      <c r="V39" s="10" t="n">
+        <f aca="false">IF(S39=0,"",T39*F39)</f>
         <v>72250</v>
       </c>
-      <c r="U39" s="6"/>
+      <c r="W39" s="6"/>
     </row>
     <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="n">
         <v>35</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F40" s="5" t="n">
         <v>50</v>
@@ -4424,39 +4538,41 @@
       <c r="N40" s="6"/>
       <c r="O40" s="7"/>
       <c r="P40" s="6"/>
-      <c r="Q40" s="5" t="n">
-        <f aca="false">COUNT(G40,I40,K40,M40,O40)</f>
+      <c r="Q40" s="7"/>
+      <c r="R40" s="6"/>
+      <c r="S40" s="5" t="n">
+        <f aca="false">COUNT(G40,I40,K40,M40,O40,Q40)</f>
         <v>0</v>
       </c>
-      <c r="R40" s="8" t="str">
-        <f aca="false">IF(Q40=0,"",MIN(G40,I40,K40,M40,O40))</f>
+      <c r="T40" s="8" t="str">
+        <f aca="false">IF(S40=0,"",MIN(G40,I40,K40,M40,O40,Q40))</f>
         <v/>
       </c>
-      <c r="S40" s="9" t="str">
-        <f aca="false">IF(Q40=0,"No quote",LEFT(IF(AND(ISNUMBER(G40),G40=R40),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I40),I40=R40),"Aslam, ","")&amp;IF(AND(ISNUMBER(K40),K40=R40),"Jamil, ","")&amp;IF(AND(ISNUMBER(M40),M40=R40),"Muller, ","")&amp;IF(AND(ISNUMBER(O40),O40=R40),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G40),G40=R40),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I40),I40=R40),"Aslam, ","")&amp;IF(AND(ISNUMBER(K40),K40=R40),"Jamil, ","")&amp;IF(AND(ISNUMBER(M40),M40=R40),"Muller, ","")&amp;IF(AND(ISNUMBER(O40),O40=R40),"NMMC, ",""))-2))</f>
+      <c r="U40" s="9" t="str">
+        <f aca="false">IF(S40=0,"No quote",LEFT(IF(AND(ISNUMBER(G40),G40=T40),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I40),I40=T40),"Aslam, ","")&amp;IF(AND(ISNUMBER(K40),K40=T40),"Jamil, ","")&amp;IF(AND(ISNUMBER(M40),M40=T40),"Muller, ","")&amp;IF(AND(ISNUMBER(O40),O40=T40),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q40),Q40=T40),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G40),G40=T40),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I40),I40=T40),"Aslam, ","")&amp;IF(AND(ISNUMBER(K40),K40=T40),"Jamil, ","")&amp;IF(AND(ISNUMBER(M40),M40=T40),"Muller, ","")&amp;IF(AND(ISNUMBER(O40),O40=T40),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q40),Q40=T40),"Platinum, ",""))-2))</f>
         <v>No quote</v>
       </c>
-      <c r="T40" s="10" t="str">
-        <f aca="false">IF(Q40=0,"",R40*F40)</f>
+      <c r="V40" s="10" t="str">
+        <f aca="false">IF(S40=0,"",T40*F40)</f>
         <v/>
       </c>
-      <c r="U40" s="6"/>
+      <c r="W40" s="6"/>
     </row>
     <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="n">
         <v>36</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F41" s="5" t="n">
         <v>100</v>
@@ -4473,41 +4589,43 @@
         <v>493</v>
       </c>
       <c r="P41" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="Q41" s="5" t="n">
-        <f aca="false">COUNT(G41,I41,K41,M41,O41)</f>
+        <v>194</v>
+      </c>
+      <c r="Q41" s="7"/>
+      <c r="R41" s="6"/>
+      <c r="S41" s="5" t="n">
+        <f aca="false">COUNT(G41,I41,K41,M41,O41,Q41)</f>
         <v>1</v>
       </c>
-      <c r="R41" s="8" t="n">
-        <f aca="false">IF(Q41=0,"",MIN(G41,I41,K41,M41,O41))</f>
+      <c r="T41" s="8" t="n">
+        <f aca="false">IF(S41=0,"",MIN(G41,I41,K41,M41,O41,Q41))</f>
         <v>493</v>
       </c>
-      <c r="S41" s="9" t="str">
-        <f aca="false">IF(Q41=0,"No quote",LEFT(IF(AND(ISNUMBER(G41),G41=R41),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I41),I41=R41),"Aslam, ","")&amp;IF(AND(ISNUMBER(K41),K41=R41),"Jamil, ","")&amp;IF(AND(ISNUMBER(M41),M41=R41),"Muller, ","")&amp;IF(AND(ISNUMBER(O41),O41=R41),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G41),G41=R41),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I41),I41=R41),"Aslam, ","")&amp;IF(AND(ISNUMBER(K41),K41=R41),"Jamil, ","")&amp;IF(AND(ISNUMBER(M41),M41=R41),"Muller, ","")&amp;IF(AND(ISNUMBER(O41),O41=R41),"NMMC, ",""))-2))</f>
+      <c r="U41" s="9" t="str">
+        <f aca="false">IF(S41=0,"No quote",LEFT(IF(AND(ISNUMBER(G41),G41=T41),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I41),I41=T41),"Aslam, ","")&amp;IF(AND(ISNUMBER(K41),K41=T41),"Jamil, ","")&amp;IF(AND(ISNUMBER(M41),M41=T41),"Muller, ","")&amp;IF(AND(ISNUMBER(O41),O41=T41),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q41),Q41=T41),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G41),G41=T41),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I41),I41=T41),"Aslam, ","")&amp;IF(AND(ISNUMBER(K41),K41=T41),"Jamil, ","")&amp;IF(AND(ISNUMBER(M41),M41=T41),"Muller, ","")&amp;IF(AND(ISNUMBER(O41),O41=T41),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q41),Q41=T41),"Platinum, ",""))-2))</f>
         <v>NMMC</v>
       </c>
-      <c r="T41" s="10" t="n">
-        <f aca="false">IF(Q41=0,"",R41*F41)</f>
+      <c r="V41" s="10" t="n">
+        <f aca="false">IF(S41=0,"",T41*F41)</f>
         <v>49300</v>
       </c>
-      <c r="U41" s="6"/>
+      <c r="W41" s="6"/>
     </row>
     <row r="42" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="n">
         <v>37</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F42" s="5" t="n">
         <v>250</v>
@@ -4516,46 +4634,48 @@
         <v>197.93</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="I42" s="7" t="n">
         <v>197.93</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K42" s="7" t="n">
         <v>502.77</v>
       </c>
       <c r="L42" s="6" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="M42" s="7" t="n">
         <v>197.93</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="O42" s="7"/>
       <c r="P42" s="6"/>
-      <c r="Q42" s="5" t="n">
-        <f aca="false">COUNT(G42,I42,K42,M42,O42)</f>
+      <c r="Q42" s="7"/>
+      <c r="R42" s="6"/>
+      <c r="S42" s="5" t="n">
+        <f aca="false">COUNT(G42,I42,K42,M42,O42,Q42)</f>
         <v>4</v>
       </c>
-      <c r="R42" s="8" t="n">
-        <f aca="false">IF(Q42=0,"",MIN(G42,I42,K42,M42,O42))</f>
+      <c r="T42" s="8" t="n">
+        <f aca="false">IF(S42=0,"",MIN(G42,I42,K42,M42,O42,Q42))</f>
         <v>197.93</v>
       </c>
-      <c r="S42" s="9" t="str">
-        <f aca="false">IF(Q42=0,"No quote",LEFT(IF(AND(ISNUMBER(G42),G42=R42),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I42),I42=R42),"Aslam, ","")&amp;IF(AND(ISNUMBER(K42),K42=R42),"Jamil, ","")&amp;IF(AND(ISNUMBER(M42),M42=R42),"Muller, ","")&amp;IF(AND(ISNUMBER(O42),O42=R42),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G42),G42=R42),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I42),I42=R42),"Aslam, ","")&amp;IF(AND(ISNUMBER(K42),K42=R42),"Jamil, ","")&amp;IF(AND(ISNUMBER(M42),M42=R42),"Muller, ","")&amp;IF(AND(ISNUMBER(O42),O42=R42),"NMMC, ",""))-2))</f>
+      <c r="U42" s="9" t="str">
+        <f aca="false">IF(S42=0,"No quote",LEFT(IF(AND(ISNUMBER(G42),G42=T42),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I42),I42=T42),"Aslam, ","")&amp;IF(AND(ISNUMBER(K42),K42=T42),"Jamil, ","")&amp;IF(AND(ISNUMBER(M42),M42=T42),"Muller, ","")&amp;IF(AND(ISNUMBER(O42),O42=T42),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q42),Q42=T42),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G42),G42=T42),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I42),I42=T42),"Aslam, ","")&amp;IF(AND(ISNUMBER(K42),K42=T42),"Jamil, ","")&amp;IF(AND(ISNUMBER(M42),M42=T42),"Muller, ","")&amp;IF(AND(ISNUMBER(O42),O42=T42),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q42),Q42=T42),"Platinum, ",""))-2))</f>
         <v>Ahsan, Aslam, Muller</v>
       </c>
-      <c r="T42" s="10" t="n">
-        <f aca="false">IF(Q42=0,"",R42*F42)</f>
+      <c r="V42" s="10" t="n">
+        <f aca="false">IF(S42=0,"",T42*F42)</f>
         <v>49482.5</v>
       </c>
-      <c r="U42" s="6" t="s">
-        <v>199</v>
+      <c r="W42" s="6" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4563,16 +4683,16 @@
         <v>38</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F43" s="5" t="n">
         <v>250</v>
@@ -4581,46 +4701,48 @@
         <v>250.46</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="I43" s="7" t="n">
         <v>250.46</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K43" s="7" t="n">
         <v>622.95</v>
       </c>
       <c r="L43" s="6" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="M43" s="7" t="n">
         <v>250.5</v>
       </c>
       <c r="N43" s="6" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="O43" s="7"/>
       <c r="P43" s="6"/>
-      <c r="Q43" s="5" t="n">
-        <f aca="false">COUNT(G43,I43,K43,M43,O43)</f>
+      <c r="Q43" s="7"/>
+      <c r="R43" s="6"/>
+      <c r="S43" s="5" t="n">
+        <f aca="false">COUNT(G43,I43,K43,M43,O43,Q43)</f>
         <v>4</v>
       </c>
-      <c r="R43" s="8" t="n">
-        <f aca="false">IF(Q43=0,"",MIN(G43,I43,K43,M43,O43))</f>
+      <c r="T43" s="8" t="n">
+        <f aca="false">IF(S43=0,"",MIN(G43,I43,K43,M43,O43,Q43))</f>
         <v>250.46</v>
       </c>
-      <c r="S43" s="9" t="str">
-        <f aca="false">IF(Q43=0,"No quote",LEFT(IF(AND(ISNUMBER(G43),G43=R43),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I43),I43=R43),"Aslam, ","")&amp;IF(AND(ISNUMBER(K43),K43=R43),"Jamil, ","")&amp;IF(AND(ISNUMBER(M43),M43=R43),"Muller, ","")&amp;IF(AND(ISNUMBER(O43),O43=R43),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G43),G43=R43),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I43),I43=R43),"Aslam, ","")&amp;IF(AND(ISNUMBER(K43),K43=R43),"Jamil, ","")&amp;IF(AND(ISNUMBER(M43),M43=R43),"Muller, ","")&amp;IF(AND(ISNUMBER(O43),O43=R43),"NMMC, ",""))-2))</f>
+      <c r="U43" s="9" t="str">
+        <f aca="false">IF(S43=0,"No quote",LEFT(IF(AND(ISNUMBER(G43),G43=T43),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I43),I43=T43),"Aslam, ","")&amp;IF(AND(ISNUMBER(K43),K43=T43),"Jamil, ","")&amp;IF(AND(ISNUMBER(M43),M43=T43),"Muller, ","")&amp;IF(AND(ISNUMBER(O43),O43=T43),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q43),Q43=T43),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G43),G43=T43),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I43),I43=T43),"Aslam, ","")&amp;IF(AND(ISNUMBER(K43),K43=T43),"Jamil, ","")&amp;IF(AND(ISNUMBER(M43),M43=T43),"Muller, ","")&amp;IF(AND(ISNUMBER(O43),O43=T43),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q43),Q43=T43),"Platinum, ",""))-2))</f>
         <v>Ahsan, Aslam</v>
       </c>
-      <c r="T43" s="10" t="n">
-        <f aca="false">IF(Q43=0,"",R43*F43)</f>
+      <c r="V43" s="10" t="n">
+        <f aca="false">IF(S43=0,"",T43*F43)</f>
         <v>62615</v>
       </c>
-      <c r="U43" s="6" t="s">
-        <v>199</v>
+      <c r="W43" s="6" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4628,16 +4750,16 @@
         <v>39</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F44" s="5" t="n">
         <v>100</v>
@@ -4652,47 +4774,49 @@
         <v>361.25</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="O44" s="7" t="n">
         <v>257.04</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="Q44" s="5" t="n">
-        <f aca="false">COUNT(G44,I44,K44,M44,O44)</f>
+        <v>210</v>
+      </c>
+      <c r="Q44" s="7"/>
+      <c r="R44" s="6"/>
+      <c r="S44" s="5" t="n">
+        <f aca="false">COUNT(G44,I44,K44,M44,O44,Q44)</f>
         <v>2</v>
       </c>
-      <c r="R44" s="8" t="n">
-        <f aca="false">IF(Q44=0,"",MIN(G44,I44,K44,M44,O44))</f>
+      <c r="T44" s="8" t="n">
+        <f aca="false">IF(S44=0,"",MIN(G44,I44,K44,M44,O44,Q44))</f>
         <v>257.04</v>
       </c>
-      <c r="S44" s="9" t="str">
-        <f aca="false">IF(Q44=0,"No quote",LEFT(IF(AND(ISNUMBER(G44),G44=R44),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I44),I44=R44),"Aslam, ","")&amp;IF(AND(ISNUMBER(K44),K44=R44),"Jamil, ","")&amp;IF(AND(ISNUMBER(M44),M44=R44),"Muller, ","")&amp;IF(AND(ISNUMBER(O44),O44=R44),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G44),G44=R44),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I44),I44=R44),"Aslam, ","")&amp;IF(AND(ISNUMBER(K44),K44=R44),"Jamil, ","")&amp;IF(AND(ISNUMBER(M44),M44=R44),"Muller, ","")&amp;IF(AND(ISNUMBER(O44),O44=R44),"NMMC, ",""))-2))</f>
+      <c r="U44" s="9" t="str">
+        <f aca="false">IF(S44=0,"No quote",LEFT(IF(AND(ISNUMBER(G44),G44=T44),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I44),I44=T44),"Aslam, ","")&amp;IF(AND(ISNUMBER(K44),K44=T44),"Jamil, ","")&amp;IF(AND(ISNUMBER(M44),M44=T44),"Muller, ","")&amp;IF(AND(ISNUMBER(O44),O44=T44),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q44),Q44=T44),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G44),G44=T44),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I44),I44=T44),"Aslam, ","")&amp;IF(AND(ISNUMBER(K44),K44=T44),"Jamil, ","")&amp;IF(AND(ISNUMBER(M44),M44=T44),"Muller, ","")&amp;IF(AND(ISNUMBER(O44),O44=T44),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q44),Q44=T44),"Platinum, ",""))-2))</f>
         <v>NMMC</v>
       </c>
-      <c r="T44" s="10" t="n">
-        <f aca="false">IF(Q44=0,"",R44*F44)</f>
+      <c r="V44" s="10" t="n">
+        <f aca="false">IF(S44=0,"",T44*F44)</f>
         <v>25704</v>
       </c>
-      <c r="U44" s="6"/>
+      <c r="W44" s="6"/>
     </row>
     <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="n">
         <v>40</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F45" s="5" t="n">
         <v>50</v>
@@ -4705,45 +4829,51 @@
         <v>363.38</v>
       </c>
       <c r="L45" s="6" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="M45" s="7"/>
       <c r="N45" s="6"/>
       <c r="O45" s="7"/>
       <c r="P45" s="6"/>
-      <c r="Q45" s="5" t="n">
-        <f aca="false">COUNT(G45,I45,K45,M45,O45)</f>
-        <v>1</v>
-      </c>
-      <c r="R45" s="8" t="n">
-        <f aca="false">IF(Q45=0,"",MIN(G45,I45,K45,M45,O45))</f>
-        <v>363.38</v>
-      </c>
-      <c r="S45" s="9" t="str">
-        <f aca="false">IF(Q45=0,"No quote",LEFT(IF(AND(ISNUMBER(G45),G45=R45),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I45),I45=R45),"Aslam, ","")&amp;IF(AND(ISNUMBER(K45),K45=R45),"Jamil, ","")&amp;IF(AND(ISNUMBER(M45),M45=R45),"Muller, ","")&amp;IF(AND(ISNUMBER(O45),O45=R45),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G45),G45=R45),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I45),I45=R45),"Aslam, ","")&amp;IF(AND(ISNUMBER(K45),K45=R45),"Jamil, ","")&amp;IF(AND(ISNUMBER(M45),M45=R45),"Muller, ","")&amp;IF(AND(ISNUMBER(O45),O45=R45),"NMMC, ",""))-2))</f>
-        <v>Jamil</v>
-      </c>
-      <c r="T45" s="10" t="n">
-        <f aca="false">IF(Q45=0,"",R45*F45)</f>
-        <v>18169</v>
-      </c>
-      <c r="U45" s="6"/>
+      <c r="Q45" s="7" t="n">
+        <v>290.32</v>
+      </c>
+      <c r="R45" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="S45" s="5" t="n">
+        <f aca="false">COUNT(G45,I45,K45,M45,O45,Q45)</f>
+        <v>2</v>
+      </c>
+      <c r="T45" s="8" t="n">
+        <f aca="false">IF(S45=0,"",MIN(G45,I45,K45,M45,O45,Q45))</f>
+        <v>290.32</v>
+      </c>
+      <c r="U45" s="9" t="str">
+        <f aca="false">IF(S45=0,"No quote",LEFT(IF(AND(ISNUMBER(G45),G45=T45),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I45),I45=T45),"Aslam, ","")&amp;IF(AND(ISNUMBER(K45),K45=T45),"Jamil, ","")&amp;IF(AND(ISNUMBER(M45),M45=T45),"Muller, ","")&amp;IF(AND(ISNUMBER(O45),O45=T45),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q45),Q45=T45),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G45),G45=T45),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I45),I45=T45),"Aslam, ","")&amp;IF(AND(ISNUMBER(K45),K45=T45),"Jamil, ","")&amp;IF(AND(ISNUMBER(M45),M45=T45),"Muller, ","")&amp;IF(AND(ISNUMBER(O45),O45=T45),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q45),Q45=T45),"Platinum, ",""))-2))</f>
+        <v>Platinum</v>
+      </c>
+      <c r="V45" s="10" t="n">
+        <f aca="false">IF(S45=0,"",T45*F45)</f>
+        <v>14516</v>
+      </c>
+      <c r="W45" s="6"/>
     </row>
     <row r="46" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="n">
         <v>41</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F46" s="5" t="n">
         <v>80</v>
@@ -4758,39 +4888,41 @@
       <c r="N46" s="6"/>
       <c r="O46" s="7"/>
       <c r="P46" s="6"/>
-      <c r="Q46" s="5" t="n">
-        <f aca="false">COUNT(G46,I46,K46,M46,O46)</f>
+      <c r="Q46" s="7"/>
+      <c r="R46" s="6"/>
+      <c r="S46" s="5" t="n">
+        <f aca="false">COUNT(G46,I46,K46,M46,O46,Q46)</f>
         <v>0</v>
       </c>
-      <c r="R46" s="8" t="str">
-        <f aca="false">IF(Q46=0,"",MIN(G46,I46,K46,M46,O46))</f>
+      <c r="T46" s="8" t="str">
+        <f aca="false">IF(S46=0,"",MIN(G46,I46,K46,M46,O46,Q46))</f>
         <v/>
       </c>
-      <c r="S46" s="9" t="str">
-        <f aca="false">IF(Q46=0,"No quote",LEFT(IF(AND(ISNUMBER(G46),G46=R46),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I46),I46=R46),"Aslam, ","")&amp;IF(AND(ISNUMBER(K46),K46=R46),"Jamil, ","")&amp;IF(AND(ISNUMBER(M46),M46=R46),"Muller, ","")&amp;IF(AND(ISNUMBER(O46),O46=R46),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G46),G46=R46),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I46),I46=R46),"Aslam, ","")&amp;IF(AND(ISNUMBER(K46),K46=R46),"Jamil, ","")&amp;IF(AND(ISNUMBER(M46),M46=R46),"Muller, ","")&amp;IF(AND(ISNUMBER(O46),O46=R46),"NMMC, ",""))-2))</f>
+      <c r="U46" s="9" t="str">
+        <f aca="false">IF(S46=0,"No quote",LEFT(IF(AND(ISNUMBER(G46),G46=T46),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I46),I46=T46),"Aslam, ","")&amp;IF(AND(ISNUMBER(K46),K46=T46),"Jamil, ","")&amp;IF(AND(ISNUMBER(M46),M46=T46),"Muller, ","")&amp;IF(AND(ISNUMBER(O46),O46=T46),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q46),Q46=T46),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G46),G46=T46),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I46),I46=T46),"Aslam, ","")&amp;IF(AND(ISNUMBER(K46),K46=T46),"Jamil, ","")&amp;IF(AND(ISNUMBER(M46),M46=T46),"Muller, ","")&amp;IF(AND(ISNUMBER(O46),O46=T46),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q46),Q46=T46),"Platinum, ",""))-2))</f>
         <v>No quote</v>
       </c>
-      <c r="T46" s="10" t="str">
-        <f aca="false">IF(Q46=0,"",R46*F46)</f>
+      <c r="V46" s="10" t="str">
+        <f aca="false">IF(S46=0,"",T46*F46)</f>
         <v/>
       </c>
-      <c r="U46" s="6"/>
+      <c r="W46" s="6"/>
     </row>
     <row r="47" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="n">
         <v>42</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F47" s="5" t="n">
         <v>600</v>
@@ -4799,7 +4931,7 @@
         <v>187</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="I47" s="7"/>
       <c r="J47" s="6"/>
@@ -4807,53 +4939,55 @@
         <v>142.8</v>
       </c>
       <c r="L47" s="6" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="M47" s="7" t="n">
         <v>697</v>
       </c>
       <c r="N47" s="6" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="O47" s="7" t="n">
         <v>122.655</v>
       </c>
       <c r="P47" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q47" s="5" t="n">
-        <f aca="false">COUNT(G47,I47,K47,M47,O47)</f>
+        <v>225</v>
+      </c>
+      <c r="Q47" s="7"/>
+      <c r="R47" s="6"/>
+      <c r="S47" s="5" t="n">
+        <f aca="false">COUNT(G47,I47,K47,M47,O47,Q47)</f>
         <v>4</v>
       </c>
-      <c r="R47" s="8" t="n">
-        <f aca="false">IF(Q47=0,"",MIN(G47,I47,K47,M47,O47))</f>
+      <c r="T47" s="8" t="n">
+        <f aca="false">IF(S47=0,"",MIN(G47,I47,K47,M47,O47,Q47))</f>
         <v>122.655</v>
       </c>
-      <c r="S47" s="9" t="str">
-        <f aca="false">IF(Q47=0,"No quote",LEFT(IF(AND(ISNUMBER(G47),G47=R47),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I47),I47=R47),"Aslam, ","")&amp;IF(AND(ISNUMBER(K47),K47=R47),"Jamil, ","")&amp;IF(AND(ISNUMBER(M47),M47=R47),"Muller, ","")&amp;IF(AND(ISNUMBER(O47),O47=R47),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G47),G47=R47),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I47),I47=R47),"Aslam, ","")&amp;IF(AND(ISNUMBER(K47),K47=R47),"Jamil, ","")&amp;IF(AND(ISNUMBER(M47),M47=R47),"Muller, ","")&amp;IF(AND(ISNUMBER(O47),O47=R47),"NMMC, ",""))-2))</f>
+      <c r="U47" s="9" t="str">
+        <f aca="false">IF(S47=0,"No quote",LEFT(IF(AND(ISNUMBER(G47),G47=T47),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I47),I47=T47),"Aslam, ","")&amp;IF(AND(ISNUMBER(K47),K47=T47),"Jamil, ","")&amp;IF(AND(ISNUMBER(M47),M47=T47),"Muller, ","")&amp;IF(AND(ISNUMBER(O47),O47=T47),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q47),Q47=T47),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G47),G47=T47),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I47),I47=T47),"Aslam, ","")&amp;IF(AND(ISNUMBER(K47),K47=T47),"Jamil, ","")&amp;IF(AND(ISNUMBER(M47),M47=T47),"Muller, ","")&amp;IF(AND(ISNUMBER(O47),O47=T47),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q47),Q47=T47),"Platinum, ",""))-2))</f>
         <v>NMMC</v>
       </c>
-      <c r="T47" s="10" t="n">
-        <f aca="false">IF(Q47=0,"",R47*F47)</f>
+      <c r="V47" s="10" t="n">
+        <f aca="false">IF(S47=0,"",T47*F47)</f>
         <v>73593</v>
       </c>
-      <c r="U47" s="6"/>
+      <c r="W47" s="6"/>
     </row>
     <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="n">
         <v>43</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F48" s="5" t="n">
         <v>50</v>
@@ -4864,7 +4998,7 @@
         <v>265.31</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="K48" s="7"/>
       <c r="L48" s="6"/>
@@ -4874,41 +5008,43 @@
         <v>69.66</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="Q48" s="5" t="n">
-        <f aca="false">COUNT(G48,I48,K48,M48,O48)</f>
+        <v>230</v>
+      </c>
+      <c r="Q48" s="7"/>
+      <c r="R48" s="6"/>
+      <c r="S48" s="5" t="n">
+        <f aca="false">COUNT(G48,I48,K48,M48,O48,Q48)</f>
         <v>2</v>
       </c>
-      <c r="R48" s="8" t="n">
-        <f aca="false">IF(Q48=0,"",MIN(G48,I48,K48,M48,O48))</f>
+      <c r="T48" s="8" t="n">
+        <f aca="false">IF(S48=0,"",MIN(G48,I48,K48,M48,O48,Q48))</f>
         <v>69.66</v>
       </c>
-      <c r="S48" s="9" t="str">
-        <f aca="false">IF(Q48=0,"No quote",LEFT(IF(AND(ISNUMBER(G48),G48=R48),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I48),I48=R48),"Aslam, ","")&amp;IF(AND(ISNUMBER(K48),K48=R48),"Jamil, ","")&amp;IF(AND(ISNUMBER(M48),M48=R48),"Muller, ","")&amp;IF(AND(ISNUMBER(O48),O48=R48),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G48),G48=R48),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I48),I48=R48),"Aslam, ","")&amp;IF(AND(ISNUMBER(K48),K48=R48),"Jamil, ","")&amp;IF(AND(ISNUMBER(M48),M48=R48),"Muller, ","")&amp;IF(AND(ISNUMBER(O48),O48=R48),"NMMC, ",""))-2))</f>
+      <c r="U48" s="9" t="str">
+        <f aca="false">IF(S48=0,"No quote",LEFT(IF(AND(ISNUMBER(G48),G48=T48),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I48),I48=T48),"Aslam, ","")&amp;IF(AND(ISNUMBER(K48),K48=T48),"Jamil, ","")&amp;IF(AND(ISNUMBER(M48),M48=T48),"Muller, ","")&amp;IF(AND(ISNUMBER(O48),O48=T48),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q48),Q48=T48),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G48),G48=T48),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I48),I48=T48),"Aslam, ","")&amp;IF(AND(ISNUMBER(K48),K48=T48),"Jamil, ","")&amp;IF(AND(ISNUMBER(M48),M48=T48),"Muller, ","")&amp;IF(AND(ISNUMBER(O48),O48=T48),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q48),Q48=T48),"Platinum, ",""))-2))</f>
         <v>NMMC</v>
       </c>
-      <c r="T48" s="10" t="n">
-        <f aca="false">IF(Q48=0,"",R48*F48)</f>
+      <c r="V48" s="10" t="n">
+        <f aca="false">IF(S48=0,"",T48*F48)</f>
         <v>3483</v>
       </c>
-      <c r="U48" s="6"/>
+      <c r="W48" s="6"/>
     </row>
     <row r="49" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="n">
         <v>44</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F49" s="5" t="n">
         <v>500</v>
@@ -4917,7 +5053,7 @@
         <v>191.25</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="I49" s="7"/>
       <c r="J49" s="6"/>
@@ -4927,47 +5063,49 @@
         <v>205.7</v>
       </c>
       <c r="N49" s="6" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="O49" s="7" t="n">
         <v>245.1287</v>
       </c>
       <c r="P49" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="Q49" s="5" t="n">
-        <f aca="false">COUNT(G49,I49,K49,M49,O49)</f>
+        <v>236</v>
+      </c>
+      <c r="Q49" s="7"/>
+      <c r="R49" s="6"/>
+      <c r="S49" s="5" t="n">
+        <f aca="false">COUNT(G49,I49,K49,M49,O49,Q49)</f>
         <v>3</v>
       </c>
-      <c r="R49" s="8" t="n">
-        <f aca="false">IF(Q49=0,"",MIN(G49,I49,K49,M49,O49))</f>
+      <c r="T49" s="8" t="n">
+        <f aca="false">IF(S49=0,"",MIN(G49,I49,K49,M49,O49,Q49))</f>
         <v>191.25</v>
       </c>
-      <c r="S49" s="9" t="str">
-        <f aca="false">IF(Q49=0,"No quote",LEFT(IF(AND(ISNUMBER(G49),G49=R49),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I49),I49=R49),"Aslam, ","")&amp;IF(AND(ISNUMBER(K49),K49=R49),"Jamil, ","")&amp;IF(AND(ISNUMBER(M49),M49=R49),"Muller, ","")&amp;IF(AND(ISNUMBER(O49),O49=R49),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G49),G49=R49),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I49),I49=R49),"Aslam, ","")&amp;IF(AND(ISNUMBER(K49),K49=R49),"Jamil, ","")&amp;IF(AND(ISNUMBER(M49),M49=R49),"Muller, ","")&amp;IF(AND(ISNUMBER(O49),O49=R49),"NMMC, ",""))-2))</f>
+      <c r="U49" s="9" t="str">
+        <f aca="false">IF(S49=0,"No quote",LEFT(IF(AND(ISNUMBER(G49),G49=T49),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I49),I49=T49),"Aslam, ","")&amp;IF(AND(ISNUMBER(K49),K49=T49),"Jamil, ","")&amp;IF(AND(ISNUMBER(M49),M49=T49),"Muller, ","")&amp;IF(AND(ISNUMBER(O49),O49=T49),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q49),Q49=T49),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G49),G49=T49),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I49),I49=T49),"Aslam, ","")&amp;IF(AND(ISNUMBER(K49),K49=T49),"Jamil, ","")&amp;IF(AND(ISNUMBER(M49),M49=T49),"Muller, ","")&amp;IF(AND(ISNUMBER(O49),O49=T49),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q49),Q49=T49),"Platinum, ",""))-2))</f>
         <v>Ahsan</v>
       </c>
-      <c r="T49" s="10" t="n">
-        <f aca="false">IF(Q49=0,"",R49*F49)</f>
+      <c r="V49" s="10" t="n">
+        <f aca="false">IF(S49=0,"",T49*F49)</f>
         <v>95625</v>
       </c>
-      <c r="U49" s="6"/>
+      <c r="W49" s="6"/>
     </row>
     <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="n">
         <v>45</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F50" s="5" t="n">
         <v>50</v>
@@ -4984,41 +5122,43 @@
         <v>93.925</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="Q50" s="5" t="n">
-        <f aca="false">COUNT(G50,I50,K50,M50,O50)</f>
+        <v>240</v>
+      </c>
+      <c r="Q50" s="7"/>
+      <c r="R50" s="6"/>
+      <c r="S50" s="5" t="n">
+        <f aca="false">COUNT(G50,I50,K50,M50,O50,Q50)</f>
         <v>1</v>
       </c>
-      <c r="R50" s="8" t="n">
-        <f aca="false">IF(Q50=0,"",MIN(G50,I50,K50,M50,O50))</f>
+      <c r="T50" s="8" t="n">
+        <f aca="false">IF(S50=0,"",MIN(G50,I50,K50,M50,O50,Q50))</f>
         <v>93.925</v>
       </c>
-      <c r="S50" s="9" t="str">
-        <f aca="false">IF(Q50=0,"No quote",LEFT(IF(AND(ISNUMBER(G50),G50=R50),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I50),I50=R50),"Aslam, ","")&amp;IF(AND(ISNUMBER(K50),K50=R50),"Jamil, ","")&amp;IF(AND(ISNUMBER(M50),M50=R50),"Muller, ","")&amp;IF(AND(ISNUMBER(O50),O50=R50),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G50),G50=R50),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I50),I50=R50),"Aslam, ","")&amp;IF(AND(ISNUMBER(K50),K50=R50),"Jamil, ","")&amp;IF(AND(ISNUMBER(M50),M50=R50),"Muller, ","")&amp;IF(AND(ISNUMBER(O50),O50=R50),"NMMC, ",""))-2))</f>
+      <c r="U50" s="9" t="str">
+        <f aca="false">IF(S50=0,"No quote",LEFT(IF(AND(ISNUMBER(G50),G50=T50),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I50),I50=T50),"Aslam, ","")&amp;IF(AND(ISNUMBER(K50),K50=T50),"Jamil, ","")&amp;IF(AND(ISNUMBER(M50),M50=T50),"Muller, ","")&amp;IF(AND(ISNUMBER(O50),O50=T50),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q50),Q50=T50),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G50),G50=T50),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I50),I50=T50),"Aslam, ","")&amp;IF(AND(ISNUMBER(K50),K50=T50),"Jamil, ","")&amp;IF(AND(ISNUMBER(M50),M50=T50),"Muller, ","")&amp;IF(AND(ISNUMBER(O50),O50=T50),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q50),Q50=T50),"Platinum, ",""))-2))</f>
         <v>NMMC</v>
       </c>
-      <c r="T50" s="10" t="n">
-        <f aca="false">IF(Q50=0,"",R50*F50)</f>
+      <c r="V50" s="10" t="n">
+        <f aca="false">IF(S50=0,"",T50*F50)</f>
         <v>4696.25</v>
       </c>
-      <c r="U50" s="6"/>
+      <c r="W50" s="6"/>
     </row>
     <row r="51" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="n">
         <v>46</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F51" s="5" t="n">
         <v>150</v>
@@ -5029,7 +5169,7 @@
         <v>214.2</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K51" s="7"/>
       <c r="L51" s="6"/>
@@ -5037,47 +5177,49 @@
         <v>165.5</v>
       </c>
       <c r="N51" s="6" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="O51" s="7" t="n">
         <v>203.49</v>
       </c>
       <c r="P51" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="Q51" s="5" t="n">
-        <f aca="false">COUNT(G51,I51,K51,M51,O51)</f>
+        <v>245</v>
+      </c>
+      <c r="Q51" s="7"/>
+      <c r="R51" s="6"/>
+      <c r="S51" s="5" t="n">
+        <f aca="false">COUNT(G51,I51,K51,M51,O51,Q51)</f>
         <v>3</v>
       </c>
-      <c r="R51" s="8" t="n">
-        <f aca="false">IF(Q51=0,"",MIN(G51,I51,K51,M51,O51))</f>
+      <c r="T51" s="8" t="n">
+        <f aca="false">IF(S51=0,"",MIN(G51,I51,K51,M51,O51,Q51))</f>
         <v>165.5</v>
       </c>
-      <c r="S51" s="9" t="str">
-        <f aca="false">IF(Q51=0,"No quote",LEFT(IF(AND(ISNUMBER(G51),G51=R51),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I51),I51=R51),"Aslam, ","")&amp;IF(AND(ISNUMBER(K51),K51=R51),"Jamil, ","")&amp;IF(AND(ISNUMBER(M51),M51=R51),"Muller, ","")&amp;IF(AND(ISNUMBER(O51),O51=R51),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G51),G51=R51),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I51),I51=R51),"Aslam, ","")&amp;IF(AND(ISNUMBER(K51),K51=R51),"Jamil, ","")&amp;IF(AND(ISNUMBER(M51),M51=R51),"Muller, ","")&amp;IF(AND(ISNUMBER(O51),O51=R51),"NMMC, ",""))-2))</f>
+      <c r="U51" s="9" t="str">
+        <f aca="false">IF(S51=0,"No quote",LEFT(IF(AND(ISNUMBER(G51),G51=T51),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I51),I51=T51),"Aslam, ","")&amp;IF(AND(ISNUMBER(K51),K51=T51),"Jamil, ","")&amp;IF(AND(ISNUMBER(M51),M51=T51),"Muller, ","")&amp;IF(AND(ISNUMBER(O51),O51=T51),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q51),Q51=T51),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G51),G51=T51),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I51),I51=T51),"Aslam, ","")&amp;IF(AND(ISNUMBER(K51),K51=T51),"Jamil, ","")&amp;IF(AND(ISNUMBER(M51),M51=T51),"Muller, ","")&amp;IF(AND(ISNUMBER(O51),O51=T51),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q51),Q51=T51),"Platinum, ",""))-2))</f>
         <v>Muller</v>
       </c>
-      <c r="T51" s="10" t="n">
-        <f aca="false">IF(Q51=0,"",R51*F51)</f>
+      <c r="V51" s="10" t="n">
+        <f aca="false">IF(S51=0,"",T51*F51)</f>
         <v>24825</v>
       </c>
-      <c r="U51" s="6"/>
+      <c r="W51" s="6"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="5" t="n">
         <v>47</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F52" s="5" t="n">
         <v>750</v>
@@ -5094,41 +5236,43 @@
         <v>411.04</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="Q52" s="5" t="n">
-        <f aca="false">COUNT(G52,I52,K52,M52,O52)</f>
+        <v>249</v>
+      </c>
+      <c r="Q52" s="7"/>
+      <c r="R52" s="6"/>
+      <c r="S52" s="5" t="n">
+        <f aca="false">COUNT(G52,I52,K52,M52,O52,Q52)</f>
         <v>1</v>
       </c>
-      <c r="R52" s="8" t="n">
-        <f aca="false">IF(Q52=0,"",MIN(G52,I52,K52,M52,O52))</f>
+      <c r="T52" s="8" t="n">
+        <f aca="false">IF(S52=0,"",MIN(G52,I52,K52,M52,O52,Q52))</f>
         <v>411.04</v>
       </c>
-      <c r="S52" s="9" t="str">
-        <f aca="false">IF(Q52=0,"No quote",LEFT(IF(AND(ISNUMBER(G52),G52=R52),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I52),I52=R52),"Aslam, ","")&amp;IF(AND(ISNUMBER(K52),K52=R52),"Jamil, ","")&amp;IF(AND(ISNUMBER(M52),M52=R52),"Muller, ","")&amp;IF(AND(ISNUMBER(O52),O52=R52),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G52),G52=R52),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I52),I52=R52),"Aslam, ","")&amp;IF(AND(ISNUMBER(K52),K52=R52),"Jamil, ","")&amp;IF(AND(ISNUMBER(M52),M52=R52),"Muller, ","")&amp;IF(AND(ISNUMBER(O52),O52=R52),"NMMC, ",""))-2))</f>
+      <c r="U52" s="9" t="str">
+        <f aca="false">IF(S52=0,"No quote",LEFT(IF(AND(ISNUMBER(G52),G52=T52),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I52),I52=T52),"Aslam, ","")&amp;IF(AND(ISNUMBER(K52),K52=T52),"Jamil, ","")&amp;IF(AND(ISNUMBER(M52),M52=T52),"Muller, ","")&amp;IF(AND(ISNUMBER(O52),O52=T52),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q52),Q52=T52),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G52),G52=T52),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I52),I52=T52),"Aslam, ","")&amp;IF(AND(ISNUMBER(K52),K52=T52),"Jamil, ","")&amp;IF(AND(ISNUMBER(M52),M52=T52),"Muller, ","")&amp;IF(AND(ISNUMBER(O52),O52=T52),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q52),Q52=T52),"Platinum, ",""))-2))</f>
         <v>NMMC</v>
       </c>
-      <c r="T52" s="10" t="n">
-        <f aca="false">IF(Q52=0,"",R52*F52)</f>
+      <c r="V52" s="10" t="n">
+        <f aca="false">IF(S52=0,"",T52*F52)</f>
         <v>308280</v>
       </c>
-      <c r="U52" s="6"/>
+      <c r="W52" s="6"/>
     </row>
     <row r="53" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="5" t="n">
         <v>48</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F53" s="5" t="n">
         <v>200</v>
@@ -5139,7 +5283,7 @@
         <v>691.52</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K53" s="7"/>
       <c r="L53" s="6"/>
@@ -5149,41 +5293,43 @@
         <v>753.57</v>
       </c>
       <c r="P53" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="Q53" s="5" t="n">
-        <f aca="false">COUNT(G53,I53,K53,M53,O53)</f>
+        <v>253</v>
+      </c>
+      <c r="Q53" s="7"/>
+      <c r="R53" s="6"/>
+      <c r="S53" s="5" t="n">
+        <f aca="false">COUNT(G53,I53,K53,M53,O53,Q53)</f>
         <v>2</v>
       </c>
-      <c r="R53" s="8" t="n">
-        <f aca="false">IF(Q53=0,"",MIN(G53,I53,K53,M53,O53))</f>
+      <c r="T53" s="8" t="n">
+        <f aca="false">IF(S53=0,"",MIN(G53,I53,K53,M53,O53,Q53))</f>
         <v>691.52</v>
       </c>
-      <c r="S53" s="9" t="str">
-        <f aca="false">IF(Q53=0,"No quote",LEFT(IF(AND(ISNUMBER(G53),G53=R53),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I53),I53=R53),"Aslam, ","")&amp;IF(AND(ISNUMBER(K53),K53=R53),"Jamil, ","")&amp;IF(AND(ISNUMBER(M53),M53=R53),"Muller, ","")&amp;IF(AND(ISNUMBER(O53),O53=R53),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G53),G53=R53),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I53),I53=R53),"Aslam, ","")&amp;IF(AND(ISNUMBER(K53),K53=R53),"Jamil, ","")&amp;IF(AND(ISNUMBER(M53),M53=R53),"Muller, ","")&amp;IF(AND(ISNUMBER(O53),O53=R53),"NMMC, ",""))-2))</f>
+      <c r="U53" s="9" t="str">
+        <f aca="false">IF(S53=0,"No quote",LEFT(IF(AND(ISNUMBER(G53),G53=T53),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I53),I53=T53),"Aslam, ","")&amp;IF(AND(ISNUMBER(K53),K53=T53),"Jamil, ","")&amp;IF(AND(ISNUMBER(M53),M53=T53),"Muller, ","")&amp;IF(AND(ISNUMBER(O53),O53=T53),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q53),Q53=T53),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G53),G53=T53),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I53),I53=T53),"Aslam, ","")&amp;IF(AND(ISNUMBER(K53),K53=T53),"Jamil, ","")&amp;IF(AND(ISNUMBER(M53),M53=T53),"Muller, ","")&amp;IF(AND(ISNUMBER(O53),O53=T53),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q53),Q53=T53),"Platinum, ",""))-2))</f>
         <v>Aslam</v>
       </c>
-      <c r="T53" s="10" t="n">
-        <f aca="false">IF(Q53=0,"",R53*F53)</f>
+      <c r="V53" s="10" t="n">
+        <f aca="false">IF(S53=0,"",T53*F53)</f>
         <v>138304</v>
       </c>
-      <c r="U53" s="6"/>
+      <c r="W53" s="6"/>
     </row>
     <row r="54" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="5" t="n">
         <v>49</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F54" s="5" t="n">
         <v>65</v>
@@ -5198,39 +5344,41 @@
       <c r="N54" s="6"/>
       <c r="O54" s="7"/>
       <c r="P54" s="6"/>
-      <c r="Q54" s="5" t="n">
-        <f aca="false">COUNT(G54,I54,K54,M54,O54)</f>
+      <c r="Q54" s="7"/>
+      <c r="R54" s="6"/>
+      <c r="S54" s="5" t="n">
+        <f aca="false">COUNT(G54,I54,K54,M54,O54,Q54)</f>
         <v>0</v>
       </c>
-      <c r="R54" s="8" t="str">
-        <f aca="false">IF(Q54=0,"",MIN(G54,I54,K54,M54,O54))</f>
+      <c r="T54" s="8" t="str">
+        <f aca="false">IF(S54=0,"",MIN(G54,I54,K54,M54,O54,Q54))</f>
         <v/>
       </c>
-      <c r="S54" s="9" t="str">
-        <f aca="false">IF(Q54=0,"No quote",LEFT(IF(AND(ISNUMBER(G54),G54=R54),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I54),I54=R54),"Aslam, ","")&amp;IF(AND(ISNUMBER(K54),K54=R54),"Jamil, ","")&amp;IF(AND(ISNUMBER(M54),M54=R54),"Muller, ","")&amp;IF(AND(ISNUMBER(O54),O54=R54),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G54),G54=R54),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I54),I54=R54),"Aslam, ","")&amp;IF(AND(ISNUMBER(K54),K54=R54),"Jamil, ","")&amp;IF(AND(ISNUMBER(M54),M54=R54),"Muller, ","")&amp;IF(AND(ISNUMBER(O54),O54=R54),"NMMC, ",""))-2))</f>
+      <c r="U54" s="9" t="str">
+        <f aca="false">IF(S54=0,"No quote",LEFT(IF(AND(ISNUMBER(G54),G54=T54),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I54),I54=T54),"Aslam, ","")&amp;IF(AND(ISNUMBER(K54),K54=T54),"Jamil, ","")&amp;IF(AND(ISNUMBER(M54),M54=T54),"Muller, ","")&amp;IF(AND(ISNUMBER(O54),O54=T54),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q54),Q54=T54),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G54),G54=T54),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I54),I54=T54),"Aslam, ","")&amp;IF(AND(ISNUMBER(K54),K54=T54),"Jamil, ","")&amp;IF(AND(ISNUMBER(M54),M54=T54),"Muller, ","")&amp;IF(AND(ISNUMBER(O54),O54=T54),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q54),Q54=T54),"Platinum, ",""))-2))</f>
         <v>No quote</v>
       </c>
-      <c r="T54" s="10" t="str">
-        <f aca="false">IF(Q54=0,"",R54*F54)</f>
+      <c r="V54" s="10" t="str">
+        <f aca="false">IF(S54=0,"",T54*F54)</f>
         <v/>
       </c>
-      <c r="U54" s="6"/>
+      <c r="W54" s="6"/>
     </row>
     <row r="55" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5" t="n">
         <v>50</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F55" s="5" t="n">
         <v>20</v>
@@ -5239,7 +5387,7 @@
         <v>221</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="I55" s="7"/>
       <c r="J55" s="6"/>
@@ -5251,41 +5399,43 @@
         <v>591.6</v>
       </c>
       <c r="P55" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="Q55" s="5" t="n">
-        <f aca="false">COUNT(G55,I55,K55,M55,O55)</f>
+        <v>261</v>
+      </c>
+      <c r="Q55" s="7"/>
+      <c r="R55" s="6"/>
+      <c r="S55" s="5" t="n">
+        <f aca="false">COUNT(G55,I55,K55,M55,O55,Q55)</f>
         <v>2</v>
       </c>
-      <c r="R55" s="8" t="n">
-        <f aca="false">IF(Q55=0,"",MIN(G55,I55,K55,M55,O55))</f>
+      <c r="T55" s="8" t="n">
+        <f aca="false">IF(S55=0,"",MIN(G55,I55,K55,M55,O55,Q55))</f>
         <v>221</v>
       </c>
-      <c r="S55" s="9" t="str">
-        <f aca="false">IF(Q55=0,"No quote",LEFT(IF(AND(ISNUMBER(G55),G55=R55),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I55),I55=R55),"Aslam, ","")&amp;IF(AND(ISNUMBER(K55),K55=R55),"Jamil, ","")&amp;IF(AND(ISNUMBER(M55),M55=R55),"Muller, ","")&amp;IF(AND(ISNUMBER(O55),O55=R55),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G55),G55=R55),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I55),I55=R55),"Aslam, ","")&amp;IF(AND(ISNUMBER(K55),K55=R55),"Jamil, ","")&amp;IF(AND(ISNUMBER(M55),M55=R55),"Muller, ","")&amp;IF(AND(ISNUMBER(O55),O55=R55),"NMMC, ",""))-2))</f>
+      <c r="U55" s="9" t="str">
+        <f aca="false">IF(S55=0,"No quote",LEFT(IF(AND(ISNUMBER(G55),G55=T55),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I55),I55=T55),"Aslam, ","")&amp;IF(AND(ISNUMBER(K55),K55=T55),"Jamil, ","")&amp;IF(AND(ISNUMBER(M55),M55=T55),"Muller, ","")&amp;IF(AND(ISNUMBER(O55),O55=T55),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q55),Q55=T55),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G55),G55=T55),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I55),I55=T55),"Aslam, ","")&amp;IF(AND(ISNUMBER(K55),K55=T55),"Jamil, ","")&amp;IF(AND(ISNUMBER(M55),M55=T55),"Muller, ","")&amp;IF(AND(ISNUMBER(O55),O55=T55),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q55),Q55=T55),"Platinum, ",""))-2))</f>
         <v>Ahsan</v>
       </c>
-      <c r="T55" s="10" t="n">
-        <f aca="false">IF(Q55=0,"",R55*F55)</f>
+      <c r="V55" s="10" t="n">
+        <f aca="false">IF(S55=0,"",T55*F55)</f>
         <v>4420</v>
       </c>
-      <c r="U55" s="6"/>
+      <c r="W55" s="6"/>
     </row>
     <row r="56" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="5" t="n">
         <v>51</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F56" s="5" t="n">
         <v>200</v>
@@ -5302,41 +5452,43 @@
         <v>321.04</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="Q56" s="5" t="n">
-        <f aca="false">COUNT(G56,I56,K56,M56,O56)</f>
+        <v>265</v>
+      </c>
+      <c r="Q56" s="7"/>
+      <c r="R56" s="6"/>
+      <c r="S56" s="5" t="n">
+        <f aca="false">COUNT(G56,I56,K56,M56,O56,Q56)</f>
         <v>1</v>
       </c>
-      <c r="R56" s="8" t="n">
-        <f aca="false">IF(Q56=0,"",MIN(G56,I56,K56,M56,O56))</f>
+      <c r="T56" s="8" t="n">
+        <f aca="false">IF(S56=0,"",MIN(G56,I56,K56,M56,O56,Q56))</f>
         <v>321.04</v>
       </c>
-      <c r="S56" s="9" t="str">
-        <f aca="false">IF(Q56=0,"No quote",LEFT(IF(AND(ISNUMBER(G56),G56=R56),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I56),I56=R56),"Aslam, ","")&amp;IF(AND(ISNUMBER(K56),K56=R56),"Jamil, ","")&amp;IF(AND(ISNUMBER(M56),M56=R56),"Muller, ","")&amp;IF(AND(ISNUMBER(O56),O56=R56),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G56),G56=R56),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I56),I56=R56),"Aslam, ","")&amp;IF(AND(ISNUMBER(K56),K56=R56),"Jamil, ","")&amp;IF(AND(ISNUMBER(M56),M56=R56),"Muller, ","")&amp;IF(AND(ISNUMBER(O56),O56=R56),"NMMC, ",""))-2))</f>
+      <c r="U56" s="9" t="str">
+        <f aca="false">IF(S56=0,"No quote",LEFT(IF(AND(ISNUMBER(G56),G56=T56),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I56),I56=T56),"Aslam, ","")&amp;IF(AND(ISNUMBER(K56),K56=T56),"Jamil, ","")&amp;IF(AND(ISNUMBER(M56),M56=T56),"Muller, ","")&amp;IF(AND(ISNUMBER(O56),O56=T56),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q56),Q56=T56),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G56),G56=T56),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I56),I56=T56),"Aslam, ","")&amp;IF(AND(ISNUMBER(K56),K56=T56),"Jamil, ","")&amp;IF(AND(ISNUMBER(M56),M56=T56),"Muller, ","")&amp;IF(AND(ISNUMBER(O56),O56=T56),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q56),Q56=T56),"Platinum, ",""))-2))</f>
         <v>NMMC</v>
       </c>
-      <c r="T56" s="10" t="n">
-        <f aca="false">IF(Q56=0,"",R56*F56)</f>
+      <c r="V56" s="10" t="n">
+        <f aca="false">IF(S56=0,"",T56*F56)</f>
         <v>64208</v>
       </c>
-      <c r="U56" s="6"/>
+      <c r="W56" s="6"/>
     </row>
     <row r="57" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="5" t="n">
         <v>52</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F57" s="5" t="n">
         <v>250</v>
@@ -5345,61 +5497,63 @@
         <v>331.5</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="I57" s="7" t="n">
         <v>382.5</v>
       </c>
       <c r="J57" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K57" s="7" t="n">
         <v>708.05</v>
       </c>
       <c r="L57" s="6" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="M57" s="7" t="n">
         <v>242.48</v>
       </c>
       <c r="N57" s="6" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="O57" s="7"/>
       <c r="P57" s="6"/>
-      <c r="Q57" s="5" t="n">
-        <f aca="false">COUNT(G57,I57,K57,M57,O57)</f>
+      <c r="Q57" s="7"/>
+      <c r="R57" s="6"/>
+      <c r="S57" s="5" t="n">
+        <f aca="false">COUNT(G57,I57,K57,M57,O57,Q57)</f>
         <v>4</v>
       </c>
-      <c r="R57" s="8" t="n">
-        <f aca="false">IF(Q57=0,"",MIN(G57,I57,K57,M57,O57))</f>
+      <c r="T57" s="8" t="n">
+        <f aca="false">IF(S57=0,"",MIN(G57,I57,K57,M57,O57,Q57))</f>
         <v>242.48</v>
       </c>
-      <c r="S57" s="9" t="str">
-        <f aca="false">IF(Q57=0,"No quote",LEFT(IF(AND(ISNUMBER(G57),G57=R57),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I57),I57=R57),"Aslam, ","")&amp;IF(AND(ISNUMBER(K57),K57=R57),"Jamil, ","")&amp;IF(AND(ISNUMBER(M57),M57=R57),"Muller, ","")&amp;IF(AND(ISNUMBER(O57),O57=R57),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G57),G57=R57),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I57),I57=R57),"Aslam, ","")&amp;IF(AND(ISNUMBER(K57),K57=R57),"Jamil, ","")&amp;IF(AND(ISNUMBER(M57),M57=R57),"Muller, ","")&amp;IF(AND(ISNUMBER(O57),O57=R57),"NMMC, ",""))-2))</f>
+      <c r="U57" s="9" t="str">
+        <f aca="false">IF(S57=0,"No quote",LEFT(IF(AND(ISNUMBER(G57),G57=T57),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I57),I57=T57),"Aslam, ","")&amp;IF(AND(ISNUMBER(K57),K57=T57),"Jamil, ","")&amp;IF(AND(ISNUMBER(M57),M57=T57),"Muller, ","")&amp;IF(AND(ISNUMBER(O57),O57=T57),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q57),Q57=T57),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G57),G57=T57),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I57),I57=T57),"Aslam, ","")&amp;IF(AND(ISNUMBER(K57),K57=T57),"Jamil, ","")&amp;IF(AND(ISNUMBER(M57),M57=T57),"Muller, ","")&amp;IF(AND(ISNUMBER(O57),O57=T57),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q57),Q57=T57),"Platinum, ",""))-2))</f>
         <v>Muller</v>
       </c>
-      <c r="T57" s="10" t="n">
-        <f aca="false">IF(Q57=0,"",R57*F57)</f>
+      <c r="V57" s="10" t="n">
+        <f aca="false">IF(S57=0,"",T57*F57)</f>
         <v>60620</v>
       </c>
-      <c r="U57" s="6"/>
+      <c r="W57" s="6"/>
     </row>
     <row r="58" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="5" t="n">
         <v>53</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F58" s="5" t="n">
         <v>200</v>
@@ -5408,65 +5562,67 @@
         <v>467.5</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="I58" s="7" t="n">
         <v>467.5</v>
       </c>
       <c r="J58" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K58" s="7" t="n">
         <v>530.4</v>
       </c>
       <c r="L58" s="6" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="M58" s="7" t="n">
         <v>518.5</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="O58" s="7" t="n">
         <v>270.725</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="Q58" s="5" t="n">
-        <f aca="false">COUNT(G58,I58,K58,M58,O58)</f>
+        <v>278</v>
+      </c>
+      <c r="Q58" s="7"/>
+      <c r="R58" s="6"/>
+      <c r="S58" s="5" t="n">
+        <f aca="false">COUNT(G58,I58,K58,M58,O58,Q58)</f>
         <v>5</v>
       </c>
-      <c r="R58" s="8" t="n">
-        <f aca="false">IF(Q58=0,"",MIN(G58,I58,K58,M58,O58))</f>
+      <c r="T58" s="8" t="n">
+        <f aca="false">IF(S58=0,"",MIN(G58,I58,K58,M58,O58,Q58))</f>
         <v>270.725</v>
       </c>
-      <c r="S58" s="9" t="str">
-        <f aca="false">IF(Q58=0,"No quote",LEFT(IF(AND(ISNUMBER(G58),G58=R58),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I58),I58=R58),"Aslam, ","")&amp;IF(AND(ISNUMBER(K58),K58=R58),"Jamil, ","")&amp;IF(AND(ISNUMBER(M58),M58=R58),"Muller, ","")&amp;IF(AND(ISNUMBER(O58),O58=R58),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G58),G58=R58),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I58),I58=R58),"Aslam, ","")&amp;IF(AND(ISNUMBER(K58),K58=R58),"Jamil, ","")&amp;IF(AND(ISNUMBER(M58),M58=R58),"Muller, ","")&amp;IF(AND(ISNUMBER(O58),O58=R58),"NMMC, ",""))-2))</f>
+      <c r="U58" s="9" t="str">
+        <f aca="false">IF(S58=0,"No quote",LEFT(IF(AND(ISNUMBER(G58),G58=T58),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I58),I58=T58),"Aslam, ","")&amp;IF(AND(ISNUMBER(K58),K58=T58),"Jamil, ","")&amp;IF(AND(ISNUMBER(M58),M58=T58),"Muller, ","")&amp;IF(AND(ISNUMBER(O58),O58=T58),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q58),Q58=T58),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G58),G58=T58),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I58),I58=T58),"Aslam, ","")&amp;IF(AND(ISNUMBER(K58),K58=T58),"Jamil, ","")&amp;IF(AND(ISNUMBER(M58),M58=T58),"Muller, ","")&amp;IF(AND(ISNUMBER(O58),O58=T58),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q58),Q58=T58),"Platinum, ",""))-2))</f>
         <v>NMMC</v>
       </c>
-      <c r="T58" s="10" t="n">
-        <f aca="false">IF(Q58=0,"",R58*F58)</f>
+      <c r="V58" s="10" t="n">
+        <f aca="false">IF(S58=0,"",T58*F58)</f>
         <v>54145</v>
       </c>
-      <c r="U58" s="6"/>
+      <c r="W58" s="6"/>
     </row>
     <row r="59" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="5" t="n">
         <v>54</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F59" s="5" t="n">
         <v>50</v>
@@ -5475,7 +5631,7 @@
         <v>318.75</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="I59" s="7"/>
       <c r="J59" s="6"/>
@@ -5485,43 +5641,45 @@
         <v>892.5</v>
       </c>
       <c r="N59" s="6" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="O59" s="7"/>
       <c r="P59" s="6"/>
-      <c r="Q59" s="5" t="n">
-        <f aca="false">COUNT(G59,I59,K59,M59,O59)</f>
+      <c r="Q59" s="7"/>
+      <c r="R59" s="6"/>
+      <c r="S59" s="5" t="n">
+        <f aca="false">COUNT(G59,I59,K59,M59,O59,Q59)</f>
         <v>2</v>
       </c>
-      <c r="R59" s="8" t="n">
-        <f aca="false">IF(Q59=0,"",MIN(G59,I59,K59,M59,O59))</f>
+      <c r="T59" s="8" t="n">
+        <f aca="false">IF(S59=0,"",MIN(G59,I59,K59,M59,O59,Q59))</f>
         <v>318.75</v>
       </c>
-      <c r="S59" s="9" t="str">
-        <f aca="false">IF(Q59=0,"No quote",LEFT(IF(AND(ISNUMBER(G59),G59=R59),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I59),I59=R59),"Aslam, ","")&amp;IF(AND(ISNUMBER(K59),K59=R59),"Jamil, ","")&amp;IF(AND(ISNUMBER(M59),M59=R59),"Muller, ","")&amp;IF(AND(ISNUMBER(O59),O59=R59),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G59),G59=R59),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I59),I59=R59),"Aslam, ","")&amp;IF(AND(ISNUMBER(K59),K59=R59),"Jamil, ","")&amp;IF(AND(ISNUMBER(M59),M59=R59),"Muller, ","")&amp;IF(AND(ISNUMBER(O59),O59=R59),"NMMC, ",""))-2))</f>
+      <c r="U59" s="9" t="str">
+        <f aca="false">IF(S59=0,"No quote",LEFT(IF(AND(ISNUMBER(G59),G59=T59),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I59),I59=T59),"Aslam, ","")&amp;IF(AND(ISNUMBER(K59),K59=T59),"Jamil, ","")&amp;IF(AND(ISNUMBER(M59),M59=T59),"Muller, ","")&amp;IF(AND(ISNUMBER(O59),O59=T59),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q59),Q59=T59),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G59),G59=T59),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I59),I59=T59),"Aslam, ","")&amp;IF(AND(ISNUMBER(K59),K59=T59),"Jamil, ","")&amp;IF(AND(ISNUMBER(M59),M59=T59),"Muller, ","")&amp;IF(AND(ISNUMBER(O59),O59=T59),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q59),Q59=T59),"Platinum, ",""))-2))</f>
         <v>Ahsan</v>
       </c>
-      <c r="T59" s="10" t="n">
-        <f aca="false">IF(Q59=0,"",R59*F59)</f>
+      <c r="V59" s="10" t="n">
+        <f aca="false">IF(S59=0,"",T59*F59)</f>
         <v>15937.5</v>
       </c>
-      <c r="U59" s="6"/>
+      <c r="W59" s="6"/>
     </row>
     <row r="60" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="5" t="n">
         <v>55</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F60" s="5" t="n">
         <v>50</v>
@@ -5530,7 +5688,7 @@
         <v>382.5</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="I60" s="7"/>
       <c r="J60" s="6"/>
@@ -5540,47 +5698,49 @@
         <v>2737.17</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="O60" s="7" t="n">
         <v>382.5</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="Q60" s="5" t="n">
-        <f aca="false">COUNT(G60,I60,K60,M60,O60)</f>
+        <v>289</v>
+      </c>
+      <c r="Q60" s="7"/>
+      <c r="R60" s="6"/>
+      <c r="S60" s="5" t="n">
+        <f aca="false">COUNT(G60,I60,K60,M60,O60,Q60)</f>
         <v>3</v>
       </c>
-      <c r="R60" s="8" t="n">
-        <f aca="false">IF(Q60=0,"",MIN(G60,I60,K60,M60,O60))</f>
+      <c r="T60" s="8" t="n">
+        <f aca="false">IF(S60=0,"",MIN(G60,I60,K60,M60,O60,Q60))</f>
         <v>382.5</v>
       </c>
-      <c r="S60" s="9" t="str">
-        <f aca="false">IF(Q60=0,"No quote",LEFT(IF(AND(ISNUMBER(G60),G60=R60),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I60),I60=R60),"Aslam, ","")&amp;IF(AND(ISNUMBER(K60),K60=R60),"Jamil, ","")&amp;IF(AND(ISNUMBER(M60),M60=R60),"Muller, ","")&amp;IF(AND(ISNUMBER(O60),O60=R60),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G60),G60=R60),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I60),I60=R60),"Aslam, ","")&amp;IF(AND(ISNUMBER(K60),K60=R60),"Jamil, ","")&amp;IF(AND(ISNUMBER(M60),M60=R60),"Muller, ","")&amp;IF(AND(ISNUMBER(O60),O60=R60),"NMMC, ",""))-2))</f>
+      <c r="U60" s="9" t="str">
+        <f aca="false">IF(S60=0,"No quote",LEFT(IF(AND(ISNUMBER(G60),G60=T60),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I60),I60=T60),"Aslam, ","")&amp;IF(AND(ISNUMBER(K60),K60=T60),"Jamil, ","")&amp;IF(AND(ISNUMBER(M60),M60=T60),"Muller, ","")&amp;IF(AND(ISNUMBER(O60),O60=T60),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q60),Q60=T60),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G60),G60=T60),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I60),I60=T60),"Aslam, ","")&amp;IF(AND(ISNUMBER(K60),K60=T60),"Jamil, ","")&amp;IF(AND(ISNUMBER(M60),M60=T60),"Muller, ","")&amp;IF(AND(ISNUMBER(O60),O60=T60),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q60),Q60=T60),"Platinum, ",""))-2))</f>
         <v>Ahsan, NMMC</v>
       </c>
-      <c r="T60" s="10" t="n">
-        <f aca="false">IF(Q60=0,"",R60*F60)</f>
+      <c r="V60" s="10" t="n">
+        <f aca="false">IF(S60=0,"",T60*F60)</f>
         <v>19125</v>
       </c>
-      <c r="U60" s="6"/>
+      <c r="W60" s="6"/>
     </row>
     <row r="61" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="5" t="n">
         <v>56</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F61" s="5" t="n">
         <v>200</v>
@@ -5589,7 +5749,7 @@
         <v>255</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="I61" s="7"/>
       <c r="J61" s="6"/>
@@ -5601,41 +5761,43 @@
         <v>193.8</v>
       </c>
       <c r="P61" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="Q61" s="5" t="n">
-        <f aca="false">COUNT(G61,I61,K61,M61,O61)</f>
+        <v>294</v>
+      </c>
+      <c r="Q61" s="7"/>
+      <c r="R61" s="6"/>
+      <c r="S61" s="5" t="n">
+        <f aca="false">COUNT(G61,I61,K61,M61,O61,Q61)</f>
         <v>2</v>
       </c>
-      <c r="R61" s="8" t="n">
-        <f aca="false">IF(Q61=0,"",MIN(G61,I61,K61,M61,O61))</f>
+      <c r="T61" s="8" t="n">
+        <f aca="false">IF(S61=0,"",MIN(G61,I61,K61,M61,O61,Q61))</f>
         <v>193.8</v>
       </c>
-      <c r="S61" s="9" t="str">
-        <f aca="false">IF(Q61=0,"No quote",LEFT(IF(AND(ISNUMBER(G61),G61=R61),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I61),I61=R61),"Aslam, ","")&amp;IF(AND(ISNUMBER(K61),K61=R61),"Jamil, ","")&amp;IF(AND(ISNUMBER(M61),M61=R61),"Muller, ","")&amp;IF(AND(ISNUMBER(O61),O61=R61),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G61),G61=R61),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I61),I61=R61),"Aslam, ","")&amp;IF(AND(ISNUMBER(K61),K61=R61),"Jamil, ","")&amp;IF(AND(ISNUMBER(M61),M61=R61),"Muller, ","")&amp;IF(AND(ISNUMBER(O61),O61=R61),"NMMC, ",""))-2))</f>
+      <c r="U61" s="9" t="str">
+        <f aca="false">IF(S61=0,"No quote",LEFT(IF(AND(ISNUMBER(G61),G61=T61),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I61),I61=T61),"Aslam, ","")&amp;IF(AND(ISNUMBER(K61),K61=T61),"Jamil, ","")&amp;IF(AND(ISNUMBER(M61),M61=T61),"Muller, ","")&amp;IF(AND(ISNUMBER(O61),O61=T61),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q61),Q61=T61),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G61),G61=T61),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I61),I61=T61),"Aslam, ","")&amp;IF(AND(ISNUMBER(K61),K61=T61),"Jamil, ","")&amp;IF(AND(ISNUMBER(M61),M61=T61),"Muller, ","")&amp;IF(AND(ISNUMBER(O61),O61=T61),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q61),Q61=T61),"Platinum, ",""))-2))</f>
         <v>NMMC</v>
       </c>
-      <c r="T61" s="10" t="n">
-        <f aca="false">IF(Q61=0,"",R61*F61)</f>
+      <c r="V61" s="10" t="n">
+        <f aca="false">IF(S61=0,"",T61*F61)</f>
         <v>38760</v>
       </c>
-      <c r="U61" s="6"/>
+      <c r="W61" s="6"/>
     </row>
     <row r="62" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="5" t="n">
         <v>57</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F62" s="5" t="n">
         <v>10</v>
@@ -5648,45 +5810,47 @@
         <v>1114.26</v>
       </c>
       <c r="L62" s="6" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="M62" s="7"/>
       <c r="N62" s="6"/>
       <c r="O62" s="7"/>
       <c r="P62" s="6"/>
-      <c r="Q62" s="5" t="n">
-        <f aca="false">COUNT(G62,I62,K62,M62,O62)</f>
+      <c r="Q62" s="7"/>
+      <c r="R62" s="6"/>
+      <c r="S62" s="5" t="n">
+        <f aca="false">COUNT(G62,I62,K62,M62,O62,Q62)</f>
         <v>1</v>
       </c>
-      <c r="R62" s="8" t="n">
-        <f aca="false">IF(Q62=0,"",MIN(G62,I62,K62,M62,O62))</f>
+      <c r="T62" s="8" t="n">
+        <f aca="false">IF(S62=0,"",MIN(G62,I62,K62,M62,O62,Q62))</f>
         <v>1114.26</v>
       </c>
-      <c r="S62" s="9" t="str">
-        <f aca="false">IF(Q62=0,"No quote",LEFT(IF(AND(ISNUMBER(G62),G62=R62),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I62),I62=R62),"Aslam, ","")&amp;IF(AND(ISNUMBER(K62),K62=R62),"Jamil, ","")&amp;IF(AND(ISNUMBER(M62),M62=R62),"Muller, ","")&amp;IF(AND(ISNUMBER(O62),O62=R62),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G62),G62=R62),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I62),I62=R62),"Aslam, ","")&amp;IF(AND(ISNUMBER(K62),K62=R62),"Jamil, ","")&amp;IF(AND(ISNUMBER(M62),M62=R62),"Muller, ","")&amp;IF(AND(ISNUMBER(O62),O62=R62),"NMMC, ",""))-2))</f>
+      <c r="U62" s="9" t="str">
+        <f aca="false">IF(S62=0,"No quote",LEFT(IF(AND(ISNUMBER(G62),G62=T62),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I62),I62=T62),"Aslam, ","")&amp;IF(AND(ISNUMBER(K62),K62=T62),"Jamil, ","")&amp;IF(AND(ISNUMBER(M62),M62=T62),"Muller, ","")&amp;IF(AND(ISNUMBER(O62),O62=T62),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q62),Q62=T62),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G62),G62=T62),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I62),I62=T62),"Aslam, ","")&amp;IF(AND(ISNUMBER(K62),K62=T62),"Jamil, ","")&amp;IF(AND(ISNUMBER(M62),M62=T62),"Muller, ","")&amp;IF(AND(ISNUMBER(O62),O62=T62),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q62),Q62=T62),"Platinum, ",""))-2))</f>
         <v>Jamil</v>
       </c>
-      <c r="T62" s="10" t="n">
-        <f aca="false">IF(Q62=0,"",R62*F62)</f>
+      <c r="V62" s="10" t="n">
+        <f aca="false">IF(S62=0,"",T62*F62)</f>
         <v>11142.6</v>
       </c>
-      <c r="U62" s="6"/>
+      <c r="W62" s="6"/>
     </row>
     <row r="63" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="5" t="n">
         <v>58</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F63" s="5" t="n">
         <v>50</v>
@@ -5699,7 +5863,7 @@
         <v>185.05</v>
       </c>
       <c r="L63" s="6" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="M63" s="7"/>
       <c r="N63" s="6"/>
@@ -5707,41 +5871,43 @@
         <v>114.75</v>
       </c>
       <c r="P63" s="6" t="s">
-        <v>300</v>
-      </c>
-      <c r="Q63" s="5" t="n">
-        <f aca="false">COUNT(G63,I63,K63,M63,O63)</f>
+        <v>303</v>
+      </c>
+      <c r="Q63" s="7"/>
+      <c r="R63" s="6"/>
+      <c r="S63" s="5" t="n">
+        <f aca="false">COUNT(G63,I63,K63,M63,O63,Q63)</f>
         <v>2</v>
       </c>
-      <c r="R63" s="8" t="n">
-        <f aca="false">IF(Q63=0,"",MIN(G63,I63,K63,M63,O63))</f>
+      <c r="T63" s="8" t="n">
+        <f aca="false">IF(S63=0,"",MIN(G63,I63,K63,M63,O63,Q63))</f>
         <v>114.75</v>
       </c>
-      <c r="S63" s="9" t="str">
-        <f aca="false">IF(Q63=0,"No quote",LEFT(IF(AND(ISNUMBER(G63),G63=R63),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I63),I63=R63),"Aslam, ","")&amp;IF(AND(ISNUMBER(K63),K63=R63),"Jamil, ","")&amp;IF(AND(ISNUMBER(M63),M63=R63),"Muller, ","")&amp;IF(AND(ISNUMBER(O63),O63=R63),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G63),G63=R63),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I63),I63=R63),"Aslam, ","")&amp;IF(AND(ISNUMBER(K63),K63=R63),"Jamil, ","")&amp;IF(AND(ISNUMBER(M63),M63=R63),"Muller, ","")&amp;IF(AND(ISNUMBER(O63),O63=R63),"NMMC, ",""))-2))</f>
+      <c r="U63" s="9" t="str">
+        <f aca="false">IF(S63=0,"No quote",LEFT(IF(AND(ISNUMBER(G63),G63=T63),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I63),I63=T63),"Aslam, ","")&amp;IF(AND(ISNUMBER(K63),K63=T63),"Jamil, ","")&amp;IF(AND(ISNUMBER(M63),M63=T63),"Muller, ","")&amp;IF(AND(ISNUMBER(O63),O63=T63),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q63),Q63=T63),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G63),G63=T63),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I63),I63=T63),"Aslam, ","")&amp;IF(AND(ISNUMBER(K63),K63=T63),"Jamil, ","")&amp;IF(AND(ISNUMBER(M63),M63=T63),"Muller, ","")&amp;IF(AND(ISNUMBER(O63),O63=T63),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q63),Q63=T63),"Platinum, ",""))-2))</f>
         <v>NMMC</v>
       </c>
-      <c r="T63" s="10" t="n">
-        <f aca="false">IF(Q63=0,"",R63*F63)</f>
+      <c r="V63" s="10" t="n">
+        <f aca="false">IF(S63=0,"",T63*F63)</f>
         <v>5737.5</v>
       </c>
-      <c r="U63" s="6"/>
+      <c r="W63" s="6"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="5" t="n">
         <v>59</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F64" s="5" t="n">
         <v>30</v>
@@ -5756,39 +5922,41 @@
       <c r="N64" s="6"/>
       <c r="O64" s="7"/>
       <c r="P64" s="6"/>
-      <c r="Q64" s="5" t="n">
-        <f aca="false">COUNT(G64,I64,K64,M64,O64)</f>
+      <c r="Q64" s="7"/>
+      <c r="R64" s="6"/>
+      <c r="S64" s="5" t="n">
+        <f aca="false">COUNT(G64,I64,K64,M64,O64,Q64)</f>
         <v>0</v>
       </c>
-      <c r="R64" s="8" t="str">
-        <f aca="false">IF(Q64=0,"",MIN(G64,I64,K64,M64,O64))</f>
+      <c r="T64" s="8" t="str">
+        <f aca="false">IF(S64=0,"",MIN(G64,I64,K64,M64,O64,Q64))</f>
         <v/>
       </c>
-      <c r="S64" s="9" t="str">
-        <f aca="false">IF(Q64=0,"No quote",LEFT(IF(AND(ISNUMBER(G64),G64=R64),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I64),I64=R64),"Aslam, ","")&amp;IF(AND(ISNUMBER(K64),K64=R64),"Jamil, ","")&amp;IF(AND(ISNUMBER(M64),M64=R64),"Muller, ","")&amp;IF(AND(ISNUMBER(O64),O64=R64),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G64),G64=R64),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I64),I64=R64),"Aslam, ","")&amp;IF(AND(ISNUMBER(K64),K64=R64),"Jamil, ","")&amp;IF(AND(ISNUMBER(M64),M64=R64),"Muller, ","")&amp;IF(AND(ISNUMBER(O64),O64=R64),"NMMC, ",""))-2))</f>
+      <c r="U64" s="9" t="str">
+        <f aca="false">IF(S64=0,"No quote",LEFT(IF(AND(ISNUMBER(G64),G64=T64),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I64),I64=T64),"Aslam, ","")&amp;IF(AND(ISNUMBER(K64),K64=T64),"Jamil, ","")&amp;IF(AND(ISNUMBER(M64),M64=T64),"Muller, ","")&amp;IF(AND(ISNUMBER(O64),O64=T64),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q64),Q64=T64),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G64),G64=T64),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I64),I64=T64),"Aslam, ","")&amp;IF(AND(ISNUMBER(K64),K64=T64),"Jamil, ","")&amp;IF(AND(ISNUMBER(M64),M64=T64),"Muller, ","")&amp;IF(AND(ISNUMBER(O64),O64=T64),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q64),Q64=T64),"Platinum, ",""))-2))</f>
         <v>No quote</v>
       </c>
-      <c r="T64" s="10" t="str">
-        <f aca="false">IF(Q64=0,"",R64*F64)</f>
+      <c r="V64" s="10" t="str">
+        <f aca="false">IF(S64=0,"",T64*F64)</f>
         <v/>
       </c>
-      <c r="U64" s="6"/>
+      <c r="W64" s="6"/>
     </row>
     <row r="65" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="5" t="n">
         <v>60</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F65" s="5" t="n">
         <v>100</v>
@@ -5805,41 +5973,43 @@
         <v>136.63</v>
       </c>
       <c r="P65" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="Q65" s="5" t="n">
-        <f aca="false">COUNT(G65,I65,K65,M65,O65)</f>
+        <v>310</v>
+      </c>
+      <c r="Q65" s="7"/>
+      <c r="R65" s="6"/>
+      <c r="S65" s="5" t="n">
+        <f aca="false">COUNT(G65,I65,K65,M65,O65,Q65)</f>
         <v>1</v>
       </c>
-      <c r="R65" s="8" t="n">
-        <f aca="false">IF(Q65=0,"",MIN(G65,I65,K65,M65,O65))</f>
+      <c r="T65" s="8" t="n">
+        <f aca="false">IF(S65=0,"",MIN(G65,I65,K65,M65,O65,Q65))</f>
         <v>136.63</v>
       </c>
-      <c r="S65" s="9" t="str">
-        <f aca="false">IF(Q65=0,"No quote",LEFT(IF(AND(ISNUMBER(G65),G65=R65),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I65),I65=R65),"Aslam, ","")&amp;IF(AND(ISNUMBER(K65),K65=R65),"Jamil, ","")&amp;IF(AND(ISNUMBER(M65),M65=R65),"Muller, ","")&amp;IF(AND(ISNUMBER(O65),O65=R65),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G65),G65=R65),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I65),I65=R65),"Aslam, ","")&amp;IF(AND(ISNUMBER(K65),K65=R65),"Jamil, ","")&amp;IF(AND(ISNUMBER(M65),M65=R65),"Muller, ","")&amp;IF(AND(ISNUMBER(O65),O65=R65),"NMMC, ",""))-2))</f>
+      <c r="U65" s="9" t="str">
+        <f aca="false">IF(S65=0,"No quote",LEFT(IF(AND(ISNUMBER(G65),G65=T65),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I65),I65=T65),"Aslam, ","")&amp;IF(AND(ISNUMBER(K65),K65=T65),"Jamil, ","")&amp;IF(AND(ISNUMBER(M65),M65=T65),"Muller, ","")&amp;IF(AND(ISNUMBER(O65),O65=T65),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q65),Q65=T65),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G65),G65=T65),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I65),I65=T65),"Aslam, ","")&amp;IF(AND(ISNUMBER(K65),K65=T65),"Jamil, ","")&amp;IF(AND(ISNUMBER(M65),M65=T65),"Muller, ","")&amp;IF(AND(ISNUMBER(O65),O65=T65),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q65),Q65=T65),"Platinum, ",""))-2))</f>
         <v>NMMC</v>
       </c>
-      <c r="T65" s="10" t="n">
-        <f aca="false">IF(Q65=0,"",R65*F65)</f>
+      <c r="V65" s="10" t="n">
+        <f aca="false">IF(S65=0,"",T65*F65)</f>
         <v>13663</v>
       </c>
-      <c r="U65" s="6"/>
+      <c r="W65" s="6"/>
     </row>
     <row r="66" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="5" t="n">
         <v>61</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F66" s="5" t="n">
         <v>100</v>
@@ -5856,41 +6026,43 @@
         <v>107.1</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="Q66" s="5" t="n">
-        <f aca="false">COUNT(G66,I66,K66,M66,O66)</f>
+        <v>314</v>
+      </c>
+      <c r="Q66" s="7"/>
+      <c r="R66" s="6"/>
+      <c r="S66" s="5" t="n">
+        <f aca="false">COUNT(G66,I66,K66,M66,O66,Q66)</f>
         <v>1</v>
       </c>
-      <c r="R66" s="8" t="n">
-        <f aca="false">IF(Q66=0,"",MIN(G66,I66,K66,M66,O66))</f>
+      <c r="T66" s="8" t="n">
+        <f aca="false">IF(S66=0,"",MIN(G66,I66,K66,M66,O66,Q66))</f>
         <v>107.1</v>
       </c>
-      <c r="S66" s="9" t="str">
-        <f aca="false">IF(Q66=0,"No quote",LEFT(IF(AND(ISNUMBER(G66),G66=R66),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I66),I66=R66),"Aslam, ","")&amp;IF(AND(ISNUMBER(K66),K66=R66),"Jamil, ","")&amp;IF(AND(ISNUMBER(M66),M66=R66),"Muller, ","")&amp;IF(AND(ISNUMBER(O66),O66=R66),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G66),G66=R66),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I66),I66=R66),"Aslam, ","")&amp;IF(AND(ISNUMBER(K66),K66=R66),"Jamil, ","")&amp;IF(AND(ISNUMBER(M66),M66=R66),"Muller, ","")&amp;IF(AND(ISNUMBER(O66),O66=R66),"NMMC, ",""))-2))</f>
+      <c r="U66" s="9" t="str">
+        <f aca="false">IF(S66=0,"No quote",LEFT(IF(AND(ISNUMBER(G66),G66=T66),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I66),I66=T66),"Aslam, ","")&amp;IF(AND(ISNUMBER(K66),K66=T66),"Jamil, ","")&amp;IF(AND(ISNUMBER(M66),M66=T66),"Muller, ","")&amp;IF(AND(ISNUMBER(O66),O66=T66),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q66),Q66=T66),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G66),G66=T66),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I66),I66=T66),"Aslam, ","")&amp;IF(AND(ISNUMBER(K66),K66=T66),"Jamil, ","")&amp;IF(AND(ISNUMBER(M66),M66=T66),"Muller, ","")&amp;IF(AND(ISNUMBER(O66),O66=T66),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q66),Q66=T66),"Platinum, ",""))-2))</f>
         <v>NMMC</v>
       </c>
-      <c r="T66" s="10" t="n">
-        <f aca="false">IF(Q66=0,"",R66*F66)</f>
+      <c r="V66" s="10" t="n">
+        <f aca="false">IF(S66=0,"",T66*F66)</f>
         <v>10710</v>
       </c>
-      <c r="U66" s="6"/>
+      <c r="W66" s="6"/>
     </row>
     <row r="67" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="5" t="n">
         <v>62</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F67" s="5" t="n">
         <v>100</v>
@@ -5901,7 +6073,7 @@
         <v>81.33</v>
       </c>
       <c r="J67" s="6" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="K67" s="7"/>
       <c r="L67" s="6"/>
@@ -5909,39 +6081,41 @@
       <c r="N67" s="6"/>
       <c r="O67" s="7"/>
       <c r="P67" s="6"/>
-      <c r="Q67" s="5" t="n">
-        <f aca="false">COUNT(G67,I67,K67,M67,O67)</f>
+      <c r="Q67" s="7"/>
+      <c r="R67" s="6"/>
+      <c r="S67" s="5" t="n">
+        <f aca="false">COUNT(G67,I67,K67,M67,O67,Q67)</f>
         <v>1</v>
       </c>
-      <c r="R67" s="8" t="n">
-        <f aca="false">IF(Q67=0,"",MIN(G67,I67,K67,M67,O67))</f>
+      <c r="T67" s="8" t="n">
+        <f aca="false">IF(S67=0,"",MIN(G67,I67,K67,M67,O67,Q67))</f>
         <v>81.33</v>
       </c>
-      <c r="S67" s="9" t="str">
-        <f aca="false">IF(Q67=0,"No quote",LEFT(IF(AND(ISNUMBER(G67),G67=R67),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I67),I67=R67),"Aslam, ","")&amp;IF(AND(ISNUMBER(K67),K67=R67),"Jamil, ","")&amp;IF(AND(ISNUMBER(M67),M67=R67),"Muller, ","")&amp;IF(AND(ISNUMBER(O67),O67=R67),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G67),G67=R67),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I67),I67=R67),"Aslam, ","")&amp;IF(AND(ISNUMBER(K67),K67=R67),"Jamil, ","")&amp;IF(AND(ISNUMBER(M67),M67=R67),"Muller, ","")&amp;IF(AND(ISNUMBER(O67),O67=R67),"NMMC, ",""))-2))</f>
+      <c r="U67" s="9" t="str">
+        <f aca="false">IF(S67=0,"No quote",LEFT(IF(AND(ISNUMBER(G67),G67=T67),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I67),I67=T67),"Aslam, ","")&amp;IF(AND(ISNUMBER(K67),K67=T67),"Jamil, ","")&amp;IF(AND(ISNUMBER(M67),M67=T67),"Muller, ","")&amp;IF(AND(ISNUMBER(O67),O67=T67),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q67),Q67=T67),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G67),G67=T67),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I67),I67=T67),"Aslam, ","")&amp;IF(AND(ISNUMBER(K67),K67=T67),"Jamil, ","")&amp;IF(AND(ISNUMBER(M67),M67=T67),"Muller, ","")&amp;IF(AND(ISNUMBER(O67),O67=T67),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q67),Q67=T67),"Platinum, ",""))-2))</f>
         <v>Aslam</v>
       </c>
-      <c r="T67" s="10" t="n">
-        <f aca="false">IF(Q67=0,"",R67*F67)</f>
+      <c r="V67" s="10" t="n">
+        <f aca="false">IF(S67=0,"",T67*F67)</f>
         <v>8133</v>
       </c>
-      <c r="U67" s="6"/>
+      <c r="W67" s="6"/>
     </row>
     <row r="68" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="5" t="n">
         <v>63</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F68" s="5" t="n">
         <v>120</v>
@@ -5958,41 +6132,43 @@
         <v>179.37</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>319</v>
-      </c>
-      <c r="Q68" s="5" t="n">
-        <f aca="false">COUNT(G68,I68,K68,M68,O68)</f>
+        <v>322</v>
+      </c>
+      <c r="Q68" s="7"/>
+      <c r="R68" s="6"/>
+      <c r="S68" s="5" t="n">
+        <f aca="false">COUNT(G68,I68,K68,M68,O68,Q68)</f>
         <v>1</v>
       </c>
-      <c r="R68" s="8" t="n">
-        <f aca="false">IF(Q68=0,"",MIN(G68,I68,K68,M68,O68))</f>
+      <c r="T68" s="8" t="n">
+        <f aca="false">IF(S68=0,"",MIN(G68,I68,K68,M68,O68,Q68))</f>
         <v>179.37</v>
       </c>
-      <c r="S68" s="9" t="str">
-        <f aca="false">IF(Q68=0,"No quote",LEFT(IF(AND(ISNUMBER(G68),G68=R68),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I68),I68=R68),"Aslam, ","")&amp;IF(AND(ISNUMBER(K68),K68=R68),"Jamil, ","")&amp;IF(AND(ISNUMBER(M68),M68=R68),"Muller, ","")&amp;IF(AND(ISNUMBER(O68),O68=R68),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G68),G68=R68),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I68),I68=R68),"Aslam, ","")&amp;IF(AND(ISNUMBER(K68),K68=R68),"Jamil, ","")&amp;IF(AND(ISNUMBER(M68),M68=R68),"Muller, ","")&amp;IF(AND(ISNUMBER(O68),O68=R68),"NMMC, ",""))-2))</f>
+      <c r="U68" s="9" t="str">
+        <f aca="false">IF(S68=0,"No quote",LEFT(IF(AND(ISNUMBER(G68),G68=T68),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I68),I68=T68),"Aslam, ","")&amp;IF(AND(ISNUMBER(K68),K68=T68),"Jamil, ","")&amp;IF(AND(ISNUMBER(M68),M68=T68),"Muller, ","")&amp;IF(AND(ISNUMBER(O68),O68=T68),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q68),Q68=T68),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G68),G68=T68),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I68),I68=T68),"Aslam, ","")&amp;IF(AND(ISNUMBER(K68),K68=T68),"Jamil, ","")&amp;IF(AND(ISNUMBER(M68),M68=T68),"Muller, ","")&amp;IF(AND(ISNUMBER(O68),O68=T68),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q68),Q68=T68),"Platinum, ",""))-2))</f>
         <v>NMMC</v>
       </c>
-      <c r="T68" s="10" t="n">
-        <f aca="false">IF(Q68=0,"",R68*F68)</f>
+      <c r="V68" s="10" t="n">
+        <f aca="false">IF(S68=0,"",T68*F68)</f>
         <v>21524.4</v>
       </c>
-      <c r="U68" s="6"/>
+      <c r="W68" s="6"/>
     </row>
     <row r="69" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="5" t="n">
         <v>64</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F69" s="5" t="n">
         <v>25</v>
@@ -6003,7 +6179,7 @@
         <v>853.56</v>
       </c>
       <c r="J69" s="6" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="K69" s="7"/>
       <c r="L69" s="6"/>
@@ -6013,39 +6189,41 @@
         <v>492.66</v>
       </c>
       <c r="P69" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="Q69" s="5" t="n">
-        <f aca="false">COUNT(G69,I69,K69,M69,O69)</f>
+        <v>327</v>
+      </c>
+      <c r="Q69" s="7"/>
+      <c r="R69" s="6"/>
+      <c r="S69" s="5" t="n">
+        <f aca="false">COUNT(G69,I69,K69,M69,O69,Q69)</f>
         <v>2</v>
       </c>
-      <c r="R69" s="8" t="n">
-        <f aca="false">IF(Q69=0,"",MIN(G69,I69,K69,M69,O69))</f>
+      <c r="T69" s="8" t="n">
+        <f aca="false">IF(S69=0,"",MIN(G69,I69,K69,M69,O69,Q69))</f>
         <v>492.66</v>
       </c>
-      <c r="S69" s="9" t="str">
-        <f aca="false">IF(Q69=0,"No quote",LEFT(IF(AND(ISNUMBER(G69),G69=R69),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I69),I69=R69),"Aslam, ","")&amp;IF(AND(ISNUMBER(K69),K69=R69),"Jamil, ","")&amp;IF(AND(ISNUMBER(M69),M69=R69),"Muller, ","")&amp;IF(AND(ISNUMBER(O69),O69=R69),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G69),G69=R69),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I69),I69=R69),"Aslam, ","")&amp;IF(AND(ISNUMBER(K69),K69=R69),"Jamil, ","")&amp;IF(AND(ISNUMBER(M69),M69=R69),"Muller, ","")&amp;IF(AND(ISNUMBER(O69),O69=R69),"NMMC, ",""))-2))</f>
+      <c r="U69" s="9" t="str">
+        <f aca="false">IF(S69=0,"No quote",LEFT(IF(AND(ISNUMBER(G69),G69=T69),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I69),I69=T69),"Aslam, ","")&amp;IF(AND(ISNUMBER(K69),K69=T69),"Jamil, ","")&amp;IF(AND(ISNUMBER(M69),M69=T69),"Muller, ","")&amp;IF(AND(ISNUMBER(O69),O69=T69),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q69),Q69=T69),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G69),G69=T69),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I69),I69=T69),"Aslam, ","")&amp;IF(AND(ISNUMBER(K69),K69=T69),"Jamil, ","")&amp;IF(AND(ISNUMBER(M69),M69=T69),"Muller, ","")&amp;IF(AND(ISNUMBER(O69),O69=T69),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q69),Q69=T69),"Platinum, ",""))-2))</f>
         <v>NMMC</v>
       </c>
-      <c r="T69" s="10" t="n">
-        <f aca="false">IF(Q69=0,"",R69*F69)</f>
+      <c r="V69" s="10" t="n">
+        <f aca="false">IF(S69=0,"",T69*F69)</f>
         <v>12316.5</v>
       </c>
-      <c r="U69" s="6"/>
+      <c r="W69" s="6"/>
     </row>
     <row r="70" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="5" t="n">
         <v>65</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="D70" s="6"/>
       <c r="E70" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F70" s="5" t="n">
         <v>50</v>
@@ -6054,7 +6232,7 @@
         <v>600.95</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="I70" s="7"/>
       <c r="J70" s="6"/>
@@ -6062,45 +6240,47 @@
         <v>617.96</v>
       </c>
       <c r="L70" s="6" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="M70" s="7"/>
       <c r="N70" s="6"/>
       <c r="O70" s="7"/>
       <c r="P70" s="6"/>
-      <c r="Q70" s="5" t="n">
-        <f aca="false">COUNT(G70,I70,K70,M70,O70)</f>
+      <c r="Q70" s="7"/>
+      <c r="R70" s="6"/>
+      <c r="S70" s="5" t="n">
+        <f aca="false">COUNT(G70,I70,K70,M70,O70,Q70)</f>
         <v>2</v>
       </c>
-      <c r="R70" s="8" t="n">
-        <f aca="false">IF(Q70=0,"",MIN(G70,I70,K70,M70,O70))</f>
+      <c r="T70" s="8" t="n">
+        <f aca="false">IF(S70=0,"",MIN(G70,I70,K70,M70,O70,Q70))</f>
         <v>600.95</v>
       </c>
-      <c r="S70" s="9" t="str">
-        <f aca="false">IF(Q70=0,"No quote",LEFT(IF(AND(ISNUMBER(G70),G70=R70),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I70),I70=R70),"Aslam, ","")&amp;IF(AND(ISNUMBER(K70),K70=R70),"Jamil, ","")&amp;IF(AND(ISNUMBER(M70),M70=R70),"Muller, ","")&amp;IF(AND(ISNUMBER(O70),O70=R70),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G70),G70=R70),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I70),I70=R70),"Aslam, ","")&amp;IF(AND(ISNUMBER(K70),K70=R70),"Jamil, ","")&amp;IF(AND(ISNUMBER(M70),M70=R70),"Muller, ","")&amp;IF(AND(ISNUMBER(O70),O70=R70),"NMMC, ",""))-2))</f>
+      <c r="U70" s="9" t="str">
+        <f aca="false">IF(S70=0,"No quote",LEFT(IF(AND(ISNUMBER(G70),G70=T70),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I70),I70=T70),"Aslam, ","")&amp;IF(AND(ISNUMBER(K70),K70=T70),"Jamil, ","")&amp;IF(AND(ISNUMBER(M70),M70=T70),"Muller, ","")&amp;IF(AND(ISNUMBER(O70),O70=T70),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q70),Q70=T70),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G70),G70=T70),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I70),I70=T70),"Aslam, ","")&amp;IF(AND(ISNUMBER(K70),K70=T70),"Jamil, ","")&amp;IF(AND(ISNUMBER(M70),M70=T70),"Muller, ","")&amp;IF(AND(ISNUMBER(O70),O70=T70),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q70),Q70=T70),"Platinum, ",""))-2))</f>
         <v>Ahsan</v>
       </c>
-      <c r="T70" s="10" t="n">
-        <f aca="false">IF(Q70=0,"",R70*F70)</f>
+      <c r="V70" s="10" t="n">
+        <f aca="false">IF(S70=0,"",T70*F70)</f>
         <v>30047.5</v>
       </c>
-      <c r="U70" s="6"/>
+      <c r="W70" s="6"/>
     </row>
     <row r="71" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="5" t="n">
         <v>66</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F71" s="5" t="n">
         <v>30</v>
@@ -6111,7 +6291,7 @@
         <v>994.5</v>
       </c>
       <c r="J71" s="6" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="K71" s="7"/>
       <c r="L71" s="6"/>
@@ -6119,43 +6299,45 @@
         <v>586.5</v>
       </c>
       <c r="N71" s="6" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="O71" s="7"/>
       <c r="P71" s="6"/>
-      <c r="Q71" s="5" t="n">
-        <f aca="false">COUNT(G71,I71,K71,M71,O71)</f>
+      <c r="Q71" s="7"/>
+      <c r="R71" s="6"/>
+      <c r="S71" s="5" t="n">
+        <f aca="false">COUNT(G71,I71,K71,M71,O71,Q71)</f>
         <v>2</v>
       </c>
-      <c r="R71" s="8" t="n">
-        <f aca="false">IF(Q71=0,"",MIN(G71,I71,K71,M71,O71))</f>
+      <c r="T71" s="8" t="n">
+        <f aca="false">IF(S71=0,"",MIN(G71,I71,K71,M71,O71,Q71))</f>
         <v>586.5</v>
       </c>
-      <c r="S71" s="9" t="str">
-        <f aca="false">IF(Q71=0,"No quote",LEFT(IF(AND(ISNUMBER(G71),G71=R71),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I71),I71=R71),"Aslam, ","")&amp;IF(AND(ISNUMBER(K71),K71=R71),"Jamil, ","")&amp;IF(AND(ISNUMBER(M71),M71=R71),"Muller, ","")&amp;IF(AND(ISNUMBER(O71),O71=R71),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G71),G71=R71),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I71),I71=R71),"Aslam, ","")&amp;IF(AND(ISNUMBER(K71),K71=R71),"Jamil, ","")&amp;IF(AND(ISNUMBER(M71),M71=R71),"Muller, ","")&amp;IF(AND(ISNUMBER(O71),O71=R71),"NMMC, ",""))-2))</f>
+      <c r="U71" s="9" t="str">
+        <f aca="false">IF(S71=0,"No quote",LEFT(IF(AND(ISNUMBER(G71),G71=T71),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I71),I71=T71),"Aslam, ","")&amp;IF(AND(ISNUMBER(K71),K71=T71),"Jamil, ","")&amp;IF(AND(ISNUMBER(M71),M71=T71),"Muller, ","")&amp;IF(AND(ISNUMBER(O71),O71=T71),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q71),Q71=T71),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G71),G71=T71),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I71),I71=T71),"Aslam, ","")&amp;IF(AND(ISNUMBER(K71),K71=T71),"Jamil, ","")&amp;IF(AND(ISNUMBER(M71),M71=T71),"Muller, ","")&amp;IF(AND(ISNUMBER(O71),O71=T71),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q71),Q71=T71),"Platinum, ",""))-2))</f>
         <v>Muller</v>
       </c>
-      <c r="T71" s="10" t="n">
-        <f aca="false">IF(Q71=0,"",R71*F71)</f>
+      <c r="V71" s="10" t="n">
+        <f aca="false">IF(S71=0,"",T71*F71)</f>
         <v>17595</v>
       </c>
-      <c r="U71" s="6"/>
+      <c r="W71" s="6"/>
     </row>
     <row r="72" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="5" t="n">
         <v>67</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F72" s="5" t="n">
         <v>200</v>
@@ -6166,7 +6348,7 @@
         <v>49.24</v>
       </c>
       <c r="J72" s="6" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="K72" s="7"/>
       <c r="L72" s="6"/>
@@ -6174,39 +6356,41 @@
       <c r="N72" s="6"/>
       <c r="O72" s="7"/>
       <c r="P72" s="6"/>
-      <c r="Q72" s="5" t="n">
-        <f aca="false">COUNT(G72,I72,K72,M72,O72)</f>
+      <c r="Q72" s="7"/>
+      <c r="R72" s="6"/>
+      <c r="S72" s="5" t="n">
+        <f aca="false">COUNT(G72,I72,K72,M72,O72,Q72)</f>
         <v>1</v>
       </c>
-      <c r="R72" s="8" t="n">
-        <f aca="false">IF(Q72=0,"",MIN(G72,I72,K72,M72,O72))</f>
+      <c r="T72" s="8" t="n">
+        <f aca="false">IF(S72=0,"",MIN(G72,I72,K72,M72,O72,Q72))</f>
         <v>49.24</v>
       </c>
-      <c r="S72" s="9" t="str">
-        <f aca="false">IF(Q72=0,"No quote",LEFT(IF(AND(ISNUMBER(G72),G72=R72),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I72),I72=R72),"Aslam, ","")&amp;IF(AND(ISNUMBER(K72),K72=R72),"Jamil, ","")&amp;IF(AND(ISNUMBER(M72),M72=R72),"Muller, ","")&amp;IF(AND(ISNUMBER(O72),O72=R72),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G72),G72=R72),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I72),I72=R72),"Aslam, ","")&amp;IF(AND(ISNUMBER(K72),K72=R72),"Jamil, ","")&amp;IF(AND(ISNUMBER(M72),M72=R72),"Muller, ","")&amp;IF(AND(ISNUMBER(O72),O72=R72),"NMMC, ",""))-2))</f>
+      <c r="U72" s="9" t="str">
+        <f aca="false">IF(S72=0,"No quote",LEFT(IF(AND(ISNUMBER(G72),G72=T72),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I72),I72=T72),"Aslam, ","")&amp;IF(AND(ISNUMBER(K72),K72=T72),"Jamil, ","")&amp;IF(AND(ISNUMBER(M72),M72=T72),"Muller, ","")&amp;IF(AND(ISNUMBER(O72),O72=T72),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q72),Q72=T72),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G72),G72=T72),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I72),I72=T72),"Aslam, ","")&amp;IF(AND(ISNUMBER(K72),K72=T72),"Jamil, ","")&amp;IF(AND(ISNUMBER(M72),M72=T72),"Muller, ","")&amp;IF(AND(ISNUMBER(O72),O72=T72),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q72),Q72=T72),"Platinum, ",""))-2))</f>
         <v>Aslam</v>
       </c>
-      <c r="T72" s="10" t="n">
-        <f aca="false">IF(Q72=0,"",R72*F72)</f>
+      <c r="V72" s="10" t="n">
+        <f aca="false">IF(S72=0,"",T72*F72)</f>
         <v>9848</v>
       </c>
-      <c r="U72" s="6"/>
+      <c r="W72" s="6"/>
     </row>
     <row r="73" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="5" t="n">
         <v>68</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F73" s="5" t="n">
         <v>100</v>
@@ -6219,45 +6403,47 @@
         <v>86.1</v>
       </c>
       <c r="L73" s="6" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="M73" s="7"/>
       <c r="N73" s="6"/>
       <c r="O73" s="7"/>
       <c r="P73" s="6"/>
-      <c r="Q73" s="5" t="n">
-        <f aca="false">COUNT(G73,I73,K73,M73,O73)</f>
+      <c r="Q73" s="7"/>
+      <c r="R73" s="6"/>
+      <c r="S73" s="5" t="n">
+        <f aca="false">COUNT(G73,I73,K73,M73,O73,Q73)</f>
         <v>1</v>
       </c>
-      <c r="R73" s="8" t="n">
-        <f aca="false">IF(Q73=0,"",MIN(G73,I73,K73,M73,O73))</f>
+      <c r="T73" s="8" t="n">
+        <f aca="false">IF(S73=0,"",MIN(G73,I73,K73,M73,O73,Q73))</f>
         <v>86.1</v>
       </c>
-      <c r="S73" s="9" t="str">
-        <f aca="false">IF(Q73=0,"No quote",LEFT(IF(AND(ISNUMBER(G73),G73=R73),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I73),I73=R73),"Aslam, ","")&amp;IF(AND(ISNUMBER(K73),K73=R73),"Jamil, ","")&amp;IF(AND(ISNUMBER(M73),M73=R73),"Muller, ","")&amp;IF(AND(ISNUMBER(O73),O73=R73),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G73),G73=R73),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I73),I73=R73),"Aslam, ","")&amp;IF(AND(ISNUMBER(K73),K73=R73),"Jamil, ","")&amp;IF(AND(ISNUMBER(M73),M73=R73),"Muller, ","")&amp;IF(AND(ISNUMBER(O73),O73=R73),"NMMC, ",""))-2))</f>
+      <c r="U73" s="9" t="str">
+        <f aca="false">IF(S73=0,"No quote",LEFT(IF(AND(ISNUMBER(G73),G73=T73),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I73),I73=T73),"Aslam, ","")&amp;IF(AND(ISNUMBER(K73),K73=T73),"Jamil, ","")&amp;IF(AND(ISNUMBER(M73),M73=T73),"Muller, ","")&amp;IF(AND(ISNUMBER(O73),O73=T73),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q73),Q73=T73),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G73),G73=T73),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I73),I73=T73),"Aslam, ","")&amp;IF(AND(ISNUMBER(K73),K73=T73),"Jamil, ","")&amp;IF(AND(ISNUMBER(M73),M73=T73),"Muller, ","")&amp;IF(AND(ISNUMBER(O73),O73=T73),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q73),Q73=T73),"Platinum, ",""))-2))</f>
         <v>Jamil</v>
       </c>
-      <c r="T73" s="10" t="n">
-        <f aca="false">IF(Q73=0,"",R73*F73)</f>
+      <c r="V73" s="10" t="n">
+        <f aca="false">IF(S73=0,"",T73*F73)</f>
         <v>8610</v>
       </c>
-      <c r="U73" s="6"/>
+      <c r="W73" s="6"/>
     </row>
     <row r="74" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="5" t="n">
         <v>69</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F74" s="5" t="n">
         <v>50</v>
@@ -6266,7 +6452,7 @@
         <v>348.5</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="I74" s="7"/>
       <c r="J74" s="6"/>
@@ -6278,41 +6464,43 @@
         <v>226.44</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>344</v>
-      </c>
-      <c r="Q74" s="5" t="n">
-        <f aca="false">COUNT(G74,I74,K74,M74,O74)</f>
+        <v>347</v>
+      </c>
+      <c r="Q74" s="7"/>
+      <c r="R74" s="6"/>
+      <c r="S74" s="5" t="n">
+        <f aca="false">COUNT(G74,I74,K74,M74,O74,Q74)</f>
         <v>2</v>
       </c>
-      <c r="R74" s="8" t="n">
-        <f aca="false">IF(Q74=0,"",MIN(G74,I74,K74,M74,O74))</f>
+      <c r="T74" s="8" t="n">
+        <f aca="false">IF(S74=0,"",MIN(G74,I74,K74,M74,O74,Q74))</f>
         <v>226.44</v>
       </c>
-      <c r="S74" s="9" t="str">
-        <f aca="false">IF(Q74=0,"No quote",LEFT(IF(AND(ISNUMBER(G74),G74=R74),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I74),I74=R74),"Aslam, ","")&amp;IF(AND(ISNUMBER(K74),K74=R74),"Jamil, ","")&amp;IF(AND(ISNUMBER(M74),M74=R74),"Muller, ","")&amp;IF(AND(ISNUMBER(O74),O74=R74),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G74),G74=R74),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I74),I74=R74),"Aslam, ","")&amp;IF(AND(ISNUMBER(K74),K74=R74),"Jamil, ","")&amp;IF(AND(ISNUMBER(M74),M74=R74),"Muller, ","")&amp;IF(AND(ISNUMBER(O74),O74=R74),"NMMC, ",""))-2))</f>
+      <c r="U74" s="9" t="str">
+        <f aca="false">IF(S74=0,"No quote",LEFT(IF(AND(ISNUMBER(G74),G74=T74),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I74),I74=T74),"Aslam, ","")&amp;IF(AND(ISNUMBER(K74),K74=T74),"Jamil, ","")&amp;IF(AND(ISNUMBER(M74),M74=T74),"Muller, ","")&amp;IF(AND(ISNUMBER(O74),O74=T74),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q74),Q74=T74),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G74),G74=T74),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I74),I74=T74),"Aslam, ","")&amp;IF(AND(ISNUMBER(K74),K74=T74),"Jamil, ","")&amp;IF(AND(ISNUMBER(M74),M74=T74),"Muller, ","")&amp;IF(AND(ISNUMBER(O74),O74=T74),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q74),Q74=T74),"Platinum, ",""))-2))</f>
         <v>NMMC</v>
       </c>
-      <c r="T74" s="10" t="n">
-        <f aca="false">IF(Q74=0,"",R74*F74)</f>
+      <c r="V74" s="10" t="n">
+        <f aca="false">IF(S74=0,"",T74*F74)</f>
         <v>11322</v>
       </c>
-      <c r="U74" s="6"/>
+      <c r="W74" s="6"/>
     </row>
     <row r="75" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="5" t="n">
         <v>70</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F75" s="5" t="n">
         <v>50</v>
@@ -6325,7 +6513,7 @@
         <v>452.2</v>
       </c>
       <c r="L75" s="6" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="M75" s="7"/>
       <c r="N75" s="6"/>
@@ -6333,41 +6521,47 @@
         <v>764.15</v>
       </c>
       <c r="P75" s="6" t="s">
-        <v>349</v>
-      </c>
-      <c r="Q75" s="5" t="n">
-        <f aca="false">COUNT(G75,I75,K75,M75,O75)</f>
-        <v>2</v>
-      </c>
-      <c r="R75" s="8" t="n">
-        <f aca="false">IF(Q75=0,"",MIN(G75,I75,K75,M75,O75))</f>
-        <v>452.2</v>
-      </c>
-      <c r="S75" s="9" t="str">
-        <f aca="false">IF(Q75=0,"No quote",LEFT(IF(AND(ISNUMBER(G75),G75=R75),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I75),I75=R75),"Aslam, ","")&amp;IF(AND(ISNUMBER(K75),K75=R75),"Jamil, ","")&amp;IF(AND(ISNUMBER(M75),M75=R75),"Muller, ","")&amp;IF(AND(ISNUMBER(O75),O75=R75),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G75),G75=R75),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I75),I75=R75),"Aslam, ","")&amp;IF(AND(ISNUMBER(K75),K75=R75),"Jamil, ","")&amp;IF(AND(ISNUMBER(M75),M75=R75),"Muller, ","")&amp;IF(AND(ISNUMBER(O75),O75=R75),"NMMC, ",""))-2))</f>
-        <v>Jamil</v>
-      </c>
-      <c r="T75" s="10" t="n">
-        <f aca="false">IF(Q75=0,"",R75*F75)</f>
-        <v>22610</v>
-      </c>
-      <c r="U75" s="6"/>
+        <v>352</v>
+      </c>
+      <c r="Q75" s="7" t="n">
+        <v>382.5</v>
+      </c>
+      <c r="R75" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="S75" s="5" t="n">
+        <f aca="false">COUNT(G75,I75,K75,M75,O75,Q75)</f>
+        <v>3</v>
+      </c>
+      <c r="T75" s="8" t="n">
+        <f aca="false">IF(S75=0,"",MIN(G75,I75,K75,M75,O75,Q75))</f>
+        <v>382.5</v>
+      </c>
+      <c r="U75" s="9" t="str">
+        <f aca="false">IF(S75=0,"No quote",LEFT(IF(AND(ISNUMBER(G75),G75=T75),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I75),I75=T75),"Aslam, ","")&amp;IF(AND(ISNUMBER(K75),K75=T75),"Jamil, ","")&amp;IF(AND(ISNUMBER(M75),M75=T75),"Muller, ","")&amp;IF(AND(ISNUMBER(O75),O75=T75),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q75),Q75=T75),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G75),G75=T75),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I75),I75=T75),"Aslam, ","")&amp;IF(AND(ISNUMBER(K75),K75=T75),"Jamil, ","")&amp;IF(AND(ISNUMBER(M75),M75=T75),"Muller, ","")&amp;IF(AND(ISNUMBER(O75),O75=T75),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q75),Q75=T75),"Platinum, ",""))-2))</f>
+        <v>Platinum</v>
+      </c>
+      <c r="V75" s="10" t="n">
+        <f aca="false">IF(S75=0,"",T75*F75)</f>
+        <v>19125</v>
+      </c>
+      <c r="W75" s="6"/>
     </row>
     <row r="76" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="5" t="n">
         <v>71</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F76" s="5" t="n">
         <v>600</v>
@@ -6376,7 +6570,7 @@
         <v>272</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="I76" s="7"/>
       <c r="J76" s="6"/>
@@ -6384,53 +6578,55 @@
         <v>244.8</v>
       </c>
       <c r="L76" s="6" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="M76" s="7" t="n">
         <v>1156</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="O76" s="7" t="n">
         <v>223.21</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>354</v>
-      </c>
-      <c r="Q76" s="5" t="n">
-        <f aca="false">COUNT(G76,I76,K76,M76,O76)</f>
+        <v>358</v>
+      </c>
+      <c r="Q76" s="7"/>
+      <c r="R76" s="6"/>
+      <c r="S76" s="5" t="n">
+        <f aca="false">COUNT(G76,I76,K76,M76,O76,Q76)</f>
         <v>4</v>
       </c>
-      <c r="R76" s="8" t="n">
-        <f aca="false">IF(Q76=0,"",MIN(G76,I76,K76,M76,O76))</f>
+      <c r="T76" s="8" t="n">
+        <f aca="false">IF(S76=0,"",MIN(G76,I76,K76,M76,O76,Q76))</f>
         <v>223.21</v>
       </c>
-      <c r="S76" s="9" t="str">
-        <f aca="false">IF(Q76=0,"No quote",LEFT(IF(AND(ISNUMBER(G76),G76=R76),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I76),I76=R76),"Aslam, ","")&amp;IF(AND(ISNUMBER(K76),K76=R76),"Jamil, ","")&amp;IF(AND(ISNUMBER(M76),M76=R76),"Muller, ","")&amp;IF(AND(ISNUMBER(O76),O76=R76),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G76),G76=R76),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I76),I76=R76),"Aslam, ","")&amp;IF(AND(ISNUMBER(K76),K76=R76),"Jamil, ","")&amp;IF(AND(ISNUMBER(M76),M76=R76),"Muller, ","")&amp;IF(AND(ISNUMBER(O76),O76=R76),"NMMC, ",""))-2))</f>
+      <c r="U76" s="9" t="str">
+        <f aca="false">IF(S76=0,"No quote",LEFT(IF(AND(ISNUMBER(G76),G76=T76),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I76),I76=T76),"Aslam, ","")&amp;IF(AND(ISNUMBER(K76),K76=T76),"Jamil, ","")&amp;IF(AND(ISNUMBER(M76),M76=T76),"Muller, ","")&amp;IF(AND(ISNUMBER(O76),O76=T76),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q76),Q76=T76),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G76),G76=T76),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I76),I76=T76),"Aslam, ","")&amp;IF(AND(ISNUMBER(K76),K76=T76),"Jamil, ","")&amp;IF(AND(ISNUMBER(M76),M76=T76),"Muller, ","")&amp;IF(AND(ISNUMBER(O76),O76=T76),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q76),Q76=T76),"Platinum, ",""))-2))</f>
         <v>NMMC</v>
       </c>
-      <c r="T76" s="10" t="n">
-        <f aca="false">IF(Q76=0,"",R76*F76)</f>
+      <c r="V76" s="10" t="n">
+        <f aca="false">IF(S76=0,"",T76*F76)</f>
         <v>133926</v>
       </c>
-      <c r="U76" s="6"/>
+      <c r="W76" s="6"/>
     </row>
     <row r="77" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="5" t="n">
         <v>72</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F77" s="5" t="n">
         <v>120</v>
@@ -6441,7 +6637,7 @@
         <v>157.2</v>
       </c>
       <c r="J77" s="6" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="K77" s="7"/>
       <c r="L77" s="6"/>
@@ -6449,39 +6645,41 @@
       <c r="N77" s="6"/>
       <c r="O77" s="7"/>
       <c r="P77" s="6"/>
-      <c r="Q77" s="5" t="n">
-        <f aca="false">COUNT(G77,I77,K77,M77,O77)</f>
+      <c r="Q77" s="7"/>
+      <c r="R77" s="6"/>
+      <c r="S77" s="5" t="n">
+        <f aca="false">COUNT(G77,I77,K77,M77,O77,Q77)</f>
         <v>1</v>
       </c>
-      <c r="R77" s="8" t="n">
-        <f aca="false">IF(Q77=0,"",MIN(G77,I77,K77,M77,O77))</f>
+      <c r="T77" s="8" t="n">
+        <f aca="false">IF(S77=0,"",MIN(G77,I77,K77,M77,O77,Q77))</f>
         <v>157.2</v>
       </c>
-      <c r="S77" s="9" t="str">
-        <f aca="false">IF(Q77=0,"No quote",LEFT(IF(AND(ISNUMBER(G77),G77=R77),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I77),I77=R77),"Aslam, ","")&amp;IF(AND(ISNUMBER(K77),K77=R77),"Jamil, ","")&amp;IF(AND(ISNUMBER(M77),M77=R77),"Muller, ","")&amp;IF(AND(ISNUMBER(O77),O77=R77),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G77),G77=R77),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I77),I77=R77),"Aslam, ","")&amp;IF(AND(ISNUMBER(K77),K77=R77),"Jamil, ","")&amp;IF(AND(ISNUMBER(M77),M77=R77),"Muller, ","")&amp;IF(AND(ISNUMBER(O77),O77=R77),"NMMC, ",""))-2))</f>
+      <c r="U77" s="9" t="str">
+        <f aca="false">IF(S77=0,"No quote",LEFT(IF(AND(ISNUMBER(G77),G77=T77),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I77),I77=T77),"Aslam, ","")&amp;IF(AND(ISNUMBER(K77),K77=T77),"Jamil, ","")&amp;IF(AND(ISNUMBER(M77),M77=T77),"Muller, ","")&amp;IF(AND(ISNUMBER(O77),O77=T77),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q77),Q77=T77),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G77),G77=T77),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I77),I77=T77),"Aslam, ","")&amp;IF(AND(ISNUMBER(K77),K77=T77),"Jamil, ","")&amp;IF(AND(ISNUMBER(M77),M77=T77),"Muller, ","")&amp;IF(AND(ISNUMBER(O77),O77=T77),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q77),Q77=T77),"Platinum, ",""))-2))</f>
         <v>Aslam</v>
       </c>
-      <c r="T77" s="10" t="n">
-        <f aca="false">IF(Q77=0,"",R77*F77)</f>
+      <c r="V77" s="10" t="n">
+        <f aca="false">IF(S77=0,"",T77*F77)</f>
         <v>18864</v>
       </c>
-      <c r="U77" s="6"/>
+      <c r="W77" s="6"/>
     </row>
     <row r="78" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="5" t="n">
         <v>73</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F78" s="5" t="n">
         <v>150</v>
@@ -6496,47 +6694,49 @@
         <v>565.25</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="O78" s="7" t="n">
         <v>578</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>360</v>
-      </c>
-      <c r="Q78" s="5" t="n">
-        <f aca="false">COUNT(G78,I78,K78,M78,O78)</f>
+        <v>364</v>
+      </c>
+      <c r="Q78" s="7"/>
+      <c r="R78" s="6"/>
+      <c r="S78" s="5" t="n">
+        <f aca="false">COUNT(G78,I78,K78,M78,O78,Q78)</f>
         <v>2</v>
       </c>
-      <c r="R78" s="8" t="n">
-        <f aca="false">IF(Q78=0,"",MIN(G78,I78,K78,M78,O78))</f>
+      <c r="T78" s="8" t="n">
+        <f aca="false">IF(S78=0,"",MIN(G78,I78,K78,M78,O78,Q78))</f>
         <v>565.25</v>
       </c>
-      <c r="S78" s="9" t="str">
-        <f aca="false">IF(Q78=0,"No quote",LEFT(IF(AND(ISNUMBER(G78),G78=R78),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I78),I78=R78),"Aslam, ","")&amp;IF(AND(ISNUMBER(K78),K78=R78),"Jamil, ","")&amp;IF(AND(ISNUMBER(M78),M78=R78),"Muller, ","")&amp;IF(AND(ISNUMBER(O78),O78=R78),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G78),G78=R78),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I78),I78=R78),"Aslam, ","")&amp;IF(AND(ISNUMBER(K78),K78=R78),"Jamil, ","")&amp;IF(AND(ISNUMBER(M78),M78=R78),"Muller, ","")&amp;IF(AND(ISNUMBER(O78),O78=R78),"NMMC, ",""))-2))</f>
+      <c r="U78" s="9" t="str">
+        <f aca="false">IF(S78=0,"No quote",LEFT(IF(AND(ISNUMBER(G78),G78=T78),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I78),I78=T78),"Aslam, ","")&amp;IF(AND(ISNUMBER(K78),K78=T78),"Jamil, ","")&amp;IF(AND(ISNUMBER(M78),M78=T78),"Muller, ","")&amp;IF(AND(ISNUMBER(O78),O78=T78),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q78),Q78=T78),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G78),G78=T78),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I78),I78=T78),"Aslam, ","")&amp;IF(AND(ISNUMBER(K78),K78=T78),"Jamil, ","")&amp;IF(AND(ISNUMBER(M78),M78=T78),"Muller, ","")&amp;IF(AND(ISNUMBER(O78),O78=T78),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q78),Q78=T78),"Platinum, ",""))-2))</f>
         <v>Muller</v>
       </c>
-      <c r="T78" s="10" t="n">
-        <f aca="false">IF(Q78=0,"",R78*F78)</f>
+      <c r="V78" s="10" t="n">
+        <f aca="false">IF(S78=0,"",T78*F78)</f>
         <v>84787.5</v>
       </c>
-      <c r="U78" s="6"/>
+      <c r="W78" s="6"/>
     </row>
     <row r="79" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="5" t="n">
         <v>74</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F79" s="5" t="n">
         <v>50</v>
@@ -6545,7 +6745,7 @@
         <v>417.35</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="I79" s="7"/>
       <c r="J79" s="6"/>
@@ -6555,47 +6755,49 @@
         <v>336.52</v>
       </c>
       <c r="N79" s="6" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="O79" s="7" t="n">
         <v>221</v>
       </c>
       <c r="P79" s="6" t="s">
-        <v>366</v>
-      </c>
-      <c r="Q79" s="5" t="n">
-        <f aca="false">COUNT(G79,I79,K79,M79,O79)</f>
+        <v>370</v>
+      </c>
+      <c r="Q79" s="7"/>
+      <c r="R79" s="6"/>
+      <c r="S79" s="5" t="n">
+        <f aca="false">COUNT(G79,I79,K79,M79,O79,Q79)</f>
         <v>3</v>
       </c>
-      <c r="R79" s="8" t="n">
-        <f aca="false">IF(Q79=0,"",MIN(G79,I79,K79,M79,O79))</f>
+      <c r="T79" s="8" t="n">
+        <f aca="false">IF(S79=0,"",MIN(G79,I79,K79,M79,O79,Q79))</f>
         <v>221</v>
       </c>
-      <c r="S79" s="9" t="str">
-        <f aca="false">IF(Q79=0,"No quote",LEFT(IF(AND(ISNUMBER(G79),G79=R79),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I79),I79=R79),"Aslam, ","")&amp;IF(AND(ISNUMBER(K79),K79=R79),"Jamil, ","")&amp;IF(AND(ISNUMBER(M79),M79=R79),"Muller, ","")&amp;IF(AND(ISNUMBER(O79),O79=R79),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G79),G79=R79),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I79),I79=R79),"Aslam, ","")&amp;IF(AND(ISNUMBER(K79),K79=R79),"Jamil, ","")&amp;IF(AND(ISNUMBER(M79),M79=R79),"Muller, ","")&amp;IF(AND(ISNUMBER(O79),O79=R79),"NMMC, ",""))-2))</f>
+      <c r="U79" s="9" t="str">
+        <f aca="false">IF(S79=0,"No quote",LEFT(IF(AND(ISNUMBER(G79),G79=T79),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I79),I79=T79),"Aslam, ","")&amp;IF(AND(ISNUMBER(K79),K79=T79),"Jamil, ","")&amp;IF(AND(ISNUMBER(M79),M79=T79),"Muller, ","")&amp;IF(AND(ISNUMBER(O79),O79=T79),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q79),Q79=T79),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G79),G79=T79),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I79),I79=T79),"Aslam, ","")&amp;IF(AND(ISNUMBER(K79),K79=T79),"Jamil, ","")&amp;IF(AND(ISNUMBER(M79),M79=T79),"Muller, ","")&amp;IF(AND(ISNUMBER(O79),O79=T79),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q79),Q79=T79),"Platinum, ",""))-2))</f>
         <v>NMMC</v>
       </c>
-      <c r="T79" s="10" t="n">
-        <f aca="false">IF(Q79=0,"",R79*F79)</f>
+      <c r="V79" s="10" t="n">
+        <f aca="false">IF(S79=0,"",T79*F79)</f>
         <v>11050</v>
       </c>
-      <c r="U79" s="6"/>
+      <c r="W79" s="6"/>
     </row>
     <row r="80" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="5" t="n">
         <v>75</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F80" s="5" t="n">
         <v>100</v>
@@ -6612,41 +6814,43 @@
         <v>198.14</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>370</v>
-      </c>
-      <c r="Q80" s="5" t="n">
-        <f aca="false">COUNT(G80,I80,K80,M80,O80)</f>
+        <v>374</v>
+      </c>
+      <c r="Q80" s="7"/>
+      <c r="R80" s="6"/>
+      <c r="S80" s="5" t="n">
+        <f aca="false">COUNT(G80,I80,K80,M80,O80,Q80)</f>
         <v>1</v>
       </c>
-      <c r="R80" s="8" t="n">
-        <f aca="false">IF(Q80=0,"",MIN(G80,I80,K80,M80,O80))</f>
+      <c r="T80" s="8" t="n">
+        <f aca="false">IF(S80=0,"",MIN(G80,I80,K80,M80,O80,Q80))</f>
         <v>198.14</v>
       </c>
-      <c r="S80" s="9" t="str">
-        <f aca="false">IF(Q80=0,"No quote",LEFT(IF(AND(ISNUMBER(G80),G80=R80),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I80),I80=R80),"Aslam, ","")&amp;IF(AND(ISNUMBER(K80),K80=R80),"Jamil, ","")&amp;IF(AND(ISNUMBER(M80),M80=R80),"Muller, ","")&amp;IF(AND(ISNUMBER(O80),O80=R80),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G80),G80=R80),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I80),I80=R80),"Aslam, ","")&amp;IF(AND(ISNUMBER(K80),K80=R80),"Jamil, ","")&amp;IF(AND(ISNUMBER(M80),M80=R80),"Muller, ","")&amp;IF(AND(ISNUMBER(O80),O80=R80),"NMMC, ",""))-2))</f>
+      <c r="U80" s="9" t="str">
+        <f aca="false">IF(S80=0,"No quote",LEFT(IF(AND(ISNUMBER(G80),G80=T80),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I80),I80=T80),"Aslam, ","")&amp;IF(AND(ISNUMBER(K80),K80=T80),"Jamil, ","")&amp;IF(AND(ISNUMBER(M80),M80=T80),"Muller, ","")&amp;IF(AND(ISNUMBER(O80),O80=T80),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q80),Q80=T80),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G80),G80=T80),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I80),I80=T80),"Aslam, ","")&amp;IF(AND(ISNUMBER(K80),K80=T80),"Jamil, ","")&amp;IF(AND(ISNUMBER(M80),M80=T80),"Muller, ","")&amp;IF(AND(ISNUMBER(O80),O80=T80),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q80),Q80=T80),"Platinum, ",""))-2))</f>
         <v>NMMC</v>
       </c>
-      <c r="T80" s="10" t="n">
-        <f aca="false">IF(Q80=0,"",R80*F80)</f>
+      <c r="V80" s="10" t="n">
+        <f aca="false">IF(S80=0,"",T80*F80)</f>
         <v>19814</v>
       </c>
-      <c r="U80" s="6"/>
+      <c r="W80" s="6"/>
     </row>
     <row r="81" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="5" t="n">
         <v>76</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F81" s="5" t="n">
         <v>500</v>
@@ -6657,59 +6861,61 @@
         <v>1440.67</v>
       </c>
       <c r="J81" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K81" s="7" t="n">
         <v>390.15</v>
       </c>
       <c r="L81" s="6" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="M81" s="7" t="n">
         <v>786.11</v>
       </c>
       <c r="N81" s="6" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="O81" s="7" t="n">
         <v>427.98</v>
       </c>
       <c r="P81" s="6" t="s">
-        <v>376</v>
-      </c>
-      <c r="Q81" s="5" t="n">
-        <f aca="false">COUNT(G81,I81,K81,M81,O81)</f>
+        <v>380</v>
+      </c>
+      <c r="Q81" s="7"/>
+      <c r="R81" s="6"/>
+      <c r="S81" s="5" t="n">
+        <f aca="false">COUNT(G81,I81,K81,M81,O81,Q81)</f>
         <v>4</v>
       </c>
-      <c r="R81" s="8" t="n">
-        <f aca="false">IF(Q81=0,"",MIN(G81,I81,K81,M81,O81))</f>
+      <c r="T81" s="8" t="n">
+        <f aca="false">IF(S81=0,"",MIN(G81,I81,K81,M81,O81,Q81))</f>
         <v>390.15</v>
       </c>
-      <c r="S81" s="9" t="str">
-        <f aca="false">IF(Q81=0,"No quote",LEFT(IF(AND(ISNUMBER(G81),G81=R81),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I81),I81=R81),"Aslam, ","")&amp;IF(AND(ISNUMBER(K81),K81=R81),"Jamil, ","")&amp;IF(AND(ISNUMBER(M81),M81=R81),"Muller, ","")&amp;IF(AND(ISNUMBER(O81),O81=R81),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G81),G81=R81),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I81),I81=R81),"Aslam, ","")&amp;IF(AND(ISNUMBER(K81),K81=R81),"Jamil, ","")&amp;IF(AND(ISNUMBER(M81),M81=R81),"Muller, ","")&amp;IF(AND(ISNUMBER(O81),O81=R81),"NMMC, ",""))-2))</f>
+      <c r="U81" s="9" t="str">
+        <f aca="false">IF(S81=0,"No quote",LEFT(IF(AND(ISNUMBER(G81),G81=T81),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I81),I81=T81),"Aslam, ","")&amp;IF(AND(ISNUMBER(K81),K81=T81),"Jamil, ","")&amp;IF(AND(ISNUMBER(M81),M81=T81),"Muller, ","")&amp;IF(AND(ISNUMBER(O81),O81=T81),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q81),Q81=T81),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G81),G81=T81),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I81),I81=T81),"Aslam, ","")&amp;IF(AND(ISNUMBER(K81),K81=T81),"Jamil, ","")&amp;IF(AND(ISNUMBER(M81),M81=T81),"Muller, ","")&amp;IF(AND(ISNUMBER(O81),O81=T81),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q81),Q81=T81),"Platinum, ",""))-2))</f>
         <v>Jamil</v>
       </c>
-      <c r="T81" s="10" t="n">
-        <f aca="false">IF(Q81=0,"",R81*F81)</f>
+      <c r="V81" s="10" t="n">
+        <f aca="false">IF(S81=0,"",T81*F81)</f>
         <v>195075</v>
       </c>
-      <c r="U81" s="6"/>
+      <c r="W81" s="6"/>
     </row>
     <row r="82" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="5" t="n">
         <v>77</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F82" s="5" t="n">
         <v>150</v>
@@ -6718,7 +6924,7 @@
         <v>310.25</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="I82" s="7"/>
       <c r="J82" s="6"/>
@@ -6728,47 +6934,49 @@
         <v>561</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="O82" s="7" t="n">
         <v>408</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>382</v>
-      </c>
-      <c r="Q82" s="5" t="n">
-        <f aca="false">COUNT(G82,I82,K82,M82,O82)</f>
+        <v>386</v>
+      </c>
+      <c r="Q82" s="7"/>
+      <c r="R82" s="6"/>
+      <c r="S82" s="5" t="n">
+        <f aca="false">COUNT(G82,I82,K82,M82,O82,Q82)</f>
         <v>3</v>
       </c>
-      <c r="R82" s="8" t="n">
-        <f aca="false">IF(Q82=0,"",MIN(G82,I82,K82,M82,O82))</f>
+      <c r="T82" s="8" t="n">
+        <f aca="false">IF(S82=0,"",MIN(G82,I82,K82,M82,O82,Q82))</f>
         <v>310.25</v>
       </c>
-      <c r="S82" s="9" t="str">
-        <f aca="false">IF(Q82=0,"No quote",LEFT(IF(AND(ISNUMBER(G82),G82=R82),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I82),I82=R82),"Aslam, ","")&amp;IF(AND(ISNUMBER(K82),K82=R82),"Jamil, ","")&amp;IF(AND(ISNUMBER(M82),M82=R82),"Muller, ","")&amp;IF(AND(ISNUMBER(O82),O82=R82),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G82),G82=R82),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I82),I82=R82),"Aslam, ","")&amp;IF(AND(ISNUMBER(K82),K82=R82),"Jamil, ","")&amp;IF(AND(ISNUMBER(M82),M82=R82),"Muller, ","")&amp;IF(AND(ISNUMBER(O82),O82=R82),"NMMC, ",""))-2))</f>
+      <c r="U82" s="9" t="str">
+        <f aca="false">IF(S82=0,"No quote",LEFT(IF(AND(ISNUMBER(G82),G82=T82),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I82),I82=T82),"Aslam, ","")&amp;IF(AND(ISNUMBER(K82),K82=T82),"Jamil, ","")&amp;IF(AND(ISNUMBER(M82),M82=T82),"Muller, ","")&amp;IF(AND(ISNUMBER(O82),O82=T82),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q82),Q82=T82),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G82),G82=T82),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I82),I82=T82),"Aslam, ","")&amp;IF(AND(ISNUMBER(K82),K82=T82),"Jamil, ","")&amp;IF(AND(ISNUMBER(M82),M82=T82),"Muller, ","")&amp;IF(AND(ISNUMBER(O82),O82=T82),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q82),Q82=T82),"Platinum, ",""))-2))</f>
         <v>Ahsan</v>
       </c>
-      <c r="T82" s="10" t="n">
-        <f aca="false">IF(Q82=0,"",R82*F82)</f>
+      <c r="V82" s="10" t="n">
+        <f aca="false">IF(S82=0,"",T82*F82)</f>
         <v>46537.5</v>
       </c>
-      <c r="U82" s="6"/>
+      <c r="W82" s="6"/>
     </row>
     <row r="83" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="5" t="n">
         <v>78</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F83" s="5" t="n">
         <v>150</v>
@@ -6783,47 +6991,49 @@
         <v>439.45</v>
       </c>
       <c r="N83" s="6" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="O83" s="7" t="n">
         <v>138.73</v>
       </c>
       <c r="P83" s="6" t="s">
-        <v>387</v>
-      </c>
-      <c r="Q83" s="5" t="n">
-        <f aca="false">COUNT(G83,I83,K83,M83,O83)</f>
+        <v>391</v>
+      </c>
+      <c r="Q83" s="7"/>
+      <c r="R83" s="6"/>
+      <c r="S83" s="5" t="n">
+        <f aca="false">COUNT(G83,I83,K83,M83,O83,Q83)</f>
         <v>2</v>
       </c>
-      <c r="R83" s="8" t="n">
-        <f aca="false">IF(Q83=0,"",MIN(G83,I83,K83,M83,O83))</f>
+      <c r="T83" s="8" t="n">
+        <f aca="false">IF(S83=0,"",MIN(G83,I83,K83,M83,O83,Q83))</f>
         <v>138.73</v>
       </c>
-      <c r="S83" s="9" t="str">
-        <f aca="false">IF(Q83=0,"No quote",LEFT(IF(AND(ISNUMBER(G83),G83=R83),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I83),I83=R83),"Aslam, ","")&amp;IF(AND(ISNUMBER(K83),K83=R83),"Jamil, ","")&amp;IF(AND(ISNUMBER(M83),M83=R83),"Muller, ","")&amp;IF(AND(ISNUMBER(O83),O83=R83),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G83),G83=R83),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I83),I83=R83),"Aslam, ","")&amp;IF(AND(ISNUMBER(K83),K83=R83),"Jamil, ","")&amp;IF(AND(ISNUMBER(M83),M83=R83),"Muller, ","")&amp;IF(AND(ISNUMBER(O83),O83=R83),"NMMC, ",""))-2))</f>
+      <c r="U83" s="9" t="str">
+        <f aca="false">IF(S83=0,"No quote",LEFT(IF(AND(ISNUMBER(G83),G83=T83),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I83),I83=T83),"Aslam, ","")&amp;IF(AND(ISNUMBER(K83),K83=T83),"Jamil, ","")&amp;IF(AND(ISNUMBER(M83),M83=T83),"Muller, ","")&amp;IF(AND(ISNUMBER(O83),O83=T83),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q83),Q83=T83),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G83),G83=T83),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I83),I83=T83),"Aslam, ","")&amp;IF(AND(ISNUMBER(K83),K83=T83),"Jamil, ","")&amp;IF(AND(ISNUMBER(M83),M83=T83),"Muller, ","")&amp;IF(AND(ISNUMBER(O83),O83=T83),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q83),Q83=T83),"Platinum, ",""))-2))</f>
         <v>NMMC</v>
       </c>
-      <c r="T83" s="10" t="n">
-        <f aca="false">IF(Q83=0,"",R83*F83)</f>
+      <c r="V83" s="10" t="n">
+        <f aca="false">IF(S83=0,"",T83*F83)</f>
         <v>20809.5</v>
       </c>
-      <c r="U83" s="6"/>
+      <c r="W83" s="6"/>
     </row>
     <row r="84" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="5" t="n">
         <v>79</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F84" s="5" t="n">
         <v>450</v>
@@ -6832,7 +7042,7 @@
         <v>204</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="I84" s="7"/>
       <c r="J84" s="6"/>
@@ -6842,47 +7052,53 @@
         <v>357</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="O84" s="7" t="n">
         <v>229.075</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>391</v>
-      </c>
-      <c r="Q84" s="5" t="n">
-        <f aca="false">COUNT(G84,I84,K84,M84,O84)</f>
-        <v>3</v>
-      </c>
-      <c r="R84" s="8" t="n">
-        <f aca="false">IF(Q84=0,"",MIN(G84,I84,K84,M84,O84))</f>
+        <v>395</v>
+      </c>
+      <c r="Q84" s="7" t="n">
+        <v>208.08</v>
+      </c>
+      <c r="R84" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="S84" s="5" t="n">
+        <f aca="false">COUNT(G84,I84,K84,M84,O84,Q84)</f>
+        <v>4</v>
+      </c>
+      <c r="T84" s="8" t="n">
+        <f aca="false">IF(S84=0,"",MIN(G84,I84,K84,M84,O84,Q84))</f>
         <v>204</v>
       </c>
-      <c r="S84" s="9" t="str">
-        <f aca="false">IF(Q84=0,"No quote",LEFT(IF(AND(ISNUMBER(G84),G84=R84),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I84),I84=R84),"Aslam, ","")&amp;IF(AND(ISNUMBER(K84),K84=R84),"Jamil, ","")&amp;IF(AND(ISNUMBER(M84),M84=R84),"Muller, ","")&amp;IF(AND(ISNUMBER(O84),O84=R84),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G84),G84=R84),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I84),I84=R84),"Aslam, ","")&amp;IF(AND(ISNUMBER(K84),K84=R84),"Jamil, ","")&amp;IF(AND(ISNUMBER(M84),M84=R84),"Muller, ","")&amp;IF(AND(ISNUMBER(O84),O84=R84),"NMMC, ",""))-2))</f>
+      <c r="U84" s="9" t="str">
+        <f aca="false">IF(S84=0,"No quote",LEFT(IF(AND(ISNUMBER(G84),G84=T84),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I84),I84=T84),"Aslam, ","")&amp;IF(AND(ISNUMBER(K84),K84=T84),"Jamil, ","")&amp;IF(AND(ISNUMBER(M84),M84=T84),"Muller, ","")&amp;IF(AND(ISNUMBER(O84),O84=T84),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q84),Q84=T84),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G84),G84=T84),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I84),I84=T84),"Aslam, ","")&amp;IF(AND(ISNUMBER(K84),K84=T84),"Jamil, ","")&amp;IF(AND(ISNUMBER(M84),M84=T84),"Muller, ","")&amp;IF(AND(ISNUMBER(O84),O84=T84),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q84),Q84=T84),"Platinum, ",""))-2))</f>
         <v>Ahsan</v>
       </c>
-      <c r="T84" s="10" t="n">
-        <f aca="false">IF(Q84=0,"",R84*F84)</f>
+      <c r="V84" s="10" t="n">
+        <f aca="false">IF(S84=0,"",T84*F84)</f>
         <v>91800</v>
       </c>
-      <c r="U84" s="6"/>
+      <c r="W84" s="6"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="5" t="n">
         <v>80</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F85" s="5" t="n">
         <v>50</v>
@@ -6897,39 +7113,41 @@
       <c r="N85" s="6"/>
       <c r="O85" s="7"/>
       <c r="P85" s="6"/>
-      <c r="Q85" s="5" t="n">
-        <f aca="false">COUNT(G85,I85,K85,M85,O85)</f>
+      <c r="Q85" s="7"/>
+      <c r="R85" s="6"/>
+      <c r="S85" s="5" t="n">
+        <f aca="false">COUNT(G85,I85,K85,M85,O85,Q85)</f>
         <v>0</v>
       </c>
-      <c r="R85" s="8" t="str">
-        <f aca="false">IF(Q85=0,"",MIN(G85,I85,K85,M85,O85))</f>
+      <c r="T85" s="8" t="str">
+        <f aca="false">IF(S85=0,"",MIN(G85,I85,K85,M85,O85,Q85))</f>
         <v/>
       </c>
-      <c r="S85" s="9" t="str">
-        <f aca="false">IF(Q85=0,"No quote",LEFT(IF(AND(ISNUMBER(G85),G85=R85),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I85),I85=R85),"Aslam, ","")&amp;IF(AND(ISNUMBER(K85),K85=R85),"Jamil, ","")&amp;IF(AND(ISNUMBER(M85),M85=R85),"Muller, ","")&amp;IF(AND(ISNUMBER(O85),O85=R85),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G85),G85=R85),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I85),I85=R85),"Aslam, ","")&amp;IF(AND(ISNUMBER(K85),K85=R85),"Jamil, ","")&amp;IF(AND(ISNUMBER(M85),M85=R85),"Muller, ","")&amp;IF(AND(ISNUMBER(O85),O85=R85),"NMMC, ",""))-2))</f>
+      <c r="U85" s="9" t="str">
+        <f aca="false">IF(S85=0,"No quote",LEFT(IF(AND(ISNUMBER(G85),G85=T85),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I85),I85=T85),"Aslam, ","")&amp;IF(AND(ISNUMBER(K85),K85=T85),"Jamil, ","")&amp;IF(AND(ISNUMBER(M85),M85=T85),"Muller, ","")&amp;IF(AND(ISNUMBER(O85),O85=T85),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q85),Q85=T85),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G85),G85=T85),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I85),I85=T85),"Aslam, ","")&amp;IF(AND(ISNUMBER(K85),K85=T85),"Jamil, ","")&amp;IF(AND(ISNUMBER(M85),M85=T85),"Muller, ","")&amp;IF(AND(ISNUMBER(O85),O85=T85),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q85),Q85=T85),"Platinum, ",""))-2))</f>
         <v>No quote</v>
       </c>
-      <c r="T85" s="10" t="str">
-        <f aca="false">IF(Q85=0,"",R85*F85)</f>
+      <c r="V85" s="10" t="str">
+        <f aca="false">IF(S85=0,"",T85*F85)</f>
         <v/>
       </c>
-      <c r="U85" s="6"/>
+      <c r="W85" s="6"/>
     </row>
     <row r="86" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="5" t="n">
         <v>81</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F86" s="5" t="n">
         <v>100</v>
@@ -6942,45 +7160,47 @@
         <v>1211.25</v>
       </c>
       <c r="L86" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="M86" s="7"/>
       <c r="N86" s="6"/>
       <c r="O86" s="7"/>
       <c r="P86" s="6"/>
-      <c r="Q86" s="5" t="n">
-        <f aca="false">COUNT(G86,I86,K86,M86,O86)</f>
+      <c r="Q86" s="7"/>
+      <c r="R86" s="6"/>
+      <c r="S86" s="5" t="n">
+        <f aca="false">COUNT(G86,I86,K86,M86,O86,Q86)</f>
         <v>1</v>
       </c>
-      <c r="R86" s="8" t="n">
-        <f aca="false">IF(Q86=0,"",MIN(G86,I86,K86,M86,O86))</f>
+      <c r="T86" s="8" t="n">
+        <f aca="false">IF(S86=0,"",MIN(G86,I86,K86,M86,O86,Q86))</f>
         <v>1211.25</v>
       </c>
-      <c r="S86" s="9" t="str">
-        <f aca="false">IF(Q86=0,"No quote",LEFT(IF(AND(ISNUMBER(G86),G86=R86),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I86),I86=R86),"Aslam, ","")&amp;IF(AND(ISNUMBER(K86),K86=R86),"Jamil, ","")&amp;IF(AND(ISNUMBER(M86),M86=R86),"Muller, ","")&amp;IF(AND(ISNUMBER(O86),O86=R86),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G86),G86=R86),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I86),I86=R86),"Aslam, ","")&amp;IF(AND(ISNUMBER(K86),K86=R86),"Jamil, ","")&amp;IF(AND(ISNUMBER(M86),M86=R86),"Muller, ","")&amp;IF(AND(ISNUMBER(O86),O86=R86),"NMMC, ",""))-2))</f>
+      <c r="U86" s="9" t="str">
+        <f aca="false">IF(S86=0,"No quote",LEFT(IF(AND(ISNUMBER(G86),G86=T86),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I86),I86=T86),"Aslam, ","")&amp;IF(AND(ISNUMBER(K86),K86=T86),"Jamil, ","")&amp;IF(AND(ISNUMBER(M86),M86=T86),"Muller, ","")&amp;IF(AND(ISNUMBER(O86),O86=T86),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q86),Q86=T86),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G86),G86=T86),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I86),I86=T86),"Aslam, ","")&amp;IF(AND(ISNUMBER(K86),K86=T86),"Jamil, ","")&amp;IF(AND(ISNUMBER(M86),M86=T86),"Muller, ","")&amp;IF(AND(ISNUMBER(O86),O86=T86),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q86),Q86=T86),"Platinum, ",""))-2))</f>
         <v>Jamil</v>
       </c>
-      <c r="T86" s="10" t="n">
-        <f aca="false">IF(Q86=0,"",R86*F86)</f>
+      <c r="V86" s="10" t="n">
+        <f aca="false">IF(S86=0,"",T86*F86)</f>
         <v>121125</v>
       </c>
-      <c r="U86" s="6"/>
+      <c r="W86" s="6"/>
     </row>
     <row r="87" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="5" t="n">
         <v>82</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F87" s="5" t="n">
         <v>150</v>
@@ -6995,39 +7215,41 @@
       <c r="N87" s="6"/>
       <c r="O87" s="7"/>
       <c r="P87" s="6"/>
-      <c r="Q87" s="5" t="n">
-        <f aca="false">COUNT(G87,I87,K87,M87,O87)</f>
+      <c r="Q87" s="7"/>
+      <c r="R87" s="6"/>
+      <c r="S87" s="5" t="n">
+        <f aca="false">COUNT(G87,I87,K87,M87,O87,Q87)</f>
         <v>0</v>
       </c>
-      <c r="R87" s="8" t="str">
-        <f aca="false">IF(Q87=0,"",MIN(G87,I87,K87,M87,O87))</f>
+      <c r="T87" s="8" t="str">
+        <f aca="false">IF(S87=0,"",MIN(G87,I87,K87,M87,O87,Q87))</f>
         <v/>
       </c>
-      <c r="S87" s="9" t="str">
-        <f aca="false">IF(Q87=0,"No quote",LEFT(IF(AND(ISNUMBER(G87),G87=R87),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I87),I87=R87),"Aslam, ","")&amp;IF(AND(ISNUMBER(K87),K87=R87),"Jamil, ","")&amp;IF(AND(ISNUMBER(M87),M87=R87),"Muller, ","")&amp;IF(AND(ISNUMBER(O87),O87=R87),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G87),G87=R87),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I87),I87=R87),"Aslam, ","")&amp;IF(AND(ISNUMBER(K87),K87=R87),"Jamil, ","")&amp;IF(AND(ISNUMBER(M87),M87=R87),"Muller, ","")&amp;IF(AND(ISNUMBER(O87),O87=R87),"NMMC, ",""))-2))</f>
+      <c r="U87" s="9" t="str">
+        <f aca="false">IF(S87=0,"No quote",LEFT(IF(AND(ISNUMBER(G87),G87=T87),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I87),I87=T87),"Aslam, ","")&amp;IF(AND(ISNUMBER(K87),K87=T87),"Jamil, ","")&amp;IF(AND(ISNUMBER(M87),M87=T87),"Muller, ","")&amp;IF(AND(ISNUMBER(O87),O87=T87),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q87),Q87=T87),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G87),G87=T87),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I87),I87=T87),"Aslam, ","")&amp;IF(AND(ISNUMBER(K87),K87=T87),"Jamil, ","")&amp;IF(AND(ISNUMBER(M87),M87=T87),"Muller, ","")&amp;IF(AND(ISNUMBER(O87),O87=T87),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q87),Q87=T87),"Platinum, ",""))-2))</f>
         <v>No quote</v>
       </c>
-      <c r="T87" s="10" t="str">
-        <f aca="false">IF(Q87=0,"",R87*F87)</f>
+      <c r="V87" s="10" t="str">
+        <f aca="false">IF(S87=0,"",T87*F87)</f>
         <v/>
       </c>
-      <c r="U87" s="6"/>
+      <c r="W87" s="6"/>
     </row>
     <row r="88" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="5" t="n">
         <v>83</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F88" s="5" t="n">
         <v>400</v>
@@ -7036,7 +7258,7 @@
         <v>650.25</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="I88" s="7"/>
       <c r="J88" s="6"/>
@@ -7046,47 +7268,49 @@
         <v>660.96</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="O88" s="7" t="n">
         <v>531.08</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>407</v>
-      </c>
-      <c r="Q88" s="5" t="n">
-        <f aca="false">COUNT(G88,I88,K88,M88,O88)</f>
+        <v>412</v>
+      </c>
+      <c r="Q88" s="7"/>
+      <c r="R88" s="6"/>
+      <c r="S88" s="5" t="n">
+        <f aca="false">COUNT(G88,I88,K88,M88,O88,Q88)</f>
         <v>3</v>
       </c>
-      <c r="R88" s="8" t="n">
-        <f aca="false">IF(Q88=0,"",MIN(G88,I88,K88,M88,O88))</f>
+      <c r="T88" s="8" t="n">
+        <f aca="false">IF(S88=0,"",MIN(G88,I88,K88,M88,O88,Q88))</f>
         <v>531.08</v>
       </c>
-      <c r="S88" s="9" t="str">
-        <f aca="false">IF(Q88=0,"No quote",LEFT(IF(AND(ISNUMBER(G88),G88=R88),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I88),I88=R88),"Aslam, ","")&amp;IF(AND(ISNUMBER(K88),K88=R88),"Jamil, ","")&amp;IF(AND(ISNUMBER(M88),M88=R88),"Muller, ","")&amp;IF(AND(ISNUMBER(O88),O88=R88),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G88),G88=R88),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I88),I88=R88),"Aslam, ","")&amp;IF(AND(ISNUMBER(K88),K88=R88),"Jamil, ","")&amp;IF(AND(ISNUMBER(M88),M88=R88),"Muller, ","")&amp;IF(AND(ISNUMBER(O88),O88=R88),"NMMC, ",""))-2))</f>
+      <c r="U88" s="9" t="str">
+        <f aca="false">IF(S88=0,"No quote",LEFT(IF(AND(ISNUMBER(G88),G88=T88),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I88),I88=T88),"Aslam, ","")&amp;IF(AND(ISNUMBER(K88),K88=T88),"Jamil, ","")&amp;IF(AND(ISNUMBER(M88),M88=T88),"Muller, ","")&amp;IF(AND(ISNUMBER(O88),O88=T88),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q88),Q88=T88),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G88),G88=T88),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I88),I88=T88),"Aslam, ","")&amp;IF(AND(ISNUMBER(K88),K88=T88),"Jamil, ","")&amp;IF(AND(ISNUMBER(M88),M88=T88),"Muller, ","")&amp;IF(AND(ISNUMBER(O88),O88=T88),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q88),Q88=T88),"Platinum, ",""))-2))</f>
         <v>NMMC</v>
       </c>
-      <c r="T88" s="10" t="n">
-        <f aca="false">IF(Q88=0,"",R88*F88)</f>
+      <c r="V88" s="10" t="n">
+        <f aca="false">IF(S88=0,"",T88*F88)</f>
         <v>212432</v>
       </c>
-      <c r="U88" s="6"/>
+      <c r="W88" s="6"/>
     </row>
     <row r="89" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="5" t="n">
         <v>84</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F89" s="5" t="n">
         <v>300</v>
@@ -7095,7 +7319,7 @@
         <v>378.25</v>
       </c>
       <c r="H89" s="6" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="I89" s="7"/>
       <c r="J89" s="6"/>
@@ -7105,47 +7329,49 @@
         <v>617.185</v>
       </c>
       <c r="N89" s="6" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="O89" s="7" t="n">
         <v>145.35</v>
       </c>
       <c r="P89" s="6" t="s">
-        <v>413</v>
-      </c>
-      <c r="Q89" s="5" t="n">
-        <f aca="false">COUNT(G89,I89,K89,M89,O89)</f>
+        <v>418</v>
+      </c>
+      <c r="Q89" s="7"/>
+      <c r="R89" s="6"/>
+      <c r="S89" s="5" t="n">
+        <f aca="false">COUNT(G89,I89,K89,M89,O89,Q89)</f>
         <v>3</v>
       </c>
-      <c r="R89" s="8" t="n">
-        <f aca="false">IF(Q89=0,"",MIN(G89,I89,K89,M89,O89))</f>
+      <c r="T89" s="8" t="n">
+        <f aca="false">IF(S89=0,"",MIN(G89,I89,K89,M89,O89,Q89))</f>
         <v>145.35</v>
       </c>
-      <c r="S89" s="9" t="str">
-        <f aca="false">IF(Q89=0,"No quote",LEFT(IF(AND(ISNUMBER(G89),G89=R89),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I89),I89=R89),"Aslam, ","")&amp;IF(AND(ISNUMBER(K89),K89=R89),"Jamil, ","")&amp;IF(AND(ISNUMBER(M89),M89=R89),"Muller, ","")&amp;IF(AND(ISNUMBER(O89),O89=R89),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G89),G89=R89),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I89),I89=R89),"Aslam, ","")&amp;IF(AND(ISNUMBER(K89),K89=R89),"Jamil, ","")&amp;IF(AND(ISNUMBER(M89),M89=R89),"Muller, ","")&amp;IF(AND(ISNUMBER(O89),O89=R89),"NMMC, ",""))-2))</f>
+      <c r="U89" s="9" t="str">
+        <f aca="false">IF(S89=0,"No quote",LEFT(IF(AND(ISNUMBER(G89),G89=T89),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I89),I89=T89),"Aslam, ","")&amp;IF(AND(ISNUMBER(K89),K89=T89),"Jamil, ","")&amp;IF(AND(ISNUMBER(M89),M89=T89),"Muller, ","")&amp;IF(AND(ISNUMBER(O89),O89=T89),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q89),Q89=T89),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G89),G89=T89),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I89),I89=T89),"Aslam, ","")&amp;IF(AND(ISNUMBER(K89),K89=T89),"Jamil, ","")&amp;IF(AND(ISNUMBER(M89),M89=T89),"Muller, ","")&amp;IF(AND(ISNUMBER(O89),O89=T89),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q89),Q89=T89),"Platinum, ",""))-2))</f>
         <v>NMMC</v>
       </c>
-      <c r="T89" s="10" t="n">
-        <f aca="false">IF(Q89=0,"",R89*F89)</f>
+      <c r="V89" s="10" t="n">
+        <f aca="false">IF(S89=0,"",T89*F89)</f>
         <v>43605</v>
       </c>
-      <c r="U89" s="6"/>
+      <c r="W89" s="6"/>
     </row>
     <row r="90" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="5" t="n">
         <v>85</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F90" s="5" t="n">
         <v>250</v>
@@ -7154,7 +7380,7 @@
         <v>340</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="I90" s="7"/>
       <c r="J90" s="6"/>
@@ -7164,43 +7390,45 @@
         <v>347.01</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="O90" s="7"/>
       <c r="P90" s="6"/>
-      <c r="Q90" s="5" t="n">
-        <f aca="false">COUNT(G90,I90,K90,M90,O90)</f>
+      <c r="Q90" s="7"/>
+      <c r="R90" s="6"/>
+      <c r="S90" s="5" t="n">
+        <f aca="false">COUNT(G90,I90,K90,M90,O90,Q90)</f>
         <v>2</v>
       </c>
-      <c r="R90" s="8" t="n">
-        <f aca="false">IF(Q90=0,"",MIN(G90,I90,K90,M90,O90))</f>
+      <c r="T90" s="8" t="n">
+        <f aca="false">IF(S90=0,"",MIN(G90,I90,K90,M90,O90,Q90))</f>
         <v>340</v>
       </c>
-      <c r="S90" s="9" t="str">
-        <f aca="false">IF(Q90=0,"No quote",LEFT(IF(AND(ISNUMBER(G90),G90=R90),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I90),I90=R90),"Aslam, ","")&amp;IF(AND(ISNUMBER(K90),K90=R90),"Jamil, ","")&amp;IF(AND(ISNUMBER(M90),M90=R90),"Muller, ","")&amp;IF(AND(ISNUMBER(O90),O90=R90),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G90),G90=R90),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I90),I90=R90),"Aslam, ","")&amp;IF(AND(ISNUMBER(K90),K90=R90),"Jamil, ","")&amp;IF(AND(ISNUMBER(M90),M90=R90),"Muller, ","")&amp;IF(AND(ISNUMBER(O90),O90=R90),"NMMC, ",""))-2))</f>
+      <c r="U90" s="9" t="str">
+        <f aca="false">IF(S90=0,"No quote",LEFT(IF(AND(ISNUMBER(G90),G90=T90),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I90),I90=T90),"Aslam, ","")&amp;IF(AND(ISNUMBER(K90),K90=T90),"Jamil, ","")&amp;IF(AND(ISNUMBER(M90),M90=T90),"Muller, ","")&amp;IF(AND(ISNUMBER(O90),O90=T90),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q90),Q90=T90),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G90),G90=T90),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I90),I90=T90),"Aslam, ","")&amp;IF(AND(ISNUMBER(K90),K90=T90),"Jamil, ","")&amp;IF(AND(ISNUMBER(M90),M90=T90),"Muller, ","")&amp;IF(AND(ISNUMBER(O90),O90=T90),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q90),Q90=T90),"Platinum, ",""))-2))</f>
         <v>Ahsan</v>
       </c>
-      <c r="T90" s="10" t="n">
-        <f aca="false">IF(Q90=0,"",R90*F90)</f>
+      <c r="V90" s="10" t="n">
+        <f aca="false">IF(S90=0,"",T90*F90)</f>
         <v>85000</v>
       </c>
-      <c r="U90" s="6"/>
+      <c r="W90" s="6"/>
     </row>
     <row r="91" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="5" t="n">
         <v>86</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F91" s="5" t="n">
         <v>50</v>
@@ -7215,43 +7443,45 @@
         <v>550.8</v>
       </c>
       <c r="N91" s="6" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="O91" s="7"/>
       <c r="P91" s="6"/>
-      <c r="Q91" s="5" t="n">
-        <f aca="false">COUNT(G91,I91,K91,M91,O91)</f>
+      <c r="Q91" s="7"/>
+      <c r="R91" s="6"/>
+      <c r="S91" s="5" t="n">
+        <f aca="false">COUNT(G91,I91,K91,M91,O91,Q91)</f>
         <v>1</v>
       </c>
-      <c r="R91" s="8" t="n">
-        <f aca="false">IF(Q91=0,"",MIN(G91,I91,K91,M91,O91))</f>
+      <c r="T91" s="8" t="n">
+        <f aca="false">IF(S91=0,"",MIN(G91,I91,K91,M91,O91,Q91))</f>
         <v>550.8</v>
       </c>
-      <c r="S91" s="9" t="str">
-        <f aca="false">IF(Q91=0,"No quote",LEFT(IF(AND(ISNUMBER(G91),G91=R91),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I91),I91=R91),"Aslam, ","")&amp;IF(AND(ISNUMBER(K91),K91=R91),"Jamil, ","")&amp;IF(AND(ISNUMBER(M91),M91=R91),"Muller, ","")&amp;IF(AND(ISNUMBER(O91),O91=R91),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G91),G91=R91),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I91),I91=R91),"Aslam, ","")&amp;IF(AND(ISNUMBER(K91),K91=R91),"Jamil, ","")&amp;IF(AND(ISNUMBER(M91),M91=R91),"Muller, ","")&amp;IF(AND(ISNUMBER(O91),O91=R91),"NMMC, ",""))-2))</f>
+      <c r="U91" s="9" t="str">
+        <f aca="false">IF(S91=0,"No quote",LEFT(IF(AND(ISNUMBER(G91),G91=T91),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I91),I91=T91),"Aslam, ","")&amp;IF(AND(ISNUMBER(K91),K91=T91),"Jamil, ","")&amp;IF(AND(ISNUMBER(M91),M91=T91),"Muller, ","")&amp;IF(AND(ISNUMBER(O91),O91=T91),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q91),Q91=T91),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G91),G91=T91),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I91),I91=T91),"Aslam, ","")&amp;IF(AND(ISNUMBER(K91),K91=T91),"Jamil, ","")&amp;IF(AND(ISNUMBER(M91),M91=T91),"Muller, ","")&amp;IF(AND(ISNUMBER(O91),O91=T91),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q91),Q91=T91),"Platinum, ",""))-2))</f>
         <v>Muller</v>
       </c>
-      <c r="T91" s="10" t="n">
-        <f aca="false">IF(Q91=0,"",R91*F91)</f>
+      <c r="V91" s="10" t="n">
+        <f aca="false">IF(S91=0,"",T91*F91)</f>
         <v>27540</v>
       </c>
-      <c r="U91" s="6"/>
+      <c r="W91" s="6"/>
     </row>
     <row r="92" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="5" t="n">
         <v>87</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F92" s="5" t="n">
         <v>25</v>
@@ -7262,7 +7492,7 @@
         <v>809.55</v>
       </c>
       <c r="J92" s="6" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="K92" s="7"/>
       <c r="L92" s="6"/>
@@ -7270,39 +7500,45 @@
       <c r="N92" s="6"/>
       <c r="O92" s="7"/>
       <c r="P92" s="6"/>
-      <c r="Q92" s="5" t="n">
-        <f aca="false">COUNT(G92,I92,K92,M92,O92)</f>
-        <v>1</v>
-      </c>
-      <c r="R92" s="8" t="n">
-        <f aca="false">IF(Q92=0,"",MIN(G92,I92,K92,M92,O92))</f>
-        <v>809.55</v>
-      </c>
-      <c r="S92" s="9" t="str">
-        <f aca="false">IF(Q92=0,"No quote",LEFT(IF(AND(ISNUMBER(G92),G92=R92),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I92),I92=R92),"Aslam, ","")&amp;IF(AND(ISNUMBER(K92),K92=R92),"Jamil, ","")&amp;IF(AND(ISNUMBER(M92),M92=R92),"Muller, ","")&amp;IF(AND(ISNUMBER(O92),O92=R92),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G92),G92=R92),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I92),I92=R92),"Aslam, ","")&amp;IF(AND(ISNUMBER(K92),K92=R92),"Jamil, ","")&amp;IF(AND(ISNUMBER(M92),M92=R92),"Muller, ","")&amp;IF(AND(ISNUMBER(O92),O92=R92),"NMMC, ",""))-2))</f>
-        <v>Aslam</v>
-      </c>
-      <c r="T92" s="10" t="n">
-        <f aca="false">IF(Q92=0,"",R92*F92)</f>
-        <v>20238.75</v>
-      </c>
-      <c r="U92" s="6"/>
+      <c r="Q92" s="7" t="n">
+        <v>312.37</v>
+      </c>
+      <c r="R92" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="S92" s="5" t="n">
+        <f aca="false">COUNT(G92,I92,K92,M92,O92,Q92)</f>
+        <v>2</v>
+      </c>
+      <c r="T92" s="8" t="n">
+        <f aca="false">IF(S92=0,"",MIN(G92,I92,K92,M92,O92,Q92))</f>
+        <v>312.37</v>
+      </c>
+      <c r="U92" s="9" t="str">
+        <f aca="false">IF(S92=0,"No quote",LEFT(IF(AND(ISNUMBER(G92),G92=T92),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I92),I92=T92),"Aslam, ","")&amp;IF(AND(ISNUMBER(K92),K92=T92),"Jamil, ","")&amp;IF(AND(ISNUMBER(M92),M92=T92),"Muller, ","")&amp;IF(AND(ISNUMBER(O92),O92=T92),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q92),Q92=T92),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G92),G92=T92),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I92),I92=T92),"Aslam, ","")&amp;IF(AND(ISNUMBER(K92),K92=T92),"Jamil, ","")&amp;IF(AND(ISNUMBER(M92),M92=T92),"Muller, ","")&amp;IF(AND(ISNUMBER(O92),O92=T92),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q92),Q92=T92),"Platinum, ",""))-2))</f>
+        <v>Platinum</v>
+      </c>
+      <c r="V92" s="10" t="n">
+        <f aca="false">IF(S92=0,"",T92*F92)</f>
+        <v>7809.25</v>
+      </c>
+      <c r="W92" s="6"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="5" t="n">
         <v>88</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F93" s="5" t="n">
         <v>100</v>
@@ -7313,7 +7549,7 @@
         <v>265.31</v>
       </c>
       <c r="J93" s="6" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="K93" s="7"/>
       <c r="L93" s="6"/>
@@ -7323,41 +7559,43 @@
         <v>1592.37</v>
       </c>
       <c r="P93" s="6" t="s">
-        <v>429</v>
-      </c>
-      <c r="Q93" s="5" t="n">
-        <f aca="false">COUNT(G93,I93,K93,M93,O93)</f>
+        <v>435</v>
+      </c>
+      <c r="Q93" s="7"/>
+      <c r="R93" s="6"/>
+      <c r="S93" s="5" t="n">
+        <f aca="false">COUNT(G93,I93,K93,M93,O93,Q93)</f>
         <v>2</v>
       </c>
-      <c r="R93" s="8" t="n">
-        <f aca="false">IF(Q93=0,"",MIN(G93,I93,K93,M93,O93))</f>
+      <c r="T93" s="8" t="n">
+        <f aca="false">IF(S93=0,"",MIN(G93,I93,K93,M93,O93,Q93))</f>
         <v>265.31</v>
       </c>
-      <c r="S93" s="9" t="str">
-        <f aca="false">IF(Q93=0,"No quote",LEFT(IF(AND(ISNUMBER(G93),G93=R93),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I93),I93=R93),"Aslam, ","")&amp;IF(AND(ISNUMBER(K93),K93=R93),"Jamil, ","")&amp;IF(AND(ISNUMBER(M93),M93=R93),"Muller, ","")&amp;IF(AND(ISNUMBER(O93),O93=R93),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G93),G93=R93),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I93),I93=R93),"Aslam, ","")&amp;IF(AND(ISNUMBER(K93),K93=R93),"Jamil, ","")&amp;IF(AND(ISNUMBER(M93),M93=R93),"Muller, ","")&amp;IF(AND(ISNUMBER(O93),O93=R93),"NMMC, ",""))-2))</f>
+      <c r="U93" s="9" t="str">
+        <f aca="false">IF(S93=0,"No quote",LEFT(IF(AND(ISNUMBER(G93),G93=T93),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I93),I93=T93),"Aslam, ","")&amp;IF(AND(ISNUMBER(K93),K93=T93),"Jamil, ","")&amp;IF(AND(ISNUMBER(M93),M93=T93),"Muller, ","")&amp;IF(AND(ISNUMBER(O93),O93=T93),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q93),Q93=T93),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G93),G93=T93),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I93),I93=T93),"Aslam, ","")&amp;IF(AND(ISNUMBER(K93),K93=T93),"Jamil, ","")&amp;IF(AND(ISNUMBER(M93),M93=T93),"Muller, ","")&amp;IF(AND(ISNUMBER(O93),O93=T93),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q93),Q93=T93),"Platinum, ",""))-2))</f>
         <v>Aslam</v>
       </c>
-      <c r="T93" s="10" t="n">
-        <f aca="false">IF(Q93=0,"",R93*F93)</f>
+      <c r="V93" s="10" t="n">
+        <f aca="false">IF(S93=0,"",T93*F93)</f>
         <v>26531</v>
       </c>
-      <c r="U93" s="6"/>
+      <c r="W93" s="6"/>
     </row>
     <row r="94" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="5" t="n">
         <v>89</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F94" s="5" t="n">
         <v>200</v>
@@ -7368,7 +7606,7 @@
         <v>61.16</v>
       </c>
       <c r="J94" s="6" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="K94" s="7"/>
       <c r="L94" s="6"/>
@@ -7376,39 +7614,41 @@
       <c r="N94" s="6"/>
       <c r="O94" s="7"/>
       <c r="P94" s="6"/>
-      <c r="Q94" s="5" t="n">
-        <f aca="false">COUNT(G94,I94,K94,M94,O94)</f>
+      <c r="Q94" s="7"/>
+      <c r="R94" s="6"/>
+      <c r="S94" s="5" t="n">
+        <f aca="false">COUNT(G94,I94,K94,M94,O94,Q94)</f>
         <v>1</v>
       </c>
-      <c r="R94" s="8" t="n">
-        <f aca="false">IF(Q94=0,"",MIN(G94,I94,K94,M94,O94))</f>
+      <c r="T94" s="8" t="n">
+        <f aca="false">IF(S94=0,"",MIN(G94,I94,K94,M94,O94,Q94))</f>
         <v>61.16</v>
       </c>
-      <c r="S94" s="9" t="str">
-        <f aca="false">IF(Q94=0,"No quote",LEFT(IF(AND(ISNUMBER(G94),G94=R94),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I94),I94=R94),"Aslam, ","")&amp;IF(AND(ISNUMBER(K94),K94=R94),"Jamil, ","")&amp;IF(AND(ISNUMBER(M94),M94=R94),"Muller, ","")&amp;IF(AND(ISNUMBER(O94),O94=R94),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G94),G94=R94),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I94),I94=R94),"Aslam, ","")&amp;IF(AND(ISNUMBER(K94),K94=R94),"Jamil, ","")&amp;IF(AND(ISNUMBER(M94),M94=R94),"Muller, ","")&amp;IF(AND(ISNUMBER(O94),O94=R94),"NMMC, ",""))-2))</f>
+      <c r="U94" s="9" t="str">
+        <f aca="false">IF(S94=0,"No quote",LEFT(IF(AND(ISNUMBER(G94),G94=T94),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I94),I94=T94),"Aslam, ","")&amp;IF(AND(ISNUMBER(K94),K94=T94),"Jamil, ","")&amp;IF(AND(ISNUMBER(M94),M94=T94),"Muller, ","")&amp;IF(AND(ISNUMBER(O94),O94=T94),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q94),Q94=T94),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G94),G94=T94),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I94),I94=T94),"Aslam, ","")&amp;IF(AND(ISNUMBER(K94),K94=T94),"Jamil, ","")&amp;IF(AND(ISNUMBER(M94),M94=T94),"Muller, ","")&amp;IF(AND(ISNUMBER(O94),O94=T94),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q94),Q94=T94),"Platinum, ",""))-2))</f>
         <v>Aslam</v>
       </c>
-      <c r="T94" s="10" t="n">
-        <f aca="false">IF(Q94=0,"",R94*F94)</f>
+      <c r="V94" s="10" t="n">
+        <f aca="false">IF(S94=0,"",T94*F94)</f>
         <v>12232</v>
       </c>
-      <c r="U94" s="6"/>
+      <c r="W94" s="6"/>
     </row>
     <row r="95" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="5" t="n">
         <v>90</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F95" s="5" t="n">
         <v>100</v>
@@ -7421,7 +7661,7 @@
         <v>153.43</v>
       </c>
       <c r="L95" s="6" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="M95" s="7"/>
       <c r="N95" s="6"/>
@@ -7429,41 +7669,43 @@
         <v>130.05</v>
       </c>
       <c r="P95" s="6" t="s">
-        <v>437</v>
-      </c>
-      <c r="Q95" s="5" t="n">
-        <f aca="false">COUNT(G95,I95,K95,M95,O95)</f>
+        <v>443</v>
+      </c>
+      <c r="Q95" s="7"/>
+      <c r="R95" s="6"/>
+      <c r="S95" s="5" t="n">
+        <f aca="false">COUNT(G95,I95,K95,M95,O95,Q95)</f>
         <v>2</v>
       </c>
-      <c r="R95" s="8" t="n">
-        <f aca="false">IF(Q95=0,"",MIN(G95,I95,K95,M95,O95))</f>
+      <c r="T95" s="8" t="n">
+        <f aca="false">IF(S95=0,"",MIN(G95,I95,K95,M95,O95,Q95))</f>
         <v>130.05</v>
       </c>
-      <c r="S95" s="9" t="str">
-        <f aca="false">IF(Q95=0,"No quote",LEFT(IF(AND(ISNUMBER(G95),G95=R95),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I95),I95=R95),"Aslam, ","")&amp;IF(AND(ISNUMBER(K95),K95=R95),"Jamil, ","")&amp;IF(AND(ISNUMBER(M95),M95=R95),"Muller, ","")&amp;IF(AND(ISNUMBER(O95),O95=R95),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G95),G95=R95),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I95),I95=R95),"Aslam, ","")&amp;IF(AND(ISNUMBER(K95),K95=R95),"Jamil, ","")&amp;IF(AND(ISNUMBER(M95),M95=R95),"Muller, ","")&amp;IF(AND(ISNUMBER(O95),O95=R95),"NMMC, ",""))-2))</f>
+      <c r="U95" s="9" t="str">
+        <f aca="false">IF(S95=0,"No quote",LEFT(IF(AND(ISNUMBER(G95),G95=T95),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I95),I95=T95),"Aslam, ","")&amp;IF(AND(ISNUMBER(K95),K95=T95),"Jamil, ","")&amp;IF(AND(ISNUMBER(M95),M95=T95),"Muller, ","")&amp;IF(AND(ISNUMBER(O95),O95=T95),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q95),Q95=T95),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G95),G95=T95),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I95),I95=T95),"Aslam, ","")&amp;IF(AND(ISNUMBER(K95),K95=T95),"Jamil, ","")&amp;IF(AND(ISNUMBER(M95),M95=T95),"Muller, ","")&amp;IF(AND(ISNUMBER(O95),O95=T95),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q95),Q95=T95),"Platinum, ",""))-2))</f>
         <v>NMMC</v>
       </c>
-      <c r="T95" s="10" t="n">
-        <f aca="false">IF(Q95=0,"",R95*F95)</f>
+      <c r="V95" s="10" t="n">
+        <f aca="false">IF(S95=0,"",T95*F95)</f>
         <v>13005</v>
       </c>
-      <c r="U95" s="6"/>
+      <c r="W95" s="6"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="5" t="n">
         <v>91</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F96" s="5" t="n">
         <v>100</v>
@@ -7478,43 +7720,45 @@
         <v>148.75</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="O96" s="7"/>
       <c r="P96" s="6"/>
-      <c r="Q96" s="5" t="n">
-        <f aca="false">COUNT(G96,I96,K96,M96,O96)</f>
+      <c r="Q96" s="7"/>
+      <c r="R96" s="6"/>
+      <c r="S96" s="5" t="n">
+        <f aca="false">COUNT(G96,I96,K96,M96,O96,Q96)</f>
         <v>1</v>
       </c>
-      <c r="R96" s="8" t="n">
-        <f aca="false">IF(Q96=0,"",MIN(G96,I96,K96,M96,O96))</f>
+      <c r="T96" s="8" t="n">
+        <f aca="false">IF(S96=0,"",MIN(G96,I96,K96,M96,O96,Q96))</f>
         <v>148.75</v>
       </c>
-      <c r="S96" s="9" t="str">
-        <f aca="false">IF(Q96=0,"No quote",LEFT(IF(AND(ISNUMBER(G96),G96=R96),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I96),I96=R96),"Aslam, ","")&amp;IF(AND(ISNUMBER(K96),K96=R96),"Jamil, ","")&amp;IF(AND(ISNUMBER(M96),M96=R96),"Muller, ","")&amp;IF(AND(ISNUMBER(O96),O96=R96),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G96),G96=R96),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I96),I96=R96),"Aslam, ","")&amp;IF(AND(ISNUMBER(K96),K96=R96),"Jamil, ","")&amp;IF(AND(ISNUMBER(M96),M96=R96),"Muller, ","")&amp;IF(AND(ISNUMBER(O96),O96=R96),"NMMC, ",""))-2))</f>
+      <c r="U96" s="9" t="str">
+        <f aca="false">IF(S96=0,"No quote",LEFT(IF(AND(ISNUMBER(G96),G96=T96),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I96),I96=T96),"Aslam, ","")&amp;IF(AND(ISNUMBER(K96),K96=T96),"Jamil, ","")&amp;IF(AND(ISNUMBER(M96),M96=T96),"Muller, ","")&amp;IF(AND(ISNUMBER(O96),O96=T96),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q96),Q96=T96),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G96),G96=T96),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I96),I96=T96),"Aslam, ","")&amp;IF(AND(ISNUMBER(K96),K96=T96),"Jamil, ","")&amp;IF(AND(ISNUMBER(M96),M96=T96),"Muller, ","")&amp;IF(AND(ISNUMBER(O96),O96=T96),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q96),Q96=T96),"Platinum, ",""))-2))</f>
         <v>Muller</v>
       </c>
-      <c r="T96" s="10" t="n">
-        <f aca="false">IF(Q96=0,"",R96*F96)</f>
+      <c r="V96" s="10" t="n">
+        <f aca="false">IF(S96=0,"",T96*F96)</f>
         <v>14875</v>
       </c>
-      <c r="U96" s="6"/>
+      <c r="W96" s="6"/>
     </row>
     <row r="97" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="5" t="n">
         <v>92</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F97" s="5" t="n">
         <v>200</v>
@@ -7531,41 +7775,43 @@
         <v>351.48</v>
       </c>
       <c r="P97" s="6" t="s">
-        <v>445</v>
-      </c>
-      <c r="Q97" s="5" t="n">
-        <f aca="false">COUNT(G97,I97,K97,M97,O97)</f>
+        <v>451</v>
+      </c>
+      <c r="Q97" s="7"/>
+      <c r="R97" s="6"/>
+      <c r="S97" s="5" t="n">
+        <f aca="false">COUNT(G97,I97,K97,M97,O97,Q97)</f>
         <v>1</v>
       </c>
-      <c r="R97" s="8" t="n">
-        <f aca="false">IF(Q97=0,"",MIN(G97,I97,K97,M97,O97))</f>
+      <c r="T97" s="8" t="n">
+        <f aca="false">IF(S97=0,"",MIN(G97,I97,K97,M97,O97,Q97))</f>
         <v>351.48</v>
       </c>
-      <c r="S97" s="9" t="str">
-        <f aca="false">IF(Q97=0,"No quote",LEFT(IF(AND(ISNUMBER(G97),G97=R97),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I97),I97=R97),"Aslam, ","")&amp;IF(AND(ISNUMBER(K97),K97=R97),"Jamil, ","")&amp;IF(AND(ISNUMBER(M97),M97=R97),"Muller, ","")&amp;IF(AND(ISNUMBER(O97),O97=R97),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G97),G97=R97),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I97),I97=R97),"Aslam, ","")&amp;IF(AND(ISNUMBER(K97),K97=R97),"Jamil, ","")&amp;IF(AND(ISNUMBER(M97),M97=R97),"Muller, ","")&amp;IF(AND(ISNUMBER(O97),O97=R97),"NMMC, ",""))-2))</f>
+      <c r="U97" s="9" t="str">
+        <f aca="false">IF(S97=0,"No quote",LEFT(IF(AND(ISNUMBER(G97),G97=T97),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I97),I97=T97),"Aslam, ","")&amp;IF(AND(ISNUMBER(K97),K97=T97),"Jamil, ","")&amp;IF(AND(ISNUMBER(M97),M97=T97),"Muller, ","")&amp;IF(AND(ISNUMBER(O97),O97=T97),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q97),Q97=T97),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G97),G97=T97),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I97),I97=T97),"Aslam, ","")&amp;IF(AND(ISNUMBER(K97),K97=T97),"Jamil, ","")&amp;IF(AND(ISNUMBER(M97),M97=T97),"Muller, ","")&amp;IF(AND(ISNUMBER(O97),O97=T97),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q97),Q97=T97),"Platinum, ",""))-2))</f>
         <v>NMMC</v>
       </c>
-      <c r="T97" s="10" t="n">
-        <f aca="false">IF(Q97=0,"",R97*F97)</f>
+      <c r="V97" s="10" t="n">
+        <f aca="false">IF(S97=0,"",T97*F97)</f>
         <v>70296</v>
       </c>
-      <c r="U97" s="6"/>
+      <c r="W97" s="6"/>
     </row>
     <row r="98" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="5" t="n">
         <v>93</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F98" s="5" t="n">
         <v>200</v>
@@ -7580,43 +7826,49 @@
         <v>569.5</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="O98" s="7"/>
       <c r="P98" s="6"/>
-      <c r="Q98" s="5" t="n">
-        <f aca="false">COUNT(G98,I98,K98,M98,O98)</f>
-        <v>1</v>
-      </c>
-      <c r="R98" s="8" t="n">
-        <f aca="false">IF(Q98=0,"",MIN(G98,I98,K98,M98,O98))</f>
-        <v>569.5</v>
-      </c>
-      <c r="S98" s="9" t="str">
-        <f aca="false">IF(Q98=0,"No quote",LEFT(IF(AND(ISNUMBER(G98),G98=R98),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I98),I98=R98),"Aslam, ","")&amp;IF(AND(ISNUMBER(K98),K98=R98),"Jamil, ","")&amp;IF(AND(ISNUMBER(M98),M98=R98),"Muller, ","")&amp;IF(AND(ISNUMBER(O98),O98=R98),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G98),G98=R98),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I98),I98=R98),"Aslam, ","")&amp;IF(AND(ISNUMBER(K98),K98=R98),"Jamil, ","")&amp;IF(AND(ISNUMBER(M98),M98=R98),"Muller, ","")&amp;IF(AND(ISNUMBER(O98),O98=R98),"NMMC, ",""))-2))</f>
-        <v>Muller</v>
-      </c>
-      <c r="T98" s="10" t="n">
-        <f aca="false">IF(Q98=0,"",R98*F98)</f>
-        <v>113900</v>
-      </c>
-      <c r="U98" s="6"/>
+      <c r="Q98" s="7" t="n">
+        <v>382.5</v>
+      </c>
+      <c r="R98" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="S98" s="5" t="n">
+        <f aca="false">COUNT(G98,I98,K98,M98,O98,Q98)</f>
+        <v>2</v>
+      </c>
+      <c r="T98" s="8" t="n">
+        <f aca="false">IF(S98=0,"",MIN(G98,I98,K98,M98,O98,Q98))</f>
+        <v>382.5</v>
+      </c>
+      <c r="U98" s="9" t="str">
+        <f aca="false">IF(S98=0,"No quote",LEFT(IF(AND(ISNUMBER(G98),G98=T98),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I98),I98=T98),"Aslam, ","")&amp;IF(AND(ISNUMBER(K98),K98=T98),"Jamil, ","")&amp;IF(AND(ISNUMBER(M98),M98=T98),"Muller, ","")&amp;IF(AND(ISNUMBER(O98),O98=T98),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q98),Q98=T98),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G98),G98=T98),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I98),I98=T98),"Aslam, ","")&amp;IF(AND(ISNUMBER(K98),K98=T98),"Jamil, ","")&amp;IF(AND(ISNUMBER(M98),M98=T98),"Muller, ","")&amp;IF(AND(ISNUMBER(O98),O98=T98),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q98),Q98=T98),"Platinum, ",""))-2))</f>
+        <v>Platinum</v>
+      </c>
+      <c r="V98" s="10" t="n">
+        <f aca="false">IF(S98=0,"",T98*F98)</f>
+        <v>76500</v>
+      </c>
+      <c r="W98" s="6"/>
     </row>
     <row r="99" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="5" t="n">
         <v>94</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F99" s="5" t="n">
         <v>100</v>
@@ -7631,37 +7883,39 @@
       <c r="N99" s="6"/>
       <c r="O99" s="7"/>
       <c r="P99" s="6"/>
-      <c r="Q99" s="5" t="n">
-        <f aca="false">COUNT(G99,I99,K99,M99,O99)</f>
+      <c r="Q99" s="7"/>
+      <c r="R99" s="6"/>
+      <c r="S99" s="5" t="n">
+        <f aca="false">COUNT(G99,I99,K99,M99,O99,Q99)</f>
         <v>0</v>
       </c>
-      <c r="R99" s="8" t="str">
-        <f aca="false">IF(Q99=0,"",MIN(G99,I99,K99,M99,O99))</f>
+      <c r="T99" s="8" t="str">
+        <f aca="false">IF(S99=0,"",MIN(G99,I99,K99,M99,O99,Q99))</f>
         <v/>
       </c>
-      <c r="S99" s="9" t="str">
-        <f aca="false">IF(Q99=0,"No quote",LEFT(IF(AND(ISNUMBER(G99),G99=R99),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I99),I99=R99),"Aslam, ","")&amp;IF(AND(ISNUMBER(K99),K99=R99),"Jamil, ","")&amp;IF(AND(ISNUMBER(M99),M99=R99),"Muller, ","")&amp;IF(AND(ISNUMBER(O99),O99=R99),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G99),G99=R99),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I99),I99=R99),"Aslam, ","")&amp;IF(AND(ISNUMBER(K99),K99=R99),"Jamil, ","")&amp;IF(AND(ISNUMBER(M99),M99=R99),"Muller, ","")&amp;IF(AND(ISNUMBER(O99),O99=R99),"NMMC, ",""))-2))</f>
+      <c r="U99" s="9" t="str">
+        <f aca="false">IF(S99=0,"No quote",LEFT(IF(AND(ISNUMBER(G99),G99=T99),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I99),I99=T99),"Aslam, ","")&amp;IF(AND(ISNUMBER(K99),K99=T99),"Jamil, ","")&amp;IF(AND(ISNUMBER(M99),M99=T99),"Muller, ","")&amp;IF(AND(ISNUMBER(O99),O99=T99),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q99),Q99=T99),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G99),G99=T99),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I99),I99=T99),"Aslam, ","")&amp;IF(AND(ISNUMBER(K99),K99=T99),"Jamil, ","")&amp;IF(AND(ISNUMBER(M99),M99=T99),"Muller, ","")&amp;IF(AND(ISNUMBER(O99),O99=T99),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q99),Q99=T99),"Platinum, ",""))-2))</f>
         <v>No quote</v>
       </c>
-      <c r="T99" s="10" t="str">
-        <f aca="false">IF(Q99=0,"",R99*F99)</f>
+      <c r="V99" s="10" t="str">
+        <f aca="false">IF(S99=0,"",T99*F99)</f>
         <v/>
       </c>
-      <c r="U99" s="6"/>
+      <c r="W99" s="6"/>
     </row>
     <row r="100" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="5" t="n">
         <v>95</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="D100" s="6"/>
       <c r="E100" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F100" s="5" t="n">
         <v>100</v>
@@ -7678,41 +7932,43 @@
         <v>146.88</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>454</v>
-      </c>
-      <c r="Q100" s="5" t="n">
-        <f aca="false">COUNT(G100,I100,K100,M100,O100)</f>
+        <v>461</v>
+      </c>
+      <c r="Q100" s="7"/>
+      <c r="R100" s="6"/>
+      <c r="S100" s="5" t="n">
+        <f aca="false">COUNT(G100,I100,K100,M100,O100,Q100)</f>
         <v>1</v>
       </c>
-      <c r="R100" s="8" t="n">
-        <f aca="false">IF(Q100=0,"",MIN(G100,I100,K100,M100,O100))</f>
+      <c r="T100" s="8" t="n">
+        <f aca="false">IF(S100=0,"",MIN(G100,I100,K100,M100,O100,Q100))</f>
         <v>146.88</v>
       </c>
-      <c r="S100" s="9" t="str">
-        <f aca="false">IF(Q100=0,"No quote",LEFT(IF(AND(ISNUMBER(G100),G100=R100),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I100),I100=R100),"Aslam, ","")&amp;IF(AND(ISNUMBER(K100),K100=R100),"Jamil, ","")&amp;IF(AND(ISNUMBER(M100),M100=R100),"Muller, ","")&amp;IF(AND(ISNUMBER(O100),O100=R100),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G100),G100=R100),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I100),I100=R100),"Aslam, ","")&amp;IF(AND(ISNUMBER(K100),K100=R100),"Jamil, ","")&amp;IF(AND(ISNUMBER(M100),M100=R100),"Muller, ","")&amp;IF(AND(ISNUMBER(O100),O100=R100),"NMMC, ",""))-2))</f>
+      <c r="U100" s="9" t="str">
+        <f aca="false">IF(S100=0,"No quote",LEFT(IF(AND(ISNUMBER(G100),G100=T100),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I100),I100=T100),"Aslam, ","")&amp;IF(AND(ISNUMBER(K100),K100=T100),"Jamil, ","")&amp;IF(AND(ISNUMBER(M100),M100=T100),"Muller, ","")&amp;IF(AND(ISNUMBER(O100),O100=T100),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q100),Q100=T100),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G100),G100=T100),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I100),I100=T100),"Aslam, ","")&amp;IF(AND(ISNUMBER(K100),K100=T100),"Jamil, ","")&amp;IF(AND(ISNUMBER(M100),M100=T100),"Muller, ","")&amp;IF(AND(ISNUMBER(O100),O100=T100),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q100),Q100=T100),"Platinum, ",""))-2))</f>
         <v>NMMC</v>
       </c>
-      <c r="T100" s="10" t="n">
-        <f aca="false">IF(Q100=0,"",R100*F100)</f>
+      <c r="V100" s="10" t="n">
+        <f aca="false">IF(S100=0,"",T100*F100)</f>
         <v>14688</v>
       </c>
-      <c r="U100" s="6"/>
+      <c r="W100" s="6"/>
     </row>
     <row r="101" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="5" t="n">
         <v>96</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F101" s="5" t="n">
         <v>1200</v>
@@ -7723,7 +7979,7 @@
         <v>186.15</v>
       </c>
       <c r="J101" s="6" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="K101" s="7"/>
       <c r="L101" s="6"/>
@@ -7731,47 +7987,49 @@
         <v>117.3</v>
       </c>
       <c r="N101" s="6" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="O101" s="7" t="n">
         <v>105.57</v>
       </c>
       <c r="P101" s="6" t="s">
-        <v>460</v>
-      </c>
-      <c r="Q101" s="5" t="n">
-        <f aca="false">COUNT(G101,I101,K101,M101,O101)</f>
+        <v>467</v>
+      </c>
+      <c r="Q101" s="7"/>
+      <c r="R101" s="6"/>
+      <c r="S101" s="5" t="n">
+        <f aca="false">COUNT(G101,I101,K101,M101,O101,Q101)</f>
         <v>3</v>
       </c>
-      <c r="R101" s="8" t="n">
-        <f aca="false">IF(Q101=0,"",MIN(G101,I101,K101,M101,O101))</f>
+      <c r="T101" s="8" t="n">
+        <f aca="false">IF(S101=0,"",MIN(G101,I101,K101,M101,O101,Q101))</f>
         <v>105.57</v>
       </c>
-      <c r="S101" s="9" t="str">
-        <f aca="false">IF(Q101=0,"No quote",LEFT(IF(AND(ISNUMBER(G101),G101=R101),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I101),I101=R101),"Aslam, ","")&amp;IF(AND(ISNUMBER(K101),K101=R101),"Jamil, ","")&amp;IF(AND(ISNUMBER(M101),M101=R101),"Muller, ","")&amp;IF(AND(ISNUMBER(O101),O101=R101),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G101),G101=R101),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I101),I101=R101),"Aslam, ","")&amp;IF(AND(ISNUMBER(K101),K101=R101),"Jamil, ","")&amp;IF(AND(ISNUMBER(M101),M101=R101),"Muller, ","")&amp;IF(AND(ISNUMBER(O101),O101=R101),"NMMC, ",""))-2))</f>
+      <c r="U101" s="9" t="str">
+        <f aca="false">IF(S101=0,"No quote",LEFT(IF(AND(ISNUMBER(G101),G101=T101),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I101),I101=T101),"Aslam, ","")&amp;IF(AND(ISNUMBER(K101),K101=T101),"Jamil, ","")&amp;IF(AND(ISNUMBER(M101),M101=T101),"Muller, ","")&amp;IF(AND(ISNUMBER(O101),O101=T101),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q101),Q101=T101),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G101),G101=T101),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I101),I101=T101),"Aslam, ","")&amp;IF(AND(ISNUMBER(K101),K101=T101),"Jamil, ","")&amp;IF(AND(ISNUMBER(M101),M101=T101),"Muller, ","")&amp;IF(AND(ISNUMBER(O101),O101=T101),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q101),Q101=T101),"Platinum, ",""))-2))</f>
         <v>NMMC</v>
       </c>
-      <c r="T101" s="10" t="n">
-        <f aca="false">IF(Q101=0,"",R101*F101)</f>
+      <c r="V101" s="10" t="n">
+        <f aca="false">IF(S101=0,"",T101*F101)</f>
         <v>126684</v>
       </c>
-      <c r="U101" s="6"/>
+      <c r="W101" s="6"/>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="5" t="n">
         <v>97</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F102" s="5" t="n">
         <v>100</v>
@@ -7782,7 +8040,7 @@
         <v>96.04</v>
       </c>
       <c r="J102" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K102" s="7"/>
       <c r="L102" s="6"/>
@@ -7790,39 +8048,41 @@
       <c r="N102" s="6"/>
       <c r="O102" s="7"/>
       <c r="P102" s="6"/>
-      <c r="Q102" s="5" t="n">
-        <f aca="false">COUNT(G102,I102,K102,M102,O102)</f>
+      <c r="Q102" s="7"/>
+      <c r="R102" s="6"/>
+      <c r="S102" s="5" t="n">
+        <f aca="false">COUNT(G102,I102,K102,M102,O102,Q102)</f>
         <v>1</v>
       </c>
-      <c r="R102" s="8" t="n">
-        <f aca="false">IF(Q102=0,"",MIN(G102,I102,K102,M102,O102))</f>
+      <c r="T102" s="8" t="n">
+        <f aca="false">IF(S102=0,"",MIN(G102,I102,K102,M102,O102,Q102))</f>
         <v>96.04</v>
       </c>
-      <c r="S102" s="9" t="str">
-        <f aca="false">IF(Q102=0,"No quote",LEFT(IF(AND(ISNUMBER(G102),G102=R102),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I102),I102=R102),"Aslam, ","")&amp;IF(AND(ISNUMBER(K102),K102=R102),"Jamil, ","")&amp;IF(AND(ISNUMBER(M102),M102=R102),"Muller, ","")&amp;IF(AND(ISNUMBER(O102),O102=R102),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G102),G102=R102),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I102),I102=R102),"Aslam, ","")&amp;IF(AND(ISNUMBER(K102),K102=R102),"Jamil, ","")&amp;IF(AND(ISNUMBER(M102),M102=R102),"Muller, ","")&amp;IF(AND(ISNUMBER(O102),O102=R102),"NMMC, ",""))-2))</f>
+      <c r="U102" s="9" t="str">
+        <f aca="false">IF(S102=0,"No quote",LEFT(IF(AND(ISNUMBER(G102),G102=T102),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I102),I102=T102),"Aslam, ","")&amp;IF(AND(ISNUMBER(K102),K102=T102),"Jamil, ","")&amp;IF(AND(ISNUMBER(M102),M102=T102),"Muller, ","")&amp;IF(AND(ISNUMBER(O102),O102=T102),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q102),Q102=T102),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G102),G102=T102),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I102),I102=T102),"Aslam, ","")&amp;IF(AND(ISNUMBER(K102),K102=T102),"Jamil, ","")&amp;IF(AND(ISNUMBER(M102),M102=T102),"Muller, ","")&amp;IF(AND(ISNUMBER(O102),O102=T102),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q102),Q102=T102),"Platinum, ",""))-2))</f>
         <v>Aslam</v>
       </c>
-      <c r="T102" s="10" t="n">
-        <f aca="false">IF(Q102=0,"",R102*F102)</f>
+      <c r="V102" s="10" t="n">
+        <f aca="false">IF(S102=0,"",T102*F102)</f>
         <v>9604</v>
       </c>
-      <c r="U102" s="6"/>
+      <c r="W102" s="6"/>
     </row>
     <row r="103" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="5" t="n">
         <v>98</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="C103" s="6" t="s">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F103" s="5" t="n">
         <v>1000</v>
@@ -7831,19 +8091,19 @@
         <v>221</v>
       </c>
       <c r="H103" s="6" t="s">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="I103" s="7" t="n">
         <v>238</v>
       </c>
       <c r="J103" s="6" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="K103" s="7" t="n">
         <v>148.58</v>
       </c>
       <c r="L103" s="6" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="M103" s="7"/>
       <c r="N103" s="6"/>
@@ -7851,41 +8111,43 @@
         <v>238</v>
       </c>
       <c r="P103" s="6" t="s">
-        <v>469</v>
-      </c>
-      <c r="Q103" s="5" t="n">
-        <f aca="false">COUNT(G103,I103,K103,M103,O103)</f>
+        <v>476</v>
+      </c>
+      <c r="Q103" s="7"/>
+      <c r="R103" s="6"/>
+      <c r="S103" s="5" t="n">
+        <f aca="false">COUNT(G103,I103,K103,M103,O103,Q103)</f>
         <v>4</v>
       </c>
-      <c r="R103" s="8" t="n">
-        <f aca="false">IF(Q103=0,"",MIN(G103,I103,K103,M103,O103))</f>
+      <c r="T103" s="8" t="n">
+        <f aca="false">IF(S103=0,"",MIN(G103,I103,K103,M103,O103,Q103))</f>
         <v>148.58</v>
       </c>
-      <c r="S103" s="9" t="str">
-        <f aca="false">IF(Q103=0,"No quote",LEFT(IF(AND(ISNUMBER(G103),G103=R103),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I103),I103=R103),"Aslam, ","")&amp;IF(AND(ISNUMBER(K103),K103=R103),"Jamil, ","")&amp;IF(AND(ISNUMBER(M103),M103=R103),"Muller, ","")&amp;IF(AND(ISNUMBER(O103),O103=R103),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G103),G103=R103),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I103),I103=R103),"Aslam, ","")&amp;IF(AND(ISNUMBER(K103),K103=R103),"Jamil, ","")&amp;IF(AND(ISNUMBER(M103),M103=R103),"Muller, ","")&amp;IF(AND(ISNUMBER(O103),O103=R103),"NMMC, ",""))-2))</f>
+      <c r="U103" s="9" t="str">
+        <f aca="false">IF(S103=0,"No quote",LEFT(IF(AND(ISNUMBER(G103),G103=T103),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I103),I103=T103),"Aslam, ","")&amp;IF(AND(ISNUMBER(K103),K103=T103),"Jamil, ","")&amp;IF(AND(ISNUMBER(M103),M103=T103),"Muller, ","")&amp;IF(AND(ISNUMBER(O103),O103=T103),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q103),Q103=T103),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G103),G103=T103),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I103),I103=T103),"Aslam, ","")&amp;IF(AND(ISNUMBER(K103),K103=T103),"Jamil, ","")&amp;IF(AND(ISNUMBER(M103),M103=T103),"Muller, ","")&amp;IF(AND(ISNUMBER(O103),O103=T103),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q103),Q103=T103),"Platinum, ",""))-2))</f>
         <v>Jamil</v>
       </c>
-      <c r="T103" s="10" t="n">
-        <f aca="false">IF(Q103=0,"",R103*F103)</f>
+      <c r="V103" s="10" t="n">
+        <f aca="false">IF(S103=0,"",T103*F103)</f>
         <v>148580</v>
       </c>
-      <c r="U103" s="6"/>
+      <c r="W103" s="6"/>
     </row>
     <row r="104" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="5" t="n">
         <v>99</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F104" s="5" t="n">
         <v>200</v>
@@ -7898,45 +8160,47 @@
         <v>249.96</v>
       </c>
       <c r="L104" s="6" t="s">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="M104" s="7"/>
       <c r="N104" s="6"/>
       <c r="O104" s="7"/>
       <c r="P104" s="6"/>
-      <c r="Q104" s="5" t="n">
-        <f aca="false">COUNT(G104,I104,K104,M104,O104)</f>
+      <c r="Q104" s="7"/>
+      <c r="R104" s="6"/>
+      <c r="S104" s="5" t="n">
+        <f aca="false">COUNT(G104,I104,K104,M104,O104,Q104)</f>
         <v>1</v>
       </c>
-      <c r="R104" s="8" t="n">
-        <f aca="false">IF(Q104=0,"",MIN(G104,I104,K104,M104,O104))</f>
+      <c r="T104" s="8" t="n">
+        <f aca="false">IF(S104=0,"",MIN(G104,I104,K104,M104,O104,Q104))</f>
         <v>249.96</v>
       </c>
-      <c r="S104" s="9" t="str">
-        <f aca="false">IF(Q104=0,"No quote",LEFT(IF(AND(ISNUMBER(G104),G104=R104),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I104),I104=R104),"Aslam, ","")&amp;IF(AND(ISNUMBER(K104),K104=R104),"Jamil, ","")&amp;IF(AND(ISNUMBER(M104),M104=R104),"Muller, ","")&amp;IF(AND(ISNUMBER(O104),O104=R104),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G104),G104=R104),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I104),I104=R104),"Aslam, ","")&amp;IF(AND(ISNUMBER(K104),K104=R104),"Jamil, ","")&amp;IF(AND(ISNUMBER(M104),M104=R104),"Muller, ","")&amp;IF(AND(ISNUMBER(O104),O104=R104),"NMMC, ",""))-2))</f>
+      <c r="U104" s="9" t="str">
+        <f aca="false">IF(S104=0,"No quote",LEFT(IF(AND(ISNUMBER(G104),G104=T104),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I104),I104=T104),"Aslam, ","")&amp;IF(AND(ISNUMBER(K104),K104=T104),"Jamil, ","")&amp;IF(AND(ISNUMBER(M104),M104=T104),"Muller, ","")&amp;IF(AND(ISNUMBER(O104),O104=T104),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q104),Q104=T104),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G104),G104=T104),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I104),I104=T104),"Aslam, ","")&amp;IF(AND(ISNUMBER(K104),K104=T104),"Jamil, ","")&amp;IF(AND(ISNUMBER(M104),M104=T104),"Muller, ","")&amp;IF(AND(ISNUMBER(O104),O104=T104),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q104),Q104=T104),"Platinum, ",""))-2))</f>
         <v>Jamil</v>
       </c>
-      <c r="T104" s="10" t="n">
-        <f aca="false">IF(Q104=0,"",R104*F104)</f>
+      <c r="V104" s="10" t="n">
+        <f aca="false">IF(S104=0,"",T104*F104)</f>
         <v>49992</v>
       </c>
-      <c r="U104" s="6"/>
+      <c r="W104" s="6"/>
     </row>
     <row r="105" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="5" t="n">
         <v>100</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F105" s="5" t="n">
         <v>100</v>
@@ -7945,7 +8209,7 @@
         <v>85</v>
       </c>
       <c r="H105" s="6" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="I105" s="7"/>
       <c r="J105" s="6"/>
@@ -7955,43 +8219,49 @@
         <v>169.15</v>
       </c>
       <c r="N105" s="6" t="s">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="O105" s="7"/>
       <c r="P105" s="6"/>
-      <c r="Q105" s="5" t="n">
-        <f aca="false">COUNT(G105,I105,K105,M105,O105)</f>
-        <v>2</v>
-      </c>
-      <c r="R105" s="8" t="n">
-        <f aca="false">IF(Q105=0,"",MIN(G105,I105,K105,M105,O105))</f>
+      <c r="Q105" s="7" t="n">
+        <v>206.28</v>
+      </c>
+      <c r="R105" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="S105" s="5" t="n">
+        <f aca="false">COUNT(G105,I105,K105,M105,O105,Q105)</f>
+        <v>3</v>
+      </c>
+      <c r="T105" s="8" t="n">
+        <f aca="false">IF(S105=0,"",MIN(G105,I105,K105,M105,O105,Q105))</f>
         <v>85</v>
       </c>
-      <c r="S105" s="9" t="str">
-        <f aca="false">IF(Q105=0,"No quote",LEFT(IF(AND(ISNUMBER(G105),G105=R105),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I105),I105=R105),"Aslam, ","")&amp;IF(AND(ISNUMBER(K105),K105=R105),"Jamil, ","")&amp;IF(AND(ISNUMBER(M105),M105=R105),"Muller, ","")&amp;IF(AND(ISNUMBER(O105),O105=R105),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G105),G105=R105),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I105),I105=R105),"Aslam, ","")&amp;IF(AND(ISNUMBER(K105),K105=R105),"Jamil, ","")&amp;IF(AND(ISNUMBER(M105),M105=R105),"Muller, ","")&amp;IF(AND(ISNUMBER(O105),O105=R105),"NMMC, ",""))-2))</f>
+      <c r="U105" s="9" t="str">
+        <f aca="false">IF(S105=0,"No quote",LEFT(IF(AND(ISNUMBER(G105),G105=T105),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I105),I105=T105),"Aslam, ","")&amp;IF(AND(ISNUMBER(K105),K105=T105),"Jamil, ","")&amp;IF(AND(ISNUMBER(M105),M105=T105),"Muller, ","")&amp;IF(AND(ISNUMBER(O105),O105=T105),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q105),Q105=T105),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G105),G105=T105),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I105),I105=T105),"Aslam, ","")&amp;IF(AND(ISNUMBER(K105),K105=T105),"Jamil, ","")&amp;IF(AND(ISNUMBER(M105),M105=T105),"Muller, ","")&amp;IF(AND(ISNUMBER(O105),O105=T105),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q105),Q105=T105),"Platinum, ",""))-2))</f>
         <v>Ahsan</v>
       </c>
-      <c r="T105" s="10" t="n">
-        <f aca="false">IF(Q105=0,"",R105*F105)</f>
+      <c r="V105" s="10" t="n">
+        <f aca="false">IF(S105=0,"",T105*F105)</f>
         <v>8500</v>
       </c>
-      <c r="U105" s="6"/>
+      <c r="W105" s="6"/>
     </row>
     <row r="106" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="5" t="n">
         <v>101</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F106" s="5" t="n">
         <v>500</v>
@@ -8004,49 +8274,51 @@
         <v>242.25</v>
       </c>
       <c r="L106" s="6" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="M106" s="7" t="n">
         <v>153</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="O106" s="7"/>
       <c r="P106" s="6"/>
-      <c r="Q106" s="5" t="n">
-        <f aca="false">COUNT(G106,I106,K106,M106,O106)</f>
+      <c r="Q106" s="7"/>
+      <c r="R106" s="6"/>
+      <c r="S106" s="5" t="n">
+        <f aca="false">COUNT(G106,I106,K106,M106,O106,Q106)</f>
         <v>2</v>
       </c>
-      <c r="R106" s="8" t="n">
-        <f aca="false">IF(Q106=0,"",MIN(G106,I106,K106,M106,O106))</f>
+      <c r="T106" s="8" t="n">
+        <f aca="false">IF(S106=0,"",MIN(G106,I106,K106,M106,O106,Q106))</f>
         <v>153</v>
       </c>
-      <c r="S106" s="9" t="str">
-        <f aca="false">IF(Q106=0,"No quote",LEFT(IF(AND(ISNUMBER(G106),G106=R106),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I106),I106=R106),"Aslam, ","")&amp;IF(AND(ISNUMBER(K106),K106=R106),"Jamil, ","")&amp;IF(AND(ISNUMBER(M106),M106=R106),"Muller, ","")&amp;IF(AND(ISNUMBER(O106),O106=R106),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G106),G106=R106),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I106),I106=R106),"Aslam, ","")&amp;IF(AND(ISNUMBER(K106),K106=R106),"Jamil, ","")&amp;IF(AND(ISNUMBER(M106),M106=R106),"Muller, ","")&amp;IF(AND(ISNUMBER(O106),O106=R106),"NMMC, ",""))-2))</f>
+      <c r="U106" s="9" t="str">
+        <f aca="false">IF(S106=0,"No quote",LEFT(IF(AND(ISNUMBER(G106),G106=T106),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I106),I106=T106),"Aslam, ","")&amp;IF(AND(ISNUMBER(K106),K106=T106),"Jamil, ","")&amp;IF(AND(ISNUMBER(M106),M106=T106),"Muller, ","")&amp;IF(AND(ISNUMBER(O106),O106=T106),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q106),Q106=T106),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G106),G106=T106),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I106),I106=T106),"Aslam, ","")&amp;IF(AND(ISNUMBER(K106),K106=T106),"Jamil, ","")&amp;IF(AND(ISNUMBER(M106),M106=T106),"Muller, ","")&amp;IF(AND(ISNUMBER(O106),O106=T106),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q106),Q106=T106),"Platinum, ",""))-2))</f>
         <v>Muller</v>
       </c>
-      <c r="T106" s="10" t="n">
-        <f aca="false">IF(Q106=0,"",R106*F106)</f>
+      <c r="V106" s="10" t="n">
+        <f aca="false">IF(S106=0,"",T106*F106)</f>
         <v>76500</v>
       </c>
-      <c r="U106" s="6"/>
+      <c r="W106" s="6"/>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="5" t="n">
         <v>102</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F107" s="5" t="n">
         <v>300</v>
@@ -8059,45 +8331,47 @@
         <v>104.26</v>
       </c>
       <c r="L107" s="6" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="M107" s="7"/>
       <c r="N107" s="6"/>
       <c r="O107" s="7"/>
       <c r="P107" s="6"/>
-      <c r="Q107" s="5" t="n">
-        <f aca="false">COUNT(G107,I107,K107,M107,O107)</f>
+      <c r="Q107" s="7"/>
+      <c r="R107" s="6"/>
+      <c r="S107" s="5" t="n">
+        <f aca="false">COUNT(G107,I107,K107,M107,O107,Q107)</f>
         <v>1</v>
       </c>
-      <c r="R107" s="8" t="n">
-        <f aca="false">IF(Q107=0,"",MIN(G107,I107,K107,M107,O107))</f>
+      <c r="T107" s="8" t="n">
+        <f aca="false">IF(S107=0,"",MIN(G107,I107,K107,M107,O107,Q107))</f>
         <v>104.26</v>
       </c>
-      <c r="S107" s="9" t="str">
-        <f aca="false">IF(Q107=0,"No quote",LEFT(IF(AND(ISNUMBER(G107),G107=R107),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I107),I107=R107),"Aslam, ","")&amp;IF(AND(ISNUMBER(K107),K107=R107),"Jamil, ","")&amp;IF(AND(ISNUMBER(M107),M107=R107),"Muller, ","")&amp;IF(AND(ISNUMBER(O107),O107=R107),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G107),G107=R107),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I107),I107=R107),"Aslam, ","")&amp;IF(AND(ISNUMBER(K107),K107=R107),"Jamil, ","")&amp;IF(AND(ISNUMBER(M107),M107=R107),"Muller, ","")&amp;IF(AND(ISNUMBER(O107),O107=R107),"NMMC, ",""))-2))</f>
+      <c r="U107" s="9" t="str">
+        <f aca="false">IF(S107=0,"No quote",LEFT(IF(AND(ISNUMBER(G107),G107=T107),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I107),I107=T107),"Aslam, ","")&amp;IF(AND(ISNUMBER(K107),K107=T107),"Jamil, ","")&amp;IF(AND(ISNUMBER(M107),M107=T107),"Muller, ","")&amp;IF(AND(ISNUMBER(O107),O107=T107),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q107),Q107=T107),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G107),G107=T107),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I107),I107=T107),"Aslam, ","")&amp;IF(AND(ISNUMBER(K107),K107=T107),"Jamil, ","")&amp;IF(AND(ISNUMBER(M107),M107=T107),"Muller, ","")&amp;IF(AND(ISNUMBER(O107),O107=T107),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q107),Q107=T107),"Platinum, ",""))-2))</f>
         <v>Jamil</v>
       </c>
-      <c r="T107" s="10" t="n">
-        <f aca="false">IF(Q107=0,"",R107*F107)</f>
+      <c r="V107" s="10" t="n">
+        <f aca="false">IF(S107=0,"",T107*F107)</f>
         <v>31278</v>
       </c>
-      <c r="U107" s="6"/>
+      <c r="W107" s="6"/>
     </row>
     <row r="108" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="5" t="n">
         <v>103</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F108" s="5" t="n">
         <v>200</v>
@@ -8106,7 +8380,7 @@
         <v>147.05</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="I108" s="7"/>
       <c r="J108" s="6"/>
@@ -8118,41 +8392,43 @@
         <v>108.8</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>492</v>
-      </c>
-      <c r="Q108" s="5" t="n">
-        <f aca="false">COUNT(G108,I108,K108,M108,O108)</f>
+        <v>500</v>
+      </c>
+      <c r="Q108" s="7"/>
+      <c r="R108" s="6"/>
+      <c r="S108" s="5" t="n">
+        <f aca="false">COUNT(G108,I108,K108,M108,O108,Q108)</f>
         <v>2</v>
       </c>
-      <c r="R108" s="8" t="n">
-        <f aca="false">IF(Q108=0,"",MIN(G108,I108,K108,M108,O108))</f>
+      <c r="T108" s="8" t="n">
+        <f aca="false">IF(S108=0,"",MIN(G108,I108,K108,M108,O108,Q108))</f>
         <v>108.8</v>
       </c>
-      <c r="S108" s="9" t="str">
-        <f aca="false">IF(Q108=0,"No quote",LEFT(IF(AND(ISNUMBER(G108),G108=R108),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I108),I108=R108),"Aslam, ","")&amp;IF(AND(ISNUMBER(K108),K108=R108),"Jamil, ","")&amp;IF(AND(ISNUMBER(M108),M108=R108),"Muller, ","")&amp;IF(AND(ISNUMBER(O108),O108=R108),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G108),G108=R108),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I108),I108=R108),"Aslam, ","")&amp;IF(AND(ISNUMBER(K108),K108=R108),"Jamil, ","")&amp;IF(AND(ISNUMBER(M108),M108=R108),"Muller, ","")&amp;IF(AND(ISNUMBER(O108),O108=R108),"NMMC, ",""))-2))</f>
+      <c r="U108" s="9" t="str">
+        <f aca="false">IF(S108=0,"No quote",LEFT(IF(AND(ISNUMBER(G108),G108=T108),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I108),I108=T108),"Aslam, ","")&amp;IF(AND(ISNUMBER(K108),K108=T108),"Jamil, ","")&amp;IF(AND(ISNUMBER(M108),M108=T108),"Muller, ","")&amp;IF(AND(ISNUMBER(O108),O108=T108),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q108),Q108=T108),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G108),G108=T108),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I108),I108=T108),"Aslam, ","")&amp;IF(AND(ISNUMBER(K108),K108=T108),"Jamil, ","")&amp;IF(AND(ISNUMBER(M108),M108=T108),"Muller, ","")&amp;IF(AND(ISNUMBER(O108),O108=T108),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q108),Q108=T108),"Platinum, ",""))-2))</f>
         <v>NMMC</v>
       </c>
-      <c r="T108" s="10" t="n">
-        <f aca="false">IF(Q108=0,"",R108*F108)</f>
+      <c r="V108" s="10" t="n">
+        <f aca="false">IF(S108=0,"",T108*F108)</f>
         <v>21760</v>
       </c>
-      <c r="U108" s="6"/>
+      <c r="W108" s="6"/>
     </row>
     <row r="109" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="5" t="n">
         <v>104</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F109" s="5" t="n">
         <v>100</v>
@@ -8161,61 +8437,63 @@
         <v>292.67</v>
       </c>
       <c r="H109" s="6" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="I109" s="7" t="n">
         <v>292.67</v>
       </c>
       <c r="J109" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K109" s="7" t="n">
         <v>531.57</v>
       </c>
       <c r="L109" s="6" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="M109" s="7" t="n">
         <v>219.5</v>
       </c>
       <c r="N109" s="6" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="O109" s="7"/>
       <c r="P109" s="6"/>
-      <c r="Q109" s="5" t="n">
-        <f aca="false">COUNT(G109,I109,K109,M109,O109)</f>
+      <c r="Q109" s="7"/>
+      <c r="R109" s="6"/>
+      <c r="S109" s="5" t="n">
+        <f aca="false">COUNT(G109,I109,K109,M109,O109,Q109)</f>
         <v>4</v>
       </c>
-      <c r="R109" s="8" t="n">
-        <f aca="false">IF(Q109=0,"",MIN(G109,I109,K109,M109,O109))</f>
+      <c r="T109" s="8" t="n">
+        <f aca="false">IF(S109=0,"",MIN(G109,I109,K109,M109,O109,Q109))</f>
         <v>219.5</v>
       </c>
-      <c r="S109" s="9" t="str">
-        <f aca="false">IF(Q109=0,"No quote",LEFT(IF(AND(ISNUMBER(G109),G109=R109),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I109),I109=R109),"Aslam, ","")&amp;IF(AND(ISNUMBER(K109),K109=R109),"Jamil, ","")&amp;IF(AND(ISNUMBER(M109),M109=R109),"Muller, ","")&amp;IF(AND(ISNUMBER(O109),O109=R109),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G109),G109=R109),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I109),I109=R109),"Aslam, ","")&amp;IF(AND(ISNUMBER(K109),K109=R109),"Jamil, ","")&amp;IF(AND(ISNUMBER(M109),M109=R109),"Muller, ","")&amp;IF(AND(ISNUMBER(O109),O109=R109),"NMMC, ",""))-2))</f>
+      <c r="U109" s="9" t="str">
+        <f aca="false">IF(S109=0,"No quote",LEFT(IF(AND(ISNUMBER(G109),G109=T109),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I109),I109=T109),"Aslam, ","")&amp;IF(AND(ISNUMBER(K109),K109=T109),"Jamil, ","")&amp;IF(AND(ISNUMBER(M109),M109=T109),"Muller, ","")&amp;IF(AND(ISNUMBER(O109),O109=T109),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q109),Q109=T109),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G109),G109=T109),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I109),I109=T109),"Aslam, ","")&amp;IF(AND(ISNUMBER(K109),K109=T109),"Jamil, ","")&amp;IF(AND(ISNUMBER(M109),M109=T109),"Muller, ","")&amp;IF(AND(ISNUMBER(O109),O109=T109),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q109),Q109=T109),"Platinum, ",""))-2))</f>
         <v>Muller</v>
       </c>
-      <c r="T109" s="10" t="n">
-        <f aca="false">IF(Q109=0,"",R109*F109)</f>
+      <c r="V109" s="10" t="n">
+        <f aca="false">IF(S109=0,"",T109*F109)</f>
         <v>21950</v>
       </c>
-      <c r="U109" s="6"/>
+      <c r="W109" s="6"/>
     </row>
     <row r="110" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="5" t="n">
         <v>105</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F110" s="5" t="n">
         <v>100</v>
@@ -8224,61 +8502,63 @@
         <v>180.11</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="I110" s="7" t="n">
         <v>180.11</v>
       </c>
       <c r="J110" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K110" s="7" t="n">
         <v>322.69</v>
       </c>
       <c r="L110" s="6" t="s">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="M110" s="7" t="n">
         <v>139.77</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="O110" s="7"/>
       <c r="P110" s="6"/>
-      <c r="Q110" s="5" t="n">
-        <f aca="false">COUNT(G110,I110,K110,M110,O110)</f>
+      <c r="Q110" s="7"/>
+      <c r="R110" s="6"/>
+      <c r="S110" s="5" t="n">
+        <f aca="false">COUNT(G110,I110,K110,M110,O110,Q110)</f>
         <v>4</v>
       </c>
-      <c r="R110" s="8" t="n">
-        <f aca="false">IF(Q110=0,"",MIN(G110,I110,K110,M110,O110))</f>
+      <c r="T110" s="8" t="n">
+        <f aca="false">IF(S110=0,"",MIN(G110,I110,K110,M110,O110,Q110))</f>
         <v>139.77</v>
       </c>
-      <c r="S110" s="9" t="str">
-        <f aca="false">IF(Q110=0,"No quote",LEFT(IF(AND(ISNUMBER(G110),G110=R110),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I110),I110=R110),"Aslam, ","")&amp;IF(AND(ISNUMBER(K110),K110=R110),"Jamil, ","")&amp;IF(AND(ISNUMBER(M110),M110=R110),"Muller, ","")&amp;IF(AND(ISNUMBER(O110),O110=R110),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G110),G110=R110),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I110),I110=R110),"Aslam, ","")&amp;IF(AND(ISNUMBER(K110),K110=R110),"Jamil, ","")&amp;IF(AND(ISNUMBER(M110),M110=R110),"Muller, ","")&amp;IF(AND(ISNUMBER(O110),O110=R110),"NMMC, ",""))-2))</f>
+      <c r="U110" s="9" t="str">
+        <f aca="false">IF(S110=0,"No quote",LEFT(IF(AND(ISNUMBER(G110),G110=T110),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I110),I110=T110),"Aslam, ","")&amp;IF(AND(ISNUMBER(K110),K110=T110),"Jamil, ","")&amp;IF(AND(ISNUMBER(M110),M110=T110),"Muller, ","")&amp;IF(AND(ISNUMBER(O110),O110=T110),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q110),Q110=T110),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G110),G110=T110),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I110),I110=T110),"Aslam, ","")&amp;IF(AND(ISNUMBER(K110),K110=T110),"Jamil, ","")&amp;IF(AND(ISNUMBER(M110),M110=T110),"Muller, ","")&amp;IF(AND(ISNUMBER(O110),O110=T110),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q110),Q110=T110),"Platinum, ",""))-2))</f>
         <v>Muller</v>
       </c>
-      <c r="T110" s="10" t="n">
-        <f aca="false">IF(Q110=0,"",R110*F110)</f>
+      <c r="V110" s="10" t="n">
+        <f aca="false">IF(S110=0,"",T110*F110)</f>
         <v>13977</v>
       </c>
-      <c r="U110" s="6"/>
+      <c r="W110" s="6"/>
     </row>
     <row r="111" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="5" t="n">
         <v>106</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F111" s="5" t="n">
         <v>500</v>
@@ -8291,45 +8571,47 @@
         <v>145.35</v>
       </c>
       <c r="L111" s="6" t="s">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="M111" s="7"/>
       <c r="N111" s="6"/>
       <c r="O111" s="7"/>
       <c r="P111" s="6"/>
-      <c r="Q111" s="5" t="n">
-        <f aca="false">COUNT(G111,I111,K111,M111,O111)</f>
+      <c r="Q111" s="7"/>
+      <c r="R111" s="6"/>
+      <c r="S111" s="5" t="n">
+        <f aca="false">COUNT(G111,I111,K111,M111,O111,Q111)</f>
         <v>1</v>
       </c>
-      <c r="R111" s="8" t="n">
-        <f aca="false">IF(Q111=0,"",MIN(G111,I111,K111,M111,O111))</f>
+      <c r="T111" s="8" t="n">
+        <f aca="false">IF(S111=0,"",MIN(G111,I111,K111,M111,O111,Q111))</f>
         <v>145.35</v>
       </c>
-      <c r="S111" s="9" t="str">
-        <f aca="false">IF(Q111=0,"No quote",LEFT(IF(AND(ISNUMBER(G111),G111=R111),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I111),I111=R111),"Aslam, ","")&amp;IF(AND(ISNUMBER(K111),K111=R111),"Jamil, ","")&amp;IF(AND(ISNUMBER(M111),M111=R111),"Muller, ","")&amp;IF(AND(ISNUMBER(O111),O111=R111),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G111),G111=R111),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I111),I111=R111),"Aslam, ","")&amp;IF(AND(ISNUMBER(K111),K111=R111),"Jamil, ","")&amp;IF(AND(ISNUMBER(M111),M111=R111),"Muller, ","")&amp;IF(AND(ISNUMBER(O111),O111=R111),"NMMC, ",""))-2))</f>
+      <c r="U111" s="9" t="str">
+        <f aca="false">IF(S111=0,"No quote",LEFT(IF(AND(ISNUMBER(G111),G111=T111),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I111),I111=T111),"Aslam, ","")&amp;IF(AND(ISNUMBER(K111),K111=T111),"Jamil, ","")&amp;IF(AND(ISNUMBER(M111),M111=T111),"Muller, ","")&amp;IF(AND(ISNUMBER(O111),O111=T111),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q111),Q111=T111),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G111),G111=T111),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I111),I111=T111),"Aslam, ","")&amp;IF(AND(ISNUMBER(K111),K111=T111),"Jamil, ","")&amp;IF(AND(ISNUMBER(M111),M111=T111),"Muller, ","")&amp;IF(AND(ISNUMBER(O111),O111=T111),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q111),Q111=T111),"Platinum, ",""))-2))</f>
         <v>Jamil</v>
       </c>
-      <c r="T111" s="10" t="n">
-        <f aca="false">IF(Q111=0,"",R111*F111)</f>
+      <c r="V111" s="10" t="n">
+        <f aca="false">IF(S111=0,"",T111*F111)</f>
         <v>72675</v>
       </c>
-      <c r="U111" s="6"/>
+      <c r="W111" s="6"/>
     </row>
     <row r="112" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="5" t="n">
         <v>107</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F112" s="5" t="n">
         <v>10</v>
@@ -8338,13 +8620,13 @@
         <v>352.75</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="I112" s="7" t="n">
         <v>510</v>
       </c>
       <c r="J112" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="6"/>
@@ -8352,47 +8634,49 @@
         <v>403.75</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="O112" s="7" t="n">
         <v>459.01</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>511</v>
-      </c>
-      <c r="Q112" s="5" t="n">
-        <f aca="false">COUNT(G112,I112,K112,M112,O112)</f>
+        <v>519</v>
+      </c>
+      <c r="Q112" s="7"/>
+      <c r="R112" s="6"/>
+      <c r="S112" s="5" t="n">
+        <f aca="false">COUNT(G112,I112,K112,M112,O112,Q112)</f>
         <v>4</v>
       </c>
-      <c r="R112" s="8" t="n">
-        <f aca="false">IF(Q112=0,"",MIN(G112,I112,K112,M112,O112))</f>
+      <c r="T112" s="8" t="n">
+        <f aca="false">IF(S112=0,"",MIN(G112,I112,K112,M112,O112,Q112))</f>
         <v>352.75</v>
       </c>
-      <c r="S112" s="9" t="str">
-        <f aca="false">IF(Q112=0,"No quote",LEFT(IF(AND(ISNUMBER(G112),G112=R112),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I112),I112=R112),"Aslam, ","")&amp;IF(AND(ISNUMBER(K112),K112=R112),"Jamil, ","")&amp;IF(AND(ISNUMBER(M112),M112=R112),"Muller, ","")&amp;IF(AND(ISNUMBER(O112),O112=R112),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G112),G112=R112),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I112),I112=R112),"Aslam, ","")&amp;IF(AND(ISNUMBER(K112),K112=R112),"Jamil, ","")&amp;IF(AND(ISNUMBER(M112),M112=R112),"Muller, ","")&amp;IF(AND(ISNUMBER(O112),O112=R112),"NMMC, ",""))-2))</f>
+      <c r="U112" s="9" t="str">
+        <f aca="false">IF(S112=0,"No quote",LEFT(IF(AND(ISNUMBER(G112),G112=T112),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I112),I112=T112),"Aslam, ","")&amp;IF(AND(ISNUMBER(K112),K112=T112),"Jamil, ","")&amp;IF(AND(ISNUMBER(M112),M112=T112),"Muller, ","")&amp;IF(AND(ISNUMBER(O112),O112=T112),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q112),Q112=T112),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G112),G112=T112),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I112),I112=T112),"Aslam, ","")&amp;IF(AND(ISNUMBER(K112),K112=T112),"Jamil, ","")&amp;IF(AND(ISNUMBER(M112),M112=T112),"Muller, ","")&amp;IF(AND(ISNUMBER(O112),O112=T112),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q112),Q112=T112),"Platinum, ",""))-2))</f>
         <v>Ahsan</v>
       </c>
-      <c r="T112" s="10" t="n">
-        <f aca="false">IF(Q112=0,"",R112*F112)</f>
+      <c r="V112" s="10" t="n">
+        <f aca="false">IF(S112=0,"",T112*F112)</f>
         <v>3527.5</v>
       </c>
-      <c r="U112" s="6"/>
+      <c r="W112" s="6"/>
     </row>
     <row r="113" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="5" t="n">
         <v>108</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F113" s="5" t="n">
         <v>40</v>
@@ -8401,7 +8685,7 @@
         <v>552.5</v>
       </c>
       <c r="H113" s="6" t="s">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="I113" s="7"/>
       <c r="J113" s="6"/>
@@ -8413,41 +8697,43 @@
         <v>880.94</v>
       </c>
       <c r="P113" s="6" t="s">
-        <v>516</v>
-      </c>
-      <c r="Q113" s="5" t="n">
-        <f aca="false">COUNT(G113,I113,K113,M113,O113)</f>
+        <v>524</v>
+      </c>
+      <c r="Q113" s="7"/>
+      <c r="R113" s="6"/>
+      <c r="S113" s="5" t="n">
+        <f aca="false">COUNT(G113,I113,K113,M113,O113,Q113)</f>
         <v>2</v>
       </c>
-      <c r="R113" s="8" t="n">
-        <f aca="false">IF(Q113=0,"",MIN(G113,I113,K113,M113,O113))</f>
+      <c r="T113" s="8" t="n">
+        <f aca="false">IF(S113=0,"",MIN(G113,I113,K113,M113,O113,Q113))</f>
         <v>552.5</v>
       </c>
-      <c r="S113" s="9" t="str">
-        <f aca="false">IF(Q113=0,"No quote",LEFT(IF(AND(ISNUMBER(G113),G113=R113),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I113),I113=R113),"Aslam, ","")&amp;IF(AND(ISNUMBER(K113),K113=R113),"Jamil, ","")&amp;IF(AND(ISNUMBER(M113),M113=R113),"Muller, ","")&amp;IF(AND(ISNUMBER(O113),O113=R113),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G113),G113=R113),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I113),I113=R113),"Aslam, ","")&amp;IF(AND(ISNUMBER(K113),K113=R113),"Jamil, ","")&amp;IF(AND(ISNUMBER(M113),M113=R113),"Muller, ","")&amp;IF(AND(ISNUMBER(O113),O113=R113),"NMMC, ",""))-2))</f>
+      <c r="U113" s="9" t="str">
+        <f aca="false">IF(S113=0,"No quote",LEFT(IF(AND(ISNUMBER(G113),G113=T113),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I113),I113=T113),"Aslam, ","")&amp;IF(AND(ISNUMBER(K113),K113=T113),"Jamil, ","")&amp;IF(AND(ISNUMBER(M113),M113=T113),"Muller, ","")&amp;IF(AND(ISNUMBER(O113),O113=T113),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q113),Q113=T113),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G113),G113=T113),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I113),I113=T113),"Aslam, ","")&amp;IF(AND(ISNUMBER(K113),K113=T113),"Jamil, ","")&amp;IF(AND(ISNUMBER(M113),M113=T113),"Muller, ","")&amp;IF(AND(ISNUMBER(O113),O113=T113),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q113),Q113=T113),"Platinum, ",""))-2))</f>
         <v>Ahsan</v>
       </c>
-      <c r="T113" s="10" t="n">
-        <f aca="false">IF(Q113=0,"",R113*F113)</f>
+      <c r="V113" s="10" t="n">
+        <f aca="false">IF(S113=0,"",T113*F113)</f>
         <v>22100</v>
       </c>
-      <c r="U113" s="6"/>
+      <c r="W113" s="6"/>
     </row>
     <row r="114" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="5" t="n">
         <v>109</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F114" s="5" t="n">
         <v>1000</v>
@@ -8462,39 +8748,41 @@
       <c r="N114" s="6"/>
       <c r="O114" s="7"/>
       <c r="P114" s="6"/>
-      <c r="Q114" s="5" t="n">
-        <f aca="false">COUNT(G114,I114,K114,M114,O114)</f>
+      <c r="Q114" s="7"/>
+      <c r="R114" s="6"/>
+      <c r="S114" s="5" t="n">
+        <f aca="false">COUNT(G114,I114,K114,M114,O114,Q114)</f>
         <v>0</v>
       </c>
-      <c r="R114" s="8" t="str">
-        <f aca="false">IF(Q114=0,"",MIN(G114,I114,K114,M114,O114))</f>
+      <c r="T114" s="8" t="str">
+        <f aca="false">IF(S114=0,"",MIN(G114,I114,K114,M114,O114,Q114))</f>
         <v/>
       </c>
-      <c r="S114" s="9" t="str">
-        <f aca="false">IF(Q114=0,"No quote",LEFT(IF(AND(ISNUMBER(G114),G114=R114),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I114),I114=R114),"Aslam, ","")&amp;IF(AND(ISNUMBER(K114),K114=R114),"Jamil, ","")&amp;IF(AND(ISNUMBER(M114),M114=R114),"Muller, ","")&amp;IF(AND(ISNUMBER(O114),O114=R114),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G114),G114=R114),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I114),I114=R114),"Aslam, ","")&amp;IF(AND(ISNUMBER(K114),K114=R114),"Jamil, ","")&amp;IF(AND(ISNUMBER(M114),M114=R114),"Muller, ","")&amp;IF(AND(ISNUMBER(O114),O114=R114),"NMMC, ",""))-2))</f>
+      <c r="U114" s="9" t="str">
+        <f aca="false">IF(S114=0,"No quote",LEFT(IF(AND(ISNUMBER(G114),G114=T114),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I114),I114=T114),"Aslam, ","")&amp;IF(AND(ISNUMBER(K114),K114=T114),"Jamil, ","")&amp;IF(AND(ISNUMBER(M114),M114=T114),"Muller, ","")&amp;IF(AND(ISNUMBER(O114),O114=T114),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q114),Q114=T114),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G114),G114=T114),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I114),I114=T114),"Aslam, ","")&amp;IF(AND(ISNUMBER(K114),K114=T114),"Jamil, ","")&amp;IF(AND(ISNUMBER(M114),M114=T114),"Muller, ","")&amp;IF(AND(ISNUMBER(O114),O114=T114),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q114),Q114=T114),"Platinum, ",""))-2))</f>
         <v>No quote</v>
       </c>
-      <c r="T114" s="10" t="str">
-        <f aca="false">IF(Q114=0,"",R114*F114)</f>
+      <c r="V114" s="10" t="str">
+        <f aca="false">IF(S114=0,"",T114*F114)</f>
         <v/>
       </c>
-      <c r="U114" s="6"/>
+      <c r="W114" s="6"/>
     </row>
     <row r="115" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="5" t="n">
         <v>110</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F115" s="5" t="n">
         <v>6</v>
@@ -8511,41 +8799,43 @@
         <v>1147.5</v>
       </c>
       <c r="P115" s="6" t="s">
-        <v>523</v>
-      </c>
-      <c r="Q115" s="5" t="n">
-        <f aca="false">COUNT(G115,I115,K115,M115,O115)</f>
+        <v>531</v>
+      </c>
+      <c r="Q115" s="7"/>
+      <c r="R115" s="6"/>
+      <c r="S115" s="5" t="n">
+        <f aca="false">COUNT(G115,I115,K115,M115,O115,Q115)</f>
         <v>1</v>
       </c>
-      <c r="R115" s="8" t="n">
-        <f aca="false">IF(Q115=0,"",MIN(G115,I115,K115,M115,O115))</f>
+      <c r="T115" s="8" t="n">
+        <f aca="false">IF(S115=0,"",MIN(G115,I115,K115,M115,O115,Q115))</f>
         <v>1147.5</v>
       </c>
-      <c r="S115" s="9" t="str">
-        <f aca="false">IF(Q115=0,"No quote",LEFT(IF(AND(ISNUMBER(G115),G115=R115),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I115),I115=R115),"Aslam, ","")&amp;IF(AND(ISNUMBER(K115),K115=R115),"Jamil, ","")&amp;IF(AND(ISNUMBER(M115),M115=R115),"Muller, ","")&amp;IF(AND(ISNUMBER(O115),O115=R115),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G115),G115=R115),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I115),I115=R115),"Aslam, ","")&amp;IF(AND(ISNUMBER(K115),K115=R115),"Jamil, ","")&amp;IF(AND(ISNUMBER(M115),M115=R115),"Muller, ","")&amp;IF(AND(ISNUMBER(O115),O115=R115),"NMMC, ",""))-2))</f>
+      <c r="U115" s="9" t="str">
+        <f aca="false">IF(S115=0,"No quote",LEFT(IF(AND(ISNUMBER(G115),G115=T115),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I115),I115=T115),"Aslam, ","")&amp;IF(AND(ISNUMBER(K115),K115=T115),"Jamil, ","")&amp;IF(AND(ISNUMBER(M115),M115=T115),"Muller, ","")&amp;IF(AND(ISNUMBER(O115),O115=T115),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q115),Q115=T115),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G115),G115=T115),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I115),I115=T115),"Aslam, ","")&amp;IF(AND(ISNUMBER(K115),K115=T115),"Jamil, ","")&amp;IF(AND(ISNUMBER(M115),M115=T115),"Muller, ","")&amp;IF(AND(ISNUMBER(O115),O115=T115),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q115),Q115=T115),"Platinum, ",""))-2))</f>
         <v>NMMC</v>
       </c>
-      <c r="T115" s="10" t="n">
-        <f aca="false">IF(Q115=0,"",R115*F115)</f>
+      <c r="V115" s="10" t="n">
+        <f aca="false">IF(S115=0,"",T115*F115)</f>
         <v>6885</v>
       </c>
-      <c r="U115" s="6"/>
+      <c r="W115" s="6"/>
     </row>
     <row r="116" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="5" t="n">
         <v>111</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F116" s="5" t="n">
         <v>20</v>
@@ -8556,7 +8846,7 @@
         <v>7336.77</v>
       </c>
       <c r="J116" s="6" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="6"/>
@@ -8564,43 +8854,45 @@
         <v>1134.75</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="O116" s="7"/>
       <c r="P116" s="6"/>
-      <c r="Q116" s="5" t="n">
-        <f aca="false">COUNT(G116,I116,K116,M116,O116)</f>
+      <c r="Q116" s="7"/>
+      <c r="R116" s="6"/>
+      <c r="S116" s="5" t="n">
+        <f aca="false">COUNT(G116,I116,K116,M116,O116,Q116)</f>
         <v>2</v>
       </c>
-      <c r="R116" s="8" t="n">
-        <f aca="false">IF(Q116=0,"",MIN(G116,I116,K116,M116,O116))</f>
+      <c r="T116" s="8" t="n">
+        <f aca="false">IF(S116=0,"",MIN(G116,I116,K116,M116,O116,Q116))</f>
         <v>1134.75</v>
       </c>
-      <c r="S116" s="9" t="str">
-        <f aca="false">IF(Q116=0,"No quote",LEFT(IF(AND(ISNUMBER(G116),G116=R116),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I116),I116=R116),"Aslam, ","")&amp;IF(AND(ISNUMBER(K116),K116=R116),"Jamil, ","")&amp;IF(AND(ISNUMBER(M116),M116=R116),"Muller, ","")&amp;IF(AND(ISNUMBER(O116),O116=R116),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G116),G116=R116),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I116),I116=R116),"Aslam, ","")&amp;IF(AND(ISNUMBER(K116),K116=R116),"Jamil, ","")&amp;IF(AND(ISNUMBER(M116),M116=R116),"Muller, ","")&amp;IF(AND(ISNUMBER(O116),O116=R116),"NMMC, ",""))-2))</f>
+      <c r="U116" s="9" t="str">
+        <f aca="false">IF(S116=0,"No quote",LEFT(IF(AND(ISNUMBER(G116),G116=T116),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I116),I116=T116),"Aslam, ","")&amp;IF(AND(ISNUMBER(K116),K116=T116),"Jamil, ","")&amp;IF(AND(ISNUMBER(M116),M116=T116),"Muller, ","")&amp;IF(AND(ISNUMBER(O116),O116=T116),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q116),Q116=T116),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G116),G116=T116),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I116),I116=T116),"Aslam, ","")&amp;IF(AND(ISNUMBER(K116),K116=T116),"Jamil, ","")&amp;IF(AND(ISNUMBER(M116),M116=T116),"Muller, ","")&amp;IF(AND(ISNUMBER(O116),O116=T116),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q116),Q116=T116),"Platinum, ",""))-2))</f>
         <v>Muller</v>
       </c>
-      <c r="T116" s="10" t="n">
-        <f aca="false">IF(Q116=0,"",R116*F116)</f>
+      <c r="V116" s="10" t="n">
+        <f aca="false">IF(S116=0,"",T116*F116)</f>
         <v>22695</v>
       </c>
-      <c r="U116" s="6"/>
+      <c r="W116" s="6"/>
     </row>
     <row r="117" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="5" t="n">
         <v>112</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F117" s="5" t="n">
         <v>4</v>
@@ -8611,7 +8903,7 @@
         <v>637.5</v>
       </c>
       <c r="J117" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K117" s="7"/>
       <c r="L117" s="6"/>
@@ -8621,41 +8913,43 @@
         <v>585</v>
       </c>
       <c r="P117" s="6" t="s">
-        <v>530</v>
-      </c>
-      <c r="Q117" s="5" t="n">
-        <f aca="false">COUNT(G117,I117,K117,M117,O117)</f>
+        <v>538</v>
+      </c>
+      <c r="Q117" s="7"/>
+      <c r="R117" s="6"/>
+      <c r="S117" s="5" t="n">
+        <f aca="false">COUNT(G117,I117,K117,M117,O117,Q117)</f>
         <v>2</v>
       </c>
-      <c r="R117" s="8" t="n">
-        <f aca="false">IF(Q117=0,"",MIN(G117,I117,K117,M117,O117))</f>
+      <c r="T117" s="8" t="n">
+        <f aca="false">IF(S117=0,"",MIN(G117,I117,K117,M117,O117,Q117))</f>
         <v>585</v>
       </c>
-      <c r="S117" s="9" t="str">
-        <f aca="false">IF(Q117=0,"No quote",LEFT(IF(AND(ISNUMBER(G117),G117=R117),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I117),I117=R117),"Aslam, ","")&amp;IF(AND(ISNUMBER(K117),K117=R117),"Jamil, ","")&amp;IF(AND(ISNUMBER(M117),M117=R117),"Muller, ","")&amp;IF(AND(ISNUMBER(O117),O117=R117),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G117),G117=R117),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I117),I117=R117),"Aslam, ","")&amp;IF(AND(ISNUMBER(K117),K117=R117),"Jamil, ","")&amp;IF(AND(ISNUMBER(M117),M117=R117),"Muller, ","")&amp;IF(AND(ISNUMBER(O117),O117=R117),"NMMC, ",""))-2))</f>
+      <c r="U117" s="9" t="str">
+        <f aca="false">IF(S117=0,"No quote",LEFT(IF(AND(ISNUMBER(G117),G117=T117),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I117),I117=T117),"Aslam, ","")&amp;IF(AND(ISNUMBER(K117),K117=T117),"Jamil, ","")&amp;IF(AND(ISNUMBER(M117),M117=T117),"Muller, ","")&amp;IF(AND(ISNUMBER(O117),O117=T117),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q117),Q117=T117),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G117),G117=T117),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I117),I117=T117),"Aslam, ","")&amp;IF(AND(ISNUMBER(K117),K117=T117),"Jamil, ","")&amp;IF(AND(ISNUMBER(M117),M117=T117),"Muller, ","")&amp;IF(AND(ISNUMBER(O117),O117=T117),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q117),Q117=T117),"Platinum, ",""))-2))</f>
         <v>NMMC</v>
       </c>
-      <c r="T117" s="10" t="n">
-        <f aca="false">IF(Q117=0,"",R117*F117)</f>
+      <c r="V117" s="10" t="n">
+        <f aca="false">IF(S117=0,"",T117*F117)</f>
         <v>2340</v>
       </c>
-      <c r="U117" s="6"/>
+      <c r="W117" s="6"/>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="5" t="n">
         <v>113</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F118" s="5" t="n">
         <v>50</v>
@@ -8664,13 +8958,13 @@
         <v>233.75</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="I118" s="7" t="n">
         <v>137.22</v>
       </c>
       <c r="J118" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="6"/>
@@ -8678,39 +8972,41 @@
       <c r="N118" s="6"/>
       <c r="O118" s="7"/>
       <c r="P118" s="6"/>
-      <c r="Q118" s="5" t="n">
-        <f aca="false">COUNT(G118,I118,K118,M118,O118)</f>
+      <c r="Q118" s="7"/>
+      <c r="R118" s="6"/>
+      <c r="S118" s="5" t="n">
+        <f aca="false">COUNT(G118,I118,K118,M118,O118,Q118)</f>
         <v>2</v>
       </c>
-      <c r="R118" s="8" t="n">
-        <f aca="false">IF(Q118=0,"",MIN(G118,I118,K118,M118,O118))</f>
+      <c r="T118" s="8" t="n">
+        <f aca="false">IF(S118=0,"",MIN(G118,I118,K118,M118,O118,Q118))</f>
         <v>137.22</v>
       </c>
-      <c r="S118" s="9" t="str">
-        <f aca="false">IF(Q118=0,"No quote",LEFT(IF(AND(ISNUMBER(G118),G118=R118),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I118),I118=R118),"Aslam, ","")&amp;IF(AND(ISNUMBER(K118),K118=R118),"Jamil, ","")&amp;IF(AND(ISNUMBER(M118),M118=R118),"Muller, ","")&amp;IF(AND(ISNUMBER(O118),O118=R118),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G118),G118=R118),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I118),I118=R118),"Aslam, ","")&amp;IF(AND(ISNUMBER(K118),K118=R118),"Jamil, ","")&amp;IF(AND(ISNUMBER(M118),M118=R118),"Muller, ","")&amp;IF(AND(ISNUMBER(O118),O118=R118),"NMMC, ",""))-2))</f>
+      <c r="U118" s="9" t="str">
+        <f aca="false">IF(S118=0,"No quote",LEFT(IF(AND(ISNUMBER(G118),G118=T118),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I118),I118=T118),"Aslam, ","")&amp;IF(AND(ISNUMBER(K118),K118=T118),"Jamil, ","")&amp;IF(AND(ISNUMBER(M118),M118=T118),"Muller, ","")&amp;IF(AND(ISNUMBER(O118),O118=T118),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q118),Q118=T118),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G118),G118=T118),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I118),I118=T118),"Aslam, ","")&amp;IF(AND(ISNUMBER(K118),K118=T118),"Jamil, ","")&amp;IF(AND(ISNUMBER(M118),M118=T118),"Muller, ","")&amp;IF(AND(ISNUMBER(O118),O118=T118),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q118),Q118=T118),"Platinum, ",""))-2))</f>
         <v>Aslam</v>
       </c>
-      <c r="T118" s="10" t="n">
-        <f aca="false">IF(Q118=0,"",R118*F118)</f>
+      <c r="V118" s="10" t="n">
+        <f aca="false">IF(S118=0,"",T118*F118)</f>
         <v>6861</v>
       </c>
-      <c r="U118" s="6"/>
+      <c r="W118" s="6"/>
     </row>
     <row r="119" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="5" t="n">
         <v>114</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F119" s="5" t="n">
         <v>40</v>
@@ -8719,7 +9015,7 @@
         <v>250.75</v>
       </c>
       <c r="H119" s="6" t="s">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="I119" s="7"/>
       <c r="J119" s="6"/>
@@ -8729,39 +9025,41 @@
       <c r="N119" s="6"/>
       <c r="O119" s="7"/>
       <c r="P119" s="6"/>
-      <c r="Q119" s="5" t="n">
-        <f aca="false">COUNT(G119,I119,K119,M119,O119)</f>
+      <c r="Q119" s="7"/>
+      <c r="R119" s="6"/>
+      <c r="S119" s="5" t="n">
+        <f aca="false">COUNT(G119,I119,K119,M119,O119,Q119)</f>
         <v>1</v>
       </c>
-      <c r="R119" s="8" t="n">
-        <f aca="false">IF(Q119=0,"",MIN(G119,I119,K119,M119,O119))</f>
+      <c r="T119" s="8" t="n">
+        <f aca="false">IF(S119=0,"",MIN(G119,I119,K119,M119,O119,Q119))</f>
         <v>250.75</v>
       </c>
-      <c r="S119" s="9" t="str">
-        <f aca="false">IF(Q119=0,"No quote",LEFT(IF(AND(ISNUMBER(G119),G119=R119),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I119),I119=R119),"Aslam, ","")&amp;IF(AND(ISNUMBER(K119),K119=R119),"Jamil, ","")&amp;IF(AND(ISNUMBER(M119),M119=R119),"Muller, ","")&amp;IF(AND(ISNUMBER(O119),O119=R119),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G119),G119=R119),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I119),I119=R119),"Aslam, ","")&amp;IF(AND(ISNUMBER(K119),K119=R119),"Jamil, ","")&amp;IF(AND(ISNUMBER(M119),M119=R119),"Muller, ","")&amp;IF(AND(ISNUMBER(O119),O119=R119),"NMMC, ",""))-2))</f>
+      <c r="U119" s="9" t="str">
+        <f aca="false">IF(S119=0,"No quote",LEFT(IF(AND(ISNUMBER(G119),G119=T119),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I119),I119=T119),"Aslam, ","")&amp;IF(AND(ISNUMBER(K119),K119=T119),"Jamil, ","")&amp;IF(AND(ISNUMBER(M119),M119=T119),"Muller, ","")&amp;IF(AND(ISNUMBER(O119),O119=T119),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q119),Q119=T119),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G119),G119=T119),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I119),I119=T119),"Aslam, ","")&amp;IF(AND(ISNUMBER(K119),K119=T119),"Jamil, ","")&amp;IF(AND(ISNUMBER(M119),M119=T119),"Muller, ","")&amp;IF(AND(ISNUMBER(O119),O119=T119),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q119),Q119=T119),"Platinum, ",""))-2))</f>
         <v>Ahsan</v>
       </c>
-      <c r="T119" s="10" t="n">
-        <f aca="false">IF(Q119=0,"",R119*F119)</f>
+      <c r="V119" s="10" t="n">
+        <f aca="false">IF(S119=0,"",T119*F119)</f>
         <v>10030</v>
       </c>
-      <c r="U119" s="6"/>
+      <c r="W119" s="6"/>
     </row>
     <row r="120" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="5" t="n">
         <v>115</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F120" s="5" t="n">
         <v>2</v>
@@ -8772,7 +9070,7 @@
         <v>1275</v>
       </c>
       <c r="J120" s="6" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="K120" s="7"/>
       <c r="L120" s="6"/>
@@ -8780,39 +9078,41 @@
       <c r="N120" s="6"/>
       <c r="O120" s="7"/>
       <c r="P120" s="6"/>
-      <c r="Q120" s="5" t="n">
-        <f aca="false">COUNT(G120,I120,K120,M120,O120)</f>
+      <c r="Q120" s="7"/>
+      <c r="R120" s="6"/>
+      <c r="S120" s="5" t="n">
+        <f aca="false">COUNT(G120,I120,K120,M120,O120,Q120)</f>
         <v>1</v>
       </c>
-      <c r="R120" s="8" t="n">
-        <f aca="false">IF(Q120=0,"",MIN(G120,I120,K120,M120,O120))</f>
+      <c r="T120" s="8" t="n">
+        <f aca="false">IF(S120=0,"",MIN(G120,I120,K120,M120,O120,Q120))</f>
         <v>1275</v>
       </c>
-      <c r="S120" s="9" t="str">
-        <f aca="false">IF(Q120=0,"No quote",LEFT(IF(AND(ISNUMBER(G120),G120=R120),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I120),I120=R120),"Aslam, ","")&amp;IF(AND(ISNUMBER(K120),K120=R120),"Jamil, ","")&amp;IF(AND(ISNUMBER(M120),M120=R120),"Muller, ","")&amp;IF(AND(ISNUMBER(O120),O120=R120),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G120),G120=R120),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I120),I120=R120),"Aslam, ","")&amp;IF(AND(ISNUMBER(K120),K120=R120),"Jamil, ","")&amp;IF(AND(ISNUMBER(M120),M120=R120),"Muller, ","")&amp;IF(AND(ISNUMBER(O120),O120=R120),"NMMC, ",""))-2))</f>
+      <c r="U120" s="9" t="str">
+        <f aca="false">IF(S120=0,"No quote",LEFT(IF(AND(ISNUMBER(G120),G120=T120),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I120),I120=T120),"Aslam, ","")&amp;IF(AND(ISNUMBER(K120),K120=T120),"Jamil, ","")&amp;IF(AND(ISNUMBER(M120),M120=T120),"Muller, ","")&amp;IF(AND(ISNUMBER(O120),O120=T120),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q120),Q120=T120),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G120),G120=T120),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I120),I120=T120),"Aslam, ","")&amp;IF(AND(ISNUMBER(K120),K120=T120),"Jamil, ","")&amp;IF(AND(ISNUMBER(M120),M120=T120),"Muller, ","")&amp;IF(AND(ISNUMBER(O120),O120=T120),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q120),Q120=T120),"Platinum, ",""))-2))</f>
         <v>Aslam</v>
       </c>
-      <c r="T120" s="10" t="n">
-        <f aca="false">IF(Q120=0,"",R120*F120)</f>
+      <c r="V120" s="10" t="n">
+        <f aca="false">IF(S120=0,"",T120*F120)</f>
         <v>2550</v>
       </c>
-      <c r="U120" s="6"/>
+      <c r="W120" s="6"/>
     </row>
     <row r="121" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="5" t="n">
         <v>116</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>544</v>
+        <v>552</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F121" s="5" t="n">
         <v>20</v>
@@ -8823,7 +9123,7 @@
         <v>6324</v>
       </c>
       <c r="J121" s="6" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="6"/>
@@ -8831,39 +9131,41 @@
       <c r="N121" s="6"/>
       <c r="O121" s="7"/>
       <c r="P121" s="6"/>
-      <c r="Q121" s="5" t="n">
-        <f aca="false">COUNT(G121,I121,K121,M121,O121)</f>
+      <c r="Q121" s="7"/>
+      <c r="R121" s="6"/>
+      <c r="S121" s="5" t="n">
+        <f aca="false">COUNT(G121,I121,K121,M121,O121,Q121)</f>
         <v>1</v>
       </c>
-      <c r="R121" s="8" t="n">
-        <f aca="false">IF(Q121=0,"",MIN(G121,I121,K121,M121,O121))</f>
+      <c r="T121" s="8" t="n">
+        <f aca="false">IF(S121=0,"",MIN(G121,I121,K121,M121,O121,Q121))</f>
         <v>6324</v>
       </c>
-      <c r="S121" s="9" t="str">
-        <f aca="false">IF(Q121=0,"No quote",LEFT(IF(AND(ISNUMBER(G121),G121=R121),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I121),I121=R121),"Aslam, ","")&amp;IF(AND(ISNUMBER(K121),K121=R121),"Jamil, ","")&amp;IF(AND(ISNUMBER(M121),M121=R121),"Muller, ","")&amp;IF(AND(ISNUMBER(O121),O121=R121),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G121),G121=R121),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I121),I121=R121),"Aslam, ","")&amp;IF(AND(ISNUMBER(K121),K121=R121),"Jamil, ","")&amp;IF(AND(ISNUMBER(M121),M121=R121),"Muller, ","")&amp;IF(AND(ISNUMBER(O121),O121=R121),"NMMC, ",""))-2))</f>
+      <c r="U121" s="9" t="str">
+        <f aca="false">IF(S121=0,"No quote",LEFT(IF(AND(ISNUMBER(G121),G121=T121),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I121),I121=T121),"Aslam, ","")&amp;IF(AND(ISNUMBER(K121),K121=T121),"Jamil, ","")&amp;IF(AND(ISNUMBER(M121),M121=T121),"Muller, ","")&amp;IF(AND(ISNUMBER(O121),O121=T121),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q121),Q121=T121),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G121),G121=T121),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I121),I121=T121),"Aslam, ","")&amp;IF(AND(ISNUMBER(K121),K121=T121),"Jamil, ","")&amp;IF(AND(ISNUMBER(M121),M121=T121),"Muller, ","")&amp;IF(AND(ISNUMBER(O121),O121=T121),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q121),Q121=T121),"Platinum, ",""))-2))</f>
         <v>Aslam</v>
       </c>
-      <c r="T121" s="10" t="n">
-        <f aca="false">IF(Q121=0,"",R121*F121)</f>
+      <c r="V121" s="10" t="n">
+        <f aca="false">IF(S121=0,"",T121*F121)</f>
         <v>126480</v>
       </c>
-      <c r="U121" s="6"/>
+      <c r="W121" s="6"/>
     </row>
     <row r="122" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="5" t="n">
         <v>117</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F122" s="5" t="n">
         <v>2000</v>
@@ -8872,7 +9174,7 @@
         <v>187</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>548</v>
+        <v>556</v>
       </c>
       <c r="I122" s="7"/>
       <c r="J122" s="6"/>
@@ -8882,47 +9184,49 @@
         <v>178.5</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="O122" s="7" t="n">
         <v>136</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>550</v>
-      </c>
-      <c r="Q122" s="5" t="n">
-        <f aca="false">COUNT(G122,I122,K122,M122,O122)</f>
+        <v>558</v>
+      </c>
+      <c r="Q122" s="7"/>
+      <c r="R122" s="6"/>
+      <c r="S122" s="5" t="n">
+        <f aca="false">COUNT(G122,I122,K122,M122,O122,Q122)</f>
         <v>3</v>
       </c>
-      <c r="R122" s="8" t="n">
-        <f aca="false">IF(Q122=0,"",MIN(G122,I122,K122,M122,O122))</f>
+      <c r="T122" s="8" t="n">
+        <f aca="false">IF(S122=0,"",MIN(G122,I122,K122,M122,O122,Q122))</f>
         <v>136</v>
       </c>
-      <c r="S122" s="9" t="str">
-        <f aca="false">IF(Q122=0,"No quote",LEFT(IF(AND(ISNUMBER(G122),G122=R122),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I122),I122=R122),"Aslam, ","")&amp;IF(AND(ISNUMBER(K122),K122=R122),"Jamil, ","")&amp;IF(AND(ISNUMBER(M122),M122=R122),"Muller, ","")&amp;IF(AND(ISNUMBER(O122),O122=R122),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G122),G122=R122),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I122),I122=R122),"Aslam, ","")&amp;IF(AND(ISNUMBER(K122),K122=R122),"Jamil, ","")&amp;IF(AND(ISNUMBER(M122),M122=R122),"Muller, ","")&amp;IF(AND(ISNUMBER(O122),O122=R122),"NMMC, ",""))-2))</f>
+      <c r="U122" s="9" t="str">
+        <f aca="false">IF(S122=0,"No quote",LEFT(IF(AND(ISNUMBER(G122),G122=T122),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I122),I122=T122),"Aslam, ","")&amp;IF(AND(ISNUMBER(K122),K122=T122),"Jamil, ","")&amp;IF(AND(ISNUMBER(M122),M122=T122),"Muller, ","")&amp;IF(AND(ISNUMBER(O122),O122=T122),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q122),Q122=T122),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G122),G122=T122),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I122),I122=T122),"Aslam, ","")&amp;IF(AND(ISNUMBER(K122),K122=T122),"Jamil, ","")&amp;IF(AND(ISNUMBER(M122),M122=T122),"Muller, ","")&amp;IF(AND(ISNUMBER(O122),O122=T122),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q122),Q122=T122),"Platinum, ",""))-2))</f>
         <v>NMMC</v>
       </c>
-      <c r="T122" s="10" t="n">
-        <f aca="false">IF(Q122=0,"",R122*F122)</f>
+      <c r="V122" s="10" t="n">
+        <f aca="false">IF(S122=0,"",T122*F122)</f>
         <v>272000</v>
       </c>
-      <c r="U122" s="6"/>
+      <c r="W122" s="6"/>
     </row>
     <row r="123" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="5" t="n">
         <v>118</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>551</v>
+        <v>559</v>
       </c>
       <c r="C123" s="6" t="s">
-        <v>552</v>
+        <v>560</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F123" s="5" t="n">
         <v>100</v>
@@ -8931,7 +9235,7 @@
         <v>272</v>
       </c>
       <c r="H123" s="6" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="I123" s="7"/>
       <c r="J123" s="6"/>
@@ -8941,43 +9245,45 @@
         <v>1006.812</v>
       </c>
       <c r="N123" s="6" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="O123" s="7"/>
       <c r="P123" s="6"/>
-      <c r="Q123" s="5" t="n">
-        <f aca="false">COUNT(G123,I123,K123,M123,O123)</f>
+      <c r="Q123" s="7"/>
+      <c r="R123" s="6"/>
+      <c r="S123" s="5" t="n">
+        <f aca="false">COUNT(G123,I123,K123,M123,O123,Q123)</f>
         <v>2</v>
       </c>
-      <c r="R123" s="8" t="n">
-        <f aca="false">IF(Q123=0,"",MIN(G123,I123,K123,M123,O123))</f>
+      <c r="T123" s="8" t="n">
+        <f aca="false">IF(S123=0,"",MIN(G123,I123,K123,M123,O123,Q123))</f>
         <v>272</v>
       </c>
-      <c r="S123" s="9" t="str">
-        <f aca="false">IF(Q123=0,"No quote",LEFT(IF(AND(ISNUMBER(G123),G123=R123),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I123),I123=R123),"Aslam, ","")&amp;IF(AND(ISNUMBER(K123),K123=R123),"Jamil, ","")&amp;IF(AND(ISNUMBER(M123),M123=R123),"Muller, ","")&amp;IF(AND(ISNUMBER(O123),O123=R123),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G123),G123=R123),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I123),I123=R123),"Aslam, ","")&amp;IF(AND(ISNUMBER(K123),K123=R123),"Jamil, ","")&amp;IF(AND(ISNUMBER(M123),M123=R123),"Muller, ","")&amp;IF(AND(ISNUMBER(O123),O123=R123),"NMMC, ",""))-2))</f>
+      <c r="U123" s="9" t="str">
+        <f aca="false">IF(S123=0,"No quote",LEFT(IF(AND(ISNUMBER(G123),G123=T123),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I123),I123=T123),"Aslam, ","")&amp;IF(AND(ISNUMBER(K123),K123=T123),"Jamil, ","")&amp;IF(AND(ISNUMBER(M123),M123=T123),"Muller, ","")&amp;IF(AND(ISNUMBER(O123),O123=T123),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q123),Q123=T123),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G123),G123=T123),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I123),I123=T123),"Aslam, ","")&amp;IF(AND(ISNUMBER(K123),K123=T123),"Jamil, ","")&amp;IF(AND(ISNUMBER(M123),M123=T123),"Muller, ","")&amp;IF(AND(ISNUMBER(O123),O123=T123),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q123),Q123=T123),"Platinum, ",""))-2))</f>
         <v>Ahsan</v>
       </c>
-      <c r="T123" s="10" t="n">
-        <f aca="false">IF(Q123=0,"",R123*F123)</f>
+      <c r="V123" s="10" t="n">
+        <f aca="false">IF(S123=0,"",T123*F123)</f>
         <v>27200</v>
       </c>
-      <c r="U123" s="6"/>
+      <c r="W123" s="6"/>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="5" t="n">
         <v>119</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>555</v>
+        <v>563</v>
       </c>
       <c r="D124" s="6" t="s">
-        <v>556</v>
+        <v>564</v>
       </c>
       <c r="E124" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F124" s="5" t="n">
         <v>50</v>
@@ -8992,43 +9298,45 @@
         <v>677.88</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>557</v>
+        <v>565</v>
       </c>
       <c r="O124" s="7"/>
       <c r="P124" s="6"/>
-      <c r="Q124" s="5" t="n">
-        <f aca="false">COUNT(G124,I124,K124,M124,O124)</f>
+      <c r="Q124" s="7"/>
+      <c r="R124" s="6"/>
+      <c r="S124" s="5" t="n">
+        <f aca="false">COUNT(G124,I124,K124,M124,O124,Q124)</f>
         <v>1</v>
       </c>
-      <c r="R124" s="8" t="n">
-        <f aca="false">IF(Q124=0,"",MIN(G124,I124,K124,M124,O124))</f>
+      <c r="T124" s="8" t="n">
+        <f aca="false">IF(S124=0,"",MIN(G124,I124,K124,M124,O124,Q124))</f>
         <v>677.88</v>
       </c>
-      <c r="S124" s="9" t="str">
-        <f aca="false">IF(Q124=0,"No quote",LEFT(IF(AND(ISNUMBER(G124),G124=R124),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I124),I124=R124),"Aslam, ","")&amp;IF(AND(ISNUMBER(K124),K124=R124),"Jamil, ","")&amp;IF(AND(ISNUMBER(M124),M124=R124),"Muller, ","")&amp;IF(AND(ISNUMBER(O124),O124=R124),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G124),G124=R124),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I124),I124=R124),"Aslam, ","")&amp;IF(AND(ISNUMBER(K124),K124=R124),"Jamil, ","")&amp;IF(AND(ISNUMBER(M124),M124=R124),"Muller, ","")&amp;IF(AND(ISNUMBER(O124),O124=R124),"NMMC, ",""))-2))</f>
+      <c r="U124" s="9" t="str">
+        <f aca="false">IF(S124=0,"No quote",LEFT(IF(AND(ISNUMBER(G124),G124=T124),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I124),I124=T124),"Aslam, ","")&amp;IF(AND(ISNUMBER(K124),K124=T124),"Jamil, ","")&amp;IF(AND(ISNUMBER(M124),M124=T124),"Muller, ","")&amp;IF(AND(ISNUMBER(O124),O124=T124),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q124),Q124=T124),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G124),G124=T124),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I124),I124=T124),"Aslam, ","")&amp;IF(AND(ISNUMBER(K124),K124=T124),"Jamil, ","")&amp;IF(AND(ISNUMBER(M124),M124=T124),"Muller, ","")&amp;IF(AND(ISNUMBER(O124),O124=T124),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q124),Q124=T124),"Platinum, ",""))-2))</f>
         <v>Muller</v>
       </c>
-      <c r="T124" s="10" t="n">
-        <f aca="false">IF(Q124=0,"",R124*F124)</f>
+      <c r="V124" s="10" t="n">
+        <f aca="false">IF(S124=0,"",T124*F124)</f>
         <v>33894</v>
       </c>
-      <c r="U124" s="6"/>
+      <c r="W124" s="6"/>
     </row>
     <row r="125" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="5" t="n">
         <v>120</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>559</v>
+        <v>567</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>560</v>
+        <v>568</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F125" s="5" t="n">
         <v>100</v>
@@ -9041,7 +9349,7 @@
         <v>529.36</v>
       </c>
       <c r="L125" s="6" t="s">
-        <v>561</v>
+        <v>569</v>
       </c>
       <c r="M125" s="7"/>
       <c r="N125" s="6"/>
@@ -9049,41 +9357,43 @@
         <v>252.45</v>
       </c>
       <c r="P125" s="6" t="s">
-        <v>562</v>
-      </c>
-      <c r="Q125" s="5" t="n">
-        <f aca="false">COUNT(G125,I125,K125,M125,O125)</f>
+        <v>570</v>
+      </c>
+      <c r="Q125" s="7"/>
+      <c r="R125" s="6"/>
+      <c r="S125" s="5" t="n">
+        <f aca="false">COUNT(G125,I125,K125,M125,O125,Q125)</f>
         <v>2</v>
       </c>
-      <c r="R125" s="8" t="n">
-        <f aca="false">IF(Q125=0,"",MIN(G125,I125,K125,M125,O125))</f>
+      <c r="T125" s="8" t="n">
+        <f aca="false">IF(S125=0,"",MIN(G125,I125,K125,M125,O125,Q125))</f>
         <v>252.45</v>
       </c>
-      <c r="S125" s="9" t="str">
-        <f aca="false">IF(Q125=0,"No quote",LEFT(IF(AND(ISNUMBER(G125),G125=R125),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I125),I125=R125),"Aslam, ","")&amp;IF(AND(ISNUMBER(K125),K125=R125),"Jamil, ","")&amp;IF(AND(ISNUMBER(M125),M125=R125),"Muller, ","")&amp;IF(AND(ISNUMBER(O125),O125=R125),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G125),G125=R125),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I125),I125=R125),"Aslam, ","")&amp;IF(AND(ISNUMBER(K125),K125=R125),"Jamil, ","")&amp;IF(AND(ISNUMBER(M125),M125=R125),"Muller, ","")&amp;IF(AND(ISNUMBER(O125),O125=R125),"NMMC, ",""))-2))</f>
+      <c r="U125" s="9" t="str">
+        <f aca="false">IF(S125=0,"No quote",LEFT(IF(AND(ISNUMBER(G125),G125=T125),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I125),I125=T125),"Aslam, ","")&amp;IF(AND(ISNUMBER(K125),K125=T125),"Jamil, ","")&amp;IF(AND(ISNUMBER(M125),M125=T125),"Muller, ","")&amp;IF(AND(ISNUMBER(O125),O125=T125),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q125),Q125=T125),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G125),G125=T125),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I125),I125=T125),"Aslam, ","")&amp;IF(AND(ISNUMBER(K125),K125=T125),"Jamil, ","")&amp;IF(AND(ISNUMBER(M125),M125=T125),"Muller, ","")&amp;IF(AND(ISNUMBER(O125),O125=T125),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q125),Q125=T125),"Platinum, ",""))-2))</f>
         <v>NMMC</v>
       </c>
-      <c r="T125" s="10" t="n">
-        <f aca="false">IF(Q125=0,"",R125*F125)</f>
+      <c r="V125" s="10" t="n">
+        <f aca="false">IF(S125=0,"",T125*F125)</f>
         <v>25245</v>
       </c>
-      <c r="U125" s="6"/>
+      <c r="W125" s="6"/>
     </row>
     <row r="126" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="5" t="n">
         <v>121</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>563</v>
+        <v>571</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="D126" s="6" t="s">
-        <v>565</v>
+        <v>573</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F126" s="5" t="n">
         <v>300</v>
@@ -9094,7 +9404,7 @@
         <v>1178.1</v>
       </c>
       <c r="J126" s="6" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="K126" s="7"/>
       <c r="L126" s="6"/>
@@ -9102,39 +9412,45 @@
       <c r="N126" s="6"/>
       <c r="O126" s="7"/>
       <c r="P126" s="6"/>
-      <c r="Q126" s="5" t="n">
-        <f aca="false">COUNT(G126,I126,K126,M126,O126)</f>
-        <v>1</v>
-      </c>
-      <c r="R126" s="8" t="n">
-        <f aca="false">IF(Q126=0,"",MIN(G126,I126,K126,M126,O126))</f>
-        <v>1178.1</v>
-      </c>
-      <c r="S126" s="9" t="str">
-        <f aca="false">IF(Q126=0,"No quote",LEFT(IF(AND(ISNUMBER(G126),G126=R126),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I126),I126=R126),"Aslam, ","")&amp;IF(AND(ISNUMBER(K126),K126=R126),"Jamil, ","")&amp;IF(AND(ISNUMBER(M126),M126=R126),"Muller, ","")&amp;IF(AND(ISNUMBER(O126),O126=R126),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G126),G126=R126),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I126),I126=R126),"Aslam, ","")&amp;IF(AND(ISNUMBER(K126),K126=R126),"Jamil, ","")&amp;IF(AND(ISNUMBER(M126),M126=R126),"Muller, ","")&amp;IF(AND(ISNUMBER(O126),O126=R126),"NMMC, ",""))-2))</f>
-        <v>Aslam</v>
-      </c>
-      <c r="T126" s="10" t="n">
-        <f aca="false">IF(Q126=0,"",R126*F126)</f>
-        <v>353430</v>
-      </c>
-      <c r="U126" s="6"/>
+      <c r="Q126" s="7" t="n">
+        <v>416.5</v>
+      </c>
+      <c r="R126" s="6" t="s">
+        <v>574</v>
+      </c>
+      <c r="S126" s="5" t="n">
+        <f aca="false">COUNT(G126,I126,K126,M126,O126,Q126)</f>
+        <v>2</v>
+      </c>
+      <c r="T126" s="8" t="n">
+        <f aca="false">IF(S126=0,"",MIN(G126,I126,K126,M126,O126,Q126))</f>
+        <v>416.5</v>
+      </c>
+      <c r="U126" s="9" t="str">
+        <f aca="false">IF(S126=0,"No quote",LEFT(IF(AND(ISNUMBER(G126),G126=T126),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I126),I126=T126),"Aslam, ","")&amp;IF(AND(ISNUMBER(K126),K126=T126),"Jamil, ","")&amp;IF(AND(ISNUMBER(M126),M126=T126),"Muller, ","")&amp;IF(AND(ISNUMBER(O126),O126=T126),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q126),Q126=T126),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G126),G126=T126),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I126),I126=T126),"Aslam, ","")&amp;IF(AND(ISNUMBER(K126),K126=T126),"Jamil, ","")&amp;IF(AND(ISNUMBER(M126),M126=T126),"Muller, ","")&amp;IF(AND(ISNUMBER(O126),O126=T126),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q126),Q126=T126),"Platinum, ",""))-2))</f>
+        <v>Platinum</v>
+      </c>
+      <c r="V126" s="10" t="n">
+        <f aca="false">IF(S126=0,"",T126*F126)</f>
+        <v>124950</v>
+      </c>
+      <c r="W126" s="6"/>
     </row>
     <row r="127" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="5" t="n">
         <v>122</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>566</v>
+        <v>575</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>567</v>
+        <v>576</v>
       </c>
       <c r="D127" s="6" t="s">
-        <v>568</v>
+        <v>577</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F127" s="5" t="n">
         <v>60</v>
@@ -9145,7 +9461,7 @@
         <v>106.85</v>
       </c>
       <c r="J127" s="6" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="K127" s="7"/>
       <c r="L127" s="6"/>
@@ -9153,43 +9469,45 @@
         <v>331.91</v>
       </c>
       <c r="N127" s="6" t="s">
-        <v>569</v>
+        <v>578</v>
       </c>
       <c r="O127" s="7"/>
       <c r="P127" s="6"/>
-      <c r="Q127" s="5" t="n">
-        <f aca="false">COUNT(G127,I127,K127,M127,O127)</f>
+      <c r="Q127" s="7"/>
+      <c r="R127" s="6"/>
+      <c r="S127" s="5" t="n">
+        <f aca="false">COUNT(G127,I127,K127,M127,O127,Q127)</f>
         <v>2</v>
       </c>
-      <c r="R127" s="8" t="n">
-        <f aca="false">IF(Q127=0,"",MIN(G127,I127,K127,M127,O127))</f>
+      <c r="T127" s="8" t="n">
+        <f aca="false">IF(S127=0,"",MIN(G127,I127,K127,M127,O127,Q127))</f>
         <v>106.85</v>
       </c>
-      <c r="S127" s="9" t="str">
-        <f aca="false">IF(Q127=0,"No quote",LEFT(IF(AND(ISNUMBER(G127),G127=R127),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I127),I127=R127),"Aslam, ","")&amp;IF(AND(ISNUMBER(K127),K127=R127),"Jamil, ","")&amp;IF(AND(ISNUMBER(M127),M127=R127),"Muller, ","")&amp;IF(AND(ISNUMBER(O127),O127=R127),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G127),G127=R127),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I127),I127=R127),"Aslam, ","")&amp;IF(AND(ISNUMBER(K127),K127=R127),"Jamil, ","")&amp;IF(AND(ISNUMBER(M127),M127=R127),"Muller, ","")&amp;IF(AND(ISNUMBER(O127),O127=R127),"NMMC, ",""))-2))</f>
+      <c r="U127" s="9" t="str">
+        <f aca="false">IF(S127=0,"No quote",LEFT(IF(AND(ISNUMBER(G127),G127=T127),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I127),I127=T127),"Aslam, ","")&amp;IF(AND(ISNUMBER(K127),K127=T127),"Jamil, ","")&amp;IF(AND(ISNUMBER(M127),M127=T127),"Muller, ","")&amp;IF(AND(ISNUMBER(O127),O127=T127),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q127),Q127=T127),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G127),G127=T127),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I127),I127=T127),"Aslam, ","")&amp;IF(AND(ISNUMBER(K127),K127=T127),"Jamil, ","")&amp;IF(AND(ISNUMBER(M127),M127=T127),"Muller, ","")&amp;IF(AND(ISNUMBER(O127),O127=T127),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q127),Q127=T127),"Platinum, ",""))-2))</f>
         <v>Aslam</v>
       </c>
-      <c r="T127" s="10" t="n">
-        <f aca="false">IF(Q127=0,"",R127*F127)</f>
+      <c r="V127" s="10" t="n">
+        <f aca="false">IF(S127=0,"",T127*F127)</f>
         <v>6411</v>
       </c>
-      <c r="U127" s="6"/>
+      <c r="W127" s="6"/>
     </row>
     <row r="128" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="5" t="n">
         <v>123</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>570</v>
+        <v>579</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>571</v>
+        <v>580</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>572</v>
+        <v>581</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F128" s="5" t="n">
         <v>100</v>
@@ -9198,7 +9516,7 @@
         <v>120.7</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>573</v>
+        <v>582</v>
       </c>
       <c r="I128" s="7"/>
       <c r="J128" s="6"/>
@@ -9208,47 +9526,49 @@
         <v>323</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>574</v>
+        <v>583</v>
       </c>
       <c r="O128" s="7" t="n">
         <v>127.5</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>575</v>
-      </c>
-      <c r="Q128" s="5" t="n">
-        <f aca="false">COUNT(G128,I128,K128,M128,O128)</f>
+        <v>584</v>
+      </c>
+      <c r="Q128" s="7"/>
+      <c r="R128" s="6"/>
+      <c r="S128" s="5" t="n">
+        <f aca="false">COUNT(G128,I128,K128,M128,O128,Q128)</f>
         <v>3</v>
       </c>
-      <c r="R128" s="8" t="n">
-        <f aca="false">IF(Q128=0,"",MIN(G128,I128,K128,M128,O128))</f>
+      <c r="T128" s="8" t="n">
+        <f aca="false">IF(S128=0,"",MIN(G128,I128,K128,M128,O128,Q128))</f>
         <v>120.7</v>
       </c>
-      <c r="S128" s="9" t="str">
-        <f aca="false">IF(Q128=0,"No quote",LEFT(IF(AND(ISNUMBER(G128),G128=R128),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I128),I128=R128),"Aslam, ","")&amp;IF(AND(ISNUMBER(K128),K128=R128),"Jamil, ","")&amp;IF(AND(ISNUMBER(M128),M128=R128),"Muller, ","")&amp;IF(AND(ISNUMBER(O128),O128=R128),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G128),G128=R128),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I128),I128=R128),"Aslam, ","")&amp;IF(AND(ISNUMBER(K128),K128=R128),"Jamil, ","")&amp;IF(AND(ISNUMBER(M128),M128=R128),"Muller, ","")&amp;IF(AND(ISNUMBER(O128),O128=R128),"NMMC, ",""))-2))</f>
+      <c r="U128" s="9" t="str">
+        <f aca="false">IF(S128=0,"No quote",LEFT(IF(AND(ISNUMBER(G128),G128=T128),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I128),I128=T128),"Aslam, ","")&amp;IF(AND(ISNUMBER(K128),K128=T128),"Jamil, ","")&amp;IF(AND(ISNUMBER(M128),M128=T128),"Muller, ","")&amp;IF(AND(ISNUMBER(O128),O128=T128),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q128),Q128=T128),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G128),G128=T128),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I128),I128=T128),"Aslam, ","")&amp;IF(AND(ISNUMBER(K128),K128=T128),"Jamil, ","")&amp;IF(AND(ISNUMBER(M128),M128=T128),"Muller, ","")&amp;IF(AND(ISNUMBER(O128),O128=T128),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q128),Q128=T128),"Platinum, ",""))-2))</f>
         <v>Ahsan</v>
       </c>
-      <c r="T128" s="10" t="n">
-        <f aca="false">IF(Q128=0,"",R128*F128)</f>
+      <c r="V128" s="10" t="n">
+        <f aca="false">IF(S128=0,"",T128*F128)</f>
         <v>12070</v>
       </c>
-      <c r="U128" s="6"/>
+      <c r="W128" s="6"/>
     </row>
     <row r="129" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="5" t="n">
         <v>124</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>576</v>
+        <v>585</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>577</v>
+        <v>586</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>578</v>
+        <v>587</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F129" s="5" t="n">
         <v>600</v>
@@ -9257,13 +9577,13 @@
         <v>450.5</v>
       </c>
       <c r="H129" s="6" t="s">
-        <v>579</v>
+        <v>588</v>
       </c>
       <c r="I129" s="7" t="n">
         <v>188.7</v>
       </c>
       <c r="J129" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K129" s="7"/>
       <c r="L129" s="6"/>
@@ -9271,39 +9591,41 @@
         <v>695.3</v>
       </c>
       <c r="N129" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O129" s="7" t="n">
         <v>299.1525</v>
       </c>
       <c r="P129" s="6" t="s">
-        <v>580</v>
-      </c>
-      <c r="Q129" s="5" t="n">
-        <f aca="false">COUNT(G129,I129,K129,M129,O129)</f>
+        <v>589</v>
+      </c>
+      <c r="Q129" s="7"/>
+      <c r="R129" s="6"/>
+      <c r="S129" s="5" t="n">
+        <f aca="false">COUNT(G129,I129,K129,M129,O129,Q129)</f>
         <v>4</v>
       </c>
-      <c r="R129" s="8" t="n">
-        <f aca="false">IF(Q129=0,"",MIN(G129,I129,K129,M129,O129))</f>
+      <c r="T129" s="8" t="n">
+        <f aca="false">IF(S129=0,"",MIN(G129,I129,K129,M129,O129,Q129))</f>
         <v>188.7</v>
       </c>
-      <c r="S129" s="9" t="str">
-        <f aca="false">IF(Q129=0,"No quote",LEFT(IF(AND(ISNUMBER(G129),G129=R129),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I129),I129=R129),"Aslam, ","")&amp;IF(AND(ISNUMBER(K129),K129=R129),"Jamil, ","")&amp;IF(AND(ISNUMBER(M129),M129=R129),"Muller, ","")&amp;IF(AND(ISNUMBER(O129),O129=R129),"NMMC, ",""),LEN(IF(AND(ISNUMBER(G129),G129=R129),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I129),I129=R129),"Aslam, ","")&amp;IF(AND(ISNUMBER(K129),K129=R129),"Jamil, ","")&amp;IF(AND(ISNUMBER(M129),M129=R129),"Muller, ","")&amp;IF(AND(ISNUMBER(O129),O129=R129),"NMMC, ",""))-2))</f>
+      <c r="U129" s="9" t="str">
+        <f aca="false">IF(S129=0,"No quote",LEFT(IF(AND(ISNUMBER(G129),G129=T129),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I129),I129=T129),"Aslam, ","")&amp;IF(AND(ISNUMBER(K129),K129=T129),"Jamil, ","")&amp;IF(AND(ISNUMBER(M129),M129=T129),"Muller, ","")&amp;IF(AND(ISNUMBER(O129),O129=T129),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q129),Q129=T129),"Platinum, ",""),LEN(IF(AND(ISNUMBER(G129),G129=T129),"Ahsan, ","")&amp;IF(AND(ISNUMBER(I129),I129=T129),"Aslam, ","")&amp;IF(AND(ISNUMBER(K129),K129=T129),"Jamil, ","")&amp;IF(AND(ISNUMBER(M129),M129=T129),"Muller, ","")&amp;IF(AND(ISNUMBER(O129),O129=T129),"NMMC, ","")&amp;IF(AND(ISNUMBER(Q129),Q129=T129),"Platinum, ",""))-2))</f>
         <v>Aslam</v>
       </c>
-      <c r="T129" s="10" t="n">
-        <f aca="false">IF(Q129=0,"",R129*F129)</f>
+      <c r="V129" s="10" t="n">
+        <f aca="false">IF(S129=0,"",T129*F129)</f>
         <v>113220</v>
       </c>
-      <c r="U129" s="6" t="s">
-        <v>199</v>
+      <c r="W129" s="6" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="11"/>
       <c r="B130" s="11"/>
       <c r="C130" s="12" t="s">
-        <v>581</v>
+        <v>590</v>
       </c>
       <c r="D130" s="11"/>
       <c r="E130" s="11"/>
@@ -9321,15 +9643,17 @@
       <c r="Q130" s="11"/>
       <c r="R130" s="11"/>
       <c r="S130" s="11"/>
-      <c r="T130" s="13" t="n">
-        <f aca="false">SUM(T6:T129)</f>
-        <v>9027422.4</v>
-      </c>
+      <c r="T130" s="11"/>
       <c r="U130" s="11"/>
+      <c r="V130" s="13" t="n">
+        <f aca="false">SUM(V6:V129)</f>
+        <v>8776293.9</v>
+      </c>
+      <c r="W130" s="11"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:U129"/>
-  <mergeCells count="16">
+  <autoFilter ref="A5:W129"/>
+  <mergeCells count="17">
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="C4:C5"/>
@@ -9341,40 +9665,46 @@
     <mergeCell ref="K4:L4"/>
     <mergeCell ref="M4:N4"/>
     <mergeCell ref="O4:P4"/>
-    <mergeCell ref="Q4:Q5"/>
-    <mergeCell ref="R4:R5"/>
+    <mergeCell ref="Q4:R4"/>
     <mergeCell ref="S4:S5"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="W4:W5"/>
   </mergeCells>
   <conditionalFormatting sqref="G6:H129">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
-      <formula>AND(ISNUMBER($G6),$G6=$R6)</formula>
+      <formula>AND(ISNUMBER($G6),$G6=$T6)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6:J129">
     <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
-      <formula>AND(ISNUMBER($I6),$I6=$R6)</formula>
+      <formula>AND(ISNUMBER($I6),$I6=$T6)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K6:L129">
     <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
-      <formula>AND(ISNUMBER($K6),$K6=$R6)</formula>
+      <formula>AND(ISNUMBER($K6),$K6=$T6)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M6:N129">
     <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
-      <formula>AND(ISNUMBER($M6),$M6=$R6)</formula>
+      <formula>AND(ISNUMBER($M6),$M6=$T6)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O6:P129">
     <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
-      <formula>AND(ISNUMBER($O6),$O6=$R6)</formula>
+      <formula>AND(ISNUMBER($O6),$O6=$T6)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S6:S129">
-    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
-      <formula>$Q6=0</formula>
+  <conditionalFormatting sqref="Q6:R129">
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+      <formula>AND(ISNUMBER($Q6),$Q6=$T6)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U6:U129">
+    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+      <formula>$S6=0</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -9393,7 +9723,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="22"/>
@@ -9401,21 +9731,21 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>582</v>
+        <v>591</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>583</v>
+        <v>592</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>584</v>
+        <v>593</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>585</v>
+        <v>594</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>586</v>
+        <v>595</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9427,11 +9757,11 @@
         <v>45</v>
       </c>
       <c r="C4" s="14" t="n">
-        <f aca="false">COUNTIF(Comparative!$S$6:$S$129,"*Ahsan*")</f>
+        <f aca="false">COUNTIF(Comparative!$U$6:$U$129,"*Ahsan*")</f>
         <v>17</v>
       </c>
       <c r="D4" s="15" t="n">
-        <f aca="false">SUMIF(Comparative!$S$6:$S$129,"*Ahsan*",Comparative!$T$6:$T$129)</f>
+        <f aca="false">SUMIF(Comparative!$U$6:$U$129,"*Ahsan*",Comparative!$V$6:$V$129)</f>
         <v>592087.5</v>
       </c>
     </row>
@@ -9444,12 +9774,12 @@
         <v>40</v>
       </c>
       <c r="C5" s="14" t="n">
-        <f aca="false">COUNTIF(Comparative!$S$6:$S$129,"*Aslam*")</f>
-        <v>17</v>
+        <f aca="false">COUNTIF(Comparative!$U$6:$U$129,"*Aslam*")</f>
+        <v>15</v>
       </c>
       <c r="D5" s="15" t="n">
-        <f aca="false">SUMIF(Comparative!$S$6:$S$129,"*Aslam*",Comparative!$T$6:$T$129)</f>
-        <v>999994.25</v>
+        <f aca="false">SUMIF(Comparative!$U$6:$U$129,"*Aslam*",Comparative!$V$6:$V$129)</f>
+        <v>626325.5</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9461,12 +9791,12 @@
         <v>33</v>
       </c>
       <c r="C6" s="14" t="n">
-        <f aca="false">COUNTIF(Comparative!$S$6:$S$129,"*Jamil*")</f>
-        <v>14</v>
+        <f aca="false">COUNTIF(Comparative!$U$6:$U$129,"*Jamil*")</f>
+        <v>12</v>
       </c>
       <c r="D6" s="15" t="n">
-        <f aca="false">SUMIF(Comparative!$S$6:$S$129,"*Jamil*",Comparative!$T$6:$T$129)</f>
-        <v>812578.6</v>
+        <f aca="false">SUMIF(Comparative!$U$6:$U$129,"*Jamil*",Comparative!$V$6:$V$129)</f>
+        <v>771799.6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9478,12 +9808,12 @@
         <v>56</v>
       </c>
       <c r="C7" s="14" t="n">
-        <f aca="false">COUNTIF(Comparative!$S$6:$S$129,"*Muller*")</f>
-        <v>18</v>
+        <f aca="false">COUNTIF(Comparative!$U$6:$U$129,"*Muller*")</f>
+        <v>17</v>
       </c>
       <c r="D7" s="15" t="n">
-        <f aca="false">SUMIF(Comparative!$S$6:$S$129,"*Muller*",Comparative!$T$6:$T$129)</f>
-        <v>3116891</v>
+        <f aca="false">SUMIF(Comparative!$U$6:$U$129,"*Muller*",Comparative!$V$6:$V$129)</f>
+        <v>3002991</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9495,64 +9825,86 @@
         <v>68</v>
       </c>
       <c r="C8" s="14" t="n">
-        <f aca="false">COUNTIF(Comparative!$S$6:$S$129,"*NMMC*")</f>
+        <f aca="false">COUNTIF(Comparative!$U$6:$U$129,"*NMMC*")</f>
         <v>51</v>
       </c>
       <c r="D8" s="15" t="n">
-        <f aca="false">SUMIF(Comparative!$S$6:$S$129,"*NMMC*",Comparative!$T$6:$T$129)</f>
+        <f aca="false">SUMIF(Comparative!$U$6:$U$129,"*NMMC*",Comparative!$V$6:$V$129)</f>
         <v>3686576.05</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="16" t="s">
-        <v>587</v>
-      </c>
-      <c r="B9" s="16"/>
-      <c r="C9" s="16" t="n">
-        <f aca="false">COUNTIF(Comparative!$S$6:$S$129,"No quote")</f>
-        <v>11</v>
-      </c>
-      <c r="D9" s="16"/>
+      <c r="A9" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="14" t="n">
+        <f aca="false">COUNT(Comparative!Q6:Q129)</f>
+        <v>8</v>
+      </c>
+      <c r="C9" s="14" t="n">
+        <f aca="false">COUNTIF(Comparative!$U$6:$U$129,"*Platinum*")</f>
+        <v>6</v>
+      </c>
+      <c r="D9" s="15" t="n">
+        <f aca="false">SUMIF(Comparative!$U$6:$U$129,"*Platinum*",Comparative!$V$6:$V$129)</f>
+        <v>277219.25</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>588</v>
+        <v>596</v>
       </c>
       <c r="B10" s="16"/>
       <c r="C10" s="16" t="n">
+        <f aca="false">COUNTIF(Comparative!$U$6:$U$129,"No quote")</f>
+        <v>10</v>
+      </c>
+      <c r="D10" s="16"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="16" t="s">
+        <v>597</v>
+      </c>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16" t="n">
         <f aca="false">COUNTA(Comparative!B6:B129)</f>
         <v>124</v>
       </c>
-      <c r="D10" s="16"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="17" t="s">
-        <v>589</v>
-      </c>
+      <c r="D11" s="16"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="18" t="s">
-        <v>590</v>
+      <c r="A13" s="17" t="s">
+        <v>598</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="18" t="s">
-        <v>591</v>
+        <v>599</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="18" t="s">
-        <v>592</v>
+        <v>600</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="18" t="s">
-        <v>593</v>
+        <v>601</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="18" t="s">
-        <v>594</v>
+        <v>602</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="18" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="18" t="s">
+        <v>604</v>
       </c>
     </row>
   </sheetData>

--- a/Quotation_Comparative.xlsx
+++ b/Quotation_Comparative.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Titles" vbProcedure="false">Comparative!$4:$5</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Comparative!$A$5:$W$129</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Comparative!$A$5:$X$129</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="605">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="801" uniqueCount="606">
   <si>
     <t xml:space="preserve">COMPARATIVE STATEMENT OF QUOTATIONS – RFQ (MEDICINES)</t>
   </si>
@@ -82,6 +82,9 @@
   </si>
   <si>
     <t xml:space="preserve">Remarks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brand of Lowest Rate (as quoted)</t>
   </si>
   <si>
     <t xml:space="preserve">Rate</t>
@@ -2396,7 +2399,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:W130"/>
+  <dimension ref="A1:X130"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -2420,7 +2423,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="23" style="0" width="30"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2490,6 +2493,9 @@
       </c>
       <c r="W4" s="3" t="s">
         <v>18</v>
+      </c>
+      <c r="X4" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2500,62 +2506,63 @@
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I5" s="4" t="s">
-        <v>19</v>
-      </c>
       <c r="J5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K5" s="4" t="s">
-        <v>19</v>
-      </c>
       <c r="L5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="M5" s="4" t="s">
-        <v>19</v>
-      </c>
       <c r="N5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="O5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="O5" s="4" t="s">
-        <v>19</v>
-      </c>
       <c r="P5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="Q5" s="4" t="s">
-        <v>19</v>
-      </c>
       <c r="R5" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S5" s="3"/>
       <c r="T5" s="3"/>
       <c r="U5" s="3"/>
       <c r="V5" s="3"/>
       <c r="W5" s="3"/>
+      <c r="X5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="n">
         <v>1</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>200</v>
@@ -2570,7 +2577,7 @@
         <v>5525</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O6" s="7"/>
       <c r="P6" s="6"/>
@@ -2593,22 +2600,26 @@
         <v>1105000</v>
       </c>
       <c r="W6" s="6"/>
+      <c r="X6" s="9" t="str">
+        <f aca="false">IF(S6=0,"",IF(ISNUMBER(SEARCH(",",U6)),LEFT(IF(AND(ISNUMBER(G6),G6=T6),IF(H6="","(brand not stated)",H6)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I6),I6=T6),IF(J6="","(brand not stated)",J6)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K6),K6=T6),IF(L6="","(brand not stated)",L6)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M6),M6=T6),IF(N6="","(brand not stated)",N6)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O6),O6=T6),IF(P6="","(brand not stated)",P6)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q6),Q6=T6),IF(R6="","(brand not stated)",R6)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G6),G6=T6),IF(H6="","(brand not stated)",H6)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I6),I6=T6),IF(J6="","(brand not stated)",J6)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K6),K6=T6),IF(L6="","(brand not stated)",L6)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M6),M6=T6),IF(N6="","(brand not stated)",N6)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O6),O6=T6),IF(P6="","(brand not stated)",P6)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q6),Q6=T6),IF(R6="","(brand not stated)",R6)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G6),G6=T6),IF(H6="","(brand not stated)",H6),"")&amp;IF(AND(ISNUMBER(I6),I6=T6),IF(J6="","(brand not stated)",J6),"")&amp;IF(AND(ISNUMBER(K6),K6=T6),IF(L6="","(brand not stated)",L6),"")&amp;IF(AND(ISNUMBER(M6),M6=T6),IF(N6="","(brand not stated)",N6),"")&amp;IF(AND(ISNUMBER(O6),O6=T6),IF(P6="","(brand not stated)",P6),"")&amp;IF(AND(ISNUMBER(Q6),Q6=T6),IF(R6="","(brand not stated)",R6),"")))</f>
+        <v>ZEPTIDE(FEROZSONS)</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="n">
         <v>2</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>200</v>
@@ -2623,7 +2634,7 @@
         <v>4207.5</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O7" s="7"/>
       <c r="P7" s="6"/>
@@ -2646,22 +2657,26 @@
         <v>841500</v>
       </c>
       <c r="W7" s="6"/>
+      <c r="X7" s="9" t="str">
+        <f aca="false">IF(S7=0,"",IF(ISNUMBER(SEARCH(",",U7)),LEFT(IF(AND(ISNUMBER(G7),G7=T7),IF(H7="","(brand not stated)",H7)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I7),I7=T7),IF(J7="","(brand not stated)",J7)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K7),K7=T7),IF(L7="","(brand not stated)",L7)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M7),M7=T7),IF(N7="","(brand not stated)",N7)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O7),O7=T7),IF(P7="","(brand not stated)",P7)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q7),Q7=T7),IF(R7="","(brand not stated)",R7)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G7),G7=T7),IF(H7="","(brand not stated)",H7)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I7),I7=T7),IF(J7="","(brand not stated)",J7)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K7),K7=T7),IF(L7="","(brand not stated)",L7)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M7),M7=T7),IF(N7="","(brand not stated)",N7)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O7),O7=T7),IF(P7="","(brand not stated)",P7)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q7),Q7=T7),IF(R7="","(brand not stated)",R7)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G7),G7=T7),IF(H7="","(brand not stated)",H7),"")&amp;IF(AND(ISNUMBER(I7),I7=T7),IF(J7="","(brand not stated)",J7),"")&amp;IF(AND(ISNUMBER(K7),K7=T7),IF(L7="","(brand not stated)",L7),"")&amp;IF(AND(ISNUMBER(M7),M7=T7),IF(N7="","(brand not stated)",N7),"")&amp;IF(AND(ISNUMBER(O7),O7=T7),IF(P7="","(brand not stated)",P7),"")&amp;IF(AND(ISNUMBER(Q7),Q7=T7),IF(R7="","(brand not stated)",R7),"")))</f>
+        <v>ZEPTIDE(FEROZSONS)</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="n">
         <v>3</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F8" s="5" t="n">
         <v>100</v>
@@ -2676,7 +2691,7 @@
         <v>3357.5</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O8" s="7"/>
       <c r="P8" s="6"/>
@@ -2699,22 +2714,26 @@
         <v>335750</v>
       </c>
       <c r="W8" s="6"/>
+      <c r="X8" s="9" t="str">
+        <f aca="false">IF(S8=0,"",IF(ISNUMBER(SEARCH(",",U8)),LEFT(IF(AND(ISNUMBER(G8),G8=T8),IF(H8="","(brand not stated)",H8)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I8),I8=T8),IF(J8="","(brand not stated)",J8)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K8),K8=T8),IF(L8="","(brand not stated)",L8)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M8),M8=T8),IF(N8="","(brand not stated)",N8)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O8),O8=T8),IF(P8="","(brand not stated)",P8)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q8),Q8=T8),IF(R8="","(brand not stated)",R8)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G8),G8=T8),IF(H8="","(brand not stated)",H8)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I8),I8=T8),IF(J8="","(brand not stated)",J8)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K8),K8=T8),IF(L8="","(brand not stated)",L8)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M8),M8=T8),IF(N8="","(brand not stated)",N8)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O8),O8=T8),IF(P8="","(brand not stated)",P8)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q8),Q8=T8),IF(R8="","(brand not stated)",R8)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G8),G8=T8),IF(H8="","(brand not stated)",H8),"")&amp;IF(AND(ISNUMBER(I8),I8=T8),IF(J8="","(brand not stated)",J8),"")&amp;IF(AND(ISNUMBER(K8),K8=T8),IF(L8="","(brand not stated)",L8),"")&amp;IF(AND(ISNUMBER(M8),M8=T8),IF(N8="","(brand not stated)",N8),"")&amp;IF(AND(ISNUMBER(O8),O8=T8),IF(P8="","(brand not stated)",P8),"")&amp;IF(AND(ISNUMBER(Q8),Q8=T8),IF(R8="","(brand not stated)",R8),"")))</f>
+        <v>ZEPTIDE(FEROZSONS)</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="n">
         <v>4</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F9" s="5" t="n">
         <v>100</v>
@@ -2729,7 +2748,7 @@
         <v>2507.5</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O9" s="7"/>
       <c r="P9" s="6"/>
@@ -2752,22 +2771,26 @@
         <v>250750</v>
       </c>
       <c r="W9" s="6"/>
+      <c r="X9" s="9" t="str">
+        <f aca="false">IF(S9=0,"",IF(ISNUMBER(SEARCH(",",U9)),LEFT(IF(AND(ISNUMBER(G9),G9=T9),IF(H9="","(brand not stated)",H9)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I9),I9=T9),IF(J9="","(brand not stated)",J9)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K9),K9=T9),IF(L9="","(brand not stated)",L9)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M9),M9=T9),IF(N9="","(brand not stated)",N9)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O9),O9=T9),IF(P9="","(brand not stated)",P9)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q9),Q9=T9),IF(R9="","(brand not stated)",R9)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G9),G9=T9),IF(H9="","(brand not stated)",H9)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I9),I9=T9),IF(J9="","(brand not stated)",J9)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K9),K9=T9),IF(L9="","(brand not stated)",L9)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M9),M9=T9),IF(N9="","(brand not stated)",N9)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O9),O9=T9),IF(P9="","(brand not stated)",P9)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q9),Q9=T9),IF(R9="","(brand not stated)",R9)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G9),G9=T9),IF(H9="","(brand not stated)",H9),"")&amp;IF(AND(ISNUMBER(I9),I9=T9),IF(J9="","(brand not stated)",J9),"")&amp;IF(AND(ISNUMBER(K9),K9=T9),IF(L9="","(brand not stated)",L9),"")&amp;IF(AND(ISNUMBER(M9),M9=T9),IF(N9="","(brand not stated)",N9),"")&amp;IF(AND(ISNUMBER(O9),O9=T9),IF(P9="","(brand not stated)",P9),"")&amp;IF(AND(ISNUMBER(Q9),Q9=T9),IF(R9="","(brand not stated)",R9),"")))</f>
+        <v>ZEPTIDE(FEROZSONS)</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="n">
         <v>5</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>100</v>
@@ -2776,31 +2799,31 @@
         <v>368.9</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I10" s="7" t="n">
         <v>348.5</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K10" s="7" t="n">
         <v>371.28</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M10" s="7" t="n">
         <v>403.55</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O10" s="7" t="n">
         <v>326.4</v>
       </c>
       <c r="P10" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q10" s="7"/>
       <c r="R10" s="6"/>
@@ -2821,22 +2844,26 @@
         <v>32640</v>
       </c>
       <c r="W10" s="6"/>
+      <c r="X10" s="9" t="str">
+        <f aca="false">IF(S10=0,"",IF(ISNUMBER(SEARCH(",",U10)),LEFT(IF(AND(ISNUMBER(G10),G10=T10),IF(H10="","(brand not stated)",H10)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I10),I10=T10),IF(J10="","(brand not stated)",J10)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K10),K10=T10),IF(L10="","(brand not stated)",L10)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M10),M10=T10),IF(N10="","(brand not stated)",N10)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O10),O10=T10),IF(P10="","(brand not stated)",P10)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q10),Q10=T10),IF(R10="","(brand not stated)",R10)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G10),G10=T10),IF(H10="","(brand not stated)",H10)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I10),I10=T10),IF(J10="","(brand not stated)",J10)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K10),K10=T10),IF(L10="","(brand not stated)",L10)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M10),M10=T10),IF(N10="","(brand not stated)",N10)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O10),O10=T10),IF(P10="","(brand not stated)",P10)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q10),Q10=T10),IF(R10="","(brand not stated)",R10)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G10),G10=T10),IF(H10="","(brand not stated)",H10),"")&amp;IF(AND(ISNUMBER(I10),I10=T10),IF(J10="","(brand not stated)",J10),"")&amp;IF(AND(ISNUMBER(K10),K10=T10),IF(L10="","(brand not stated)",L10),"")&amp;IF(AND(ISNUMBER(M10),M10=T10),IF(N10="","(brand not stated)",N10),"")&amp;IF(AND(ISNUMBER(O10),O10=T10),IF(P10="","(brand not stated)",P10),"")&amp;IF(AND(ISNUMBER(Q10),Q10=T10),IF(R10="","(brand not stated)",R10),"")))</f>
+        <v>SOLO 4MG SACHET</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="n">
         <v>6</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F11" s="5" t="n">
         <v>100</v>
@@ -2847,7 +2874,7 @@
         <v>786.25</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K11" s="7"/>
       <c r="L11" s="6"/>
@@ -2855,7 +2882,7 @@
         <v>212.5</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O11" s="7"/>
       <c r="P11" s="6"/>
@@ -2878,7 +2905,11 @@
         <v>21250</v>
       </c>
       <c r="W11" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="X11" s="9" t="str">
+        <f aca="false">IF(S11=0,"",IF(ISNUMBER(SEARCH(",",U11)),LEFT(IF(AND(ISNUMBER(G11),G11=T11),IF(H11="","(brand not stated)",H11)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I11),I11=T11),IF(J11="","(brand not stated)",J11)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K11),K11=T11),IF(L11="","(brand not stated)",L11)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M11),M11=T11),IF(N11="","(brand not stated)",N11)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O11),O11=T11),IF(P11="","(brand not stated)",P11)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q11),Q11=T11),IF(R11="","(brand not stated)",R11)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G11),G11=T11),IF(H11="","(brand not stated)",H11)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I11),I11=T11),IF(J11="","(brand not stated)",J11)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K11),K11=T11),IF(L11="","(brand not stated)",L11)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M11),M11=T11),IF(N11="","(brand not stated)",N11)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O11),O11=T11),IF(P11="","(brand not stated)",P11)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q11),Q11=T11),IF(R11="","(brand not stated)",R11)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G11),G11=T11),IF(H11="","(brand not stated)",H11),"")&amp;IF(AND(ISNUMBER(I11),I11=T11),IF(J11="","(brand not stated)",J11),"")&amp;IF(AND(ISNUMBER(K11),K11=T11),IF(L11="","(brand not stated)",L11),"")&amp;IF(AND(ISNUMBER(M11),M11=T11),IF(N11="","(brand not stated)",N11),"")&amp;IF(AND(ISNUMBER(O11),O11=T11),IF(P11="","(brand not stated)",P11),"")&amp;IF(AND(ISNUMBER(Q11),Q11=T11),IF(R11="","(brand not stated)",R11),"")))</f>
+        <v>ZOFRAN (OBS/AGP)</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2886,16 +2917,16 @@
         <v>7</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F12" s="5" t="n">
         <v>30</v>
@@ -2912,7 +2943,7 @@
         <v>345.02</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q12" s="7"/>
       <c r="R12" s="6"/>
@@ -2933,22 +2964,26 @@
         <v>10350.6</v>
       </c>
       <c r="W12" s="6"/>
+      <c r="X12" s="9" t="str">
+        <f aca="false">IF(S12=0,"",IF(ISNUMBER(SEARCH(",",U12)),LEFT(IF(AND(ISNUMBER(G12),G12=T12),IF(H12="","(brand not stated)",H12)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I12),I12=T12),IF(J12="","(brand not stated)",J12)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K12),K12=T12),IF(L12="","(brand not stated)",L12)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M12),M12=T12),IF(N12="","(brand not stated)",N12)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O12),O12=T12),IF(P12="","(brand not stated)",P12)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q12),Q12=T12),IF(R12="","(brand not stated)",R12)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G12),G12=T12),IF(H12="","(brand not stated)",H12)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I12),I12=T12),IF(J12="","(brand not stated)",J12)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K12),K12=T12),IF(L12="","(brand not stated)",L12)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M12),M12=T12),IF(N12="","(brand not stated)",N12)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O12),O12=T12),IF(P12="","(brand not stated)",P12)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q12),Q12=T12),IF(R12="","(brand not stated)",R12)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G12),G12=T12),IF(H12="","(brand not stated)",H12),"")&amp;IF(AND(ISNUMBER(I12),I12=T12),IF(J12="","(brand not stated)",J12),"")&amp;IF(AND(ISNUMBER(K12),K12=T12),IF(L12="","(brand not stated)",L12),"")&amp;IF(AND(ISNUMBER(M12),M12=T12),IF(N12="","(brand not stated)",N12),"")&amp;IF(AND(ISNUMBER(O12),O12=T12),IF(P12="","(brand not stated)",P12),"")&amp;IF(AND(ISNUMBER(Q12),Q12=T12),IF(R12="","(brand not stated)",R12),"")))</f>
+        <v>IVERMITE 6MG TAB</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="n">
         <v>8</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F13" s="5" t="n">
         <v>100</v>
@@ -2957,19 +2992,19 @@
         <v>80.7</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I13" s="7" t="n">
         <v>115.38</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K13" s="7" t="n">
         <v>101.48</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M13" s="7"/>
       <c r="N13" s="6"/>
@@ -2977,7 +3012,7 @@
         <v>124.45</v>
       </c>
       <c r="P13" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Q13" s="7"/>
       <c r="R13" s="6"/>
@@ -2998,22 +3033,26 @@
         <v>8070</v>
       </c>
       <c r="W13" s="6"/>
+      <c r="X13" s="9" t="str">
+        <f aca="false">IF(S13=0,"",IF(ISNUMBER(SEARCH(",",U13)),LEFT(IF(AND(ISNUMBER(G13),G13=T13),IF(H13="","(brand not stated)",H13)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I13),I13=T13),IF(J13="","(brand not stated)",J13)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K13),K13=T13),IF(L13="","(brand not stated)",L13)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M13),M13=T13),IF(N13="","(brand not stated)",N13)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O13),O13=T13),IF(P13="","(brand not stated)",P13)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q13),Q13=T13),IF(R13="","(brand not stated)",R13)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G13),G13=T13),IF(H13="","(brand not stated)",H13)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I13),I13=T13),IF(J13="","(brand not stated)",J13)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K13),K13=T13),IF(L13="","(brand not stated)",L13)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M13),M13=T13),IF(N13="","(brand not stated)",N13)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O13),O13=T13),IF(P13="","(brand not stated)",P13)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q13),Q13=T13),IF(R13="","(brand not stated)",R13)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G13),G13=T13),IF(H13="","(brand not stated)",H13),"")&amp;IF(AND(ISNUMBER(I13),I13=T13),IF(J13="","(brand not stated)",J13),"")&amp;IF(AND(ISNUMBER(K13),K13=T13),IF(L13="","(brand not stated)",L13),"")&amp;IF(AND(ISNUMBER(M13),M13=T13),IF(N13="","(brand not stated)",N13),"")&amp;IF(AND(ISNUMBER(O13),O13=T13),IF(P13="","(brand not stated)",P13),"")&amp;IF(AND(ISNUMBER(Q13),Q13=T13),IF(R13="","(brand not stated)",R13),"")))</f>
+        <v>FEBROL-DS</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="n">
         <v>9</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F14" s="5" t="n">
         <v>100</v>
@@ -3047,22 +3086,26 @@
         <v/>
       </c>
       <c r="W14" s="6"/>
+      <c r="X14" s="9" t="str">
+        <f aca="false">IF(S14=0,"",IF(ISNUMBER(SEARCH(",",U14)),LEFT(IF(AND(ISNUMBER(G14),G14=T14),IF(H14="","(brand not stated)",H14)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I14),I14=T14),IF(J14="","(brand not stated)",J14)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K14),K14=T14),IF(L14="","(brand not stated)",L14)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M14),M14=T14),IF(N14="","(brand not stated)",N14)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O14),O14=T14),IF(P14="","(brand not stated)",P14)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q14),Q14=T14),IF(R14="","(brand not stated)",R14)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G14),G14=T14),IF(H14="","(brand not stated)",H14)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I14),I14=T14),IF(J14="","(brand not stated)",J14)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K14),K14=T14),IF(L14="","(brand not stated)",L14)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M14),M14=T14),IF(N14="","(brand not stated)",N14)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O14),O14=T14),IF(P14="","(brand not stated)",P14)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q14),Q14=T14),IF(R14="","(brand not stated)",R14)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G14),G14=T14),IF(H14="","(brand not stated)",H14),"")&amp;IF(AND(ISNUMBER(I14),I14=T14),IF(J14="","(brand not stated)",J14),"")&amp;IF(AND(ISNUMBER(K14),K14=T14),IF(L14="","(brand not stated)",L14),"")&amp;IF(AND(ISNUMBER(M14),M14=T14),IF(N14="","(brand not stated)",N14),"")&amp;IF(AND(ISNUMBER(O14),O14=T14),IF(P14="","(brand not stated)",P14),"")&amp;IF(AND(ISNUMBER(Q14),Q14=T14),IF(R14="","(brand not stated)",R14),"")))</f>
+        <v/>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="n">
         <v>10</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F15" s="5" t="n">
         <v>100</v>
@@ -3075,7 +3118,7 @@
         <v>301.55</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M15" s="7"/>
       <c r="N15" s="6"/>
@@ -3100,22 +3143,26 @@
         <v>30155</v>
       </c>
       <c r="W15" s="6"/>
+      <c r="X15" s="9" t="str">
+        <f aca="false">IF(S15=0,"",IF(ISNUMBER(SEARCH(",",U15)),LEFT(IF(AND(ISNUMBER(G15),G15=T15),IF(H15="","(brand not stated)",H15)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I15),I15=T15),IF(J15="","(brand not stated)",J15)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K15),K15=T15),IF(L15="","(brand not stated)",L15)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M15),M15=T15),IF(N15="","(brand not stated)",N15)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O15),O15=T15),IF(P15="","(brand not stated)",P15)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q15),Q15=T15),IF(R15="","(brand not stated)",R15)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G15),G15=T15),IF(H15="","(brand not stated)",H15)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I15),I15=T15),IF(J15="","(brand not stated)",J15)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K15),K15=T15),IF(L15="","(brand not stated)",L15)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M15),M15=T15),IF(N15="","(brand not stated)",N15)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O15),O15=T15),IF(P15="","(brand not stated)",P15)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q15),Q15=T15),IF(R15="","(brand not stated)",R15)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G15),G15=T15),IF(H15="","(brand not stated)",H15),"")&amp;IF(AND(ISNUMBER(I15),I15=T15),IF(J15="","(brand not stated)",J15),"")&amp;IF(AND(ISNUMBER(K15),K15=T15),IF(L15="","(brand not stated)",L15),"")&amp;IF(AND(ISNUMBER(M15),M15=T15),IF(N15="","(brand not stated)",N15),"")&amp;IF(AND(ISNUMBER(O15),O15=T15),IF(P15="","(brand not stated)",P15),"")&amp;IF(AND(ISNUMBER(Q15),Q15=T15),IF(R15="","(brand not stated)",R15),"")))</f>
+        <v>CUTIVATE OINT</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="n">
         <v>11</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F16" s="5" t="n">
         <v>200</v>
@@ -3124,13 +3171,13 @@
         <v>195.5</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I16" s="7" t="n">
         <v>212.5</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K16" s="7"/>
       <c r="L16" s="6"/>
@@ -3140,7 +3187,7 @@
         <v>135</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q16" s="7"/>
       <c r="R16" s="6"/>
@@ -3161,22 +3208,26 @@
         <v>27000</v>
       </c>
       <c r="W16" s="6"/>
+      <c r="X16" s="9" t="str">
+        <f aca="false">IF(S16=0,"",IF(ISNUMBER(SEARCH(",",U16)),LEFT(IF(AND(ISNUMBER(G16),G16=T16),IF(H16="","(brand not stated)",H16)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I16),I16=T16),IF(J16="","(brand not stated)",J16)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K16),K16=T16),IF(L16="","(brand not stated)",L16)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M16),M16=T16),IF(N16="","(brand not stated)",N16)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O16),O16=T16),IF(P16="","(brand not stated)",P16)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q16),Q16=T16),IF(R16="","(brand not stated)",R16)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G16),G16=T16),IF(H16="","(brand not stated)",H16)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I16),I16=T16),IF(J16="","(brand not stated)",J16)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K16),K16=T16),IF(L16="","(brand not stated)",L16)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M16),M16=T16),IF(N16="","(brand not stated)",N16)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O16),O16=T16),IF(P16="","(brand not stated)",P16)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q16),Q16=T16),IF(R16="","(brand not stated)",R16)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G16),G16=T16),IF(H16="","(brand not stated)",H16),"")&amp;IF(AND(ISNUMBER(I16),I16=T16),IF(J16="","(brand not stated)",J16),"")&amp;IF(AND(ISNUMBER(K16),K16=T16),IF(L16="","(brand not stated)",L16),"")&amp;IF(AND(ISNUMBER(M16),M16=T16),IF(N16="","(brand not stated)",N16),"")&amp;IF(AND(ISNUMBER(O16),O16=T16),IF(P16="","(brand not stated)",P16),"")&amp;IF(AND(ISNUMBER(Q16),Q16=T16),IF(R16="","(brand not stated)",R16),"")))</f>
+        <v>NUBEROL P 100ML INJ</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="n">
         <v>12</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F17" s="5" t="n">
         <v>200</v>
@@ -3189,7 +3240,7 @@
         <v>272</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M17" s="7"/>
       <c r="N17" s="6"/>
@@ -3197,7 +3248,7 @@
         <v>279.898</v>
       </c>
       <c r="P17" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q17" s="7"/>
       <c r="R17" s="6"/>
@@ -3218,22 +3269,26 @@
         <v>54400</v>
       </c>
       <c r="W17" s="6"/>
+      <c r="X17" s="9" t="str">
+        <f aca="false">IF(S17=0,"",IF(ISNUMBER(SEARCH(",",U17)),LEFT(IF(AND(ISNUMBER(G17),G17=T17),IF(H17="","(brand not stated)",H17)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I17),I17=T17),IF(J17="","(brand not stated)",J17)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K17),K17=T17),IF(L17="","(brand not stated)",L17)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M17),M17=T17),IF(N17="","(brand not stated)",N17)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O17),O17=T17),IF(P17="","(brand not stated)",P17)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q17),Q17=T17),IF(R17="","(brand not stated)",R17)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G17),G17=T17),IF(H17="","(brand not stated)",H17)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I17),I17=T17),IF(J17="","(brand not stated)",J17)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K17),K17=T17),IF(L17="","(brand not stated)",L17)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M17),M17=T17),IF(N17="","(brand not stated)",N17)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O17),O17=T17),IF(P17="","(brand not stated)",P17)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q17),Q17=T17),IF(R17="","(brand not stated)",R17)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G17),G17=T17),IF(H17="","(brand not stated)",H17),"")&amp;IF(AND(ISNUMBER(I17),I17=T17),IF(J17="","(brand not stated)",J17),"")&amp;IF(AND(ISNUMBER(K17),K17=T17),IF(L17="","(brand not stated)",L17),"")&amp;IF(AND(ISNUMBER(M17),M17=T17),IF(N17="","(brand not stated)",N17),"")&amp;IF(AND(ISNUMBER(O17),O17=T17),IF(P17="","(brand not stated)",P17),"")&amp;IF(AND(ISNUMBER(Q17),Q17=T17),IF(R17="","(brand not stated)",R17),"")))</f>
+        <v>VIDAYLIN L SYP</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="n">
         <v>13</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F18" s="5" t="n">
         <v>200</v>
@@ -3244,7 +3299,7 @@
         <v>175.95</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K18" s="7"/>
       <c r="L18" s="6"/>
@@ -3271,22 +3326,26 @@
         <v>35190</v>
       </c>
       <c r="W18" s="6"/>
+      <c r="X18" s="9" t="str">
+        <f aca="false">IF(S18=0,"",IF(ISNUMBER(SEARCH(",",U18)),LEFT(IF(AND(ISNUMBER(G18),G18=T18),IF(H18="","(brand not stated)",H18)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I18),I18=T18),IF(J18="","(brand not stated)",J18)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K18),K18=T18),IF(L18="","(brand not stated)",L18)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M18),M18=T18),IF(N18="","(brand not stated)",N18)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O18),O18=T18),IF(P18="","(brand not stated)",P18)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q18),Q18=T18),IF(R18="","(brand not stated)",R18)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G18),G18=T18),IF(H18="","(brand not stated)",H18)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I18),I18=T18),IF(J18="","(brand not stated)",J18)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K18),K18=T18),IF(L18="","(brand not stated)",L18)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M18),M18=T18),IF(N18="","(brand not stated)",N18)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O18),O18=T18),IF(P18="","(brand not stated)",P18)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q18),Q18=T18),IF(R18="","(brand not stated)",R18)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G18),G18=T18),IF(H18="","(brand not stated)",H18),"")&amp;IF(AND(ISNUMBER(I18),I18=T18),IF(J18="","(brand not stated)",J18),"")&amp;IF(AND(ISNUMBER(K18),K18=T18),IF(L18="","(brand not stated)",L18),"")&amp;IF(AND(ISNUMBER(M18),M18=T18),IF(N18="","(brand not stated)",N18),"")&amp;IF(AND(ISNUMBER(O18),O18=T18),IF(P18="","(brand not stated)",P18),"")&amp;IF(AND(ISNUMBER(Q18),Q18=T18),IF(R18="","(brand not stated)",R18),"")))</f>
+        <v>Schazoo</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="n">
         <v>14</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F19" s="5" t="n">
         <v>50</v>
@@ -3303,7 +3362,7 @@
         <v>316.2</v>
       </c>
       <c r="P19" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q19" s="7"/>
       <c r="R19" s="6"/>
@@ -3324,22 +3383,26 @@
         <v>15810</v>
       </c>
       <c r="W19" s="6"/>
+      <c r="X19" s="9" t="str">
+        <f aca="false">IF(S19=0,"",IF(ISNUMBER(SEARCH(",",U19)),LEFT(IF(AND(ISNUMBER(G19),G19=T19),IF(H19="","(brand not stated)",H19)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I19),I19=T19),IF(J19="","(brand not stated)",J19)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K19),K19=T19),IF(L19="","(brand not stated)",L19)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M19),M19=T19),IF(N19="","(brand not stated)",N19)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O19),O19=T19),IF(P19="","(brand not stated)",P19)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q19),Q19=T19),IF(R19="","(brand not stated)",R19)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G19),G19=T19),IF(H19="","(brand not stated)",H19)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I19),I19=T19),IF(J19="","(brand not stated)",J19)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K19),K19=T19),IF(L19="","(brand not stated)",L19)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M19),M19=T19),IF(N19="","(brand not stated)",N19)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O19),O19=T19),IF(P19="","(brand not stated)",P19)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q19),Q19=T19),IF(R19="","(brand not stated)",R19)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G19),G19=T19),IF(H19="","(brand not stated)",H19),"")&amp;IF(AND(ISNUMBER(I19),I19=T19),IF(J19="","(brand not stated)",J19),"")&amp;IF(AND(ISNUMBER(K19),K19=T19),IF(L19="","(brand not stated)",L19),"")&amp;IF(AND(ISNUMBER(M19),M19=T19),IF(N19="","(brand not stated)",N19),"")&amp;IF(AND(ISNUMBER(O19),O19=T19),IF(P19="","(brand not stated)",P19),"")&amp;IF(AND(ISNUMBER(Q19),Q19=T19),IF(R19="","(brand not stated)",R19),"")))</f>
+        <v>ERTUCO-M 2.5/500MG TAB</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="n">
         <v>15</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F20" s="5" t="n">
         <v>300</v>
@@ -3348,7 +3411,7 @@
         <v>620.5</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I20" s="7"/>
       <c r="J20" s="6"/>
@@ -3358,13 +3421,13 @@
         <v>403.75</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O20" s="7" t="n">
         <v>355.536</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q20" s="7"/>
       <c r="R20" s="6"/>
@@ -3385,22 +3448,26 @@
         <v>106660.8</v>
       </c>
       <c r="W20" s="6"/>
+      <c r="X20" s="9" t="str">
+        <f aca="false">IF(S20=0,"",IF(ISNUMBER(SEARCH(",",U20)),LEFT(IF(AND(ISNUMBER(G20),G20=T20),IF(H20="","(brand not stated)",H20)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I20),I20=T20),IF(J20="","(brand not stated)",J20)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K20),K20=T20),IF(L20="","(brand not stated)",L20)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M20),M20=T20),IF(N20="","(brand not stated)",N20)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O20),O20=T20),IF(P20="","(brand not stated)",P20)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q20),Q20=T20),IF(R20="","(brand not stated)",R20)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G20),G20=T20),IF(H20="","(brand not stated)",H20)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I20),I20=T20),IF(J20="","(brand not stated)",J20)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K20),K20=T20),IF(L20="","(brand not stated)",L20)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M20),M20=T20),IF(N20="","(brand not stated)",N20)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O20),O20=T20),IF(P20="","(brand not stated)",P20)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q20),Q20=T20),IF(R20="","(brand not stated)",R20)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G20),G20=T20),IF(H20="","(brand not stated)",H20),"")&amp;IF(AND(ISNUMBER(I20),I20=T20),IF(J20="","(brand not stated)",J20),"")&amp;IF(AND(ISNUMBER(K20),K20=T20),IF(L20="","(brand not stated)",L20),"")&amp;IF(AND(ISNUMBER(M20),M20=T20),IF(N20="","(brand not stated)",N20),"")&amp;IF(AND(ISNUMBER(O20),O20=T20),IF(P20="","(brand not stated)",P20),"")&amp;IF(AND(ISNUMBER(Q20),Q20=T20),IF(R20="","(brand not stated)",R20),"")))</f>
+        <v>EFIX 400MG CAPSULE</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="n">
         <v>16</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F21" s="5" t="n">
         <v>1000</v>
@@ -3409,7 +3476,7 @@
         <v>425.85</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I21" s="7"/>
       <c r="J21" s="6"/>
@@ -3419,13 +3486,13 @@
         <v>306</v>
       </c>
       <c r="N21" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O21" s="7" t="n">
         <v>287.81</v>
       </c>
       <c r="P21" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q21" s="7"/>
       <c r="R21" s="6"/>
@@ -3446,22 +3513,26 @@
         <v>287810</v>
       </c>
       <c r="W21" s="6"/>
+      <c r="X21" s="9" t="str">
+        <f aca="false">IF(S21=0,"",IF(ISNUMBER(SEARCH(",",U21)),LEFT(IF(AND(ISNUMBER(G21),G21=T21),IF(H21="","(brand not stated)",H21)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I21),I21=T21),IF(J21="","(brand not stated)",J21)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K21),K21=T21),IF(L21="","(brand not stated)",L21)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M21),M21=T21),IF(N21="","(brand not stated)",N21)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O21),O21=T21),IF(P21="","(brand not stated)",P21)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q21),Q21=T21),IF(R21="","(brand not stated)",R21)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G21),G21=T21),IF(H21="","(brand not stated)",H21)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I21),I21=T21),IF(J21="","(brand not stated)",J21)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K21),K21=T21),IF(L21="","(brand not stated)",L21)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M21),M21=T21),IF(N21="","(brand not stated)",N21)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O21),O21=T21),IF(P21="","(brand not stated)",P21)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q21),Q21=T21),IF(R21="","(brand not stated)",R21)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G21),G21=T21),IF(H21="","(brand not stated)",H21),"")&amp;IF(AND(ISNUMBER(I21),I21=T21),IF(J21="","(brand not stated)",J21),"")&amp;IF(AND(ISNUMBER(K21),K21=T21),IF(L21="","(brand not stated)",L21),"")&amp;IF(AND(ISNUMBER(M21),M21=T21),IF(N21="","(brand not stated)",N21),"")&amp;IF(AND(ISNUMBER(O21),O21=T21),IF(P21="","(brand not stated)",P21),"")&amp;IF(AND(ISNUMBER(Q21),Q21=T21),IF(R21="","(brand not stated)",R21),"")))</f>
+        <v>FIXICEF DS 200 MG 30ML SYRUP</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="n">
         <v>17</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F22" s="5" t="n">
         <v>100</v>
@@ -3470,7 +3541,7 @@
         <v>127.5</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I22" s="7"/>
       <c r="J22" s="6"/>
@@ -3480,13 +3551,13 @@
         <v>212.5</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O22" s="7" t="n">
         <v>115.6</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Q22" s="7"/>
       <c r="R22" s="6"/>
@@ -3507,22 +3578,26 @@
         <v>11560</v>
       </c>
       <c r="W22" s="6"/>
+      <c r="X22" s="9" t="str">
+        <f aca="false">IF(S22=0,"",IF(ISNUMBER(SEARCH(",",U22)),LEFT(IF(AND(ISNUMBER(G22),G22=T22),IF(H22="","(brand not stated)",H22)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I22),I22=T22),IF(J22="","(brand not stated)",J22)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K22),K22=T22),IF(L22="","(brand not stated)",L22)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M22),M22=T22),IF(N22="","(brand not stated)",N22)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O22),O22=T22),IF(P22="","(brand not stated)",P22)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q22),Q22=T22),IF(R22="","(brand not stated)",R22)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G22),G22=T22),IF(H22="","(brand not stated)",H22)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I22),I22=T22),IF(J22="","(brand not stated)",J22)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K22),K22=T22),IF(L22="","(brand not stated)",L22)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M22),M22=T22),IF(N22="","(brand not stated)",N22)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O22),O22=T22),IF(P22="","(brand not stated)",P22)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q22),Q22=T22),IF(R22="","(brand not stated)",R22)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G22),G22=T22),IF(H22="","(brand not stated)",H22),"")&amp;IF(AND(ISNUMBER(I22),I22=T22),IF(J22="","(brand not stated)",J22),"")&amp;IF(AND(ISNUMBER(K22),K22=T22),IF(L22="","(brand not stated)",L22),"")&amp;IF(AND(ISNUMBER(M22),M22=T22),IF(N22="","(brand not stated)",N22),"")&amp;IF(AND(ISNUMBER(O22),O22=T22),IF(P22="","(brand not stated)",P22),"")&amp;IF(AND(ISNUMBER(Q22),Q22=T22),IF(R22="","(brand not stated)",R22),"")))</f>
+        <v>UBKINO 50ML SYRUP</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="n">
         <v>18</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F23" s="5" t="n">
         <v>500</v>
@@ -3539,13 +3614,13 @@
         <v>348.5</v>
       </c>
       <c r="N23" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O23" s="7" t="n">
         <v>164.543</v>
       </c>
       <c r="P23" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q23" s="7"/>
       <c r="R23" s="6"/>
@@ -3566,22 +3641,26 @@
         <v>82271.5</v>
       </c>
       <c r="W23" s="6"/>
+      <c r="X23" s="9" t="str">
+        <f aca="false">IF(S23=0,"",IF(ISNUMBER(SEARCH(",",U23)),LEFT(IF(AND(ISNUMBER(G23),G23=T23),IF(H23="","(brand not stated)",H23)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I23),I23=T23),IF(J23="","(brand not stated)",J23)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K23),K23=T23),IF(L23="","(brand not stated)",L23)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M23),M23=T23),IF(N23="","(brand not stated)",N23)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O23),O23=T23),IF(P23="","(brand not stated)",P23)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q23),Q23=T23),IF(R23="","(brand not stated)",R23)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G23),G23=T23),IF(H23="","(brand not stated)",H23)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I23),I23=T23),IF(J23="","(brand not stated)",J23)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K23),K23=T23),IF(L23="","(brand not stated)",L23)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M23),M23=T23),IF(N23="","(brand not stated)",N23)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O23),O23=T23),IF(P23="","(brand not stated)",P23)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q23),Q23=T23),IF(R23="","(brand not stated)",R23)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G23),G23=T23),IF(H23="","(brand not stated)",H23),"")&amp;IF(AND(ISNUMBER(I23),I23=T23),IF(J23="","(brand not stated)",J23),"")&amp;IF(AND(ISNUMBER(K23),K23=T23),IF(L23="","(brand not stated)",L23),"")&amp;IF(AND(ISNUMBER(M23),M23=T23),IF(N23="","(brand not stated)",N23),"")&amp;IF(AND(ISNUMBER(O23),O23=T23),IF(P23="","(brand not stated)",P23),"")&amp;IF(AND(ISNUMBER(Q23),Q23=T23),IF(R23="","(brand not stated)",R23),"")))</f>
+        <v>AZIPOS 200MG 15ML SYRUP</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="n">
         <v>19</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F24" s="5" t="n">
         <v>100</v>
@@ -3590,7 +3669,7 @@
         <v>1015.75</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I24" s="7"/>
       <c r="J24" s="6"/>
@@ -3602,7 +3681,7 @@
         <v>294.53</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q24" s="7"/>
       <c r="R24" s="6"/>
@@ -3623,22 +3702,26 @@
         <v>29453</v>
       </c>
       <c r="W24" s="6"/>
+      <c r="X24" s="9" t="str">
+        <f aca="false">IF(S24=0,"",IF(ISNUMBER(SEARCH(",",U24)),LEFT(IF(AND(ISNUMBER(G24),G24=T24),IF(H24="","(brand not stated)",H24)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I24),I24=T24),IF(J24="","(brand not stated)",J24)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K24),K24=T24),IF(L24="","(brand not stated)",L24)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M24),M24=T24),IF(N24="","(brand not stated)",N24)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O24),O24=T24),IF(P24="","(brand not stated)",P24)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q24),Q24=T24),IF(R24="","(brand not stated)",R24)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G24),G24=T24),IF(H24="","(brand not stated)",H24)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I24),I24=T24),IF(J24="","(brand not stated)",J24)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K24),K24=T24),IF(L24="","(brand not stated)",L24)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M24),M24=T24),IF(N24="","(brand not stated)",N24)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O24),O24=T24),IF(P24="","(brand not stated)",P24)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q24),Q24=T24),IF(R24="","(brand not stated)",R24)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G24),G24=T24),IF(H24="","(brand not stated)",H24),"")&amp;IF(AND(ISNUMBER(I24),I24=T24),IF(J24="","(brand not stated)",J24),"")&amp;IF(AND(ISNUMBER(K24),K24=T24),IF(L24="","(brand not stated)",L24),"")&amp;IF(AND(ISNUMBER(M24),M24=T24),IF(N24="","(brand not stated)",N24),"")&amp;IF(AND(ISNUMBER(O24),O24=T24),IF(P24="","(brand not stated)",P24),"")&amp;IF(AND(ISNUMBER(Q24),Q24=T24),IF(R24="","(brand not stated)",R24),"")))</f>
+        <v>ATCODAP 10MG TABLET</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="n">
         <v>20</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F25" s="5" t="n">
         <v>300</v>
@@ -3647,7 +3730,7 @@
         <v>348.5</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I25" s="7"/>
       <c r="J25" s="6"/>
@@ -3657,13 +3740,13 @@
         <v>291.04</v>
       </c>
       <c r="N25" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O25" s="7" t="n">
         <v>152.405</v>
       </c>
       <c r="P25" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q25" s="7"/>
       <c r="R25" s="6"/>
@@ -3684,22 +3767,26 @@
         <v>45721.5</v>
       </c>
       <c r="W25" s="6"/>
+      <c r="X25" s="9" t="str">
+        <f aca="false">IF(S25=0,"",IF(ISNUMBER(SEARCH(",",U25)),LEFT(IF(AND(ISNUMBER(G25),G25=T25),IF(H25="","(brand not stated)",H25)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I25),I25=T25),IF(J25="","(brand not stated)",J25)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K25),K25=T25),IF(L25="","(brand not stated)",L25)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M25),M25=T25),IF(N25="","(brand not stated)",N25)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O25),O25=T25),IF(P25="","(brand not stated)",P25)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q25),Q25=T25),IF(R25="","(brand not stated)",R25)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G25),G25=T25),IF(H25="","(brand not stated)",H25)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I25),I25=T25),IF(J25="","(brand not stated)",J25)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K25),K25=T25),IF(L25="","(brand not stated)",L25)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M25),M25=T25),IF(N25="","(brand not stated)",N25)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O25),O25=T25),IF(P25="","(brand not stated)",P25)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q25),Q25=T25),IF(R25="","(brand not stated)",R25)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G25),G25=T25),IF(H25="","(brand not stated)",H25),"")&amp;IF(AND(ISNUMBER(I25),I25=T25),IF(J25="","(brand not stated)",J25),"")&amp;IF(AND(ISNUMBER(K25),K25=T25),IF(L25="","(brand not stated)",L25),"")&amp;IF(AND(ISNUMBER(M25),M25=T25),IF(N25="","(brand not stated)",N25),"")&amp;IF(AND(ISNUMBER(O25),O25=T25),IF(P25="","(brand not stated)",P25),"")&amp;IF(AND(ISNUMBER(Q25),Q25=T25),IF(R25="","(brand not stated)",R25),"")))</f>
+        <v>MOBLO 500MCG TABLET</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="n">
         <v>21</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F26" s="5" t="n">
         <v>35</v>
@@ -3710,7 +3797,7 @@
         <v>578</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K26" s="7"/>
       <c r="L26" s="6"/>
@@ -3718,13 +3805,13 @@
         <v>509.32</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O26" s="7" t="n">
         <v>387.6</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q26" s="7"/>
       <c r="R26" s="6"/>
@@ -3745,22 +3832,26 @@
         <v>13566</v>
       </c>
       <c r="W26" s="6"/>
+      <c r="X26" s="9" t="str">
+        <f aca="false">IF(S26=0,"",IF(ISNUMBER(SEARCH(",",U26)),LEFT(IF(AND(ISNUMBER(G26),G26=T26),IF(H26="","(brand not stated)",H26)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I26),I26=T26),IF(J26="","(brand not stated)",J26)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K26),K26=T26),IF(L26="","(brand not stated)",L26)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M26),M26=T26),IF(N26="","(brand not stated)",N26)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O26),O26=T26),IF(P26="","(brand not stated)",P26)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q26),Q26=T26),IF(R26="","(brand not stated)",R26)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G26),G26=T26),IF(H26="","(brand not stated)",H26)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I26),I26=T26),IF(J26="","(brand not stated)",J26)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K26),K26=T26),IF(L26="","(brand not stated)",L26)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M26),M26=T26),IF(N26="","(brand not stated)",N26)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O26),O26=T26),IF(P26="","(brand not stated)",P26)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q26),Q26=T26),IF(R26="","(brand not stated)",R26)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G26),G26=T26),IF(H26="","(brand not stated)",H26),"")&amp;IF(AND(ISNUMBER(I26),I26=T26),IF(J26="","(brand not stated)",J26),"")&amp;IF(AND(ISNUMBER(K26),K26=T26),IF(L26="","(brand not stated)",L26),"")&amp;IF(AND(ISNUMBER(M26),M26=T26),IF(N26="","(brand not stated)",N26),"")&amp;IF(AND(ISNUMBER(O26),O26=T26),IF(P26="","(brand not stated)",P26),"")&amp;IF(AND(ISNUMBER(Q26),Q26=T26),IF(R26="","(brand not stated)",R26),"")))</f>
+        <v>BIFORGE 10/160MG TABLET</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="n">
         <v>22</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F27" s="5" t="n">
         <v>50</v>
@@ -3769,7 +3860,7 @@
         <v>403.75</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I27" s="7"/>
       <c r="J27" s="6"/>
@@ -3779,13 +3870,13 @@
         <v>516.757</v>
       </c>
       <c r="N27" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O27" s="7" t="n">
         <v>267.75</v>
       </c>
       <c r="P27" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q27" s="7"/>
       <c r="R27" s="6"/>
@@ -3806,22 +3897,26 @@
         <v>13387.5</v>
       </c>
       <c r="W27" s="6"/>
+      <c r="X27" s="9" t="str">
+        <f aca="false">IF(S27=0,"",IF(ISNUMBER(SEARCH(",",U27)),LEFT(IF(AND(ISNUMBER(G27),G27=T27),IF(H27="","(brand not stated)",H27)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I27),I27=T27),IF(J27="","(brand not stated)",J27)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K27),K27=T27),IF(L27="","(brand not stated)",L27)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M27),M27=T27),IF(N27="","(brand not stated)",N27)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O27),O27=T27),IF(P27="","(brand not stated)",P27)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q27),Q27=T27),IF(R27="","(brand not stated)",R27)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G27),G27=T27),IF(H27="","(brand not stated)",H27)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I27),I27=T27),IF(J27="","(brand not stated)",J27)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K27),K27=T27),IF(L27="","(brand not stated)",L27)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M27),M27=T27),IF(N27="","(brand not stated)",N27)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O27),O27=T27),IF(P27="","(brand not stated)",P27)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q27),Q27=T27),IF(R27="","(brand not stated)",R27)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G27),G27=T27),IF(H27="","(brand not stated)",H27),"")&amp;IF(AND(ISNUMBER(I27),I27=T27),IF(J27="","(brand not stated)",J27),"")&amp;IF(AND(ISNUMBER(K27),K27=T27),IF(L27="","(brand not stated)",L27),"")&amp;IF(AND(ISNUMBER(M27),M27=T27),IF(N27="","(brand not stated)",N27),"")&amp;IF(AND(ISNUMBER(O27),O27=T27),IF(P27="","(brand not stated)",P27),"")&amp;IF(AND(ISNUMBER(Q27),Q27=T27),IF(R27="","(brand not stated)",R27),"")))</f>
+        <v>HILORIC 40MG TABLET</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="n">
         <v>23</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F28" s="5" t="n">
         <v>1000</v>
@@ -3830,31 +3925,31 @@
         <v>408</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I28" s="7" t="n">
         <v>425</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K28" s="7" t="n">
         <v>333.2</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M28" s="7" t="n">
         <v>357</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O28" s="7" t="n">
         <v>306</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q28" s="7"/>
       <c r="R28" s="6"/>
@@ -3875,7 +3970,11 @@
         <v>306000</v>
       </c>
       <c r="W28" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
+      </c>
+      <c r="X28" s="9" t="str">
+        <f aca="false">IF(S28=0,"",IF(ISNUMBER(SEARCH(",",U28)),LEFT(IF(AND(ISNUMBER(G28),G28=T28),IF(H28="","(brand not stated)",H28)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I28),I28=T28),IF(J28="","(brand not stated)",J28)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K28),K28=T28),IF(L28="","(brand not stated)",L28)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M28),M28=T28),IF(N28="","(brand not stated)",N28)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O28),O28=T28),IF(P28="","(brand not stated)",P28)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q28),Q28=T28),IF(R28="","(brand not stated)",R28)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G28),G28=T28),IF(H28="","(brand not stated)",H28)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I28),I28=T28),IF(J28="","(brand not stated)",J28)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K28),K28=T28),IF(L28="","(brand not stated)",L28)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M28),M28=T28),IF(N28="","(brand not stated)",N28)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O28),O28=T28),IF(P28="","(brand not stated)",P28)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q28),Q28=T28),IF(R28="","(brand not stated)",R28)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G28),G28=T28),IF(H28="","(brand not stated)",H28),"")&amp;IF(AND(ISNUMBER(I28),I28=T28),IF(J28="","(brand not stated)",J28),"")&amp;IF(AND(ISNUMBER(K28),K28=T28),IF(L28="","(brand not stated)",L28),"")&amp;IF(AND(ISNUMBER(M28),M28=T28),IF(N28="","(brand not stated)",N28),"")&amp;IF(AND(ISNUMBER(O28),O28=T28),IF(P28="","(brand not stated)",P28),"")&amp;IF(AND(ISNUMBER(Q28),Q28=T28),IF(R28="","(brand not stated)",R28),"")))</f>
+        <v>SOLO 10MG TABLET</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3883,16 +3982,16 @@
         <v>24</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F29" s="5" t="n">
         <v>300</v>
@@ -3905,19 +4004,19 @@
         <v>245.48</v>
       </c>
       <c r="L29" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="M29" s="7" t="n">
         <v>261.8</v>
       </c>
       <c r="N29" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O29" s="7" t="n">
         <v>111.69</v>
       </c>
       <c r="P29" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q29" s="7"/>
       <c r="R29" s="6"/>
@@ -3938,22 +4037,26 @@
         <v>33507</v>
       </c>
       <c r="W29" s="6"/>
+      <c r="X29" s="9" t="str">
+        <f aca="false">IF(S29=0,"",IF(ISNUMBER(SEARCH(",",U29)),LEFT(IF(AND(ISNUMBER(G29),G29=T29),IF(H29="","(brand not stated)",H29)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I29),I29=T29),IF(J29="","(brand not stated)",J29)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K29),K29=T29),IF(L29="","(brand not stated)",L29)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M29),M29=T29),IF(N29="","(brand not stated)",N29)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O29),O29=T29),IF(P29="","(brand not stated)",P29)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q29),Q29=T29),IF(R29="","(brand not stated)",R29)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G29),G29=T29),IF(H29="","(brand not stated)",H29)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I29),I29=T29),IF(J29="","(brand not stated)",J29)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K29),K29=T29),IF(L29="","(brand not stated)",L29)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M29),M29=T29),IF(N29="","(brand not stated)",N29)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O29),O29=T29),IF(P29="","(brand not stated)",P29)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q29),Q29=T29),IF(R29="","(brand not stated)",R29)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G29),G29=T29),IF(H29="","(brand not stated)",H29),"")&amp;IF(AND(ISNUMBER(I29),I29=T29),IF(J29="","(brand not stated)",J29),"")&amp;IF(AND(ISNUMBER(K29),K29=T29),IF(L29="","(brand not stated)",L29),"")&amp;IF(AND(ISNUMBER(M29),M29=T29),IF(N29="","(brand not stated)",N29),"")&amp;IF(AND(ISNUMBER(O29),O29=T29),IF(P29="","(brand not stated)",P29),"")&amp;IF(AND(ISNUMBER(Q29),Q29=T29),IF(R29="","(brand not stated)",R29),"")))</f>
+        <v>HEALIT 18GM OINTMENT</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="n">
         <v>25</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F30" s="5" t="n">
         <v>100</v>
@@ -3966,7 +4069,7 @@
         <v>267.75</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M30" s="7"/>
       <c r="N30" s="6"/>
@@ -3991,22 +4094,26 @@
         <v>26775</v>
       </c>
       <c r="W30" s="6"/>
+      <c r="X30" s="9" t="str">
+        <f aca="false">IF(S30=0,"",IF(ISNUMBER(SEARCH(",",U30)),LEFT(IF(AND(ISNUMBER(G30),G30=T30),IF(H30="","(brand not stated)",H30)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I30),I30=T30),IF(J30="","(brand not stated)",J30)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K30),K30=T30),IF(L30="","(brand not stated)",L30)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M30),M30=T30),IF(N30="","(brand not stated)",N30)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O30),O30=T30),IF(P30="","(brand not stated)",P30)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q30),Q30=T30),IF(R30="","(brand not stated)",R30)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G30),G30=T30),IF(H30="","(brand not stated)",H30)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I30),I30=T30),IF(J30="","(brand not stated)",J30)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K30),K30=T30),IF(L30="","(brand not stated)",L30)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M30),M30=T30),IF(N30="","(brand not stated)",N30)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O30),O30=T30),IF(P30="","(brand not stated)",P30)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q30),Q30=T30),IF(R30="","(brand not stated)",R30)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G30),G30=T30),IF(H30="","(brand not stated)",H30),"")&amp;IF(AND(ISNUMBER(I30),I30=T30),IF(J30="","(brand not stated)",J30),"")&amp;IF(AND(ISNUMBER(K30),K30=T30),IF(L30="","(brand not stated)",L30),"")&amp;IF(AND(ISNUMBER(M30),M30=T30),IF(N30="","(brand not stated)",N30),"")&amp;IF(AND(ISNUMBER(O30),O30=T30),IF(P30="","(brand not stated)",P30),"")&amp;IF(AND(ISNUMBER(Q30),Q30=T30),IF(R30="","(brand not stated)",R30),"")))</f>
+        <v>SURBEX T TAB</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="n">
         <v>26</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F31" s="5" t="n">
         <v>100</v>
@@ -4023,7 +4130,7 @@
         <v>147.9</v>
       </c>
       <c r="P31" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q31" s="7"/>
       <c r="R31" s="6"/>
@@ -4044,22 +4151,26 @@
         <v>14790</v>
       </c>
       <c r="W31" s="6"/>
+      <c r="X31" s="9" t="str">
+        <f aca="false">IF(S31=0,"",IF(ISNUMBER(SEARCH(",",U31)),LEFT(IF(AND(ISNUMBER(G31),G31=T31),IF(H31="","(brand not stated)",H31)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I31),I31=T31),IF(J31="","(brand not stated)",J31)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K31),K31=T31),IF(L31="","(brand not stated)",L31)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M31),M31=T31),IF(N31="","(brand not stated)",N31)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O31),O31=T31),IF(P31="","(brand not stated)",P31)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q31),Q31=T31),IF(R31="","(brand not stated)",R31)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G31),G31=T31),IF(H31="","(brand not stated)",H31)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I31),I31=T31),IF(J31="","(brand not stated)",J31)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K31),K31=T31),IF(L31="","(brand not stated)",L31)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M31),M31=T31),IF(N31="","(brand not stated)",N31)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O31),O31=T31),IF(P31="","(brand not stated)",P31)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q31),Q31=T31),IF(R31="","(brand not stated)",R31)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G31),G31=T31),IF(H31="","(brand not stated)",H31),"")&amp;IF(AND(ISNUMBER(I31),I31=T31),IF(J31="","(brand not stated)",J31),"")&amp;IF(AND(ISNUMBER(K31),K31=T31),IF(L31="","(brand not stated)",L31),"")&amp;IF(AND(ISNUMBER(M31),M31=T31),IF(N31="","(brand not stated)",N31),"")&amp;IF(AND(ISNUMBER(O31),O31=T31),IF(P31="","(brand not stated)",P31),"")&amp;IF(AND(ISNUMBER(Q31),Q31=T31),IF(R31="","(brand not stated)",R31),"")))</f>
+        <v>CITRALKA 150ML SYRUP</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="n">
         <v>27</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F32" s="5" t="n">
         <v>100</v>
@@ -4078,7 +4189,7 @@
         <v>343.19</v>
       </c>
       <c r="R32" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="S32" s="5" t="n">
         <f aca="false">COUNT(G32,I32,K32,M32,O32,Q32)</f>
@@ -4097,22 +4208,26 @@
         <v>34319</v>
       </c>
       <c r="W32" s="6"/>
+      <c r="X32" s="9" t="str">
+        <f aca="false">IF(S32=0,"",IF(ISNUMBER(SEARCH(",",U32)),LEFT(IF(AND(ISNUMBER(G32),G32=T32),IF(H32="","(brand not stated)",H32)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I32),I32=T32),IF(J32="","(brand not stated)",J32)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K32),K32=T32),IF(L32="","(brand not stated)",L32)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M32),M32=T32),IF(N32="","(brand not stated)",N32)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O32),O32=T32),IF(P32="","(brand not stated)",P32)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q32),Q32=T32),IF(R32="","(brand not stated)",R32)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G32),G32=T32),IF(H32="","(brand not stated)",H32)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I32),I32=T32),IF(J32="","(brand not stated)",J32)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K32),K32=T32),IF(L32="","(brand not stated)",L32)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M32),M32=T32),IF(N32="","(brand not stated)",N32)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O32),O32=T32),IF(P32="","(brand not stated)",P32)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q32),Q32=T32),IF(R32="","(brand not stated)",R32)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G32),G32=T32),IF(H32="","(brand not stated)",H32),"")&amp;IF(AND(ISNUMBER(I32),I32=T32),IF(J32="","(brand not stated)",J32),"")&amp;IF(AND(ISNUMBER(K32),K32=T32),IF(L32="","(brand not stated)",L32),"")&amp;IF(AND(ISNUMBER(M32),M32=T32),IF(N32="","(brand not stated)",N32),"")&amp;IF(AND(ISNUMBER(O32),O32=T32),IF(P32="","(brand not stated)",P32),"")&amp;IF(AND(ISNUMBER(Q32),Q32=T32),IF(R32="","(brand not stated)",R32),"")))</f>
+        <v>Revomet Plus Gel</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="n">
         <v>28</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F33" s="5" t="n">
         <v>2500</v>
@@ -4127,13 +4242,13 @@
         <v>743.4</v>
       </c>
       <c r="N33" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O33" s="7" t="n">
         <v>329.73</v>
       </c>
       <c r="P33" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q33" s="7"/>
       <c r="R33" s="6"/>
@@ -4154,22 +4269,26 @@
         <v>824325</v>
       </c>
       <c r="W33" s="6"/>
+      <c r="X33" s="9" t="str">
+        <f aca="false">IF(S33=0,"",IF(ISNUMBER(SEARCH(",",U33)),LEFT(IF(AND(ISNUMBER(G33),G33=T33),IF(H33="","(brand not stated)",H33)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I33),I33=T33),IF(J33="","(brand not stated)",J33)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K33),K33=T33),IF(L33="","(brand not stated)",L33)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M33),M33=T33),IF(N33="","(brand not stated)",N33)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O33),O33=T33),IF(P33="","(brand not stated)",P33)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q33),Q33=T33),IF(R33="","(brand not stated)",R33)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G33),G33=T33),IF(H33="","(brand not stated)",H33)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I33),I33=T33),IF(J33="","(brand not stated)",J33)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K33),K33=T33),IF(L33="","(brand not stated)",L33)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M33),M33=T33),IF(N33="","(brand not stated)",N33)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O33),O33=T33),IF(P33="","(brand not stated)",P33)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q33),Q33=T33),IF(R33="","(brand not stated)",R33)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G33),G33=T33),IF(H33="","(brand not stated)",H33),"")&amp;IF(AND(ISNUMBER(I33),I33=T33),IF(J33="","(brand not stated)",J33),"")&amp;IF(AND(ISNUMBER(K33),K33=T33),IF(L33="","(brand not stated)",L33),"")&amp;IF(AND(ISNUMBER(M33),M33=T33),IF(N33="","(brand not stated)",N33),"")&amp;IF(AND(ISNUMBER(O33),O33=T33),IF(P33="","(brand not stated)",P33),"")&amp;IF(AND(ISNUMBER(Q33),Q33=T33),IF(R33="","(brand not stated)",R33),"")))</f>
+        <v>OSMOLAR POWDER-ORS SACHET</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="n">
         <v>29</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F34" s="5" t="n">
         <v>50</v>
@@ -4182,7 +4301,7 @@
         <v>153.53</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M34" s="7"/>
       <c r="N34" s="6"/>
@@ -4190,7 +4309,7 @@
         <v>102</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q34" s="7"/>
       <c r="R34" s="6"/>
@@ -4211,22 +4330,26 @@
         <v>5100</v>
       </c>
       <c r="W34" s="6"/>
+      <c r="X34" s="9" t="str">
+        <f aca="false">IF(S34=0,"",IF(ISNUMBER(SEARCH(",",U34)),LEFT(IF(AND(ISNUMBER(G34),G34=T34),IF(H34="","(brand not stated)",H34)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I34),I34=T34),IF(J34="","(brand not stated)",J34)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K34),K34=T34),IF(L34="","(brand not stated)",L34)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M34),M34=T34),IF(N34="","(brand not stated)",N34)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O34),O34=T34),IF(P34="","(brand not stated)",P34)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q34),Q34=T34),IF(R34="","(brand not stated)",R34)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G34),G34=T34),IF(H34="","(brand not stated)",H34)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I34),I34=T34),IF(J34="","(brand not stated)",J34)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K34),K34=T34),IF(L34="","(brand not stated)",L34)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M34),M34=T34),IF(N34="","(brand not stated)",N34)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O34),O34=T34),IF(P34="","(brand not stated)",P34)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q34),Q34=T34),IF(R34="","(brand not stated)",R34)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G34),G34=T34),IF(H34="","(brand not stated)",H34),"")&amp;IF(AND(ISNUMBER(I34),I34=T34),IF(J34="","(brand not stated)",J34),"")&amp;IF(AND(ISNUMBER(K34),K34=T34),IF(L34="","(brand not stated)",L34),"")&amp;IF(AND(ISNUMBER(M34),M34=T34),IF(N34="","(brand not stated)",N34),"")&amp;IF(AND(ISNUMBER(O34),O34=T34),IF(P34="","(brand not stated)",P34),"")&amp;IF(AND(ISNUMBER(Q34),Q34=T34),IF(R34="","(brand not stated)",R34),"")))</f>
+        <v>BETADERM-N 20GM OINTMENT</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="n">
         <v>30</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F35" s="5" t="n">
         <v>200</v>
@@ -4237,25 +4360,25 @@
         <v>254.27</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K35" s="7" t="n">
         <v>254.29</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M35" s="7" t="n">
         <v>165.82</v>
       </c>
       <c r="N35" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O35" s="7" t="n">
         <v>153.43</v>
       </c>
       <c r="P35" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q35" s="7"/>
       <c r="R35" s="6"/>
@@ -4276,22 +4399,26 @@
         <v>30686</v>
       </c>
       <c r="W35" s="6"/>
+      <c r="X35" s="9" t="str">
+        <f aca="false">IF(S35=0,"",IF(ISNUMBER(SEARCH(",",U35)),LEFT(IF(AND(ISNUMBER(G35),G35=T35),IF(H35="","(brand not stated)",H35)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I35),I35=T35),IF(J35="","(brand not stated)",J35)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K35),K35=T35),IF(L35="","(brand not stated)",L35)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M35),M35=T35),IF(N35="","(brand not stated)",N35)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O35),O35=T35),IF(P35="","(brand not stated)",P35)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q35),Q35=T35),IF(R35="","(brand not stated)",R35)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G35),G35=T35),IF(H35="","(brand not stated)",H35)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I35),I35=T35),IF(J35="","(brand not stated)",J35)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K35),K35=T35),IF(L35="","(brand not stated)",L35)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M35),M35=T35),IF(N35="","(brand not stated)",N35)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O35),O35=T35),IF(P35="","(brand not stated)",P35)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q35),Q35=T35),IF(R35="","(brand not stated)",R35)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G35),G35=T35),IF(H35="","(brand not stated)",H35),"")&amp;IF(AND(ISNUMBER(I35),I35=T35),IF(J35="","(brand not stated)",J35),"")&amp;IF(AND(ISNUMBER(K35),K35=T35),IF(L35="","(brand not stated)",L35),"")&amp;IF(AND(ISNUMBER(M35),M35=T35),IF(N35="","(brand not stated)",N35),"")&amp;IF(AND(ISNUMBER(O35),O35=T35),IF(P35="","(brand not stated)",P35),"")&amp;IF(AND(ISNUMBER(Q35),Q35=T35),IF(R35="","(brand not stated)",R35),"")))</f>
+        <v>CUREZOLE 20G CREAM</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="n">
         <v>31</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F36" s="5" t="n">
         <v>200</v>
@@ -4304,7 +4431,7 @@
         <v>109.96</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M36" s="7"/>
       <c r="N36" s="6"/>
@@ -4329,22 +4456,26 @@
         <v>21992</v>
       </c>
       <c r="W36" s="6"/>
+      <c r="X36" s="9" t="str">
+        <f aca="false">IF(S36=0,"",IF(ISNUMBER(SEARCH(",",U36)),LEFT(IF(AND(ISNUMBER(G36),G36=T36),IF(H36="","(brand not stated)",H36)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I36),I36=T36),IF(J36="","(brand not stated)",J36)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K36),K36=T36),IF(L36="","(brand not stated)",L36)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M36),M36=T36),IF(N36="","(brand not stated)",N36)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O36),O36=T36),IF(P36="","(brand not stated)",P36)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q36),Q36=T36),IF(R36="","(brand not stated)",R36)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G36),G36=T36),IF(H36="","(brand not stated)",H36)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I36),I36=T36),IF(J36="","(brand not stated)",J36)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K36),K36=T36),IF(L36="","(brand not stated)",L36)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M36),M36=T36),IF(N36="","(brand not stated)",N36)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O36),O36=T36),IF(P36="","(brand not stated)",P36)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q36),Q36=T36),IF(R36="","(brand not stated)",R36)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G36),G36=T36),IF(H36="","(brand not stated)",H36),"")&amp;IF(AND(ISNUMBER(I36),I36=T36),IF(J36="","(brand not stated)",J36),"")&amp;IF(AND(ISNUMBER(K36),K36=T36),IF(L36="","(brand not stated)",L36),"")&amp;IF(AND(ISNUMBER(M36),M36=T36),IF(N36="","(brand not stated)",N36),"")&amp;IF(AND(ISNUMBER(O36),O36=T36),IF(P36="","(brand not stated)",P36),"")&amp;IF(AND(ISNUMBER(Q36),Q36=T36),IF(R36="","(brand not stated)",R36),"")))</f>
+        <v>POLYFAX EYE OINT</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="n">
         <v>32</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F37" s="5" t="n">
         <v>50</v>
@@ -4378,22 +4509,26 @@
         <v/>
       </c>
       <c r="W37" s="6"/>
+      <c r="X37" s="9" t="str">
+        <f aca="false">IF(S37=0,"",IF(ISNUMBER(SEARCH(",",U37)),LEFT(IF(AND(ISNUMBER(G37),G37=T37),IF(H37="","(brand not stated)",H37)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I37),I37=T37),IF(J37="","(brand not stated)",J37)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K37),K37=T37),IF(L37="","(brand not stated)",L37)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M37),M37=T37),IF(N37="","(brand not stated)",N37)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O37),O37=T37),IF(P37="","(brand not stated)",P37)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q37),Q37=T37),IF(R37="","(brand not stated)",R37)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G37),G37=T37),IF(H37="","(brand not stated)",H37)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I37),I37=T37),IF(J37="","(brand not stated)",J37)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K37),K37=T37),IF(L37="","(brand not stated)",L37)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M37),M37=T37),IF(N37="","(brand not stated)",N37)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O37),O37=T37),IF(P37="","(brand not stated)",P37)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q37),Q37=T37),IF(R37="","(brand not stated)",R37)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G37),G37=T37),IF(H37="","(brand not stated)",H37),"")&amp;IF(AND(ISNUMBER(I37),I37=T37),IF(J37="","(brand not stated)",J37),"")&amp;IF(AND(ISNUMBER(K37),K37=T37),IF(L37="","(brand not stated)",L37),"")&amp;IF(AND(ISNUMBER(M37),M37=T37),IF(N37="","(brand not stated)",N37),"")&amp;IF(AND(ISNUMBER(O37),O37=T37),IF(P37="","(brand not stated)",P37),"")&amp;IF(AND(ISNUMBER(Q37),Q37=T37),IF(R37="","(brand not stated)",R37),"")))</f>
+        <v/>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="n">
         <v>33</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F38" s="5" t="n">
         <v>50</v>
@@ -4402,13 +4537,13 @@
         <v>335.75</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I38" s="7" t="n">
         <v>382.5</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K38" s="7"/>
       <c r="L38" s="6"/>
@@ -4416,13 +4551,13 @@
         <v>552.5</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O38" s="7" t="n">
         <v>251.6</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q38" s="7"/>
       <c r="R38" s="6"/>
@@ -4443,22 +4578,26 @@
         <v>12580</v>
       </c>
       <c r="W38" s="6"/>
+      <c r="X38" s="9" t="str">
+        <f aca="false">IF(S38=0,"",IF(ISNUMBER(SEARCH(",",U38)),LEFT(IF(AND(ISNUMBER(G38),G38=T38),IF(H38="","(brand not stated)",H38)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I38),I38=T38),IF(J38="","(brand not stated)",J38)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K38),K38=T38),IF(L38="","(brand not stated)",L38)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M38),M38=T38),IF(N38="","(brand not stated)",N38)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O38),O38=T38),IF(P38="","(brand not stated)",P38)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q38),Q38=T38),IF(R38="","(brand not stated)",R38)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G38),G38=T38),IF(H38="","(brand not stated)",H38)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I38),I38=T38),IF(J38="","(brand not stated)",J38)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K38),K38=T38),IF(L38="","(brand not stated)",L38)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M38),M38=T38),IF(N38="","(brand not stated)",N38)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O38),O38=T38),IF(P38="","(brand not stated)",P38)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q38),Q38=T38),IF(R38="","(brand not stated)",R38)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G38),G38=T38),IF(H38="","(brand not stated)",H38),"")&amp;IF(AND(ISNUMBER(I38),I38=T38),IF(J38="","(brand not stated)",J38),"")&amp;IF(AND(ISNUMBER(K38),K38=T38),IF(L38="","(brand not stated)",L38),"")&amp;IF(AND(ISNUMBER(M38),M38=T38),IF(N38="","(brand not stated)",N38),"")&amp;IF(AND(ISNUMBER(O38),O38=T38),IF(P38="","(brand not stated)",P38),"")&amp;IF(AND(ISNUMBER(Q38),Q38=T38),IF(R38="","(brand not stated)",R38),"")))</f>
+        <v>UBKINO 8MG TABLET</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="n">
         <v>34</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F39" s="5" t="n">
         <v>500</v>
@@ -4467,13 +4606,13 @@
         <v>187</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I39" s="7" t="n">
         <v>170</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K39" s="7"/>
       <c r="L39" s="6"/>
@@ -4481,13 +4620,13 @@
         <v>262.65</v>
       </c>
       <c r="N39" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O39" s="7" t="n">
         <v>144.5</v>
       </c>
       <c r="P39" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q39" s="7"/>
       <c r="R39" s="6"/>
@@ -4508,22 +4647,26 @@
         <v>72250</v>
       </c>
       <c r="W39" s="6"/>
+      <c r="X39" s="9" t="str">
+        <f aca="false">IF(S39=0,"",IF(ISNUMBER(SEARCH(",",U39)),LEFT(IF(AND(ISNUMBER(G39),G39=T39),IF(H39="","(brand not stated)",H39)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I39),I39=T39),IF(J39="","(brand not stated)",J39)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K39),K39=T39),IF(L39="","(brand not stated)",L39)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M39),M39=T39),IF(N39="","(brand not stated)",N39)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O39),O39=T39),IF(P39="","(brand not stated)",P39)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q39),Q39=T39),IF(R39="","(brand not stated)",R39)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G39),G39=T39),IF(H39="","(brand not stated)",H39)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I39),I39=T39),IF(J39="","(brand not stated)",J39)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K39),K39=T39),IF(L39="","(brand not stated)",L39)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M39),M39=T39),IF(N39="","(brand not stated)",N39)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O39),O39=T39),IF(P39="","(brand not stated)",P39)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q39),Q39=T39),IF(R39="","(brand not stated)",R39)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G39),G39=T39),IF(H39="","(brand not stated)",H39),"")&amp;IF(AND(ISNUMBER(I39),I39=T39),IF(J39="","(brand not stated)",J39),"")&amp;IF(AND(ISNUMBER(K39),K39=T39),IF(L39="","(brand not stated)",L39),"")&amp;IF(AND(ISNUMBER(M39),M39=T39),IF(N39="","(brand not stated)",N39),"")&amp;IF(AND(ISNUMBER(O39),O39=T39),IF(P39="","(brand not stated)",P39),"")&amp;IF(AND(ISNUMBER(Q39),Q39=T39),IF(R39="","(brand not stated)",R39),"")))</f>
+        <v>NUBEROL FORTE TABLET</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="n">
         <v>35</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F40" s="5" t="n">
         <v>50</v>
@@ -4557,22 +4700,26 @@
         <v/>
       </c>
       <c r="W40" s="6"/>
+      <c r="X40" s="9" t="str">
+        <f aca="false">IF(S40=0,"",IF(ISNUMBER(SEARCH(",",U40)),LEFT(IF(AND(ISNUMBER(G40),G40=T40),IF(H40="","(brand not stated)",H40)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I40),I40=T40),IF(J40="","(brand not stated)",J40)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K40),K40=T40),IF(L40="","(brand not stated)",L40)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M40),M40=T40),IF(N40="","(brand not stated)",N40)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O40),O40=T40),IF(P40="","(brand not stated)",P40)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q40),Q40=T40),IF(R40="","(brand not stated)",R40)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G40),G40=T40),IF(H40="","(brand not stated)",H40)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I40),I40=T40),IF(J40="","(brand not stated)",J40)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K40),K40=T40),IF(L40="","(brand not stated)",L40)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M40),M40=T40),IF(N40="","(brand not stated)",N40)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O40),O40=T40),IF(P40="","(brand not stated)",P40)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q40),Q40=T40),IF(R40="","(brand not stated)",R40)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G40),G40=T40),IF(H40="","(brand not stated)",H40),"")&amp;IF(AND(ISNUMBER(I40),I40=T40),IF(J40="","(brand not stated)",J40),"")&amp;IF(AND(ISNUMBER(K40),K40=T40),IF(L40="","(brand not stated)",L40),"")&amp;IF(AND(ISNUMBER(M40),M40=T40),IF(N40="","(brand not stated)",N40),"")&amp;IF(AND(ISNUMBER(O40),O40=T40),IF(P40="","(brand not stated)",P40),"")&amp;IF(AND(ISNUMBER(Q40),Q40=T40),IF(R40="","(brand not stated)",R40),"")))</f>
+        <v/>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="n">
         <v>36</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F41" s="5" t="n">
         <v>100</v>
@@ -4589,7 +4736,7 @@
         <v>493</v>
       </c>
       <c r="P41" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q41" s="7"/>
       <c r="R41" s="6"/>
@@ -4610,22 +4757,26 @@
         <v>49300</v>
       </c>
       <c r="W41" s="6"/>
+      <c r="X41" s="9" t="str">
+        <f aca="false">IF(S41=0,"",IF(ISNUMBER(SEARCH(",",U41)),LEFT(IF(AND(ISNUMBER(G41),G41=T41),IF(H41="","(brand not stated)",H41)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I41),I41=T41),IF(J41="","(brand not stated)",J41)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K41),K41=T41),IF(L41="","(brand not stated)",L41)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M41),M41=T41),IF(N41="","(brand not stated)",N41)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O41),O41=T41),IF(P41="","(brand not stated)",P41)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q41),Q41=T41),IF(R41="","(brand not stated)",R41)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G41),G41=T41),IF(H41="","(brand not stated)",H41)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I41),I41=T41),IF(J41="","(brand not stated)",J41)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K41),K41=T41),IF(L41="","(brand not stated)",L41)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M41),M41=T41),IF(N41="","(brand not stated)",N41)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O41),O41=T41),IF(P41="","(brand not stated)",P41)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q41),Q41=T41),IF(R41="","(brand not stated)",R41)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G41),G41=T41),IF(H41="","(brand not stated)",H41),"")&amp;IF(AND(ISNUMBER(I41),I41=T41),IF(J41="","(brand not stated)",J41),"")&amp;IF(AND(ISNUMBER(K41),K41=T41),IF(L41="","(brand not stated)",L41),"")&amp;IF(AND(ISNUMBER(M41),M41=T41),IF(N41="","(brand not stated)",N41),"")&amp;IF(AND(ISNUMBER(O41),O41=T41),IF(P41="","(brand not stated)",P41),"")&amp;IF(AND(ISNUMBER(Q41),Q41=T41),IF(R41="","(brand not stated)",R41),"")))</f>
+        <v>ATCONATE 150MG TABLET</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="n">
         <v>37</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F42" s="5" t="n">
         <v>250</v>
@@ -4634,25 +4785,25 @@
         <v>197.93</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I42" s="7" t="n">
         <v>197.93</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K42" s="7" t="n">
         <v>502.77</v>
       </c>
       <c r="L42" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M42" s="7" t="n">
         <v>197.93</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O42" s="7"/>
       <c r="P42" s="6"/>
@@ -4675,7 +4826,11 @@
         <v>49482.5</v>
       </c>
       <c r="W42" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
+      </c>
+      <c r="X42" s="9" t="str">
+        <f aca="false">IF(S42=0,"",IF(ISNUMBER(SEARCH(",",U42)),LEFT(IF(AND(ISNUMBER(G42),G42=T42),IF(H42="","(brand not stated)",H42)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I42),I42=T42),IF(J42="","(brand not stated)",J42)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K42),K42=T42),IF(L42="","(brand not stated)",L42)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M42),M42=T42),IF(N42="","(brand not stated)",N42)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O42),O42=T42),IF(P42="","(brand not stated)",P42)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q42),Q42=T42),IF(R42="","(brand not stated)",R42)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G42),G42=T42),IF(H42="","(brand not stated)",H42)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I42),I42=T42),IF(J42="","(brand not stated)",J42)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K42),K42=T42),IF(L42="","(brand not stated)",L42)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M42),M42=T42),IF(N42="","(brand not stated)",N42)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O42),O42=T42),IF(P42="","(brand not stated)",P42)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q42),Q42=T42),IF(R42="","(brand not stated)",R42)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G42),G42=T42),IF(H42="","(brand not stated)",H42),"")&amp;IF(AND(ISNUMBER(I42),I42=T42),IF(J42="","(brand not stated)",J42),"")&amp;IF(AND(ISNUMBER(K42),K42=T42),IF(L42="","(brand not stated)",L42),"")&amp;IF(AND(ISNUMBER(M42),M42=T42),IF(N42="","(brand not stated)",N42),"")&amp;IF(AND(ISNUMBER(O42),O42=T42),IF(P42="","(brand not stated)",P42),"")&amp;IF(AND(ISNUMBER(Q42),Q42=T42),IF(R42="","(brand not stated)",R42),"")))</f>
+        <v>SAM-CLAV (Ahsan); Bosch (Aslam); AMOXI-CLAV (OBS/AGP) (Muller)</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4683,16 +4838,16 @@
         <v>38</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F43" s="5" t="n">
         <v>250</v>
@@ -4701,25 +4856,25 @@
         <v>250.46</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I43" s="7" t="n">
         <v>250.46</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K43" s="7" t="n">
         <v>622.95</v>
       </c>
       <c r="L43" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="M43" s="7" t="n">
         <v>250.5</v>
       </c>
       <c r="N43" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O43" s="7"/>
       <c r="P43" s="6"/>
@@ -4742,7 +4897,11 @@
         <v>62615</v>
       </c>
       <c r="W43" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
+      </c>
+      <c r="X43" s="9" t="str">
+        <f aca="false">IF(S43=0,"",IF(ISNUMBER(SEARCH(",",U43)),LEFT(IF(AND(ISNUMBER(G43),G43=T43),IF(H43="","(brand not stated)",H43)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I43),I43=T43),IF(J43="","(brand not stated)",J43)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K43),K43=T43),IF(L43="","(brand not stated)",L43)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M43),M43=T43),IF(N43="","(brand not stated)",N43)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O43),O43=T43),IF(P43="","(brand not stated)",P43)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q43),Q43=T43),IF(R43="","(brand not stated)",R43)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G43),G43=T43),IF(H43="","(brand not stated)",H43)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I43),I43=T43),IF(J43="","(brand not stated)",J43)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K43),K43=T43),IF(L43="","(brand not stated)",L43)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M43),M43=T43),IF(N43="","(brand not stated)",N43)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O43),O43=T43),IF(P43="","(brand not stated)",P43)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q43),Q43=T43),IF(R43="","(brand not stated)",R43)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G43),G43=T43),IF(H43="","(brand not stated)",H43),"")&amp;IF(AND(ISNUMBER(I43),I43=T43),IF(J43="","(brand not stated)",J43),"")&amp;IF(AND(ISNUMBER(K43),K43=T43),IF(L43="","(brand not stated)",L43),"")&amp;IF(AND(ISNUMBER(M43),M43=T43),IF(N43="","(brand not stated)",N43),"")&amp;IF(AND(ISNUMBER(O43),O43=T43),IF(P43="","(brand not stated)",P43),"")&amp;IF(AND(ISNUMBER(Q43),Q43=T43),IF(R43="","(brand not stated)",R43),"")))</f>
+        <v>SAM-CLAV (Ahsan); Bosch (Aslam)</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4750,16 +4909,16 @@
         <v>39</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F44" s="5" t="n">
         <v>100</v>
@@ -4774,13 +4933,13 @@
         <v>361.25</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="O44" s="7" t="n">
         <v>257.04</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q44" s="7"/>
       <c r="R44" s="6"/>
@@ -4801,22 +4960,26 @@
         <v>25704</v>
       </c>
       <c r="W44" s="6"/>
+      <c r="X44" s="9" t="str">
+        <f aca="false">IF(S44=0,"",IF(ISNUMBER(SEARCH(",",U44)),LEFT(IF(AND(ISNUMBER(G44),G44=T44),IF(H44="","(brand not stated)",H44)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I44),I44=T44),IF(J44="","(brand not stated)",J44)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K44),K44=T44),IF(L44="","(brand not stated)",L44)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M44),M44=T44),IF(N44="","(brand not stated)",N44)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O44),O44=T44),IF(P44="","(brand not stated)",P44)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q44),Q44=T44),IF(R44="","(brand not stated)",R44)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G44),G44=T44),IF(H44="","(brand not stated)",H44)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I44),I44=T44),IF(J44="","(brand not stated)",J44)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K44),K44=T44),IF(L44="","(brand not stated)",L44)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M44),M44=T44),IF(N44="","(brand not stated)",N44)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O44),O44=T44),IF(P44="","(brand not stated)",P44)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q44),Q44=T44),IF(R44="","(brand not stated)",R44)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G44),G44=T44),IF(H44="","(brand not stated)",H44),"")&amp;IF(AND(ISNUMBER(I44),I44=T44),IF(J44="","(brand not stated)",J44),"")&amp;IF(AND(ISNUMBER(K44),K44=T44),IF(L44="","(brand not stated)",L44),"")&amp;IF(AND(ISNUMBER(M44),M44=T44),IF(N44="","(brand not stated)",N44),"")&amp;IF(AND(ISNUMBER(O44),O44=T44),IF(P44="","(brand not stated)",P44),"")&amp;IF(AND(ISNUMBER(Q44),Q44=T44),IF(R44="","(brand not stated)",R44),"")))</f>
+        <v>DIAJARD-M 5/500MG TABLET</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="n">
         <v>40</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F45" s="5" t="n">
         <v>50</v>
@@ -4829,7 +4992,7 @@
         <v>363.38</v>
       </c>
       <c r="L45" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M45" s="7"/>
       <c r="N45" s="6"/>
@@ -4839,7 +5002,7 @@
         <v>290.32</v>
       </c>
       <c r="R45" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="S45" s="5" t="n">
         <f aca="false">COUNT(G45,I45,K45,M45,O45,Q45)</f>
@@ -4858,22 +5021,26 @@
         <v>14516</v>
       </c>
       <c r="W45" s="6"/>
+      <c r="X45" s="9" t="str">
+        <f aca="false">IF(S45=0,"",IF(ISNUMBER(SEARCH(",",U45)),LEFT(IF(AND(ISNUMBER(G45),G45=T45),IF(H45="","(brand not stated)",H45)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I45),I45=T45),IF(J45="","(brand not stated)",J45)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K45),K45=T45),IF(L45="","(brand not stated)",L45)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M45),M45=T45),IF(N45="","(brand not stated)",N45)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O45),O45=T45),IF(P45="","(brand not stated)",P45)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q45),Q45=T45),IF(R45="","(brand not stated)",R45)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G45),G45=T45),IF(H45="","(brand not stated)",H45)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I45),I45=T45),IF(J45="","(brand not stated)",J45)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K45),K45=T45),IF(L45="","(brand not stated)",L45)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M45),M45=T45),IF(N45="","(brand not stated)",N45)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O45),O45=T45),IF(P45="","(brand not stated)",P45)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q45),Q45=T45),IF(R45="","(brand not stated)",R45)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G45),G45=T45),IF(H45="","(brand not stated)",H45),"")&amp;IF(AND(ISNUMBER(I45),I45=T45),IF(J45="","(brand not stated)",J45),"")&amp;IF(AND(ISNUMBER(K45),K45=T45),IF(L45="","(brand not stated)",L45),"")&amp;IF(AND(ISNUMBER(M45),M45=T45),IF(N45="","(brand not stated)",N45),"")&amp;IF(AND(ISNUMBER(O45),O45=T45),IF(P45="","(brand not stated)",P45),"")&amp;IF(AND(ISNUMBER(Q45),Q45=T45),IF(R45="","(brand not stated)",R45),"")))</f>
+        <v>Synalgo</v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="n">
         <v>41</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F46" s="5" t="n">
         <v>80</v>
@@ -4907,22 +5074,26 @@
         <v/>
       </c>
       <c r="W46" s="6"/>
+      <c r="X46" s="9" t="str">
+        <f aca="false">IF(S46=0,"",IF(ISNUMBER(SEARCH(",",U46)),LEFT(IF(AND(ISNUMBER(G46),G46=T46),IF(H46="","(brand not stated)",H46)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I46),I46=T46),IF(J46="","(brand not stated)",J46)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K46),K46=T46),IF(L46="","(brand not stated)",L46)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M46),M46=T46),IF(N46="","(brand not stated)",N46)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O46),O46=T46),IF(P46="","(brand not stated)",P46)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q46),Q46=T46),IF(R46="","(brand not stated)",R46)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G46),G46=T46),IF(H46="","(brand not stated)",H46)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I46),I46=T46),IF(J46="","(brand not stated)",J46)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K46),K46=T46),IF(L46="","(brand not stated)",L46)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M46),M46=T46),IF(N46="","(brand not stated)",N46)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O46),O46=T46),IF(P46="","(brand not stated)",P46)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q46),Q46=T46),IF(R46="","(brand not stated)",R46)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G46),G46=T46),IF(H46="","(brand not stated)",H46),"")&amp;IF(AND(ISNUMBER(I46),I46=T46),IF(J46="","(brand not stated)",J46),"")&amp;IF(AND(ISNUMBER(K46),K46=T46),IF(L46="","(brand not stated)",L46),"")&amp;IF(AND(ISNUMBER(M46),M46=T46),IF(N46="","(brand not stated)",N46),"")&amp;IF(AND(ISNUMBER(O46),O46=T46),IF(P46="","(brand not stated)",P46),"")&amp;IF(AND(ISNUMBER(Q46),Q46=T46),IF(R46="","(brand not stated)",R46),"")))</f>
+        <v/>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="n">
         <v>42</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F47" s="5" t="n">
         <v>600</v>
@@ -4931,7 +5102,7 @@
         <v>187</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I47" s="7"/>
       <c r="J47" s="6"/>
@@ -4939,19 +5110,19 @@
         <v>142.8</v>
       </c>
       <c r="L47" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M47" s="7" t="n">
         <v>697</v>
       </c>
       <c r="N47" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O47" s="7" t="n">
         <v>122.655</v>
       </c>
       <c r="P47" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q47" s="7"/>
       <c r="R47" s="6"/>
@@ -4972,22 +5143,26 @@
         <v>73593</v>
       </c>
       <c r="W47" s="6"/>
+      <c r="X47" s="9" t="str">
+        <f aca="false">IF(S47=0,"",IF(ISNUMBER(SEARCH(",",U47)),LEFT(IF(AND(ISNUMBER(G47),G47=T47),IF(H47="","(brand not stated)",H47)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I47),I47=T47),IF(J47="","(brand not stated)",J47)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K47),K47=T47),IF(L47="","(brand not stated)",L47)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M47),M47=T47),IF(N47="","(brand not stated)",N47)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O47),O47=T47),IF(P47="","(brand not stated)",P47)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q47),Q47=T47),IF(R47="","(brand not stated)",R47)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G47),G47=T47),IF(H47="","(brand not stated)",H47)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I47),I47=T47),IF(J47="","(brand not stated)",J47)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K47),K47=T47),IF(L47="","(brand not stated)",L47)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M47),M47=T47),IF(N47="","(brand not stated)",N47)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O47),O47=T47),IF(P47="","(brand not stated)",P47)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q47),Q47=T47),IF(R47="","(brand not stated)",R47)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G47),G47=T47),IF(H47="","(brand not stated)",H47),"")&amp;IF(AND(ISNUMBER(I47),I47=T47),IF(J47="","(brand not stated)",J47),"")&amp;IF(AND(ISNUMBER(K47),K47=T47),IF(L47="","(brand not stated)",L47),"")&amp;IF(AND(ISNUMBER(M47),M47=T47),IF(N47="","(brand not stated)",N47),"")&amp;IF(AND(ISNUMBER(O47),O47=T47),IF(P47="","(brand not stated)",P47),"")&amp;IF(AND(ISNUMBER(Q47),Q47=T47),IF(R47="","(brand not stated)",R47),"")))</f>
+        <v>ROSULIN 5MG TABLET</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="n">
         <v>43</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F48" s="5" t="n">
         <v>50</v>
@@ -4998,7 +5173,7 @@
         <v>265.31</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K48" s="7"/>
       <c r="L48" s="6"/>
@@ -5008,7 +5183,7 @@
         <v>69.66</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q48" s="7"/>
       <c r="R48" s="6"/>
@@ -5029,22 +5204,26 @@
         <v>3483</v>
       </c>
       <c r="W48" s="6"/>
+      <c r="X48" s="9" t="str">
+        <f aca="false">IF(S48=0,"",IF(ISNUMBER(SEARCH(",",U48)),LEFT(IF(AND(ISNUMBER(G48),G48=T48),IF(H48="","(brand not stated)",H48)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I48),I48=T48),IF(J48="","(brand not stated)",J48)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K48),K48=T48),IF(L48="","(brand not stated)",L48)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M48),M48=T48),IF(N48="","(brand not stated)",N48)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O48),O48=T48),IF(P48="","(brand not stated)",P48)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q48),Q48=T48),IF(R48="","(brand not stated)",R48)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G48),G48=T48),IF(H48="","(brand not stated)",H48)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I48),I48=T48),IF(J48="","(brand not stated)",J48)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K48),K48=T48),IF(L48="","(brand not stated)",L48)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M48),M48=T48),IF(N48="","(brand not stated)",N48)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O48),O48=T48),IF(P48="","(brand not stated)",P48)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q48),Q48=T48),IF(R48="","(brand not stated)",R48)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G48),G48=T48),IF(H48="","(brand not stated)",H48),"")&amp;IF(AND(ISNUMBER(I48),I48=T48),IF(J48="","(brand not stated)",J48),"")&amp;IF(AND(ISNUMBER(K48),K48=T48),IF(L48="","(brand not stated)",L48),"")&amp;IF(AND(ISNUMBER(M48),M48=T48),IF(N48="","(brand not stated)",N48),"")&amp;IF(AND(ISNUMBER(O48),O48=T48),IF(P48="","(brand not stated)",P48),"")&amp;IF(AND(ISNUMBER(Q48),Q48=T48),IF(R48="","(brand not stated)",R48),"")))</f>
+        <v>LOPRIN 75MG TABLET</v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="n">
         <v>44</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F49" s="5" t="n">
         <v>500</v>
@@ -5053,7 +5232,7 @@
         <v>191.25</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="I49" s="7"/>
       <c r="J49" s="6"/>
@@ -5063,13 +5242,13 @@
         <v>205.7</v>
       </c>
       <c r="N49" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="O49" s="7" t="n">
         <v>245.1287</v>
       </c>
       <c r="P49" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q49" s="7"/>
       <c r="R49" s="6"/>
@@ -5090,22 +5269,26 @@
         <v>95625</v>
       </c>
       <c r="W49" s="6"/>
+      <c r="X49" s="9" t="str">
+        <f aca="false">IF(S49=0,"",IF(ISNUMBER(SEARCH(",",U49)),LEFT(IF(AND(ISNUMBER(G49),G49=T49),IF(H49="","(brand not stated)",H49)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I49),I49=T49),IF(J49="","(brand not stated)",J49)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K49),K49=T49),IF(L49="","(brand not stated)",L49)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M49),M49=T49),IF(N49="","(brand not stated)",N49)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O49),O49=T49),IF(P49="","(brand not stated)",P49)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q49),Q49=T49),IF(R49="","(brand not stated)",R49)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G49),G49=T49),IF(H49="","(brand not stated)",H49)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I49),I49=T49),IF(J49="","(brand not stated)",J49)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K49),K49=T49),IF(L49="","(brand not stated)",L49)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M49),M49=T49),IF(N49="","(brand not stated)",N49)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O49),O49=T49),IF(P49="","(brand not stated)",P49)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q49),Q49=T49),IF(R49="","(brand not stated)",R49)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G49),G49=T49),IF(H49="","(brand not stated)",H49),"")&amp;IF(AND(ISNUMBER(I49),I49=T49),IF(J49="","(brand not stated)",J49),"")&amp;IF(AND(ISNUMBER(K49),K49=T49),IF(L49="","(brand not stated)",L49),"")&amp;IF(AND(ISNUMBER(M49),M49=T49),IF(N49="","(brand not stated)",N49),"")&amp;IF(AND(ISNUMBER(O49),O49=T49),IF(P49="","(brand not stated)",P49),"")&amp;IF(AND(ISNUMBER(Q49),Q49=T49),IF(R49="","(brand not stated)",R49),"")))</f>
+        <v>BECEPTOR</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="n">
         <v>45</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F50" s="5" t="n">
         <v>50</v>
@@ -5122,7 +5305,7 @@
         <v>93.925</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q50" s="7"/>
       <c r="R50" s="6"/>
@@ -5143,22 +5326,26 @@
         <v>4696.25</v>
       </c>
       <c r="W50" s="6"/>
+      <c r="X50" s="9" t="str">
+        <f aca="false">IF(S50=0,"",IF(ISNUMBER(SEARCH(",",U50)),LEFT(IF(AND(ISNUMBER(G50),G50=T50),IF(H50="","(brand not stated)",H50)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I50),I50=T50),IF(J50="","(brand not stated)",J50)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K50),K50=T50),IF(L50="","(brand not stated)",L50)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M50),M50=T50),IF(N50="","(brand not stated)",N50)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O50),O50=T50),IF(P50="","(brand not stated)",P50)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q50),Q50=T50),IF(R50="","(brand not stated)",R50)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G50),G50=T50),IF(H50="","(brand not stated)",H50)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I50),I50=T50),IF(J50="","(brand not stated)",J50)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K50),K50=T50),IF(L50="","(brand not stated)",L50)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M50),M50=T50),IF(N50="","(brand not stated)",N50)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O50),O50=T50),IF(P50="","(brand not stated)",P50)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q50),Q50=T50),IF(R50="","(brand not stated)",R50)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G50),G50=T50),IF(H50="","(brand not stated)",H50),"")&amp;IF(AND(ISNUMBER(I50),I50=T50),IF(J50="","(brand not stated)",J50),"")&amp;IF(AND(ISNUMBER(K50),K50=T50),IF(L50="","(brand not stated)",L50),"")&amp;IF(AND(ISNUMBER(M50),M50=T50),IF(N50="","(brand not stated)",N50),"")&amp;IF(AND(ISNUMBER(O50),O50=T50),IF(P50="","(brand not stated)",P50),"")&amp;IF(AND(ISNUMBER(Q50),Q50=T50),IF(R50="","(brand not stated)",R50),"")))</f>
+        <v>SKILAX 30ML DROP</v>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="n">
         <v>46</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F51" s="5" t="n">
         <v>150</v>
@@ -5169,7 +5356,7 @@
         <v>214.2</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K51" s="7"/>
       <c r="L51" s="6"/>
@@ -5177,13 +5364,13 @@
         <v>165.5</v>
       </c>
       <c r="N51" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O51" s="7" t="n">
         <v>203.49</v>
       </c>
       <c r="P51" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q51" s="7"/>
       <c r="R51" s="6"/>
@@ -5204,22 +5391,26 @@
         <v>24825</v>
       </c>
       <c r="W51" s="6"/>
+      <c r="X51" s="9" t="str">
+        <f aca="false">IF(S51=0,"",IF(ISNUMBER(SEARCH(",",U51)),LEFT(IF(AND(ISNUMBER(G51),G51=T51),IF(H51="","(brand not stated)",H51)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I51),I51=T51),IF(J51="","(brand not stated)",J51)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K51),K51=T51),IF(L51="","(brand not stated)",L51)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M51),M51=T51),IF(N51="","(brand not stated)",N51)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O51),O51=T51),IF(P51="","(brand not stated)",P51)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q51),Q51=T51),IF(R51="","(brand not stated)",R51)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G51),G51=T51),IF(H51="","(brand not stated)",H51)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I51),I51=T51),IF(J51="","(brand not stated)",J51)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K51),K51=T51),IF(L51="","(brand not stated)",L51)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M51),M51=T51),IF(N51="","(brand not stated)",N51)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O51),O51=T51),IF(P51="","(brand not stated)",P51)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q51),Q51=T51),IF(R51="","(brand not stated)",R51)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G51),G51=T51),IF(H51="","(brand not stated)",H51),"")&amp;IF(AND(ISNUMBER(I51),I51=T51),IF(J51="","(brand not stated)",J51),"")&amp;IF(AND(ISNUMBER(K51),K51=T51),IF(L51="","(brand not stated)",L51),"")&amp;IF(AND(ISNUMBER(M51),M51=T51),IF(N51="","(brand not stated)",N51),"")&amp;IF(AND(ISNUMBER(O51),O51=T51),IF(P51="","(brand not stated)",P51),"")&amp;IF(AND(ISNUMBER(Q51),Q51=T51),IF(R51="","(brand not stated)",R51),"")))</f>
+        <v>NEBTEC 2.5MG (PHARMATEC)</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="5" t="n">
         <v>47</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F52" s="5" t="n">
         <v>750</v>
@@ -5236,7 +5427,7 @@
         <v>411.04</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q52" s="7"/>
       <c r="R52" s="6"/>
@@ -5257,22 +5448,26 @@
         <v>308280</v>
       </c>
       <c r="W52" s="6"/>
+      <c r="X52" s="9" t="str">
+        <f aca="false">IF(S52=0,"",IF(ISNUMBER(SEARCH(",",U52)),LEFT(IF(AND(ISNUMBER(G52),G52=T52),IF(H52="","(brand not stated)",H52)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I52),I52=T52),IF(J52="","(brand not stated)",J52)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K52),K52=T52),IF(L52="","(brand not stated)",L52)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M52),M52=T52),IF(N52="","(brand not stated)",N52)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O52),O52=T52),IF(P52="","(brand not stated)",P52)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q52),Q52=T52),IF(R52="","(brand not stated)",R52)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G52),G52=T52),IF(H52="","(brand not stated)",H52)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I52),I52=T52),IF(J52="","(brand not stated)",J52)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K52),K52=T52),IF(L52="","(brand not stated)",L52)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M52),M52=T52),IF(N52="","(brand not stated)",N52)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O52),O52=T52),IF(P52="","(brand not stated)",P52)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q52),Q52=T52),IF(R52="","(brand not stated)",R52)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G52),G52=T52),IF(H52="","(brand not stated)",H52),"")&amp;IF(AND(ISNUMBER(I52),I52=T52),IF(J52="","(brand not stated)",J52),"")&amp;IF(AND(ISNUMBER(K52),K52=T52),IF(L52="","(brand not stated)",L52),"")&amp;IF(AND(ISNUMBER(M52),M52=T52),IF(N52="","(brand not stated)",N52),"")&amp;IF(AND(ISNUMBER(O52),O52=T52),IF(P52="","(brand not stated)",P52),"")&amp;IF(AND(ISNUMBER(Q52),Q52=T52),IF(R52="","(brand not stated)",R52),"")))</f>
+        <v>MY-D 50,000 IU TABLET</v>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="5" t="n">
         <v>48</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F53" s="5" t="n">
         <v>200</v>
@@ -5283,7 +5478,7 @@
         <v>691.52</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K53" s="7"/>
       <c r="L53" s="6"/>
@@ -5293,7 +5488,7 @@
         <v>753.57</v>
       </c>
       <c r="P53" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q53" s="7"/>
       <c r="R53" s="6"/>
@@ -5314,22 +5509,26 @@
         <v>138304</v>
       </c>
       <c r="W53" s="6"/>
+      <c r="X53" s="9" t="str">
+        <f aca="false">IF(S53=0,"",IF(ISNUMBER(SEARCH(",",U53)),LEFT(IF(AND(ISNUMBER(G53),G53=T53),IF(H53="","(brand not stated)",H53)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I53),I53=T53),IF(J53="","(brand not stated)",J53)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K53),K53=T53),IF(L53="","(brand not stated)",L53)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M53),M53=T53),IF(N53="","(brand not stated)",N53)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O53),O53=T53),IF(P53="","(brand not stated)",P53)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q53),Q53=T53),IF(R53="","(brand not stated)",R53)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G53),G53=T53),IF(H53="","(brand not stated)",H53)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I53),I53=T53),IF(J53="","(brand not stated)",J53)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K53),K53=T53),IF(L53="","(brand not stated)",L53)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M53),M53=T53),IF(N53="","(brand not stated)",N53)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O53),O53=T53),IF(P53="","(brand not stated)",P53)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q53),Q53=T53),IF(R53="","(brand not stated)",R53)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G53),G53=T53),IF(H53="","(brand not stated)",H53),"")&amp;IF(AND(ISNUMBER(I53),I53=T53),IF(J53="","(brand not stated)",J53),"")&amp;IF(AND(ISNUMBER(K53),K53=T53),IF(L53="","(brand not stated)",L53),"")&amp;IF(AND(ISNUMBER(M53),M53=T53),IF(N53="","(brand not stated)",N53),"")&amp;IF(AND(ISNUMBER(O53),O53=T53),IF(P53="","(brand not stated)",P53),"")&amp;IF(AND(ISNUMBER(Q53),Q53=T53),IF(R53="","(brand not stated)",R53),"")))</f>
+        <v>Searle</v>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="5" t="n">
         <v>49</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F54" s="5" t="n">
         <v>65</v>
@@ -5363,22 +5562,26 @@
         <v/>
       </c>
       <c r="W54" s="6"/>
+      <c r="X54" s="9" t="str">
+        <f aca="false">IF(S54=0,"",IF(ISNUMBER(SEARCH(",",U54)),LEFT(IF(AND(ISNUMBER(G54),G54=T54),IF(H54="","(brand not stated)",H54)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I54),I54=T54),IF(J54="","(brand not stated)",J54)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K54),K54=T54),IF(L54="","(brand not stated)",L54)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M54),M54=T54),IF(N54="","(brand not stated)",N54)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O54),O54=T54),IF(P54="","(brand not stated)",P54)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q54),Q54=T54),IF(R54="","(brand not stated)",R54)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G54),G54=T54),IF(H54="","(brand not stated)",H54)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I54),I54=T54),IF(J54="","(brand not stated)",J54)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K54),K54=T54),IF(L54="","(brand not stated)",L54)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M54),M54=T54),IF(N54="","(brand not stated)",N54)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O54),O54=T54),IF(P54="","(brand not stated)",P54)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q54),Q54=T54),IF(R54="","(brand not stated)",R54)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G54),G54=T54),IF(H54="","(brand not stated)",H54),"")&amp;IF(AND(ISNUMBER(I54),I54=T54),IF(J54="","(brand not stated)",J54),"")&amp;IF(AND(ISNUMBER(K54),K54=T54),IF(L54="","(brand not stated)",L54),"")&amp;IF(AND(ISNUMBER(M54),M54=T54),IF(N54="","(brand not stated)",N54),"")&amp;IF(AND(ISNUMBER(O54),O54=T54),IF(P54="","(brand not stated)",P54),"")&amp;IF(AND(ISNUMBER(Q54),Q54=T54),IF(R54="","(brand not stated)",R54),"")))</f>
+        <v/>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5" t="n">
         <v>50</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F55" s="5" t="n">
         <v>20</v>
@@ -5387,7 +5590,7 @@
         <v>221</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I55" s="7"/>
       <c r="J55" s="6"/>
@@ -5399,7 +5602,7 @@
         <v>591.6</v>
       </c>
       <c r="P55" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q55" s="7"/>
       <c r="R55" s="6"/>
@@ -5420,22 +5623,26 @@
         <v>4420</v>
       </c>
       <c r="W55" s="6"/>
+      <c r="X55" s="9" t="str">
+        <f aca="false">IF(S55=0,"",IF(ISNUMBER(SEARCH(",",U55)),LEFT(IF(AND(ISNUMBER(G55),G55=T55),IF(H55="","(brand not stated)",H55)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I55),I55=T55),IF(J55="","(brand not stated)",J55)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K55),K55=T55),IF(L55="","(brand not stated)",L55)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M55),M55=T55),IF(N55="","(brand not stated)",N55)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O55),O55=T55),IF(P55="","(brand not stated)",P55)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q55),Q55=T55),IF(R55="","(brand not stated)",R55)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G55),G55=T55),IF(H55="","(brand not stated)",H55)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I55),I55=T55),IF(J55="","(brand not stated)",J55)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K55),K55=T55),IF(L55="","(brand not stated)",L55)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M55),M55=T55),IF(N55="","(brand not stated)",N55)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O55),O55=T55),IF(P55="","(brand not stated)",P55)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q55),Q55=T55),IF(R55="","(brand not stated)",R55)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G55),G55=T55),IF(H55="","(brand not stated)",H55),"")&amp;IF(AND(ISNUMBER(I55),I55=T55),IF(J55="","(brand not stated)",J55),"")&amp;IF(AND(ISNUMBER(K55),K55=T55),IF(L55="","(brand not stated)",L55),"")&amp;IF(AND(ISNUMBER(M55),M55=T55),IF(N55="","(brand not stated)",N55),"")&amp;IF(AND(ISNUMBER(O55),O55=T55),IF(P55="","(brand not stated)",P55),"")&amp;IF(AND(ISNUMBER(Q55),Q55=T55),IF(R55="","(brand not stated)",R55),"")))</f>
+        <v>SAMBRO</v>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="5" t="n">
         <v>51</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F56" s="5" t="n">
         <v>200</v>
@@ -5452,7 +5659,7 @@
         <v>321.04</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q56" s="7"/>
       <c r="R56" s="6"/>
@@ -5473,22 +5680,26 @@
         <v>64208</v>
       </c>
       <c r="W56" s="6"/>
+      <c r="X56" s="9" t="str">
+        <f aca="false">IF(S56=0,"",IF(ISNUMBER(SEARCH(",",U56)),LEFT(IF(AND(ISNUMBER(G56),G56=T56),IF(H56="","(brand not stated)",H56)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I56),I56=T56),IF(J56="","(brand not stated)",J56)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K56),K56=T56),IF(L56="","(brand not stated)",L56)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M56),M56=T56),IF(N56="","(brand not stated)",N56)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O56),O56=T56),IF(P56="","(brand not stated)",P56)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q56),Q56=T56),IF(R56="","(brand not stated)",R56)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G56),G56=T56),IF(H56="","(brand not stated)",H56)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I56),I56=T56),IF(J56="","(brand not stated)",J56)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K56),K56=T56),IF(L56="","(brand not stated)",L56)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M56),M56=T56),IF(N56="","(brand not stated)",N56)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O56),O56=T56),IF(P56="","(brand not stated)",P56)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q56),Q56=T56),IF(R56="","(brand not stated)",R56)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G56),G56=T56),IF(H56="","(brand not stated)",H56),"")&amp;IF(AND(ISNUMBER(I56),I56=T56),IF(J56="","(brand not stated)",J56),"")&amp;IF(AND(ISNUMBER(K56),K56=T56),IF(L56="","(brand not stated)",L56),"")&amp;IF(AND(ISNUMBER(M56),M56=T56),IF(N56="","(brand not stated)",N56),"")&amp;IF(AND(ISNUMBER(O56),O56=T56),IF(P56="","(brand not stated)",P56),"")&amp;IF(AND(ISNUMBER(Q56),Q56=T56),IF(R56="","(brand not stated)",R56),"")))</f>
+        <v>GLUCOPHAGE-XR 750 MG TABLET</v>
+      </c>
     </row>
     <row r="57" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="5" t="n">
         <v>52</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F57" s="5" t="n">
         <v>250</v>
@@ -5497,25 +5708,25 @@
         <v>331.5</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="I57" s="7" t="n">
         <v>382.5</v>
       </c>
       <c r="J57" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K57" s="7" t="n">
         <v>708.05</v>
       </c>
       <c r="L57" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M57" s="7" t="n">
         <v>242.48</v>
       </c>
       <c r="N57" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O57" s="7"/>
       <c r="P57" s="6"/>
@@ -5538,22 +5749,26 @@
         <v>60620</v>
       </c>
       <c r="W57" s="6"/>
+      <c r="X57" s="9" t="str">
+        <f aca="false">IF(S57=0,"",IF(ISNUMBER(SEARCH(",",U57)),LEFT(IF(AND(ISNUMBER(G57),G57=T57),IF(H57="","(brand not stated)",H57)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I57),I57=T57),IF(J57="","(brand not stated)",J57)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K57),K57=T57),IF(L57="","(brand not stated)",L57)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M57),M57=T57),IF(N57="","(brand not stated)",N57)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O57),O57=T57),IF(P57="","(brand not stated)",P57)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q57),Q57=T57),IF(R57="","(brand not stated)",R57)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G57),G57=T57),IF(H57="","(brand not stated)",H57)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I57),I57=T57),IF(J57="","(brand not stated)",J57)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K57),K57=T57),IF(L57="","(brand not stated)",L57)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M57),M57=T57),IF(N57="","(brand not stated)",N57)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O57),O57=T57),IF(P57="","(brand not stated)",P57)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q57),Q57=T57),IF(R57="","(brand not stated)",R57)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G57),G57=T57),IF(H57="","(brand not stated)",H57),"")&amp;IF(AND(ISNUMBER(I57),I57=T57),IF(J57="","(brand not stated)",J57),"")&amp;IF(AND(ISNUMBER(K57),K57=T57),IF(L57="","(brand not stated)",L57),"")&amp;IF(AND(ISNUMBER(M57),M57=T57),IF(N57="","(brand not stated)",N57),"")&amp;IF(AND(ISNUMBER(O57),O57=T57),IF(P57="","(brand not stated)",P57),"")&amp;IF(AND(ISNUMBER(Q57),Q57=T57),IF(R57="","(brand not stated)",R57),"")))</f>
+        <v>VOLTRAL (NOVARTIS)</v>
+      </c>
     </row>
     <row r="58" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="5" t="n">
         <v>53</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F58" s="5" t="n">
         <v>200</v>
@@ -5562,31 +5777,31 @@
         <v>467.5</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I58" s="7" t="n">
         <v>467.5</v>
       </c>
       <c r="J58" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K58" s="7" t="n">
         <v>530.4</v>
       </c>
       <c r="L58" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M58" s="7" t="n">
         <v>518.5</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O58" s="7" t="n">
         <v>270.725</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q58" s="7"/>
       <c r="R58" s="6"/>
@@ -5607,22 +5822,26 @@
         <v>54145</v>
       </c>
       <c r="W58" s="6"/>
+      <c r="X58" s="9" t="str">
+        <f aca="false">IF(S58=0,"",IF(ISNUMBER(SEARCH(",",U58)),LEFT(IF(AND(ISNUMBER(G58),G58=T58),IF(H58="","(brand not stated)",H58)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I58),I58=T58),IF(J58="","(brand not stated)",J58)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K58),K58=T58),IF(L58="","(brand not stated)",L58)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M58),M58=T58),IF(N58="","(brand not stated)",N58)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O58),O58=T58),IF(P58="","(brand not stated)",P58)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q58),Q58=T58),IF(R58="","(brand not stated)",R58)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G58),G58=T58),IF(H58="","(brand not stated)",H58)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I58),I58=T58),IF(J58="","(brand not stated)",J58)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K58),K58=T58),IF(L58="","(brand not stated)",L58)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M58),M58=T58),IF(N58="","(brand not stated)",N58)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O58),O58=T58),IF(P58="","(brand not stated)",P58)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q58),Q58=T58),IF(R58="","(brand not stated)",R58)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G58),G58=T58),IF(H58="","(brand not stated)",H58),"")&amp;IF(AND(ISNUMBER(I58),I58=T58),IF(J58="","(brand not stated)",J58),"")&amp;IF(AND(ISNUMBER(K58),K58=T58),IF(L58="","(brand not stated)",L58),"")&amp;IF(AND(ISNUMBER(M58),M58=T58),IF(N58="","(brand not stated)",N58),"")&amp;IF(AND(ISNUMBER(O58),O58=T58),IF(P58="","(brand not stated)",P58),"")&amp;IF(AND(ISNUMBER(Q58),Q58=T58),IF(R58="","(brand not stated)",R58),"")))</f>
+        <v>OXAQUIN 400MG TABLET</v>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="5" t="n">
         <v>54</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F59" s="5" t="n">
         <v>50</v>
@@ -5631,7 +5850,7 @@
         <v>318.75</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="I59" s="7"/>
       <c r="J59" s="6"/>
@@ -5641,7 +5860,7 @@
         <v>892.5</v>
       </c>
       <c r="N59" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O59" s="7"/>
       <c r="P59" s="6"/>
@@ -5664,22 +5883,26 @@
         <v>15937.5</v>
       </c>
       <c r="W59" s="6"/>
+      <c r="X59" s="9" t="str">
+        <f aca="false">IF(S59=0,"",IF(ISNUMBER(SEARCH(",",U59)),LEFT(IF(AND(ISNUMBER(G59),G59=T59),IF(H59="","(brand not stated)",H59)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I59),I59=T59),IF(J59="","(brand not stated)",J59)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K59),K59=T59),IF(L59="","(brand not stated)",L59)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M59),M59=T59),IF(N59="","(brand not stated)",N59)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O59),O59=T59),IF(P59="","(brand not stated)",P59)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q59),Q59=T59),IF(R59="","(brand not stated)",R59)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G59),G59=T59),IF(H59="","(brand not stated)",H59)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I59),I59=T59),IF(J59="","(brand not stated)",J59)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K59),K59=T59),IF(L59="","(brand not stated)",L59)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M59),M59=T59),IF(N59="","(brand not stated)",N59)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O59),O59=T59),IF(P59="","(brand not stated)",P59)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q59),Q59=T59),IF(R59="","(brand not stated)",R59)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G59),G59=T59),IF(H59="","(brand not stated)",H59),"")&amp;IF(AND(ISNUMBER(I59),I59=T59),IF(J59="","(brand not stated)",J59),"")&amp;IF(AND(ISNUMBER(K59),K59=T59),IF(L59="","(brand not stated)",L59),"")&amp;IF(AND(ISNUMBER(M59),M59=T59),IF(N59="","(brand not stated)",N59),"")&amp;IF(AND(ISNUMBER(O59),O59=T59),IF(P59="","(brand not stated)",P59),"")&amp;IF(AND(ISNUMBER(Q59),Q59=T59),IF(R59="","(brand not stated)",R59),"")))</f>
+        <v>ORGLU</v>
+      </c>
     </row>
     <row r="60" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="5" t="n">
         <v>55</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F60" s="5" t="n">
         <v>50</v>
@@ -5688,7 +5911,7 @@
         <v>382.5</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="I60" s="7"/>
       <c r="J60" s="6"/>
@@ -5698,13 +5921,13 @@
         <v>2737.17</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O60" s="7" t="n">
         <v>382.5</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q60" s="7"/>
       <c r="R60" s="6"/>
@@ -5725,22 +5948,26 @@
         <v>19125</v>
       </c>
       <c r="W60" s="6"/>
+      <c r="X60" s="9" t="str">
+        <f aca="false">IF(S60=0,"",IF(ISNUMBER(SEARCH(",",U60)),LEFT(IF(AND(ISNUMBER(G60),G60=T60),IF(H60="","(brand not stated)",H60)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I60),I60=T60),IF(J60="","(brand not stated)",J60)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K60),K60=T60),IF(L60="","(brand not stated)",L60)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M60),M60=T60),IF(N60="","(brand not stated)",N60)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O60),O60=T60),IF(P60="","(brand not stated)",P60)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q60),Q60=T60),IF(R60="","(brand not stated)",R60)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G60),G60=T60),IF(H60="","(brand not stated)",H60)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I60),I60=T60),IF(J60="","(brand not stated)",J60)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K60),K60=T60),IF(L60="","(brand not stated)",L60)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M60),M60=T60),IF(N60="","(brand not stated)",N60)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O60),O60=T60),IF(P60="","(brand not stated)",P60)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q60),Q60=T60),IF(R60="","(brand not stated)",R60)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G60),G60=T60),IF(H60="","(brand not stated)",H60),"")&amp;IF(AND(ISNUMBER(I60),I60=T60),IF(J60="","(brand not stated)",J60),"")&amp;IF(AND(ISNUMBER(K60),K60=T60),IF(L60="","(brand not stated)",L60),"")&amp;IF(AND(ISNUMBER(M60),M60=T60),IF(N60="","(brand not stated)",N60),"")&amp;IF(AND(ISNUMBER(O60),O60=T60),IF(P60="","(brand not stated)",P60),"")&amp;IF(AND(ISNUMBER(Q60),Q60=T60),IF(R60="","(brand not stated)",R60),"")))</f>
+        <v>SERT (Ahsan); SERT 50MG TABLET (NMMC)</v>
+      </c>
     </row>
     <row r="61" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="5" t="n">
         <v>56</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F61" s="5" t="n">
         <v>200</v>
@@ -5749,7 +5976,7 @@
         <v>255</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="I61" s="7"/>
       <c r="J61" s="6"/>
@@ -5761,7 +5988,7 @@
         <v>193.8</v>
       </c>
       <c r="P61" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q61" s="7"/>
       <c r="R61" s="6"/>
@@ -5782,22 +6009,26 @@
         <v>38760</v>
       </c>
       <c r="W61" s="6"/>
+      <c r="X61" s="9" t="str">
+        <f aca="false">IF(S61=0,"",IF(ISNUMBER(SEARCH(",",U61)),LEFT(IF(AND(ISNUMBER(G61),G61=T61),IF(H61="","(brand not stated)",H61)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I61),I61=T61),IF(J61="","(brand not stated)",J61)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K61),K61=T61),IF(L61="","(brand not stated)",L61)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M61),M61=T61),IF(N61="","(brand not stated)",N61)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O61),O61=T61),IF(P61="","(brand not stated)",P61)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q61),Q61=T61),IF(R61="","(brand not stated)",R61)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G61),G61=T61),IF(H61="","(brand not stated)",H61)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I61),I61=T61),IF(J61="","(brand not stated)",J61)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K61),K61=T61),IF(L61="","(brand not stated)",L61)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M61),M61=T61),IF(N61="","(brand not stated)",N61)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O61),O61=T61),IF(P61="","(brand not stated)",P61)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q61),Q61=T61),IF(R61="","(brand not stated)",R61)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G61),G61=T61),IF(H61="","(brand not stated)",H61),"")&amp;IF(AND(ISNUMBER(I61),I61=T61),IF(J61="","(brand not stated)",J61),"")&amp;IF(AND(ISNUMBER(K61),K61=T61),IF(L61="","(brand not stated)",L61),"")&amp;IF(AND(ISNUMBER(M61),M61=T61),IF(N61="","(brand not stated)",N61),"")&amp;IF(AND(ISNUMBER(O61),O61=T61),IF(P61="","(brand not stated)",P61),"")&amp;IF(AND(ISNUMBER(Q61),Q61=T61),IF(R61="","(brand not stated)",R61),"")))</f>
+        <v>BRACIN-D EYE DROP</v>
+      </c>
     </row>
     <row r="62" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="5" t="n">
         <v>57</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F62" s="5" t="n">
         <v>10</v>
@@ -5810,7 +6041,7 @@
         <v>1114.26</v>
       </c>
       <c r="L62" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M62" s="7"/>
       <c r="N62" s="6"/>
@@ -5835,22 +6066,26 @@
         <v>11142.6</v>
       </c>
       <c r="W62" s="6"/>
+      <c r="X62" s="9" t="str">
+        <f aca="false">IF(S62=0,"",IF(ISNUMBER(SEARCH(",",U62)),LEFT(IF(AND(ISNUMBER(G62),G62=T62),IF(H62="","(brand not stated)",H62)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I62),I62=T62),IF(J62="","(brand not stated)",J62)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K62),K62=T62),IF(L62="","(brand not stated)",L62)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M62),M62=T62),IF(N62="","(brand not stated)",N62)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O62),O62=T62),IF(P62="","(brand not stated)",P62)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q62),Q62=T62),IF(R62="","(brand not stated)",R62)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G62),G62=T62),IF(H62="","(brand not stated)",H62)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I62),I62=T62),IF(J62="","(brand not stated)",J62)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K62),K62=T62),IF(L62="","(brand not stated)",L62)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M62),M62=T62),IF(N62="","(brand not stated)",N62)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O62),O62=T62),IF(P62="","(brand not stated)",P62)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q62),Q62=T62),IF(R62="","(brand not stated)",R62)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G62),G62=T62),IF(H62="","(brand not stated)",H62),"")&amp;IF(AND(ISNUMBER(I62),I62=T62),IF(J62="","(brand not stated)",J62),"")&amp;IF(AND(ISNUMBER(K62),K62=T62),IF(L62="","(brand not stated)",L62),"")&amp;IF(AND(ISNUMBER(M62),M62=T62),IF(N62="","(brand not stated)",N62),"")&amp;IF(AND(ISNUMBER(O62),O62=T62),IF(P62="","(brand not stated)",P62),"")&amp;IF(AND(ISNUMBER(Q62),Q62=T62),IF(R62="","(brand not stated)",R62),"")))</f>
+        <v>BETNELAN TAB</v>
+      </c>
     </row>
     <row r="63" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="5" t="n">
         <v>58</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F63" s="5" t="n">
         <v>50</v>
@@ -5863,7 +6098,7 @@
         <v>185.05</v>
       </c>
       <c r="L63" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M63" s="7"/>
       <c r="N63" s="6"/>
@@ -5871,7 +6106,7 @@
         <v>114.75</v>
       </c>
       <c r="P63" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q63" s="7"/>
       <c r="R63" s="6"/>
@@ -5892,22 +6127,26 @@
         <v>5737.5</v>
       </c>
       <c r="W63" s="6"/>
+      <c r="X63" s="9" t="str">
+        <f aca="false">IF(S63=0,"",IF(ISNUMBER(SEARCH(",",U63)),LEFT(IF(AND(ISNUMBER(G63),G63=T63),IF(H63="","(brand not stated)",H63)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I63),I63=T63),IF(J63="","(brand not stated)",J63)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K63),K63=T63),IF(L63="","(brand not stated)",L63)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M63),M63=T63),IF(N63="","(brand not stated)",N63)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O63),O63=T63),IF(P63="","(brand not stated)",P63)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q63),Q63=T63),IF(R63="","(brand not stated)",R63)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G63),G63=T63),IF(H63="","(brand not stated)",H63)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I63),I63=T63),IF(J63="","(brand not stated)",J63)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K63),K63=T63),IF(L63="","(brand not stated)",L63)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M63),M63=T63),IF(N63="","(brand not stated)",N63)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O63),O63=T63),IF(P63="","(brand not stated)",P63)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q63),Q63=T63),IF(R63="","(brand not stated)",R63)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G63),G63=T63),IF(H63="","(brand not stated)",H63),"")&amp;IF(AND(ISNUMBER(I63),I63=T63),IF(J63="","(brand not stated)",J63),"")&amp;IF(AND(ISNUMBER(K63),K63=T63),IF(L63="","(brand not stated)",L63),"")&amp;IF(AND(ISNUMBER(M63),M63=T63),IF(N63="","(brand not stated)",N63),"")&amp;IF(AND(ISNUMBER(O63),O63=T63),IF(P63="","(brand not stated)",P63),"")&amp;IF(AND(ISNUMBER(Q63),Q63=T63),IF(R63="","(brand not stated)",R63),"")))</f>
+        <v>CLOBDERM 20GM CREAM</v>
+      </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="5" t="n">
         <v>59</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F64" s="5" t="n">
         <v>30</v>
@@ -5941,22 +6180,26 @@
         <v/>
       </c>
       <c r="W64" s="6"/>
+      <c r="X64" s="9" t="str">
+        <f aca="false">IF(S64=0,"",IF(ISNUMBER(SEARCH(",",U64)),LEFT(IF(AND(ISNUMBER(G64),G64=T64),IF(H64="","(brand not stated)",H64)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I64),I64=T64),IF(J64="","(brand not stated)",J64)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K64),K64=T64),IF(L64="","(brand not stated)",L64)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M64),M64=T64),IF(N64="","(brand not stated)",N64)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O64),O64=T64),IF(P64="","(brand not stated)",P64)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q64),Q64=T64),IF(R64="","(brand not stated)",R64)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G64),G64=T64),IF(H64="","(brand not stated)",H64)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I64),I64=T64),IF(J64="","(brand not stated)",J64)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K64),K64=T64),IF(L64="","(brand not stated)",L64)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M64),M64=T64),IF(N64="","(brand not stated)",N64)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O64),O64=T64),IF(P64="","(brand not stated)",P64)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q64),Q64=T64),IF(R64="","(brand not stated)",R64)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G64),G64=T64),IF(H64="","(brand not stated)",H64),"")&amp;IF(AND(ISNUMBER(I64),I64=T64),IF(J64="","(brand not stated)",J64),"")&amp;IF(AND(ISNUMBER(K64),K64=T64),IF(L64="","(brand not stated)",L64),"")&amp;IF(AND(ISNUMBER(M64),M64=T64),IF(N64="","(brand not stated)",N64),"")&amp;IF(AND(ISNUMBER(O64),O64=T64),IF(P64="","(brand not stated)",P64),"")&amp;IF(AND(ISNUMBER(Q64),Q64=T64),IF(R64="","(brand not stated)",R64),"")))</f>
+        <v/>
+      </c>
     </row>
     <row r="65" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="5" t="n">
         <v>60</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F65" s="5" t="n">
         <v>100</v>
@@ -5973,7 +6216,7 @@
         <v>136.63</v>
       </c>
       <c r="P65" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q65" s="7"/>
       <c r="R65" s="6"/>
@@ -5994,22 +6237,26 @@
         <v>13663</v>
       </c>
       <c r="W65" s="6"/>
+      <c r="X65" s="9" t="str">
+        <f aca="false">IF(S65=0,"",IF(ISNUMBER(SEARCH(",",U65)),LEFT(IF(AND(ISNUMBER(G65),G65=T65),IF(H65="","(brand not stated)",H65)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I65),I65=T65),IF(J65="","(brand not stated)",J65)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K65),K65=T65),IF(L65="","(brand not stated)",L65)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M65),M65=T65),IF(N65="","(brand not stated)",N65)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O65),O65=T65),IF(P65="","(brand not stated)",P65)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q65),Q65=T65),IF(R65="","(brand not stated)",R65)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G65),G65=T65),IF(H65="","(brand not stated)",H65)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I65),I65=T65),IF(J65="","(brand not stated)",J65)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K65),K65=T65),IF(L65="","(brand not stated)",L65)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M65),M65=T65),IF(N65="","(brand not stated)",N65)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O65),O65=T65),IF(P65="","(brand not stated)",P65)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q65),Q65=T65),IF(R65="","(brand not stated)",R65)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G65),G65=T65),IF(H65="","(brand not stated)",H65),"")&amp;IF(AND(ISNUMBER(I65),I65=T65),IF(J65="","(brand not stated)",J65),"")&amp;IF(AND(ISNUMBER(K65),K65=T65),IF(L65="","(brand not stated)",L65),"")&amp;IF(AND(ISNUMBER(M65),M65=T65),IF(N65="","(brand not stated)",N65),"")&amp;IF(AND(ISNUMBER(O65),O65=T65),IF(P65="","(brand not stated)",P65),"")&amp;IF(AND(ISNUMBER(Q65),Q65=T65),IF(R65="","(brand not stated)",R65),"")))</f>
+        <v>SCABFREE 60ML LOTION</v>
+      </c>
     </row>
     <row r="66" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="5" t="n">
         <v>61</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F66" s="5" t="n">
         <v>100</v>
@@ -6026,7 +6273,7 @@
         <v>107.1</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q66" s="7"/>
       <c r="R66" s="6"/>
@@ -6047,22 +6294,26 @@
         <v>10710</v>
       </c>
       <c r="W66" s="6"/>
+      <c r="X66" s="9" t="str">
+        <f aca="false">IF(S66=0,"",IF(ISNUMBER(SEARCH(",",U66)),LEFT(IF(AND(ISNUMBER(G66),G66=T66),IF(H66="","(brand not stated)",H66)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I66),I66=T66),IF(J66="","(brand not stated)",J66)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K66),K66=T66),IF(L66="","(brand not stated)",L66)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M66),M66=T66),IF(N66="","(brand not stated)",N66)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O66),O66=T66),IF(P66="","(brand not stated)",P66)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q66),Q66=T66),IF(R66="","(brand not stated)",R66)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G66),G66=T66),IF(H66="","(brand not stated)",H66)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I66),I66=T66),IF(J66="","(brand not stated)",J66)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K66),K66=T66),IF(L66="","(brand not stated)",L66)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M66),M66=T66),IF(N66="","(brand not stated)",N66)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O66),O66=T66),IF(P66="","(brand not stated)",P66)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q66),Q66=T66),IF(R66="","(brand not stated)",R66)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G66),G66=T66),IF(H66="","(brand not stated)",H66),"")&amp;IF(AND(ISNUMBER(I66),I66=T66),IF(J66="","(brand not stated)",J66),"")&amp;IF(AND(ISNUMBER(K66),K66=T66),IF(L66="","(brand not stated)",L66),"")&amp;IF(AND(ISNUMBER(M66),M66=T66),IF(N66="","(brand not stated)",N66),"")&amp;IF(AND(ISNUMBER(O66),O66=T66),IF(P66="","(brand not stated)",P66),"")&amp;IF(AND(ISNUMBER(Q66),Q66=T66),IF(R66="","(brand not stated)",R66),"")))</f>
+        <v>NORSALINE-P NASAL DROP</v>
+      </c>
     </row>
     <row r="67" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="5" t="n">
         <v>62</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F67" s="5" t="n">
         <v>100</v>
@@ -6073,7 +6324,7 @@
         <v>81.33</v>
       </c>
       <c r="J67" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K67" s="7"/>
       <c r="L67" s="6"/>
@@ -6100,22 +6351,26 @@
         <v>8133</v>
       </c>
       <c r="W67" s="6"/>
+      <c r="X67" s="9" t="str">
+        <f aca="false">IF(S67=0,"",IF(ISNUMBER(SEARCH(",",U67)),LEFT(IF(AND(ISNUMBER(G67),G67=T67),IF(H67="","(brand not stated)",H67)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I67),I67=T67),IF(J67="","(brand not stated)",J67)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K67),K67=T67),IF(L67="","(brand not stated)",L67)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M67),M67=T67),IF(N67="","(brand not stated)",N67)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O67),O67=T67),IF(P67="","(brand not stated)",P67)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q67),Q67=T67),IF(R67="","(brand not stated)",R67)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G67),G67=T67),IF(H67="","(brand not stated)",H67)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I67),I67=T67),IF(J67="","(brand not stated)",J67)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K67),K67=T67),IF(L67="","(brand not stated)",L67)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M67),M67=T67),IF(N67="","(brand not stated)",N67)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O67),O67=T67),IF(P67="","(brand not stated)",P67)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q67),Q67=T67),IF(R67="","(brand not stated)",R67)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G67),G67=T67),IF(H67="","(brand not stated)",H67),"")&amp;IF(AND(ISNUMBER(I67),I67=T67),IF(J67="","(brand not stated)",J67),"")&amp;IF(AND(ISNUMBER(K67),K67=T67),IF(L67="","(brand not stated)",L67),"")&amp;IF(AND(ISNUMBER(M67),M67=T67),IF(N67="","(brand not stated)",N67),"")&amp;IF(AND(ISNUMBER(O67),O67=T67),IF(P67="","(brand not stated)",P67),"")&amp;IF(AND(ISNUMBER(Q67),Q67=T67),IF(R67="","(brand not stated)",R67),"")))</f>
+        <v>Zafa</v>
+      </c>
     </row>
     <row r="68" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="5" t="n">
         <v>63</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F68" s="5" t="n">
         <v>120</v>
@@ -6132,7 +6387,7 @@
         <v>179.37</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q68" s="7"/>
       <c r="R68" s="6"/>
@@ -6153,22 +6408,26 @@
         <v>21524.4</v>
       </c>
       <c r="W68" s="6"/>
+      <c r="X68" s="9" t="str">
+        <f aca="false">IF(S68=0,"",IF(ISNUMBER(SEARCH(",",U68)),LEFT(IF(AND(ISNUMBER(G68),G68=T68),IF(H68="","(brand not stated)",H68)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I68),I68=T68),IF(J68="","(brand not stated)",J68)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K68),K68=T68),IF(L68="","(brand not stated)",L68)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M68),M68=T68),IF(N68="","(brand not stated)",N68)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O68),O68=T68),IF(P68="","(brand not stated)",P68)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q68),Q68=T68),IF(R68="","(brand not stated)",R68)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G68),G68=T68),IF(H68="","(brand not stated)",H68)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I68),I68=T68),IF(J68="","(brand not stated)",J68)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K68),K68=T68),IF(L68="","(brand not stated)",L68)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M68),M68=T68),IF(N68="","(brand not stated)",N68)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O68),O68=T68),IF(P68="","(brand not stated)",P68)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q68),Q68=T68),IF(R68="","(brand not stated)",R68)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G68),G68=T68),IF(H68="","(brand not stated)",H68),"")&amp;IF(AND(ISNUMBER(I68),I68=T68),IF(J68="","(brand not stated)",J68),"")&amp;IF(AND(ISNUMBER(K68),K68=T68),IF(L68="","(brand not stated)",L68),"")&amp;IF(AND(ISNUMBER(M68),M68=T68),IF(N68="","(brand not stated)",N68),"")&amp;IF(AND(ISNUMBER(O68),O68=T68),IF(P68="","(brand not stated)",P68),"")&amp;IF(AND(ISNUMBER(Q68),Q68=T68),IF(R68="","(brand not stated)",R68),"")))</f>
+        <v>GLUCOPHAGE 500MG TABLET</v>
+      </c>
     </row>
     <row r="69" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="5" t="n">
         <v>64</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F69" s="5" t="n">
         <v>25</v>
@@ -6179,7 +6438,7 @@
         <v>853.56</v>
       </c>
       <c r="J69" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K69" s="7"/>
       <c r="L69" s="6"/>
@@ -6189,7 +6448,7 @@
         <v>492.66</v>
       </c>
       <c r="P69" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q69" s="7"/>
       <c r="R69" s="6"/>
@@ -6210,20 +6469,24 @@
         <v>12316.5</v>
       </c>
       <c r="W69" s="6"/>
+      <c r="X69" s="9" t="str">
+        <f aca="false">IF(S69=0,"",IF(ISNUMBER(SEARCH(",",U69)),LEFT(IF(AND(ISNUMBER(G69),G69=T69),IF(H69="","(brand not stated)",H69)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I69),I69=T69),IF(J69="","(brand not stated)",J69)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K69),K69=T69),IF(L69="","(brand not stated)",L69)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M69),M69=T69),IF(N69="","(brand not stated)",N69)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O69),O69=T69),IF(P69="","(brand not stated)",P69)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q69),Q69=T69),IF(R69="","(brand not stated)",R69)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G69),G69=T69),IF(H69="","(brand not stated)",H69)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I69),I69=T69),IF(J69="","(brand not stated)",J69)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K69),K69=T69),IF(L69="","(brand not stated)",L69)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M69),M69=T69),IF(N69="","(brand not stated)",N69)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O69),O69=T69),IF(P69="","(brand not stated)",P69)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q69),Q69=T69),IF(R69="","(brand not stated)",R69)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G69),G69=T69),IF(H69="","(brand not stated)",H69),"")&amp;IF(AND(ISNUMBER(I69),I69=T69),IF(J69="","(brand not stated)",J69),"")&amp;IF(AND(ISNUMBER(K69),K69=T69),IF(L69="","(brand not stated)",L69),"")&amp;IF(AND(ISNUMBER(M69),M69=T69),IF(N69="","(brand not stated)",N69),"")&amp;IF(AND(ISNUMBER(O69),O69=T69),IF(P69="","(brand not stated)",P69),"")&amp;IF(AND(ISNUMBER(Q69),Q69=T69),IF(R69="","(brand not stated)",R69),"")))</f>
+        <v>RAMIPACE 2.5MG TABLET</v>
+      </c>
     </row>
     <row r="70" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="5" t="n">
         <v>65</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D70" s="6"/>
       <c r="E70" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F70" s="5" t="n">
         <v>50</v>
@@ -6232,7 +6495,7 @@
         <v>600.95</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="I70" s="7"/>
       <c r="J70" s="6"/>
@@ -6240,7 +6503,7 @@
         <v>617.96</v>
       </c>
       <c r="L70" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="M70" s="7"/>
       <c r="N70" s="6"/>
@@ -6265,22 +6528,26 @@
         <v>30047.5</v>
       </c>
       <c r="W70" s="6"/>
+      <c r="X70" s="9" t="str">
+        <f aca="false">IF(S70=0,"",IF(ISNUMBER(SEARCH(",",U70)),LEFT(IF(AND(ISNUMBER(G70),G70=T70),IF(H70="","(brand not stated)",H70)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I70),I70=T70),IF(J70="","(brand not stated)",J70)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K70),K70=T70),IF(L70="","(brand not stated)",L70)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M70),M70=T70),IF(N70="","(brand not stated)",N70)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O70),O70=T70),IF(P70="","(brand not stated)",P70)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q70),Q70=T70),IF(R70="","(brand not stated)",R70)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G70),G70=T70),IF(H70="","(brand not stated)",H70)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I70),I70=T70),IF(J70="","(brand not stated)",J70)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K70),K70=T70),IF(L70="","(brand not stated)",L70)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M70),M70=T70),IF(N70="","(brand not stated)",N70)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O70),O70=T70),IF(P70="","(brand not stated)",P70)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q70),Q70=T70),IF(R70="","(brand not stated)",R70)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G70),G70=T70),IF(H70="","(brand not stated)",H70),"")&amp;IF(AND(ISNUMBER(I70),I70=T70),IF(J70="","(brand not stated)",J70),"")&amp;IF(AND(ISNUMBER(K70),K70=T70),IF(L70="","(brand not stated)",L70),"")&amp;IF(AND(ISNUMBER(M70),M70=T70),IF(N70="","(brand not stated)",N70),"")&amp;IF(AND(ISNUMBER(O70),O70=T70),IF(P70="","(brand not stated)",P70),"")&amp;IF(AND(ISNUMBER(Q70),Q70=T70),IF(R70="","(brand not stated)",R70),"")))</f>
+        <v>FEBROL</v>
+      </c>
     </row>
     <row r="71" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="5" t="n">
         <v>66</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F71" s="5" t="n">
         <v>30</v>
@@ -6291,7 +6558,7 @@
         <v>994.5</v>
       </c>
       <c r="J71" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K71" s="7"/>
       <c r="L71" s="6"/>
@@ -6299,7 +6566,7 @@
         <v>586.5</v>
       </c>
       <c r="N71" s="6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O71" s="7"/>
       <c r="P71" s="6"/>
@@ -6322,22 +6589,26 @@
         <v>17595</v>
       </c>
       <c r="W71" s="6"/>
+      <c r="X71" s="9" t="str">
+        <f aca="false">IF(S71=0,"",IF(ISNUMBER(SEARCH(",",U71)),LEFT(IF(AND(ISNUMBER(G71),G71=T71),IF(H71="","(brand not stated)",H71)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I71),I71=T71),IF(J71="","(brand not stated)",J71)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K71),K71=T71),IF(L71="","(brand not stated)",L71)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M71),M71=T71),IF(N71="","(brand not stated)",N71)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O71),O71=T71),IF(P71="","(brand not stated)",P71)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q71),Q71=T71),IF(R71="","(brand not stated)",R71)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G71),G71=T71),IF(H71="","(brand not stated)",H71)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I71),I71=T71),IF(J71="","(brand not stated)",J71)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K71),K71=T71),IF(L71="","(brand not stated)",L71)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M71),M71=T71),IF(N71="","(brand not stated)",N71)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O71),O71=T71),IF(P71="","(brand not stated)",P71)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q71),Q71=T71),IF(R71="","(brand not stated)",R71)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G71),G71=T71),IF(H71="","(brand not stated)",H71),"")&amp;IF(AND(ISNUMBER(I71),I71=T71),IF(J71="","(brand not stated)",J71),"")&amp;IF(AND(ISNUMBER(K71),K71=T71),IF(L71="","(brand not stated)",L71),"")&amp;IF(AND(ISNUMBER(M71),M71=T71),IF(N71="","(brand not stated)",N71),"")&amp;IF(AND(ISNUMBER(O71),O71=T71),IF(P71="","(brand not stated)",P71),"")&amp;IF(AND(ISNUMBER(Q71),Q71=T71),IF(R71="","(brand not stated)",R71),"")))</f>
+        <v>GETFORMIN (GETZ)</v>
+      </c>
     </row>
     <row r="72" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="5" t="n">
         <v>67</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F72" s="5" t="n">
         <v>200</v>
@@ -6348,7 +6619,7 @@
         <v>49.24</v>
       </c>
       <c r="J72" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K72" s="7"/>
       <c r="L72" s="6"/>
@@ -6375,22 +6646,26 @@
         <v>9848</v>
       </c>
       <c r="W72" s="6"/>
+      <c r="X72" s="9" t="str">
+        <f aca="false">IF(S72=0,"",IF(ISNUMBER(SEARCH(",",U72)),LEFT(IF(AND(ISNUMBER(G72),G72=T72),IF(H72="","(brand not stated)",H72)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I72),I72=T72),IF(J72="","(brand not stated)",J72)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K72),K72=T72),IF(L72="","(brand not stated)",L72)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M72),M72=T72),IF(N72="","(brand not stated)",N72)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O72),O72=T72),IF(P72="","(brand not stated)",P72)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q72),Q72=T72),IF(R72="","(brand not stated)",R72)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G72),G72=T72),IF(H72="","(brand not stated)",H72)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I72),I72=T72),IF(J72="","(brand not stated)",J72)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K72),K72=T72),IF(L72="","(brand not stated)",L72)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M72),M72=T72),IF(N72="","(brand not stated)",N72)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O72),O72=T72),IF(P72="","(brand not stated)",P72)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q72),Q72=T72),IF(R72="","(brand not stated)",R72)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G72),G72=T72),IF(H72="","(brand not stated)",H72),"")&amp;IF(AND(ISNUMBER(I72),I72=T72),IF(J72="","(brand not stated)",J72),"")&amp;IF(AND(ISNUMBER(K72),K72=T72),IF(L72="","(brand not stated)",L72),"")&amp;IF(AND(ISNUMBER(M72),M72=T72),IF(N72="","(brand not stated)",N72),"")&amp;IF(AND(ISNUMBER(O72),O72=T72),IF(P72="","(brand not stated)",P72),"")&amp;IF(AND(ISNUMBER(Q72),Q72=T72),IF(R72="","(brand not stated)",R72),"")))</f>
+        <v>Zafa</v>
+      </c>
     </row>
     <row r="73" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="5" t="n">
         <v>68</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F73" s="5" t="n">
         <v>100</v>
@@ -6403,7 +6678,7 @@
         <v>86.1</v>
       </c>
       <c r="L73" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M73" s="7"/>
       <c r="N73" s="6"/>
@@ -6428,22 +6703,26 @@
         <v>8610</v>
       </c>
       <c r="W73" s="6"/>
+      <c r="X73" s="9" t="str">
+        <f aca="false">IF(S73=0,"",IF(ISNUMBER(SEARCH(",",U73)),LEFT(IF(AND(ISNUMBER(G73),G73=T73),IF(H73="","(brand not stated)",H73)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I73),I73=T73),IF(J73="","(brand not stated)",J73)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K73),K73=T73),IF(L73="","(brand not stated)",L73)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M73),M73=T73),IF(N73="","(brand not stated)",N73)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O73),O73=T73),IF(P73="","(brand not stated)",P73)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q73),Q73=T73),IF(R73="","(brand not stated)",R73)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G73),G73=T73),IF(H73="","(brand not stated)",H73)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I73),I73=T73),IF(J73="","(brand not stated)",J73)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K73),K73=T73),IF(L73="","(brand not stated)",L73)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M73),M73=T73),IF(N73="","(brand not stated)",N73)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O73),O73=T73),IF(P73="","(brand not stated)",P73)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q73),Q73=T73),IF(R73="","(brand not stated)",R73)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G73),G73=T73),IF(H73="","(brand not stated)",H73),"")&amp;IF(AND(ISNUMBER(I73),I73=T73),IF(J73="","(brand not stated)",J73),"")&amp;IF(AND(ISNUMBER(K73),K73=T73),IF(L73="","(brand not stated)",L73),"")&amp;IF(AND(ISNUMBER(M73),M73=T73),IF(N73="","(brand not stated)",N73),"")&amp;IF(AND(ISNUMBER(O73),O73=T73),IF(P73="","(brand not stated)",P73),"")&amp;IF(AND(ISNUMBER(Q73),Q73=T73),IF(R73="","(brand not stated)",R73),"")))</f>
+        <v>PANADOL DROP</v>
+      </c>
     </row>
     <row r="74" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="5" t="n">
         <v>69</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F74" s="5" t="n">
         <v>50</v>
@@ -6452,7 +6731,7 @@
         <v>348.5</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="I74" s="7"/>
       <c r="J74" s="6"/>
@@ -6464,7 +6743,7 @@
         <v>226.44</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q74" s="7"/>
       <c r="R74" s="6"/>
@@ -6485,22 +6764,26 @@
         <v>11322</v>
       </c>
       <c r="W74" s="6"/>
+      <c r="X74" s="9" t="str">
+        <f aca="false">IF(S74=0,"",IF(ISNUMBER(SEARCH(",",U74)),LEFT(IF(AND(ISNUMBER(G74),G74=T74),IF(H74="","(brand not stated)",H74)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I74),I74=T74),IF(J74="","(brand not stated)",J74)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K74),K74=T74),IF(L74="","(brand not stated)",L74)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M74),M74=T74),IF(N74="","(brand not stated)",N74)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O74),O74=T74),IF(P74="","(brand not stated)",P74)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q74),Q74=T74),IF(R74="","(brand not stated)",R74)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G74),G74=T74),IF(H74="","(brand not stated)",H74)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I74),I74=T74),IF(J74="","(brand not stated)",J74)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K74),K74=T74),IF(L74="","(brand not stated)",L74)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M74),M74=T74),IF(N74="","(brand not stated)",N74)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O74),O74=T74),IF(P74="","(brand not stated)",P74)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q74),Q74=T74),IF(R74="","(brand not stated)",R74)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G74),G74=T74),IF(H74="","(brand not stated)",H74),"")&amp;IF(AND(ISNUMBER(I74),I74=T74),IF(J74="","(brand not stated)",J74),"")&amp;IF(AND(ISNUMBER(K74),K74=T74),IF(L74="","(brand not stated)",L74),"")&amp;IF(AND(ISNUMBER(M74),M74=T74),IF(N74="","(brand not stated)",N74),"")&amp;IF(AND(ISNUMBER(O74),O74=T74),IF(P74="","(brand not stated)",P74),"")&amp;IF(AND(ISNUMBER(Q74),Q74=T74),IF(R74="","(brand not stated)",R74),"")))</f>
+        <v>AZOLAM 0.5MG TABLET</v>
+      </c>
     </row>
     <row r="75" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="5" t="n">
         <v>70</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F75" s="5" t="n">
         <v>50</v>
@@ -6513,7 +6796,7 @@
         <v>452.2</v>
       </c>
       <c r="L75" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M75" s="7"/>
       <c r="N75" s="6"/>
@@ -6521,13 +6804,13 @@
         <v>764.15</v>
       </c>
       <c r="P75" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q75" s="7" t="n">
         <v>382.5</v>
       </c>
       <c r="R75" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="S75" s="5" t="n">
         <f aca="false">COUNT(G75,I75,K75,M75,O75,Q75)</f>
@@ -6546,22 +6829,26 @@
         <v>19125</v>
       </c>
       <c r="W75" s="6"/>
+      <c r="X75" s="9" t="str">
+        <f aca="false">IF(S75=0,"",IF(ISNUMBER(SEARCH(",",U75)),LEFT(IF(AND(ISNUMBER(G75),G75=T75),IF(H75="","(brand not stated)",H75)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I75),I75=T75),IF(J75="","(brand not stated)",J75)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K75),K75=T75),IF(L75="","(brand not stated)",L75)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M75),M75=T75),IF(N75="","(brand not stated)",N75)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O75),O75=T75),IF(P75="","(brand not stated)",P75)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q75),Q75=T75),IF(R75="","(brand not stated)",R75)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G75),G75=T75),IF(H75="","(brand not stated)",H75)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I75),I75=T75),IF(J75="","(brand not stated)",J75)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K75),K75=T75),IF(L75="","(brand not stated)",L75)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M75),M75=T75),IF(N75="","(brand not stated)",N75)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O75),O75=T75),IF(P75="","(brand not stated)",P75)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q75),Q75=T75),IF(R75="","(brand not stated)",R75)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G75),G75=T75),IF(H75="","(brand not stated)",H75),"")&amp;IF(AND(ISNUMBER(I75),I75=T75),IF(J75="","(brand not stated)",J75),"")&amp;IF(AND(ISNUMBER(K75),K75=T75),IF(L75="","(brand not stated)",L75),"")&amp;IF(AND(ISNUMBER(M75),M75=T75),IF(N75="","(brand not stated)",N75),"")&amp;IF(AND(ISNUMBER(O75),O75=T75),IF(P75="","(brand not stated)",P75),"")&amp;IF(AND(ISNUMBER(Q75),Q75=T75),IF(R75="","(brand not stated)",R75),"")))</f>
+        <v>Dolonap</v>
+      </c>
     </row>
     <row r="76" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="5" t="n">
         <v>71</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F76" s="5" t="n">
         <v>600</v>
@@ -6570,7 +6857,7 @@
         <v>272</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I76" s="7"/>
       <c r="J76" s="6"/>
@@ -6578,19 +6865,19 @@
         <v>244.8</v>
       </c>
       <c r="L76" s="6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M76" s="7" t="n">
         <v>1156</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O76" s="7" t="n">
         <v>223.21</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q76" s="7"/>
       <c r="R76" s="6"/>
@@ -6611,22 +6898,26 @@
         <v>133926</v>
       </c>
       <c r="W76" s="6"/>
+      <c r="X76" s="9" t="str">
+        <f aca="false">IF(S76=0,"",IF(ISNUMBER(SEARCH(",",U76)),LEFT(IF(AND(ISNUMBER(G76),G76=T76),IF(H76="","(brand not stated)",H76)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I76),I76=T76),IF(J76="","(brand not stated)",J76)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K76),K76=T76),IF(L76="","(brand not stated)",L76)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M76),M76=T76),IF(N76="","(brand not stated)",N76)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O76),O76=T76),IF(P76="","(brand not stated)",P76)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q76),Q76=T76),IF(R76="","(brand not stated)",R76)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G76),G76=T76),IF(H76="","(brand not stated)",H76)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I76),I76=T76),IF(J76="","(brand not stated)",J76)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K76),K76=T76),IF(L76="","(brand not stated)",L76)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M76),M76=T76),IF(N76="","(brand not stated)",N76)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O76),O76=T76),IF(P76="","(brand not stated)",P76)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q76),Q76=T76),IF(R76="","(brand not stated)",R76)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G76),G76=T76),IF(H76="","(brand not stated)",H76),"")&amp;IF(AND(ISNUMBER(I76),I76=T76),IF(J76="","(brand not stated)",J76),"")&amp;IF(AND(ISNUMBER(K76),K76=T76),IF(L76="","(brand not stated)",L76),"")&amp;IF(AND(ISNUMBER(M76),M76=T76),IF(N76="","(brand not stated)",N76),"")&amp;IF(AND(ISNUMBER(O76),O76=T76),IF(P76="","(brand not stated)",P76),"")&amp;IF(AND(ISNUMBER(Q76),Q76=T76),IF(R76="","(brand not stated)",R76),"")))</f>
+        <v>ROSULIN 10MG TABLET</v>
+      </c>
     </row>
     <row r="77" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="5" t="n">
         <v>72</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F77" s="5" t="n">
         <v>120</v>
@@ -6637,7 +6928,7 @@
         <v>157.2</v>
       </c>
       <c r="J77" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K77" s="7"/>
       <c r="L77" s="6"/>
@@ -6664,22 +6955,26 @@
         <v>18864</v>
       </c>
       <c r="W77" s="6"/>
+      <c r="X77" s="9" t="str">
+        <f aca="false">IF(S77=0,"",IF(ISNUMBER(SEARCH(",",U77)),LEFT(IF(AND(ISNUMBER(G77),G77=T77),IF(H77="","(brand not stated)",H77)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I77),I77=T77),IF(J77="","(brand not stated)",J77)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K77),K77=T77),IF(L77="","(brand not stated)",L77)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M77),M77=T77),IF(N77="","(brand not stated)",N77)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O77),O77=T77),IF(P77="","(brand not stated)",P77)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q77),Q77=T77),IF(R77="","(brand not stated)",R77)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G77),G77=T77),IF(H77="","(brand not stated)",H77)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I77),I77=T77),IF(J77="","(brand not stated)",J77)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K77),K77=T77),IF(L77="","(brand not stated)",L77)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M77),M77=T77),IF(N77="","(brand not stated)",N77)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O77),O77=T77),IF(P77="","(brand not stated)",P77)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q77),Q77=T77),IF(R77="","(brand not stated)",R77)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G77),G77=T77),IF(H77="","(brand not stated)",H77),"")&amp;IF(AND(ISNUMBER(I77),I77=T77),IF(J77="","(brand not stated)",J77),"")&amp;IF(AND(ISNUMBER(K77),K77=T77),IF(L77="","(brand not stated)",L77),"")&amp;IF(AND(ISNUMBER(M77),M77=T77),IF(N77="","(brand not stated)",N77),"")&amp;IF(AND(ISNUMBER(O77),O77=T77),IF(P77="","(brand not stated)",P77),"")&amp;IF(AND(ISNUMBER(Q77),Q77=T77),IF(R77="","(brand not stated)",R77),"")))</f>
+        <v>Hochest</v>
+      </c>
     </row>
     <row r="78" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="5" t="n">
         <v>73</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F78" s="5" t="n">
         <v>150</v>
@@ -6694,13 +6989,13 @@
         <v>565.25</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O78" s="7" t="n">
         <v>578</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q78" s="7"/>
       <c r="R78" s="6"/>
@@ -6721,22 +7016,26 @@
         <v>84787.5</v>
       </c>
       <c r="W78" s="6"/>
+      <c r="X78" s="9" t="str">
+        <f aca="false">IF(S78=0,"",IF(ISNUMBER(SEARCH(",",U78)),LEFT(IF(AND(ISNUMBER(G78),G78=T78),IF(H78="","(brand not stated)",H78)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I78),I78=T78),IF(J78="","(brand not stated)",J78)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K78),K78=T78),IF(L78="","(brand not stated)",L78)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M78),M78=T78),IF(N78="","(brand not stated)",N78)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O78),O78=T78),IF(P78="","(brand not stated)",P78)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q78),Q78=T78),IF(R78="","(brand not stated)",R78)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G78),G78=T78),IF(H78="","(brand not stated)",H78)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I78),I78=T78),IF(J78="","(brand not stated)",J78)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K78),K78=T78),IF(L78="","(brand not stated)",L78)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M78),M78=T78),IF(N78="","(brand not stated)",N78)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O78),O78=T78),IF(P78="","(brand not stated)",P78)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q78),Q78=T78),IF(R78="","(brand not stated)",R78)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G78),G78=T78),IF(H78="","(brand not stated)",H78),"")&amp;IF(AND(ISNUMBER(I78),I78=T78),IF(J78="","(brand not stated)",J78),"")&amp;IF(AND(ISNUMBER(K78),K78=T78),IF(L78="","(brand not stated)",L78),"")&amp;IF(AND(ISNUMBER(M78),M78=T78),IF(N78="","(brand not stated)",N78),"")&amp;IF(AND(ISNUMBER(O78),O78=T78),IF(P78="","(brand not stated)",P78),"")&amp;IF(AND(ISNUMBER(Q78),Q78=T78),IF(R78="","(brand not stated)",R78),"")))</f>
+        <v>TREVIA-R 2 (GETZ)</v>
+      </c>
     </row>
     <row r="79" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="5" t="n">
         <v>74</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F79" s="5" t="n">
         <v>50</v>
@@ -6745,7 +7044,7 @@
         <v>417.35</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="I79" s="7"/>
       <c r="J79" s="6"/>
@@ -6755,13 +7054,13 @@
         <v>336.52</v>
       </c>
       <c r="N79" s="6" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="O79" s="7" t="n">
         <v>221</v>
       </c>
       <c r="P79" s="6" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q79" s="7"/>
       <c r="R79" s="6"/>
@@ -6782,22 +7081,26 @@
         <v>11050</v>
       </c>
       <c r="W79" s="6"/>
+      <c r="X79" s="9" t="str">
+        <f aca="false">IF(S79=0,"",IF(ISNUMBER(SEARCH(",",U79)),LEFT(IF(AND(ISNUMBER(G79),G79=T79),IF(H79="","(brand not stated)",H79)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I79),I79=T79),IF(J79="","(brand not stated)",J79)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K79),K79=T79),IF(L79="","(brand not stated)",L79)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M79),M79=T79),IF(N79="","(brand not stated)",N79)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O79),O79=T79),IF(P79="","(brand not stated)",P79)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q79),Q79=T79),IF(R79="","(brand not stated)",R79)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G79),G79=T79),IF(H79="","(brand not stated)",H79)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I79),I79=T79),IF(J79="","(brand not stated)",J79)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K79),K79=T79),IF(L79="","(brand not stated)",L79)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M79),M79=T79),IF(N79="","(brand not stated)",N79)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O79),O79=T79),IF(P79="","(brand not stated)",P79)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q79),Q79=T79),IF(R79="","(brand not stated)",R79)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G79),G79=T79),IF(H79="","(brand not stated)",H79),"")&amp;IF(AND(ISNUMBER(I79),I79=T79),IF(J79="","(brand not stated)",J79),"")&amp;IF(AND(ISNUMBER(K79),K79=T79),IF(L79="","(brand not stated)",L79),"")&amp;IF(AND(ISNUMBER(M79),M79=T79),IF(N79="","(brand not stated)",N79),"")&amp;IF(AND(ISNUMBER(O79),O79=T79),IF(P79="","(brand not stated)",P79),"")&amp;IF(AND(ISNUMBER(Q79),Q79=T79),IF(R79="","(brand not stated)",R79),"")))</f>
+        <v>ATCOPRAM 10MG TABLET</v>
+      </c>
     </row>
     <row r="80" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="5" t="n">
         <v>75</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F80" s="5" t="n">
         <v>100</v>
@@ -6814,7 +7117,7 @@
         <v>198.14</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q80" s="7"/>
       <c r="R80" s="6"/>
@@ -6835,22 +7138,26 @@
         <v>19814</v>
       </c>
       <c r="W80" s="6"/>
+      <c r="X80" s="9" t="str">
+        <f aca="false">IF(S80=0,"",IF(ISNUMBER(SEARCH(",",U80)),LEFT(IF(AND(ISNUMBER(G80),G80=T80),IF(H80="","(brand not stated)",H80)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I80),I80=T80),IF(J80="","(brand not stated)",J80)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K80),K80=T80),IF(L80="","(brand not stated)",L80)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M80),M80=T80),IF(N80="","(brand not stated)",N80)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O80),O80=T80),IF(P80="","(brand not stated)",P80)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q80),Q80=T80),IF(R80="","(brand not stated)",R80)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G80),G80=T80),IF(H80="","(brand not stated)",H80)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I80),I80=T80),IF(J80="","(brand not stated)",J80)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K80),K80=T80),IF(L80="","(brand not stated)",L80)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M80),M80=T80),IF(N80="","(brand not stated)",N80)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O80),O80=T80),IF(P80="","(brand not stated)",P80)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q80),Q80=T80),IF(R80="","(brand not stated)",R80)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G80),G80=T80),IF(H80="","(brand not stated)",H80),"")&amp;IF(AND(ISNUMBER(I80),I80=T80),IF(J80="","(brand not stated)",J80),"")&amp;IF(AND(ISNUMBER(K80),K80=T80),IF(L80="","(brand not stated)",L80),"")&amp;IF(AND(ISNUMBER(M80),M80=T80),IF(N80="","(brand not stated)",N80),"")&amp;IF(AND(ISNUMBER(O80),O80=T80),IF(P80="","(brand not stated)",P80),"")&amp;IF(AND(ISNUMBER(Q80),Q80=T80),IF(R80="","(brand not stated)",R80),"")))</f>
+        <v>CLOBDERM S 60ML LOTION</v>
+      </c>
     </row>
     <row r="81" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="5" t="n">
         <v>76</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F81" s="5" t="n">
         <v>500</v>
@@ -6861,25 +7168,25 @@
         <v>1440.67</v>
       </c>
       <c r="J81" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K81" s="7" t="n">
         <v>390.15</v>
       </c>
       <c r="L81" s="6" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M81" s="7" t="n">
         <v>786.11</v>
       </c>
       <c r="N81" s="6" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="O81" s="7" t="n">
         <v>427.98</v>
       </c>
       <c r="P81" s="6" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q81" s="7"/>
       <c r="R81" s="6"/>
@@ -6900,22 +7207,26 @@
         <v>195075</v>
       </c>
       <c r="W81" s="6"/>
+      <c r="X81" s="9" t="str">
+        <f aca="false">IF(S81=0,"",IF(ISNUMBER(SEARCH(",",U81)),LEFT(IF(AND(ISNUMBER(G81),G81=T81),IF(H81="","(brand not stated)",H81)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I81),I81=T81),IF(J81="","(brand not stated)",J81)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K81),K81=T81),IF(L81="","(brand not stated)",L81)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M81),M81=T81),IF(N81="","(brand not stated)",N81)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O81),O81=T81),IF(P81="","(brand not stated)",P81)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q81),Q81=T81),IF(R81="","(brand not stated)",R81)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G81),G81=T81),IF(H81="","(brand not stated)",H81)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I81),I81=T81),IF(J81="","(brand not stated)",J81)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K81),K81=T81),IF(L81="","(brand not stated)",L81)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M81),M81=T81),IF(N81="","(brand not stated)",N81)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O81),O81=T81),IF(P81="","(brand not stated)",P81)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q81),Q81=T81),IF(R81="","(brand not stated)",R81)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G81),G81=T81),IF(H81="","(brand not stated)",H81),"")&amp;IF(AND(ISNUMBER(I81),I81=T81),IF(J81="","(brand not stated)",J81),"")&amp;IF(AND(ISNUMBER(K81),K81=T81),IF(L81="","(brand not stated)",L81),"")&amp;IF(AND(ISNUMBER(M81),M81=T81),IF(N81="","(brand not stated)",N81),"")&amp;IF(AND(ISNUMBER(O81),O81=T81),IF(P81="","(brand not stated)",P81),"")&amp;IF(AND(ISNUMBER(Q81),Q81=T81),IF(R81="","(brand not stated)",R81),"")))</f>
+        <v>SURBEX Z TAB</v>
+      </c>
     </row>
     <row r="82" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="5" t="n">
         <v>77</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F82" s="5" t="n">
         <v>150</v>
@@ -6924,7 +7235,7 @@
         <v>310.25</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="I82" s="7"/>
       <c r="J82" s="6"/>
@@ -6934,13 +7245,13 @@
         <v>561</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O82" s="7" t="n">
         <v>408</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q82" s="7"/>
       <c r="R82" s="6"/>
@@ -6961,22 +7272,26 @@
         <v>46537.5</v>
       </c>
       <c r="W82" s="6"/>
+      <c r="X82" s="9" t="str">
+        <f aca="false">IF(S82=0,"",IF(ISNUMBER(SEARCH(",",U82)),LEFT(IF(AND(ISNUMBER(G82),G82=T82),IF(H82="","(brand not stated)",H82)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I82),I82=T82),IF(J82="","(brand not stated)",J82)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K82),K82=T82),IF(L82="","(brand not stated)",L82)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M82),M82=T82),IF(N82="","(brand not stated)",N82)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O82),O82=T82),IF(P82="","(brand not stated)",P82)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q82),Q82=T82),IF(R82="","(brand not stated)",R82)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G82),G82=T82),IF(H82="","(brand not stated)",H82)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I82),I82=T82),IF(J82="","(brand not stated)",J82)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K82),K82=T82),IF(L82="","(brand not stated)",L82)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M82),M82=T82),IF(N82="","(brand not stated)",N82)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O82),O82=T82),IF(P82="","(brand not stated)",P82)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q82),Q82=T82),IF(R82="","(brand not stated)",R82)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G82),G82=T82),IF(H82="","(brand not stated)",H82),"")&amp;IF(AND(ISNUMBER(I82),I82=T82),IF(J82="","(brand not stated)",J82),"")&amp;IF(AND(ISNUMBER(K82),K82=T82),IF(L82="","(brand not stated)",L82),"")&amp;IF(AND(ISNUMBER(M82),M82=T82),IF(N82="","(brand not stated)",N82),"")&amp;IF(AND(ISNUMBER(O82),O82=T82),IF(P82="","(brand not stated)",P82),"")&amp;IF(AND(ISNUMBER(Q82),Q82=T82),IF(R82="","(brand not stated)",R82),"")))</f>
+        <v>TRUVA</v>
+      </c>
     </row>
     <row r="83" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="5" t="n">
         <v>78</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F83" s="5" t="n">
         <v>150</v>
@@ -6991,13 +7306,13 @@
         <v>439.45</v>
       </c>
       <c r="N83" s="6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="O83" s="7" t="n">
         <v>138.73</v>
       </c>
       <c r="P83" s="6" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q83" s="7"/>
       <c r="R83" s="6"/>
@@ -7018,22 +7333,26 @@
         <v>20809.5</v>
       </c>
       <c r="W83" s="6"/>
+      <c r="X83" s="9" t="str">
+        <f aca="false">IF(S83=0,"",IF(ISNUMBER(SEARCH(",",U83)),LEFT(IF(AND(ISNUMBER(G83),G83=T83),IF(H83="","(brand not stated)",H83)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I83),I83=T83),IF(J83="","(brand not stated)",J83)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K83),K83=T83),IF(L83="","(brand not stated)",L83)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M83),M83=T83),IF(N83="","(brand not stated)",N83)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O83),O83=T83),IF(P83="","(brand not stated)",P83)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q83),Q83=T83),IF(R83="","(brand not stated)",R83)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G83),G83=T83),IF(H83="","(brand not stated)",H83)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I83),I83=T83),IF(J83="","(brand not stated)",J83)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K83),K83=T83),IF(L83="","(brand not stated)",L83)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M83),M83=T83),IF(N83="","(brand not stated)",N83)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O83),O83=T83),IF(P83="","(brand not stated)",P83)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q83),Q83=T83),IF(R83="","(brand not stated)",R83)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G83),G83=T83),IF(H83="","(brand not stated)",H83),"")&amp;IF(AND(ISNUMBER(I83),I83=T83),IF(J83="","(brand not stated)",J83),"")&amp;IF(AND(ISNUMBER(K83),K83=T83),IF(L83="","(brand not stated)",L83),"")&amp;IF(AND(ISNUMBER(M83),M83=T83),IF(N83="","(brand not stated)",N83),"")&amp;IF(AND(ISNUMBER(O83),O83=T83),IF(P83="","(brand not stated)",P83),"")&amp;IF(AND(ISNUMBER(Q83),Q83=T83),IF(R83="","(brand not stated)",R83),"")))</f>
+        <v>LODOPIN 5MG TABLET</v>
+      </c>
     </row>
     <row r="84" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="5" t="n">
         <v>79</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F84" s="5" t="n">
         <v>450</v>
@@ -7042,7 +7361,7 @@
         <v>204</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="I84" s="7"/>
       <c r="J84" s="6"/>
@@ -7052,19 +7371,19 @@
         <v>357</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O84" s="7" t="n">
         <v>229.075</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q84" s="7" t="n">
         <v>208.08</v>
       </c>
       <c r="R84" s="6" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="S84" s="5" t="n">
         <f aca="false">COUNT(G84,I84,K84,M84,O84,Q84)</f>
@@ -7083,22 +7402,26 @@
         <v>91800</v>
       </c>
       <c r="W84" s="6"/>
+      <c r="X84" s="9" t="str">
+        <f aca="false">IF(S84=0,"",IF(ISNUMBER(SEARCH(",",U84)),LEFT(IF(AND(ISNUMBER(G84),G84=T84),IF(H84="","(brand not stated)",H84)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I84),I84=T84),IF(J84="","(brand not stated)",J84)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K84),K84=T84),IF(L84="","(brand not stated)",L84)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M84),M84=T84),IF(N84="","(brand not stated)",N84)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O84),O84=T84),IF(P84="","(brand not stated)",P84)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q84),Q84=T84),IF(R84="","(brand not stated)",R84)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G84),G84=T84),IF(H84="","(brand not stated)",H84)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I84),I84=T84),IF(J84="","(brand not stated)",J84)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K84),K84=T84),IF(L84="","(brand not stated)",L84)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M84),M84=T84),IF(N84="","(brand not stated)",N84)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O84),O84=T84),IF(P84="","(brand not stated)",P84)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q84),Q84=T84),IF(R84="","(brand not stated)",R84)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G84),G84=T84),IF(H84="","(brand not stated)",H84),"")&amp;IF(AND(ISNUMBER(I84),I84=T84),IF(J84="","(brand not stated)",J84),"")&amp;IF(AND(ISNUMBER(K84),K84=T84),IF(L84="","(brand not stated)",L84),"")&amp;IF(AND(ISNUMBER(M84),M84=T84),IF(N84="","(brand not stated)",N84),"")&amp;IF(AND(ISNUMBER(O84),O84=T84),IF(P84="","(brand not stated)",P84),"")&amp;IF(AND(ISNUMBER(Q84),Q84=T84),IF(R84="","(brand not stated)",R84),"")))</f>
+        <v>TRUVA</v>
+      </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="5" t="n">
         <v>80</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F85" s="5" t="n">
         <v>50</v>
@@ -7132,22 +7455,26 @@
         <v/>
       </c>
       <c r="W85" s="6"/>
+      <c r="X85" s="9" t="str">
+        <f aca="false">IF(S85=0,"",IF(ISNUMBER(SEARCH(",",U85)),LEFT(IF(AND(ISNUMBER(G85),G85=T85),IF(H85="","(brand not stated)",H85)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I85),I85=T85),IF(J85="","(brand not stated)",J85)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K85),K85=T85),IF(L85="","(brand not stated)",L85)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M85),M85=T85),IF(N85="","(brand not stated)",N85)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O85),O85=T85),IF(P85="","(brand not stated)",P85)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q85),Q85=T85),IF(R85="","(brand not stated)",R85)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G85),G85=T85),IF(H85="","(brand not stated)",H85)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I85),I85=T85),IF(J85="","(brand not stated)",J85)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K85),K85=T85),IF(L85="","(brand not stated)",L85)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M85),M85=T85),IF(N85="","(brand not stated)",N85)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O85),O85=T85),IF(P85="","(brand not stated)",P85)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q85),Q85=T85),IF(R85="","(brand not stated)",R85)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G85),G85=T85),IF(H85="","(brand not stated)",H85),"")&amp;IF(AND(ISNUMBER(I85),I85=T85),IF(J85="","(brand not stated)",J85),"")&amp;IF(AND(ISNUMBER(K85),K85=T85),IF(L85="","(brand not stated)",L85),"")&amp;IF(AND(ISNUMBER(M85),M85=T85),IF(N85="","(brand not stated)",N85),"")&amp;IF(AND(ISNUMBER(O85),O85=T85),IF(P85="","(brand not stated)",P85),"")&amp;IF(AND(ISNUMBER(Q85),Q85=T85),IF(R85="","(brand not stated)",R85),"")))</f>
+        <v/>
+      </c>
     </row>
     <row r="86" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="5" t="n">
         <v>81</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F86" s="5" t="n">
         <v>100</v>
@@ -7160,7 +7487,7 @@
         <v>1211.25</v>
       </c>
       <c r="L86" s="6" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M86" s="7"/>
       <c r="N86" s="6"/>
@@ -7185,22 +7512,26 @@
         <v>121125</v>
       </c>
       <c r="W86" s="6"/>
+      <c r="X86" s="9" t="str">
+        <f aca="false">IF(S86=0,"",IF(ISNUMBER(SEARCH(",",U86)),LEFT(IF(AND(ISNUMBER(G86),G86=T86),IF(H86="","(brand not stated)",H86)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I86),I86=T86),IF(J86="","(brand not stated)",J86)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K86),K86=T86),IF(L86="","(brand not stated)",L86)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M86),M86=T86),IF(N86="","(brand not stated)",N86)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O86),O86=T86),IF(P86="","(brand not stated)",P86)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q86),Q86=T86),IF(R86="","(brand not stated)",R86)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G86),G86=T86),IF(H86="","(brand not stated)",H86)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I86),I86=T86),IF(J86="","(brand not stated)",J86)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K86),K86=T86),IF(L86="","(brand not stated)",L86)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M86),M86=T86),IF(N86="","(brand not stated)",N86)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O86),O86=T86),IF(P86="","(brand not stated)",P86)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q86),Q86=T86),IF(R86="","(brand not stated)",R86)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G86),G86=T86),IF(H86="","(brand not stated)",H86),"")&amp;IF(AND(ISNUMBER(I86),I86=T86),IF(J86="","(brand not stated)",J86),"")&amp;IF(AND(ISNUMBER(K86),K86=T86),IF(L86="","(brand not stated)",L86),"")&amp;IF(AND(ISNUMBER(M86),M86=T86),IF(N86="","(brand not stated)",N86),"")&amp;IF(AND(ISNUMBER(O86),O86=T86),IF(P86="","(brand not stated)",P86),"")&amp;IF(AND(ISNUMBER(Q86),Q86=T86),IF(R86="","(brand not stated)",R86),"")))</f>
+        <v>ARINAC FORT TAB</v>
+      </c>
     </row>
     <row r="87" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="5" t="n">
         <v>82</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F87" s="5" t="n">
         <v>150</v>
@@ -7234,22 +7565,26 @@
         <v/>
       </c>
       <c r="W87" s="6"/>
+      <c r="X87" s="9" t="str">
+        <f aca="false">IF(S87=0,"",IF(ISNUMBER(SEARCH(",",U87)),LEFT(IF(AND(ISNUMBER(G87),G87=T87),IF(H87="","(brand not stated)",H87)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I87),I87=T87),IF(J87="","(brand not stated)",J87)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K87),K87=T87),IF(L87="","(brand not stated)",L87)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M87),M87=T87),IF(N87="","(brand not stated)",N87)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O87),O87=T87),IF(P87="","(brand not stated)",P87)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q87),Q87=T87),IF(R87="","(brand not stated)",R87)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G87),G87=T87),IF(H87="","(brand not stated)",H87)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I87),I87=T87),IF(J87="","(brand not stated)",J87)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K87),K87=T87),IF(L87="","(brand not stated)",L87)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M87),M87=T87),IF(N87="","(brand not stated)",N87)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O87),O87=T87),IF(P87="","(brand not stated)",P87)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q87),Q87=T87),IF(R87="","(brand not stated)",R87)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G87),G87=T87),IF(H87="","(brand not stated)",H87),"")&amp;IF(AND(ISNUMBER(I87),I87=T87),IF(J87="","(brand not stated)",J87),"")&amp;IF(AND(ISNUMBER(K87),K87=T87),IF(L87="","(brand not stated)",L87),"")&amp;IF(AND(ISNUMBER(M87),M87=T87),IF(N87="","(brand not stated)",N87),"")&amp;IF(AND(ISNUMBER(O87),O87=T87),IF(P87="","(brand not stated)",P87),"")&amp;IF(AND(ISNUMBER(Q87),Q87=T87),IF(R87="","(brand not stated)",R87),"")))</f>
+        <v/>
+      </c>
     </row>
     <row r="88" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="5" t="n">
         <v>83</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F88" s="5" t="n">
         <v>400</v>
@@ -7258,7 +7593,7 @@
         <v>650.25</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="I88" s="7"/>
       <c r="J88" s="6"/>
@@ -7268,13 +7603,13 @@
         <v>660.96</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O88" s="7" t="n">
         <v>531.08</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q88" s="7"/>
       <c r="R88" s="6"/>
@@ -7295,22 +7630,26 @@
         <v>212432</v>
       </c>
       <c r="W88" s="6"/>
+      <c r="X88" s="9" t="str">
+        <f aca="false">IF(S88=0,"",IF(ISNUMBER(SEARCH(",",U88)),LEFT(IF(AND(ISNUMBER(G88),G88=T88),IF(H88="","(brand not stated)",H88)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I88),I88=T88),IF(J88="","(brand not stated)",J88)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K88),K88=T88),IF(L88="","(brand not stated)",L88)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M88),M88=T88),IF(N88="","(brand not stated)",N88)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O88),O88=T88),IF(P88="","(brand not stated)",P88)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q88),Q88=T88),IF(R88="","(brand not stated)",R88)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G88),G88=T88),IF(H88="","(brand not stated)",H88)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I88),I88=T88),IF(J88="","(brand not stated)",J88)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K88),K88=T88),IF(L88="","(brand not stated)",L88)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M88),M88=T88),IF(N88="","(brand not stated)",N88)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O88),O88=T88),IF(P88="","(brand not stated)",P88)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q88),Q88=T88),IF(R88="","(brand not stated)",R88)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G88),G88=T88),IF(H88="","(brand not stated)",H88),"")&amp;IF(AND(ISNUMBER(I88),I88=T88),IF(J88="","(brand not stated)",J88),"")&amp;IF(AND(ISNUMBER(K88),K88=T88),IF(L88="","(brand not stated)",L88),"")&amp;IF(AND(ISNUMBER(M88),M88=T88),IF(N88="","(brand not stated)",N88),"")&amp;IF(AND(ISNUMBER(O88),O88=T88),IF(P88="","(brand not stated)",P88),"")&amp;IF(AND(ISNUMBER(Q88),Q88=T88),IF(R88="","(brand not stated)",R88),"")))</f>
+        <v>DXL 30MG CAPSULE</v>
+      </c>
     </row>
     <row r="89" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="5" t="n">
         <v>84</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F89" s="5" t="n">
         <v>300</v>
@@ -7319,7 +7658,7 @@
         <v>378.25</v>
       </c>
       <c r="H89" s="6" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="I89" s="7"/>
       <c r="J89" s="6"/>
@@ -7329,13 +7668,13 @@
         <v>617.185</v>
       </c>
       <c r="N89" s="6" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O89" s="7" t="n">
         <v>145.35</v>
       </c>
       <c r="P89" s="6" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q89" s="7"/>
       <c r="R89" s="6"/>
@@ -7356,22 +7695,26 @@
         <v>43605</v>
       </c>
       <c r="W89" s="6"/>
+      <c r="X89" s="9" t="str">
+        <f aca="false">IF(S89=0,"",IF(ISNUMBER(SEARCH(",",U89)),LEFT(IF(AND(ISNUMBER(G89),G89=T89),IF(H89="","(brand not stated)",H89)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I89),I89=T89),IF(J89="","(brand not stated)",J89)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K89),K89=T89),IF(L89="","(brand not stated)",L89)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M89),M89=T89),IF(N89="","(brand not stated)",N89)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O89),O89=T89),IF(P89="","(brand not stated)",P89)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q89),Q89=T89),IF(R89="","(brand not stated)",R89)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G89),G89=T89),IF(H89="","(brand not stated)",H89)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I89),I89=T89),IF(J89="","(brand not stated)",J89)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K89),K89=T89),IF(L89="","(brand not stated)",L89)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M89),M89=T89),IF(N89="","(brand not stated)",N89)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O89),O89=T89),IF(P89="","(brand not stated)",P89)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q89),Q89=T89),IF(R89="","(brand not stated)",R89)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G89),G89=T89),IF(H89="","(brand not stated)",H89),"")&amp;IF(AND(ISNUMBER(I89),I89=T89),IF(J89="","(brand not stated)",J89),"")&amp;IF(AND(ISNUMBER(K89),K89=T89),IF(L89="","(brand not stated)",L89),"")&amp;IF(AND(ISNUMBER(M89),M89=T89),IF(N89="","(brand not stated)",N89),"")&amp;IF(AND(ISNUMBER(O89),O89=T89),IF(P89="","(brand not stated)",P89),"")&amp;IF(AND(ISNUMBER(Q89),Q89=T89),IF(R89="","(brand not stated)",R89),"")))</f>
+        <v>CYROCIN 500MG TABLET</v>
+      </c>
     </row>
     <row r="90" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="5" t="n">
         <v>85</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F90" s="5" t="n">
         <v>250</v>
@@ -7380,7 +7723,7 @@
         <v>340</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="I90" s="7"/>
       <c r="J90" s="6"/>
@@ -7390,7 +7733,7 @@
         <v>347.01</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="O90" s="7"/>
       <c r="P90" s="6"/>
@@ -7413,22 +7756,26 @@
         <v>85000</v>
       </c>
       <c r="W90" s="6"/>
+      <c r="X90" s="9" t="str">
+        <f aca="false">IF(S90=0,"",IF(ISNUMBER(SEARCH(",",U90)),LEFT(IF(AND(ISNUMBER(G90),G90=T90),IF(H90="","(brand not stated)",H90)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I90),I90=T90),IF(J90="","(brand not stated)",J90)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K90),K90=T90),IF(L90="","(brand not stated)",L90)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M90),M90=T90),IF(N90="","(brand not stated)",N90)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O90),O90=T90),IF(P90="","(brand not stated)",P90)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q90),Q90=T90),IF(R90="","(brand not stated)",R90)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G90),G90=T90),IF(H90="","(brand not stated)",H90)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I90),I90=T90),IF(J90="","(brand not stated)",J90)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K90),K90=T90),IF(L90="","(brand not stated)",L90)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M90),M90=T90),IF(N90="","(brand not stated)",N90)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O90),O90=T90),IF(P90="","(brand not stated)",P90)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q90),Q90=T90),IF(R90="","(brand not stated)",R90)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G90),G90=T90),IF(H90="","(brand not stated)",H90),"")&amp;IF(AND(ISNUMBER(I90),I90=T90),IF(J90="","(brand not stated)",J90),"")&amp;IF(AND(ISNUMBER(K90),K90=T90),IF(L90="","(brand not stated)",L90),"")&amp;IF(AND(ISNUMBER(M90),M90=T90),IF(N90="","(brand not stated)",N90),"")&amp;IF(AND(ISNUMBER(O90),O90=T90),IF(P90="","(brand not stated)",P90),"")&amp;IF(AND(ISNUMBER(Q90),Q90=T90),IF(R90="","(brand not stated)",R90),"")))</f>
+        <v>DICLOREP</v>
+      </c>
     </row>
     <row r="91" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="5" t="n">
         <v>86</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F91" s="5" t="n">
         <v>50</v>
@@ -7443,7 +7790,7 @@
         <v>550.8</v>
       </c>
       <c r="N91" s="6" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="O91" s="7"/>
       <c r="P91" s="6"/>
@@ -7466,22 +7813,26 @@
         <v>27540</v>
       </c>
       <c r="W91" s="6"/>
+      <c r="X91" s="9" t="str">
+        <f aca="false">IF(S91=0,"",IF(ISNUMBER(SEARCH(",",U91)),LEFT(IF(AND(ISNUMBER(G91),G91=T91),IF(H91="","(brand not stated)",H91)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I91),I91=T91),IF(J91="","(brand not stated)",J91)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K91),K91=T91),IF(L91="","(brand not stated)",L91)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M91),M91=T91),IF(N91="","(brand not stated)",N91)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O91),O91=T91),IF(P91="","(brand not stated)",P91)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q91),Q91=T91),IF(R91="","(brand not stated)",R91)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G91),G91=T91),IF(H91="","(brand not stated)",H91)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I91),I91=T91),IF(J91="","(brand not stated)",J91)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K91),K91=T91),IF(L91="","(brand not stated)",L91)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M91),M91=T91),IF(N91="","(brand not stated)",N91)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O91),O91=T91),IF(P91="","(brand not stated)",P91)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q91),Q91=T91),IF(R91="","(brand not stated)",R91)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G91),G91=T91),IF(H91="","(brand not stated)",H91),"")&amp;IF(AND(ISNUMBER(I91),I91=T91),IF(J91="","(brand not stated)",J91),"")&amp;IF(AND(ISNUMBER(K91),K91=T91),IF(L91="","(brand not stated)",L91),"")&amp;IF(AND(ISNUMBER(M91),M91=T91),IF(N91="","(brand not stated)",N91),"")&amp;IF(AND(ISNUMBER(O91),O91=T91),IF(P91="","(brand not stated)",P91),"")&amp;IF(AND(ISNUMBER(Q91),Q91=T91),IF(R91="","(brand not stated)",R91),"")))</f>
+        <v>COVA (GETZ)</v>
+      </c>
     </row>
     <row r="92" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="5" t="n">
         <v>87</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F92" s="5" t="n">
         <v>25</v>
@@ -7492,7 +7843,7 @@
         <v>809.55</v>
       </c>
       <c r="J92" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K92" s="7"/>
       <c r="L92" s="6"/>
@@ -7504,7 +7855,7 @@
         <v>312.37</v>
       </c>
       <c r="R92" s="6" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="S92" s="5" t="n">
         <f aca="false">COUNT(G92,I92,K92,M92,O92,Q92)</f>
@@ -7523,22 +7874,26 @@
         <v>7809.25</v>
       </c>
       <c r="W92" s="6"/>
+      <c r="X92" s="9" t="str">
+        <f aca="false">IF(S92=0,"",IF(ISNUMBER(SEARCH(",",U92)),LEFT(IF(AND(ISNUMBER(G92),G92=T92),IF(H92="","(brand not stated)",H92)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I92),I92=T92),IF(J92="","(brand not stated)",J92)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K92),K92=T92),IF(L92="","(brand not stated)",L92)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M92),M92=T92),IF(N92="","(brand not stated)",N92)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O92),O92=T92),IF(P92="","(brand not stated)",P92)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q92),Q92=T92),IF(R92="","(brand not stated)",R92)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G92),G92=T92),IF(H92="","(brand not stated)",H92)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I92),I92=T92),IF(J92="","(brand not stated)",J92)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K92),K92=T92),IF(L92="","(brand not stated)",L92)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M92),M92=T92),IF(N92="","(brand not stated)",N92)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O92),O92=T92),IF(P92="","(brand not stated)",P92)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q92),Q92=T92),IF(R92="","(brand not stated)",R92)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G92),G92=T92),IF(H92="","(brand not stated)",H92),"")&amp;IF(AND(ISNUMBER(I92),I92=T92),IF(J92="","(brand not stated)",J92),"")&amp;IF(AND(ISNUMBER(K92),K92=T92),IF(L92="","(brand not stated)",L92),"")&amp;IF(AND(ISNUMBER(M92),M92=T92),IF(N92="","(brand not stated)",N92),"")&amp;IF(AND(ISNUMBER(O92),O92=T92),IF(P92="","(brand not stated)",P92),"")&amp;IF(AND(ISNUMBER(Q92),Q92=T92),IF(R92="","(brand not stated)",R92),"")))</f>
+        <v>Gramex</v>
+      </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="5" t="n">
         <v>88</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F93" s="5" t="n">
         <v>100</v>
@@ -7549,7 +7904,7 @@
         <v>265.31</v>
       </c>
       <c r="J93" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K93" s="7"/>
       <c r="L93" s="6"/>
@@ -7559,7 +7914,7 @@
         <v>1592.37</v>
       </c>
       <c r="P93" s="6" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Q93" s="7"/>
       <c r="R93" s="6"/>
@@ -7580,22 +7935,26 @@
         <v>26531</v>
       </c>
       <c r="W93" s="6"/>
+      <c r="X93" s="9" t="str">
+        <f aca="false">IF(S93=0,"",IF(ISNUMBER(SEARCH(",",U93)),LEFT(IF(AND(ISNUMBER(G93),G93=T93),IF(H93="","(brand not stated)",H93)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I93),I93=T93),IF(J93="","(brand not stated)",J93)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K93),K93=T93),IF(L93="","(brand not stated)",L93)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M93),M93=T93),IF(N93="","(brand not stated)",N93)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O93),O93=T93),IF(P93="","(brand not stated)",P93)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q93),Q93=T93),IF(R93="","(brand not stated)",R93)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G93),G93=T93),IF(H93="","(brand not stated)",H93)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I93),I93=T93),IF(J93="","(brand not stated)",J93)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K93),K93=T93),IF(L93="","(brand not stated)",L93)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M93),M93=T93),IF(N93="","(brand not stated)",N93)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O93),O93=T93),IF(P93="","(brand not stated)",P93)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q93),Q93=T93),IF(R93="","(brand not stated)",R93)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G93),G93=T93),IF(H93="","(brand not stated)",H93),"")&amp;IF(AND(ISNUMBER(I93),I93=T93),IF(J93="","(brand not stated)",J93),"")&amp;IF(AND(ISNUMBER(K93),K93=T93),IF(L93="","(brand not stated)",L93),"")&amp;IF(AND(ISNUMBER(M93),M93=T93),IF(N93="","(brand not stated)",N93),"")&amp;IF(AND(ISNUMBER(O93),O93=T93),IF(P93="","(brand not stated)",P93),"")&amp;IF(AND(ISNUMBER(Q93),Q93=T93),IF(R93="","(brand not stated)",R93),"")))</f>
+        <v>Reckitt</v>
+      </c>
     </row>
     <row r="94" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="5" t="n">
         <v>89</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F94" s="5" t="n">
         <v>200</v>
@@ -7606,7 +7965,7 @@
         <v>61.16</v>
       </c>
       <c r="J94" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K94" s="7"/>
       <c r="L94" s="6"/>
@@ -7633,22 +7992,26 @@
         <v>12232</v>
       </c>
       <c r="W94" s="6"/>
+      <c r="X94" s="9" t="str">
+        <f aca="false">IF(S94=0,"",IF(ISNUMBER(SEARCH(",",U94)),LEFT(IF(AND(ISNUMBER(G94),G94=T94),IF(H94="","(brand not stated)",H94)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I94),I94=T94),IF(J94="","(brand not stated)",J94)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K94),K94=T94),IF(L94="","(brand not stated)",L94)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M94),M94=T94),IF(N94="","(brand not stated)",N94)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O94),O94=T94),IF(P94="","(brand not stated)",P94)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q94),Q94=T94),IF(R94="","(brand not stated)",R94)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G94),G94=T94),IF(H94="","(brand not stated)",H94)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I94),I94=T94),IF(J94="","(brand not stated)",J94)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K94),K94=T94),IF(L94="","(brand not stated)",L94)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M94),M94=T94),IF(N94="","(brand not stated)",N94)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O94),O94=T94),IF(P94="","(brand not stated)",P94)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q94),Q94=T94),IF(R94="","(brand not stated)",R94)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G94),G94=T94),IF(H94="","(brand not stated)",H94),"")&amp;IF(AND(ISNUMBER(I94),I94=T94),IF(J94="","(brand not stated)",J94),"")&amp;IF(AND(ISNUMBER(K94),K94=T94),IF(L94="","(brand not stated)",L94),"")&amp;IF(AND(ISNUMBER(M94),M94=T94),IF(N94="","(brand not stated)",N94),"")&amp;IF(AND(ISNUMBER(O94),O94=T94),IF(P94="","(brand not stated)",P94),"")&amp;IF(AND(ISNUMBER(Q94),Q94=T94),IF(R94="","(brand not stated)",R94),"")))</f>
+        <v>Zafa</v>
+      </c>
     </row>
     <row r="95" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="5" t="n">
         <v>90</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F95" s="5" t="n">
         <v>100</v>
@@ -7661,7 +8024,7 @@
         <v>153.43</v>
       </c>
       <c r="L95" s="6" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M95" s="7"/>
       <c r="N95" s="6"/>
@@ -7669,7 +8032,7 @@
         <v>130.05</v>
       </c>
       <c r="P95" s="6" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="Q95" s="7"/>
       <c r="R95" s="6"/>
@@ -7690,22 +8053,26 @@
         <v>13005</v>
       </c>
       <c r="W95" s="6"/>
+      <c r="X95" s="9" t="str">
+        <f aca="false">IF(S95=0,"",IF(ISNUMBER(SEARCH(",",U95)),LEFT(IF(AND(ISNUMBER(G95),G95=T95),IF(H95="","(brand not stated)",H95)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I95),I95=T95),IF(J95="","(brand not stated)",J95)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K95),K95=T95),IF(L95="","(brand not stated)",L95)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M95),M95=T95),IF(N95="","(brand not stated)",N95)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O95),O95=T95),IF(P95="","(brand not stated)",P95)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q95),Q95=T95),IF(R95="","(brand not stated)",R95)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G95),G95=T95),IF(H95="","(brand not stated)",H95)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I95),I95=T95),IF(J95="","(brand not stated)",J95)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K95),K95=T95),IF(L95="","(brand not stated)",L95)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M95),M95=T95),IF(N95="","(brand not stated)",N95)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O95),O95=T95),IF(P95="","(brand not stated)",P95)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q95),Q95=T95),IF(R95="","(brand not stated)",R95)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G95),G95=T95),IF(H95="","(brand not stated)",H95),"")&amp;IF(AND(ISNUMBER(I95),I95=T95),IF(J95="","(brand not stated)",J95),"")&amp;IF(AND(ISNUMBER(K95),K95=T95),IF(L95="","(brand not stated)",L95),"")&amp;IF(AND(ISNUMBER(M95),M95=T95),IF(N95="","(brand not stated)",N95),"")&amp;IF(AND(ISNUMBER(O95),O95=T95),IF(P95="","(brand not stated)",P95),"")&amp;IF(AND(ISNUMBER(Q95),Q95=T95),IF(R95="","(brand not stated)",R95),"")))</f>
+        <v>POLYBION FORTE 120ML SYRUP</v>
+      </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="5" t="n">
         <v>91</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F96" s="5" t="n">
         <v>100</v>
@@ -7720,7 +8087,7 @@
         <v>148.75</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O96" s="7"/>
       <c r="P96" s="6"/>
@@ -7743,22 +8110,26 @@
         <v>14875</v>
       </c>
       <c r="W96" s="6"/>
+      <c r="X96" s="9" t="str">
+        <f aca="false">IF(S96=0,"",IF(ISNUMBER(SEARCH(",",U96)),LEFT(IF(AND(ISNUMBER(G96),G96=T96),IF(H96="","(brand not stated)",H96)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I96),I96=T96),IF(J96="","(brand not stated)",J96)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K96),K96=T96),IF(L96="","(brand not stated)",L96)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M96),M96=T96),IF(N96="","(brand not stated)",N96)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O96),O96=T96),IF(P96="","(brand not stated)",P96)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q96),Q96=T96),IF(R96="","(brand not stated)",R96)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G96),G96=T96),IF(H96="","(brand not stated)",H96)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I96),I96=T96),IF(J96="","(brand not stated)",J96)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K96),K96=T96),IF(L96="","(brand not stated)",L96)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M96),M96=T96),IF(N96="","(brand not stated)",N96)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O96),O96=T96),IF(P96="","(brand not stated)",P96)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q96),Q96=T96),IF(R96="","(brand not stated)",R96)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G96),G96=T96),IF(H96="","(brand not stated)",H96),"")&amp;IF(AND(ISNUMBER(I96),I96=T96),IF(J96="","(brand not stated)",J96),"")&amp;IF(AND(ISNUMBER(K96),K96=T96),IF(L96="","(brand not stated)",L96),"")&amp;IF(AND(ISNUMBER(M96),M96=T96),IF(N96="","(brand not stated)",N96),"")&amp;IF(AND(ISNUMBER(O96),O96=T96),IF(P96="","(brand not stated)",P96),"")&amp;IF(AND(ISNUMBER(Q96),Q96=T96),IF(R96="","(brand not stated)",R96),"")))</f>
+        <v>VERMOX (ASPIN)</v>
+      </c>
     </row>
     <row r="97" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="5" t="n">
         <v>92</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F97" s="5" t="n">
         <v>200</v>
@@ -7775,7 +8146,7 @@
         <v>351.48</v>
       </c>
       <c r="P97" s="6" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="Q97" s="7"/>
       <c r="R97" s="6"/>
@@ -7796,22 +8167,26 @@
         <v>70296</v>
       </c>
       <c r="W97" s="6"/>
+      <c r="X97" s="9" t="str">
+        <f aca="false">IF(S97=0,"",IF(ISNUMBER(SEARCH(",",U97)),LEFT(IF(AND(ISNUMBER(G97),G97=T97),IF(H97="","(brand not stated)",H97)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I97),I97=T97),IF(J97="","(brand not stated)",J97)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K97),K97=T97),IF(L97="","(brand not stated)",L97)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M97),M97=T97),IF(N97="","(brand not stated)",N97)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O97),O97=T97),IF(P97="","(brand not stated)",P97)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q97),Q97=T97),IF(R97="","(brand not stated)",R97)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G97),G97=T97),IF(H97="","(brand not stated)",H97)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I97),I97=T97),IF(J97="","(brand not stated)",J97)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K97),K97=T97),IF(L97="","(brand not stated)",L97)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M97),M97=T97),IF(N97="","(brand not stated)",N97)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O97),O97=T97),IF(P97="","(brand not stated)",P97)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q97),Q97=T97),IF(R97="","(brand not stated)",R97)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G97),G97=T97),IF(H97="","(brand not stated)",H97),"")&amp;IF(AND(ISNUMBER(I97),I97=T97),IF(J97="","(brand not stated)",J97),"")&amp;IF(AND(ISNUMBER(K97),K97=T97),IF(L97="","(brand not stated)",L97),"")&amp;IF(AND(ISNUMBER(M97),M97=T97),IF(N97="","(brand not stated)",N97),"")&amp;IF(AND(ISNUMBER(O97),O97=T97),IF(P97="","(brand not stated)",P97),"")&amp;IF(AND(ISNUMBER(Q97),Q97=T97),IF(R97="","(brand not stated)",R97),"")))</f>
+        <v>ULSANIC 1G/5ML 20ML SYRUP</v>
+      </c>
     </row>
     <row r="98" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="5" t="n">
         <v>93</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F98" s="5" t="n">
         <v>200</v>
@@ -7826,7 +8201,7 @@
         <v>569.5</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O98" s="7"/>
       <c r="P98" s="6"/>
@@ -7834,7 +8209,7 @@
         <v>382.5</v>
       </c>
       <c r="R98" s="6" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="S98" s="5" t="n">
         <f aca="false">COUNT(G98,I98,K98,M98,O98,Q98)</f>
@@ -7853,22 +8228,26 @@
         <v>76500</v>
       </c>
       <c r="W98" s="6"/>
+      <c r="X98" s="9" t="str">
+        <f aca="false">IF(S98=0,"",IF(ISNUMBER(SEARCH(",",U98)),LEFT(IF(AND(ISNUMBER(G98),G98=T98),IF(H98="","(brand not stated)",H98)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I98),I98=T98),IF(J98="","(brand not stated)",J98)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K98),K98=T98),IF(L98="","(brand not stated)",L98)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M98),M98=T98),IF(N98="","(brand not stated)",N98)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O98),O98=T98),IF(P98="","(brand not stated)",P98)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q98),Q98=T98),IF(R98="","(brand not stated)",R98)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G98),G98=T98),IF(H98="","(brand not stated)",H98)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I98),I98=T98),IF(J98="","(brand not stated)",J98)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K98),K98=T98),IF(L98="","(brand not stated)",L98)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M98),M98=T98),IF(N98="","(brand not stated)",N98)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O98),O98=T98),IF(P98="","(brand not stated)",P98)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q98),Q98=T98),IF(R98="","(brand not stated)",R98)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G98),G98=T98),IF(H98="","(brand not stated)",H98),"")&amp;IF(AND(ISNUMBER(I98),I98=T98),IF(J98="","(brand not stated)",J98),"")&amp;IF(AND(ISNUMBER(K98),K98=T98),IF(L98="","(brand not stated)",L98),"")&amp;IF(AND(ISNUMBER(M98),M98=T98),IF(N98="","(brand not stated)",N98),"")&amp;IF(AND(ISNUMBER(O98),O98=T98),IF(P98="","(brand not stated)",P98),"")&amp;IF(AND(ISNUMBER(Q98),Q98=T98),IF(R98="","(brand not stated)",R98),"")))</f>
+        <v>Ossobon-D</v>
+      </c>
     </row>
     <row r="99" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="5" t="n">
         <v>94</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F99" s="5" t="n">
         <v>100</v>
@@ -7902,20 +8281,24 @@
         <v/>
       </c>
       <c r="W99" s="6"/>
+      <c r="X99" s="9" t="str">
+        <f aca="false">IF(S99=0,"",IF(ISNUMBER(SEARCH(",",U99)),LEFT(IF(AND(ISNUMBER(G99),G99=T99),IF(H99="","(brand not stated)",H99)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I99),I99=T99),IF(J99="","(brand not stated)",J99)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K99),K99=T99),IF(L99="","(brand not stated)",L99)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M99),M99=T99),IF(N99="","(brand not stated)",N99)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O99),O99=T99),IF(P99="","(brand not stated)",P99)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q99),Q99=T99),IF(R99="","(brand not stated)",R99)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G99),G99=T99),IF(H99="","(brand not stated)",H99)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I99),I99=T99),IF(J99="","(brand not stated)",J99)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K99),K99=T99),IF(L99="","(brand not stated)",L99)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M99),M99=T99),IF(N99="","(brand not stated)",N99)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O99),O99=T99),IF(P99="","(brand not stated)",P99)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q99),Q99=T99),IF(R99="","(brand not stated)",R99)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G99),G99=T99),IF(H99="","(brand not stated)",H99),"")&amp;IF(AND(ISNUMBER(I99),I99=T99),IF(J99="","(brand not stated)",J99),"")&amp;IF(AND(ISNUMBER(K99),K99=T99),IF(L99="","(brand not stated)",L99),"")&amp;IF(AND(ISNUMBER(M99),M99=T99),IF(N99="","(brand not stated)",N99),"")&amp;IF(AND(ISNUMBER(O99),O99=T99),IF(P99="","(brand not stated)",P99),"")&amp;IF(AND(ISNUMBER(Q99),Q99=T99),IF(R99="","(brand not stated)",R99),"")))</f>
+        <v/>
+      </c>
     </row>
     <row r="100" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="5" t="n">
         <v>95</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D100" s="6"/>
       <c r="E100" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F100" s="5" t="n">
         <v>100</v>
@@ -7932,7 +8315,7 @@
         <v>146.88</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="Q100" s="7"/>
       <c r="R100" s="6"/>
@@ -7953,22 +8336,26 @@
         <v>14688</v>
       </c>
       <c r="W100" s="6"/>
+      <c r="X100" s="9" t="str">
+        <f aca="false">IF(S100=0,"",IF(ISNUMBER(SEARCH(",",U100)),LEFT(IF(AND(ISNUMBER(G100),G100=T100),IF(H100="","(brand not stated)",H100)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I100),I100=T100),IF(J100="","(brand not stated)",J100)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K100),K100=T100),IF(L100="","(brand not stated)",L100)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M100),M100=T100),IF(N100="","(brand not stated)",N100)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O100),O100=T100),IF(P100="","(brand not stated)",P100)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q100),Q100=T100),IF(R100="","(brand not stated)",R100)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G100),G100=T100),IF(H100="","(brand not stated)",H100)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I100),I100=T100),IF(J100="","(brand not stated)",J100)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K100),K100=T100),IF(L100="","(brand not stated)",L100)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M100),M100=T100),IF(N100="","(brand not stated)",N100)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O100),O100=T100),IF(P100="","(brand not stated)",P100)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q100),Q100=T100),IF(R100="","(brand not stated)",R100)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G100),G100=T100),IF(H100="","(brand not stated)",H100),"")&amp;IF(AND(ISNUMBER(I100),I100=T100),IF(J100="","(brand not stated)",J100),"")&amp;IF(AND(ISNUMBER(K100),K100=T100),IF(L100="","(brand not stated)",L100),"")&amp;IF(AND(ISNUMBER(M100),M100=T100),IF(N100="","(brand not stated)",N100),"")&amp;IF(AND(ISNUMBER(O100),O100=T100),IF(P100="","(brand not stated)",P100),"")&amp;IF(AND(ISNUMBER(Q100),Q100=T100),IF(R100="","(brand not stated)",R100),"")))</f>
+        <v>HYDRYLLIN-DM 120 ML SYRUP</v>
+      </c>
     </row>
     <row r="101" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="5" t="n">
         <v>96</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F101" s="5" t="n">
         <v>1200</v>
@@ -7979,7 +8366,7 @@
         <v>186.15</v>
       </c>
       <c r="J101" s="6" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="K101" s="7"/>
       <c r="L101" s="6"/>
@@ -7987,13 +8374,13 @@
         <v>117.3</v>
       </c>
       <c r="N101" s="6" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="O101" s="7" t="n">
         <v>105.57</v>
       </c>
       <c r="P101" s="6" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="Q101" s="7"/>
       <c r="R101" s="6"/>
@@ -8014,22 +8401,26 @@
         <v>126684</v>
       </c>
       <c r="W101" s="6"/>
+      <c r="X101" s="9" t="str">
+        <f aca="false">IF(S101=0,"",IF(ISNUMBER(SEARCH(",",U101)),LEFT(IF(AND(ISNUMBER(G101),G101=T101),IF(H101="","(brand not stated)",H101)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I101),I101=T101),IF(J101="","(brand not stated)",J101)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K101),K101=T101),IF(L101="","(brand not stated)",L101)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M101),M101=T101),IF(N101="","(brand not stated)",N101)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O101),O101=T101),IF(P101="","(brand not stated)",P101)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q101),Q101=T101),IF(R101="","(brand not stated)",R101)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G101),G101=T101),IF(H101="","(brand not stated)",H101)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I101),I101=T101),IF(J101="","(brand not stated)",J101)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K101),K101=T101),IF(L101="","(brand not stated)",L101)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M101),M101=T101),IF(N101="","(brand not stated)",N101)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O101),O101=T101),IF(P101="","(brand not stated)",P101)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q101),Q101=T101),IF(R101="","(brand not stated)",R101)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G101),G101=T101),IF(H101="","(brand not stated)",H101),"")&amp;IF(AND(ISNUMBER(I101),I101=T101),IF(J101="","(brand not stated)",J101),"")&amp;IF(AND(ISNUMBER(K101),K101=T101),IF(L101="","(brand not stated)",L101),"")&amp;IF(AND(ISNUMBER(M101),M101=T101),IF(N101="","(brand not stated)",N101),"")&amp;IF(AND(ISNUMBER(O101),O101=T101),IF(P101="","(brand not stated)",P101),"")&amp;IF(AND(ISNUMBER(Q101),Q101=T101),IF(R101="","(brand not stated)",R101),"")))</f>
+        <v>COSOME-E COUGH 120ML SYRUP</v>
+      </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="5" t="n">
         <v>97</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F102" s="5" t="n">
         <v>100</v>
@@ -8040,7 +8431,7 @@
         <v>96.04</v>
       </c>
       <c r="J102" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K102" s="7"/>
       <c r="L102" s="6"/>
@@ -8067,22 +8458,26 @@
         <v>9604</v>
       </c>
       <c r="W102" s="6"/>
+      <c r="X102" s="9" t="str">
+        <f aca="false">IF(S102=0,"",IF(ISNUMBER(SEARCH(",",U102)),LEFT(IF(AND(ISNUMBER(G102),G102=T102),IF(H102="","(brand not stated)",H102)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I102),I102=T102),IF(J102="","(brand not stated)",J102)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K102),K102=T102),IF(L102="","(brand not stated)",L102)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M102),M102=T102),IF(N102="","(brand not stated)",N102)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O102),O102=T102),IF(P102="","(brand not stated)",P102)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q102),Q102=T102),IF(R102="","(brand not stated)",R102)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G102),G102=T102),IF(H102="","(brand not stated)",H102)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I102),I102=T102),IF(J102="","(brand not stated)",J102)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K102),K102=T102),IF(L102="","(brand not stated)",L102)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M102),M102=T102),IF(N102="","(brand not stated)",N102)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O102),O102=T102),IF(P102="","(brand not stated)",P102)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q102),Q102=T102),IF(R102="","(brand not stated)",R102)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G102),G102=T102),IF(H102="","(brand not stated)",H102),"")&amp;IF(AND(ISNUMBER(I102),I102=T102),IF(J102="","(brand not stated)",J102),"")&amp;IF(AND(ISNUMBER(K102),K102=T102),IF(L102="","(brand not stated)",L102),"")&amp;IF(AND(ISNUMBER(M102),M102=T102),IF(N102="","(brand not stated)",N102),"")&amp;IF(AND(ISNUMBER(O102),O102=T102),IF(P102="","(brand not stated)",P102),"")&amp;IF(AND(ISNUMBER(Q102),Q102=T102),IF(R102="","(brand not stated)",R102),"")))</f>
+        <v>Searle</v>
+      </c>
     </row>
     <row r="103" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="5" t="n">
         <v>98</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C103" s="6" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F103" s="5" t="n">
         <v>1000</v>
@@ -8091,19 +8486,19 @@
         <v>221</v>
       </c>
       <c r="H103" s="6" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="I103" s="7" t="n">
         <v>238</v>
       </c>
       <c r="J103" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K103" s="7" t="n">
         <v>148.58</v>
       </c>
       <c r="L103" s="6" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M103" s="7"/>
       <c r="N103" s="6"/>
@@ -8111,7 +8506,7 @@
         <v>238</v>
       </c>
       <c r="P103" s="6" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="Q103" s="7"/>
       <c r="R103" s="6"/>
@@ -8132,22 +8527,26 @@
         <v>148580</v>
       </c>
       <c r="W103" s="6"/>
+      <c r="X103" s="9" t="str">
+        <f aca="false">IF(S103=0,"",IF(ISNUMBER(SEARCH(",",U103)),LEFT(IF(AND(ISNUMBER(G103),G103=T103),IF(H103="","(brand not stated)",H103)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I103),I103=T103),IF(J103="","(brand not stated)",J103)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K103),K103=T103),IF(L103="","(brand not stated)",L103)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M103),M103=T103),IF(N103="","(brand not stated)",N103)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O103),O103=T103),IF(P103="","(brand not stated)",P103)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q103),Q103=T103),IF(R103="","(brand not stated)",R103)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G103),G103=T103),IF(H103="","(brand not stated)",H103)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I103),I103=T103),IF(J103="","(brand not stated)",J103)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K103),K103=T103),IF(L103="","(brand not stated)",L103)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M103),M103=T103),IF(N103="","(brand not stated)",N103)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O103),O103=T103),IF(P103="","(brand not stated)",P103)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q103),Q103=T103),IF(R103="","(brand not stated)",R103)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G103),G103=T103),IF(H103="","(brand not stated)",H103),"")&amp;IF(AND(ISNUMBER(I103),I103=T103),IF(J103="","(brand not stated)",J103),"")&amp;IF(AND(ISNUMBER(K103),K103=T103),IF(L103="","(brand not stated)",L103),"")&amp;IF(AND(ISNUMBER(M103),M103=T103),IF(N103="","(brand not stated)",N103),"")&amp;IF(AND(ISNUMBER(O103),O103=T103),IF(P103="","(brand not stated)",P103),"")&amp;IF(AND(ISNUMBER(Q103),Q103=T103),IF(R103="","(brand not stated)",R103),"")))</f>
+        <v>DIJEX MP SYP</v>
+      </c>
     </row>
     <row r="104" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="5" t="n">
         <v>99</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F104" s="5" t="n">
         <v>200</v>
@@ -8160,7 +8559,7 @@
         <v>249.96</v>
       </c>
       <c r="L104" s="6" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="M104" s="7"/>
       <c r="N104" s="6"/>
@@ -8185,22 +8584,26 @@
         <v>49992</v>
       </c>
       <c r="W104" s="6"/>
+      <c r="X104" s="9" t="str">
+        <f aca="false">IF(S104=0,"",IF(ISNUMBER(SEARCH(",",U104)),LEFT(IF(AND(ISNUMBER(G104),G104=T104),IF(H104="","(brand not stated)",H104)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I104),I104=T104),IF(J104="","(brand not stated)",J104)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K104),K104=T104),IF(L104="","(brand not stated)",L104)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M104),M104=T104),IF(N104="","(brand not stated)",N104)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O104),O104=T104),IF(P104="","(brand not stated)",P104)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q104),Q104=T104),IF(R104="","(brand not stated)",R104)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G104),G104=T104),IF(H104="","(brand not stated)",H104)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I104),I104=T104),IF(J104="","(brand not stated)",J104)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K104),K104=T104),IF(L104="","(brand not stated)",L104)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M104),M104=T104),IF(N104="","(brand not stated)",N104)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O104),O104=T104),IF(P104="","(brand not stated)",P104)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q104),Q104=T104),IF(R104="","(brand not stated)",R104)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G104),G104=T104),IF(H104="","(brand not stated)",H104),"")&amp;IF(AND(ISNUMBER(I104),I104=T104),IF(J104="","(brand not stated)",J104),"")&amp;IF(AND(ISNUMBER(K104),K104=T104),IF(L104="","(brand not stated)",L104),"")&amp;IF(AND(ISNUMBER(M104),M104=T104),IF(N104="","(brand not stated)",N104),"")&amp;IF(AND(ISNUMBER(O104),O104=T104),IF(P104="","(brand not stated)",P104),"")&amp;IF(AND(ISNUMBER(Q104),Q104=T104),IF(R104="","(brand not stated)",R104),"")))</f>
+        <v>DUPHALAC SYRUP</v>
+      </c>
     </row>
     <row r="105" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="5" t="n">
         <v>100</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F105" s="5" t="n">
         <v>100</v>
@@ -8209,7 +8612,7 @@
         <v>85</v>
       </c>
       <c r="H105" s="6" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="I105" s="7"/>
       <c r="J105" s="6"/>
@@ -8219,7 +8622,7 @@
         <v>169.15</v>
       </c>
       <c r="N105" s="6" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="O105" s="7"/>
       <c r="P105" s="6"/>
@@ -8227,7 +8630,7 @@
         <v>206.28</v>
       </c>
       <c r="R105" s="6" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="S105" s="5" t="n">
         <f aca="false">COUNT(G105,I105,K105,M105,O105,Q105)</f>
@@ -8246,22 +8649,26 @@
         <v>8500</v>
       </c>
       <c r="W105" s="6"/>
+      <c r="X105" s="9" t="str">
+        <f aca="false">IF(S105=0,"",IF(ISNUMBER(SEARCH(",",U105)),LEFT(IF(AND(ISNUMBER(G105),G105=T105),IF(H105="","(brand not stated)",H105)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I105),I105=T105),IF(J105="","(brand not stated)",J105)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K105),K105=T105),IF(L105="","(brand not stated)",L105)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M105),M105=T105),IF(N105="","(brand not stated)",N105)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O105),O105=T105),IF(P105="","(brand not stated)",P105)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q105),Q105=T105),IF(R105="","(brand not stated)",R105)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G105),G105=T105),IF(H105="","(brand not stated)",H105)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I105),I105=T105),IF(J105="","(brand not stated)",J105)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K105),K105=T105),IF(L105="","(brand not stated)",L105)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M105),M105=T105),IF(N105="","(brand not stated)",N105)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O105),O105=T105),IF(P105="","(brand not stated)",P105)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q105),Q105=T105),IF(R105="","(brand not stated)",R105)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G105),G105=T105),IF(H105="","(brand not stated)",H105),"")&amp;IF(AND(ISNUMBER(I105),I105=T105),IF(J105="","(brand not stated)",J105),"")&amp;IF(AND(ISNUMBER(K105),K105=T105),IF(L105="","(brand not stated)",L105),"")&amp;IF(AND(ISNUMBER(M105),M105=T105),IF(N105="","(brand not stated)",N105),"")&amp;IF(AND(ISNUMBER(O105),O105=T105),IF(P105="","(brand not stated)",P105),"")&amp;IF(AND(ISNUMBER(Q105),Q105=T105),IF(R105="","(brand not stated)",R105),"")))</f>
+        <v>BH DOMEL</v>
+      </c>
     </row>
     <row r="106" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="5" t="n">
         <v>101</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F106" s="5" t="n">
         <v>500</v>
@@ -8274,13 +8681,13 @@
         <v>242.25</v>
       </c>
       <c r="L106" s="6" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M106" s="7" t="n">
         <v>153</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O106" s="7"/>
       <c r="P106" s="6"/>
@@ -8303,22 +8710,26 @@
         <v>76500</v>
       </c>
       <c r="W106" s="6"/>
+      <c r="X106" s="9" t="str">
+        <f aca="false">IF(S106=0,"",IF(ISNUMBER(SEARCH(",",U106)),LEFT(IF(AND(ISNUMBER(G106),G106=T106),IF(H106="","(brand not stated)",H106)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I106),I106=T106),IF(J106="","(brand not stated)",J106)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K106),K106=T106),IF(L106="","(brand not stated)",L106)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M106),M106=T106),IF(N106="","(brand not stated)",N106)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O106),O106=T106),IF(P106="","(brand not stated)",P106)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q106),Q106=T106),IF(R106="","(brand not stated)",R106)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G106),G106=T106),IF(H106="","(brand not stated)",H106)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I106),I106=T106),IF(J106="","(brand not stated)",J106)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K106),K106=T106),IF(L106="","(brand not stated)",L106)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M106),M106=T106),IF(N106="","(brand not stated)",N106)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O106),O106=T106),IF(P106="","(brand not stated)",P106)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q106),Q106=T106),IF(R106="","(brand not stated)",R106)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G106),G106=T106),IF(H106="","(brand not stated)",H106),"")&amp;IF(AND(ISNUMBER(I106),I106=T106),IF(J106="","(brand not stated)",J106),"")&amp;IF(AND(ISNUMBER(K106),K106=T106),IF(L106="","(brand not stated)",L106),"")&amp;IF(AND(ISNUMBER(M106),M106=T106),IF(N106="","(brand not stated)",N106),"")&amp;IF(AND(ISNUMBER(O106),O106=T106),IF(P106="","(brand not stated)",P106),"")&amp;IF(AND(ISNUMBER(Q106),Q106=T106),IF(R106="","(brand not stated)",R106),"")))</f>
+        <v>RELTUS DM (PHARMATEC)</v>
+      </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="5" t="n">
         <v>102</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F107" s="5" t="n">
         <v>300</v>
@@ -8331,7 +8742,7 @@
         <v>104.26</v>
       </c>
       <c r="L107" s="6" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M107" s="7"/>
       <c r="N107" s="6"/>
@@ -8356,22 +8767,26 @@
         <v>31278</v>
       </c>
       <c r="W107" s="6"/>
+      <c r="X107" s="9" t="str">
+        <f aca="false">IF(S107=0,"",IF(ISNUMBER(SEARCH(",",U107)),LEFT(IF(AND(ISNUMBER(G107),G107=T107),IF(H107="","(brand not stated)",H107)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I107),I107=T107),IF(J107="","(brand not stated)",J107)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K107),K107=T107),IF(L107="","(brand not stated)",L107)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M107),M107=T107),IF(N107="","(brand not stated)",N107)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O107),O107=T107),IF(P107="","(brand not stated)",P107)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q107),Q107=T107),IF(R107="","(brand not stated)",R107)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G107),G107=T107),IF(H107="","(brand not stated)",H107)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I107),I107=T107),IF(J107="","(brand not stated)",J107)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K107),K107=T107),IF(L107="","(brand not stated)",L107)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M107),M107=T107),IF(N107="","(brand not stated)",N107)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O107),O107=T107),IF(P107="","(brand not stated)",P107)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q107),Q107=T107),IF(R107="","(brand not stated)",R107)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G107),G107=T107),IF(H107="","(brand not stated)",H107),"")&amp;IF(AND(ISNUMBER(I107),I107=T107),IF(J107="","(brand not stated)",J107),"")&amp;IF(AND(ISNUMBER(K107),K107=T107),IF(L107="","(brand not stated)",L107),"")&amp;IF(AND(ISNUMBER(M107),M107=T107),IF(N107="","(brand not stated)",N107),"")&amp;IF(AND(ISNUMBER(O107),O107=T107),IF(P107="","(brand not stated)",P107),"")&amp;IF(AND(ISNUMBER(Q107),Q107=T107),IF(R107="","(brand not stated)",R107),"")))</f>
+        <v>BRUFEN SYRUP</v>
+      </c>
     </row>
     <row r="108" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="5" t="n">
         <v>103</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F108" s="5" t="n">
         <v>200</v>
@@ -8380,7 +8795,7 @@
         <v>147.05</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I108" s="7"/>
       <c r="J108" s="6"/>
@@ -8392,7 +8807,7 @@
         <v>108.8</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="Q108" s="7"/>
       <c r="R108" s="6"/>
@@ -8413,22 +8828,26 @@
         <v>21760</v>
       </c>
       <c r="W108" s="6"/>
+      <c r="X108" s="9" t="str">
+        <f aca="false">IF(S108=0,"",IF(ISNUMBER(SEARCH(",",U108)),LEFT(IF(AND(ISNUMBER(G108),G108=T108),IF(H108="","(brand not stated)",H108)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I108),I108=T108),IF(J108="","(brand not stated)",J108)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K108),K108=T108),IF(L108="","(brand not stated)",L108)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M108),M108=T108),IF(N108="","(brand not stated)",N108)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O108),O108=T108),IF(P108="","(brand not stated)",P108)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q108),Q108=T108),IF(R108="","(brand not stated)",R108)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G108),G108=T108),IF(H108="","(brand not stated)",H108)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I108),I108=T108),IF(J108="","(brand not stated)",J108)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K108),K108=T108),IF(L108="","(brand not stated)",L108)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M108),M108=T108),IF(N108="","(brand not stated)",N108)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O108),O108=T108),IF(P108="","(brand not stated)",P108)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q108),Q108=T108),IF(R108="","(brand not stated)",R108)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G108),G108=T108),IF(H108="","(brand not stated)",H108),"")&amp;IF(AND(ISNUMBER(I108),I108=T108),IF(J108="","(brand not stated)",J108),"")&amp;IF(AND(ISNUMBER(K108),K108=T108),IF(L108="","(brand not stated)",L108),"")&amp;IF(AND(ISNUMBER(M108),M108=T108),IF(N108="","(brand not stated)",N108),"")&amp;IF(AND(ISNUMBER(O108),O108=T108),IF(P108="","(brand not stated)",P108),"")&amp;IF(AND(ISNUMBER(Q108),Q108=T108),IF(R108="","(brand not stated)",R108),"")))</f>
+        <v>ADDFER 60ML SYRUP</v>
+      </c>
     </row>
     <row r="109" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="5" t="n">
         <v>104</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F109" s="5" t="n">
         <v>100</v>
@@ -8437,25 +8856,25 @@
         <v>292.67</v>
       </c>
       <c r="H109" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I109" s="7" t="n">
         <v>292.67</v>
       </c>
       <c r="J109" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K109" s="7" t="n">
         <v>531.57</v>
       </c>
       <c r="L109" s="6" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M109" s="7" t="n">
         <v>219.5</v>
       </c>
       <c r="N109" s="6" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="O109" s="7"/>
       <c r="P109" s="6"/>
@@ -8478,22 +8897,26 @@
         <v>21950</v>
       </c>
       <c r="W109" s="6"/>
+      <c r="X109" s="9" t="str">
+        <f aca="false">IF(S109=0,"",IF(ISNUMBER(SEARCH(",",U109)),LEFT(IF(AND(ISNUMBER(G109),G109=T109),IF(H109="","(brand not stated)",H109)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I109),I109=T109),IF(J109="","(brand not stated)",J109)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K109),K109=T109),IF(L109="","(brand not stated)",L109)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M109),M109=T109),IF(N109="","(brand not stated)",N109)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O109),O109=T109),IF(P109="","(brand not stated)",P109)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q109),Q109=T109),IF(R109="","(brand not stated)",R109)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G109),G109=T109),IF(H109="","(brand not stated)",H109)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I109),I109=T109),IF(J109="","(brand not stated)",J109)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K109),K109=T109),IF(L109="","(brand not stated)",L109)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M109),M109=T109),IF(N109="","(brand not stated)",N109)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O109),O109=T109),IF(P109="","(brand not stated)",P109)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q109),Q109=T109),IF(R109="","(brand not stated)",R109)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G109),G109=T109),IF(H109="","(brand not stated)",H109),"")&amp;IF(AND(ISNUMBER(I109),I109=T109),IF(J109="","(brand not stated)",J109),"")&amp;IF(AND(ISNUMBER(K109),K109=T109),IF(L109="","(brand not stated)",L109),"")&amp;IF(AND(ISNUMBER(M109),M109=T109),IF(N109="","(brand not stated)",N109),"")&amp;IF(AND(ISNUMBER(O109),O109=T109),IF(P109="","(brand not stated)",P109),"")&amp;IF(AND(ISNUMBER(Q109),Q109=T109),IF(R109="","(brand not stated)",R109),"")))</f>
+        <v>AMCLAV (GETZ)</v>
+      </c>
     </row>
     <row r="110" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="5" t="n">
         <v>105</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F110" s="5" t="n">
         <v>100</v>
@@ -8502,25 +8925,25 @@
         <v>180.11</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I110" s="7" t="n">
         <v>180.11</v>
       </c>
       <c r="J110" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K110" s="7" t="n">
         <v>322.69</v>
       </c>
       <c r="L110" s="6" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="M110" s="7" t="n">
         <v>139.77</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="O110" s="7"/>
       <c r="P110" s="6"/>
@@ -8543,22 +8966,26 @@
         <v>13977</v>
       </c>
       <c r="W110" s="6"/>
+      <c r="X110" s="9" t="str">
+        <f aca="false">IF(S110=0,"",IF(ISNUMBER(SEARCH(",",U110)),LEFT(IF(AND(ISNUMBER(G110),G110=T110),IF(H110="","(brand not stated)",H110)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I110),I110=T110),IF(J110="","(brand not stated)",J110)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K110),K110=T110),IF(L110="","(brand not stated)",L110)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M110),M110=T110),IF(N110="","(brand not stated)",N110)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O110),O110=T110),IF(P110="","(brand not stated)",P110)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q110),Q110=T110),IF(R110="","(brand not stated)",R110)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G110),G110=T110),IF(H110="","(brand not stated)",H110)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I110),I110=T110),IF(J110="","(brand not stated)",J110)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K110),K110=T110),IF(L110="","(brand not stated)",L110)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M110),M110=T110),IF(N110="","(brand not stated)",N110)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O110),O110=T110),IF(P110="","(brand not stated)",P110)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q110),Q110=T110),IF(R110="","(brand not stated)",R110)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G110),G110=T110),IF(H110="","(brand not stated)",H110),"")&amp;IF(AND(ISNUMBER(I110),I110=T110),IF(J110="","(brand not stated)",J110),"")&amp;IF(AND(ISNUMBER(K110),K110=T110),IF(L110="","(brand not stated)",L110),"")&amp;IF(AND(ISNUMBER(M110),M110=T110),IF(N110="","(brand not stated)",N110),"")&amp;IF(AND(ISNUMBER(O110),O110=T110),IF(P110="","(brand not stated)",P110),"")&amp;IF(AND(ISNUMBER(Q110),Q110=T110),IF(R110="","(brand not stated)",R110),"")))</f>
+        <v>AMCLAV (GETZ)</v>
+      </c>
     </row>
     <row r="111" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="5" t="n">
         <v>106</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F111" s="5" t="n">
         <v>500</v>
@@ -8571,7 +8998,7 @@
         <v>145.35</v>
       </c>
       <c r="L111" s="6" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M111" s="7"/>
       <c r="N111" s="6"/>
@@ -8596,22 +9023,26 @@
         <v>72675</v>
       </c>
       <c r="W111" s="6"/>
+      <c r="X111" s="9" t="str">
+        <f aca="false">IF(S111=0,"",IF(ISNUMBER(SEARCH(",",U111)),LEFT(IF(AND(ISNUMBER(G111),G111=T111),IF(H111="","(brand not stated)",H111)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I111),I111=T111),IF(J111="","(brand not stated)",J111)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K111),K111=T111),IF(L111="","(brand not stated)",L111)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M111),M111=T111),IF(N111="","(brand not stated)",N111)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O111),O111=T111),IF(P111="","(brand not stated)",P111)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q111),Q111=T111),IF(R111="","(brand not stated)",R111)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G111),G111=T111),IF(H111="","(brand not stated)",H111)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I111),I111=T111),IF(J111="","(brand not stated)",J111)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K111),K111=T111),IF(L111="","(brand not stated)",L111)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M111),M111=T111),IF(N111="","(brand not stated)",N111)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O111),O111=T111),IF(P111="","(brand not stated)",P111)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q111),Q111=T111),IF(R111="","(brand not stated)",R111)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G111),G111=T111),IF(H111="","(brand not stated)",H111),"")&amp;IF(AND(ISNUMBER(I111),I111=T111),IF(J111="","(brand not stated)",J111),"")&amp;IF(AND(ISNUMBER(K111),K111=T111),IF(L111="","(brand not stated)",L111),"")&amp;IF(AND(ISNUMBER(M111),M111=T111),IF(N111="","(brand not stated)",N111),"")&amp;IF(AND(ISNUMBER(O111),O111=T111),IF(P111="","(brand not stated)",P111),"")&amp;IF(AND(ISNUMBER(Q111),Q111=T111),IF(R111="","(brand not stated)",R111),"")))</f>
+        <v>ARINAC SYRUP</v>
+      </c>
     </row>
     <row r="112" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="5" t="n">
         <v>107</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F112" s="5" t="n">
         <v>10</v>
@@ -8620,13 +9051,13 @@
         <v>352.75</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="I112" s="7" t="n">
         <v>510</v>
       </c>
       <c r="J112" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="6"/>
@@ -8634,13 +9065,13 @@
         <v>403.75</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="O112" s="7" t="n">
         <v>459.01</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="Q112" s="7"/>
       <c r="R112" s="6"/>
@@ -8661,22 +9092,26 @@
         <v>3527.5</v>
       </c>
       <c r="W112" s="6"/>
+      <c r="X112" s="9" t="str">
+        <f aca="false">IF(S112=0,"",IF(ISNUMBER(SEARCH(",",U112)),LEFT(IF(AND(ISNUMBER(G112),G112=T112),IF(H112="","(brand not stated)",H112)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I112),I112=T112),IF(J112="","(brand not stated)",J112)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K112),K112=T112),IF(L112="","(brand not stated)",L112)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M112),M112=T112),IF(N112="","(brand not stated)",N112)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O112),O112=T112),IF(P112="","(brand not stated)",P112)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q112),Q112=T112),IF(R112="","(brand not stated)",R112)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G112),G112=T112),IF(H112="","(brand not stated)",H112)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I112),I112=T112),IF(J112="","(brand not stated)",J112)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K112),K112=T112),IF(L112="","(brand not stated)",L112)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M112),M112=T112),IF(N112="","(brand not stated)",N112)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O112),O112=T112),IF(P112="","(brand not stated)",P112)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q112),Q112=T112),IF(R112="","(brand not stated)",R112)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G112),G112=T112),IF(H112="","(brand not stated)",H112),"")&amp;IF(AND(ISNUMBER(I112),I112=T112),IF(J112="","(brand not stated)",J112),"")&amp;IF(AND(ISNUMBER(K112),K112=T112),IF(L112="","(brand not stated)",L112),"")&amp;IF(AND(ISNUMBER(M112),M112=T112),IF(N112="","(brand not stated)",N112),"")&amp;IF(AND(ISNUMBER(O112),O112=T112),IF(P112="","(brand not stated)",P112),"")&amp;IF(AND(ISNUMBER(Q112),Q112=T112),IF(R112="","(brand not stated)",R112),"")))</f>
+        <v>TONOFLEX</v>
+      </c>
     </row>
     <row r="113" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="5" t="n">
         <v>108</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F113" s="5" t="n">
         <v>40</v>
@@ -8685,7 +9120,7 @@
         <v>552.5</v>
       </c>
       <c r="H113" s="6" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="I113" s="7"/>
       <c r="J113" s="6"/>
@@ -8697,7 +9132,7 @@
         <v>880.94</v>
       </c>
       <c r="P113" s="6" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="Q113" s="7"/>
       <c r="R113" s="6"/>
@@ -8718,22 +9153,26 @@
         <v>22100</v>
       </c>
       <c r="W113" s="6"/>
+      <c r="X113" s="9" t="str">
+        <f aca="false">IF(S113=0,"",IF(ISNUMBER(SEARCH(",",U113)),LEFT(IF(AND(ISNUMBER(G113),G113=T113),IF(H113="","(brand not stated)",H113)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I113),I113=T113),IF(J113="","(brand not stated)",J113)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K113),K113=T113),IF(L113="","(brand not stated)",L113)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M113),M113=T113),IF(N113="","(brand not stated)",N113)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O113),O113=T113),IF(P113="","(brand not stated)",P113)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q113),Q113=T113),IF(R113="","(brand not stated)",R113)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G113),G113=T113),IF(H113="","(brand not stated)",H113)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I113),I113=T113),IF(J113="","(brand not stated)",J113)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K113),K113=T113),IF(L113="","(brand not stated)",L113)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M113),M113=T113),IF(N113="","(brand not stated)",N113)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O113),O113=T113),IF(P113="","(brand not stated)",P113)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q113),Q113=T113),IF(R113="","(brand not stated)",R113)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G113),G113=T113),IF(H113="","(brand not stated)",H113),"")&amp;IF(AND(ISNUMBER(I113),I113=T113),IF(J113="","(brand not stated)",J113),"")&amp;IF(AND(ISNUMBER(K113),K113=T113),IF(L113="","(brand not stated)",L113),"")&amp;IF(AND(ISNUMBER(M113),M113=T113),IF(N113="","(brand not stated)",N113),"")&amp;IF(AND(ISNUMBER(O113),O113=T113),IF(P113="","(brand not stated)",P113),"")&amp;IF(AND(ISNUMBER(Q113),Q113=T113),IF(R113="","(brand not stated)",R113),"")))</f>
+        <v>KETOBAR</v>
+      </c>
     </row>
     <row r="114" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="5" t="n">
         <v>109</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F114" s="5" t="n">
         <v>1000</v>
@@ -8767,22 +9206,26 @@
         <v/>
       </c>
       <c r="W114" s="6"/>
+      <c r="X114" s="9" t="str">
+        <f aca="false">IF(S114=0,"",IF(ISNUMBER(SEARCH(",",U114)),LEFT(IF(AND(ISNUMBER(G114),G114=T114),IF(H114="","(brand not stated)",H114)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I114),I114=T114),IF(J114="","(brand not stated)",J114)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K114),K114=T114),IF(L114="","(brand not stated)",L114)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M114),M114=T114),IF(N114="","(brand not stated)",N114)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O114),O114=T114),IF(P114="","(brand not stated)",P114)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q114),Q114=T114),IF(R114="","(brand not stated)",R114)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G114),G114=T114),IF(H114="","(brand not stated)",H114)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I114),I114=T114),IF(J114="","(brand not stated)",J114)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K114),K114=T114),IF(L114="","(brand not stated)",L114)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M114),M114=T114),IF(N114="","(brand not stated)",N114)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O114),O114=T114),IF(P114="","(brand not stated)",P114)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q114),Q114=T114),IF(R114="","(brand not stated)",R114)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G114),G114=T114),IF(H114="","(brand not stated)",H114),"")&amp;IF(AND(ISNUMBER(I114),I114=T114),IF(J114="","(brand not stated)",J114),"")&amp;IF(AND(ISNUMBER(K114),K114=T114),IF(L114="","(brand not stated)",L114),"")&amp;IF(AND(ISNUMBER(M114),M114=T114),IF(N114="","(brand not stated)",N114),"")&amp;IF(AND(ISNUMBER(O114),O114=T114),IF(P114="","(brand not stated)",P114),"")&amp;IF(AND(ISNUMBER(Q114),Q114=T114),IF(R114="","(brand not stated)",R114),"")))</f>
+        <v/>
+      </c>
     </row>
     <row r="115" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="5" t="n">
         <v>110</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F115" s="5" t="n">
         <v>6</v>
@@ -8799,7 +9242,7 @@
         <v>1147.5</v>
       </c>
       <c r="P115" s="6" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="Q115" s="7"/>
       <c r="R115" s="6"/>
@@ -8820,22 +9263,26 @@
         <v>6885</v>
       </c>
       <c r="W115" s="6"/>
+      <c r="X115" s="9" t="str">
+        <f aca="false">IF(S115=0,"",IF(ISNUMBER(SEARCH(",",U115)),LEFT(IF(AND(ISNUMBER(G115),G115=T115),IF(H115="","(brand not stated)",H115)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I115),I115=T115),IF(J115="","(brand not stated)",J115)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K115),K115=T115),IF(L115="","(brand not stated)",L115)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M115),M115=T115),IF(N115="","(brand not stated)",N115)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O115),O115=T115),IF(P115="","(brand not stated)",P115)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q115),Q115=T115),IF(R115="","(brand not stated)",R115)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G115),G115=T115),IF(H115="","(brand not stated)",H115)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I115),I115=T115),IF(J115="","(brand not stated)",J115)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K115),K115=T115),IF(L115="","(brand not stated)",L115)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M115),M115=T115),IF(N115="","(brand not stated)",N115)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O115),O115=T115),IF(P115="","(brand not stated)",P115)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q115),Q115=T115),IF(R115="","(brand not stated)",R115)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G115),G115=T115),IF(H115="","(brand not stated)",H115),"")&amp;IF(AND(ISNUMBER(I115),I115=T115),IF(J115="","(brand not stated)",J115),"")&amp;IF(AND(ISNUMBER(K115),K115=T115),IF(L115="","(brand not stated)",L115),"")&amp;IF(AND(ISNUMBER(M115),M115=T115),IF(N115="","(brand not stated)",N115),"")&amp;IF(AND(ISNUMBER(O115),O115=T115),IF(P115="","(brand not stated)",P115),"")&amp;IF(AND(ISNUMBER(Q115),Q115=T115),IF(R115="","(brand not stated)",R115),"")))</f>
+        <v>NEUROBION INJECTION</v>
+      </c>
     </row>
     <row r="116" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="5" t="n">
         <v>111</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F116" s="5" t="n">
         <v>20</v>
@@ -8846,7 +9293,7 @@
         <v>7336.77</v>
       </c>
       <c r="J116" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="6"/>
@@ -8854,7 +9301,7 @@
         <v>1134.75</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="O116" s="7"/>
       <c r="P116" s="6"/>
@@ -8877,22 +9324,26 @@
         <v>22695</v>
       </c>
       <c r="W116" s="6"/>
+      <c r="X116" s="9" t="str">
+        <f aca="false">IF(S116=0,"",IF(ISNUMBER(SEARCH(",",U116)),LEFT(IF(AND(ISNUMBER(G116),G116=T116),IF(H116="","(brand not stated)",H116)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I116),I116=T116),IF(J116="","(brand not stated)",J116)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K116),K116=T116),IF(L116="","(brand not stated)",L116)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M116),M116=T116),IF(N116="","(brand not stated)",N116)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O116),O116=T116),IF(P116="","(brand not stated)",P116)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q116),Q116=T116),IF(R116="","(brand not stated)",R116)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G116),G116=T116),IF(H116="","(brand not stated)",H116)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I116),I116=T116),IF(J116="","(brand not stated)",J116)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K116),K116=T116),IF(L116="","(brand not stated)",L116)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M116),M116=T116),IF(N116="","(brand not stated)",N116)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O116),O116=T116),IF(P116="","(brand not stated)",P116)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q116),Q116=T116),IF(R116="","(brand not stated)",R116)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G116),G116=T116),IF(H116="","(brand not stated)",H116),"")&amp;IF(AND(ISNUMBER(I116),I116=T116),IF(J116="","(brand not stated)",J116),"")&amp;IF(AND(ISNUMBER(K116),K116=T116),IF(L116="","(brand not stated)",L116),"")&amp;IF(AND(ISNUMBER(M116),M116=T116),IF(N116="","(brand not stated)",N116),"")&amp;IF(AND(ISNUMBER(O116),O116=T116),IF(P116="","(brand not stated)",P116),"")&amp;IF(AND(ISNUMBER(Q116),Q116=T116),IF(R116="","(brand not stated)",R116),"")))</f>
+        <v>BASAGINE (GETZ)</v>
+      </c>
     </row>
     <row r="117" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="5" t="n">
         <v>112</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F117" s="5" t="n">
         <v>4</v>
@@ -8903,7 +9354,7 @@
         <v>637.5</v>
       </c>
       <c r="J117" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K117" s="7"/>
       <c r="L117" s="6"/>
@@ -8913,7 +9364,7 @@
         <v>585</v>
       </c>
       <c r="P117" s="6" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="Q117" s="7"/>
       <c r="R117" s="6"/>
@@ -8934,22 +9385,26 @@
         <v>2340</v>
       </c>
       <c r="W117" s="6"/>
+      <c r="X117" s="9" t="str">
+        <f aca="false">IF(S117=0,"",IF(ISNUMBER(SEARCH(",",U117)),LEFT(IF(AND(ISNUMBER(G117),G117=T117),IF(H117="","(brand not stated)",H117)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I117),I117=T117),IF(J117="","(brand not stated)",J117)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K117),K117=T117),IF(L117="","(brand not stated)",L117)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M117),M117=T117),IF(N117="","(brand not stated)",N117)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O117),O117=T117),IF(P117="","(brand not stated)",P117)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q117),Q117=T117),IF(R117="","(brand not stated)",R117)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G117),G117=T117),IF(H117="","(brand not stated)",H117)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I117),I117=T117),IF(J117="","(brand not stated)",J117)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K117),K117=T117),IF(L117="","(brand not stated)",L117)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M117),M117=T117),IF(N117="","(brand not stated)",N117)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O117),O117=T117),IF(P117="","(brand not stated)",P117)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q117),Q117=T117),IF(R117="","(brand not stated)",R117)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G117),G117=T117),IF(H117="","(brand not stated)",H117),"")&amp;IF(AND(ISNUMBER(I117),I117=T117),IF(J117="","(brand not stated)",J117),"")&amp;IF(AND(ISNUMBER(K117),K117=T117),IF(L117="","(brand not stated)",L117),"")&amp;IF(AND(ISNUMBER(M117),M117=T117),IF(N117="","(brand not stated)",N117),"")&amp;IF(AND(ISNUMBER(O117),O117=T117),IF(P117="","(brand not stated)",P117),"")&amp;IF(AND(ISNUMBER(Q117),Q117=T117),IF(R117="","(brand not stated)",R117),"")))</f>
+        <v>GRAVINATE 1ML INJECTION</v>
+      </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="5" t="n">
         <v>113</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F118" s="5" t="n">
         <v>50</v>
@@ -8958,13 +9413,13 @@
         <v>233.75</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="I118" s="7" t="n">
         <v>137.22</v>
       </c>
       <c r="J118" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="6"/>
@@ -8991,22 +9446,26 @@
         <v>6861</v>
       </c>
       <c r="W118" s="6"/>
+      <c r="X118" s="9" t="str">
+        <f aca="false">IF(S118=0,"",IF(ISNUMBER(SEARCH(",",U118)),LEFT(IF(AND(ISNUMBER(G118),G118=T118),IF(H118="","(brand not stated)",H118)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I118),I118=T118),IF(J118="","(brand not stated)",J118)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K118),K118=T118),IF(L118="","(brand not stated)",L118)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M118),M118=T118),IF(N118="","(brand not stated)",N118)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O118),O118=T118),IF(P118="","(brand not stated)",P118)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q118),Q118=T118),IF(R118="","(brand not stated)",R118)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G118),G118=T118),IF(H118="","(brand not stated)",H118)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I118),I118=T118),IF(J118="","(brand not stated)",J118)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K118),K118=T118),IF(L118="","(brand not stated)",L118)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M118),M118=T118),IF(N118="","(brand not stated)",N118)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O118),O118=T118),IF(P118="","(brand not stated)",P118)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q118),Q118=T118),IF(R118="","(brand not stated)",R118)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G118),G118=T118),IF(H118="","(brand not stated)",H118),"")&amp;IF(AND(ISNUMBER(I118),I118=T118),IF(J118="","(brand not stated)",J118),"")&amp;IF(AND(ISNUMBER(K118),K118=T118),IF(L118="","(brand not stated)",L118),"")&amp;IF(AND(ISNUMBER(M118),M118=T118),IF(N118="","(brand not stated)",N118),"")&amp;IF(AND(ISNUMBER(O118),O118=T118),IF(P118="","(brand not stated)",P118),"")&amp;IF(AND(ISNUMBER(Q118),Q118=T118),IF(R118="","(brand not stated)",R118),"")))</f>
+        <v>Bosch</v>
+      </c>
     </row>
     <row r="119" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="5" t="n">
         <v>114</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F119" s="5" t="n">
         <v>40</v>
@@ -9015,7 +9474,7 @@
         <v>250.75</v>
       </c>
       <c r="H119" s="6" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="I119" s="7"/>
       <c r="J119" s="6"/>
@@ -9044,22 +9503,26 @@
         <v>10030</v>
       </c>
       <c r="W119" s="6"/>
+      <c r="X119" s="9" t="str">
+        <f aca="false">IF(S119=0,"",IF(ISNUMBER(SEARCH(",",U119)),LEFT(IF(AND(ISNUMBER(G119),G119=T119),IF(H119="","(brand not stated)",H119)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I119),I119=T119),IF(J119="","(brand not stated)",J119)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K119),K119=T119),IF(L119="","(brand not stated)",L119)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M119),M119=T119),IF(N119="","(brand not stated)",N119)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O119),O119=T119),IF(P119="","(brand not stated)",P119)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q119),Q119=T119),IF(R119="","(brand not stated)",R119)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G119),G119=T119),IF(H119="","(brand not stated)",H119)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I119),I119=T119),IF(J119="","(brand not stated)",J119)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K119),K119=T119),IF(L119="","(brand not stated)",L119)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M119),M119=T119),IF(N119="","(brand not stated)",N119)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O119),O119=T119),IF(P119="","(brand not stated)",P119)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q119),Q119=T119),IF(R119="","(brand not stated)",R119)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G119),G119=T119),IF(H119="","(brand not stated)",H119),"")&amp;IF(AND(ISNUMBER(I119),I119=T119),IF(J119="","(brand not stated)",J119),"")&amp;IF(AND(ISNUMBER(K119),K119=T119),IF(L119="","(brand not stated)",L119),"")&amp;IF(AND(ISNUMBER(M119),M119=T119),IF(N119="","(brand not stated)",N119),"")&amp;IF(AND(ISNUMBER(O119),O119=T119),IF(P119="","(brand not stated)",P119),"")&amp;IF(AND(ISNUMBER(Q119),Q119=T119),IF(R119="","(brand not stated)",R119),"")))</f>
+        <v>DICLORAN INJ</v>
+      </c>
     </row>
     <row r="120" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="5" t="n">
         <v>115</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F120" s="5" t="n">
         <v>2</v>
@@ -9070,7 +9533,7 @@
         <v>1275</v>
       </c>
       <c r="J120" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K120" s="7"/>
       <c r="L120" s="6"/>
@@ -9097,22 +9560,26 @@
         <v>2550</v>
       </c>
       <c r="W120" s="6"/>
+      <c r="X120" s="9" t="str">
+        <f aca="false">IF(S120=0,"",IF(ISNUMBER(SEARCH(",",U120)),LEFT(IF(AND(ISNUMBER(G120),G120=T120),IF(H120="","(brand not stated)",H120)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I120),I120=T120),IF(J120="","(brand not stated)",J120)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K120),K120=T120),IF(L120="","(brand not stated)",L120)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M120),M120=T120),IF(N120="","(brand not stated)",N120)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O120),O120=T120),IF(P120="","(brand not stated)",P120)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q120),Q120=T120),IF(R120="","(brand not stated)",R120)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G120),G120=T120),IF(H120="","(brand not stated)",H120)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I120),I120=T120),IF(J120="","(brand not stated)",J120)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K120),K120=T120),IF(L120="","(brand not stated)",L120)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M120),M120=T120),IF(N120="","(brand not stated)",N120)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O120),O120=T120),IF(P120="","(brand not stated)",P120)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q120),Q120=T120),IF(R120="","(brand not stated)",R120)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G120),G120=T120),IF(H120="","(brand not stated)",H120),"")&amp;IF(AND(ISNUMBER(I120),I120=T120),IF(J120="","(brand not stated)",J120),"")&amp;IF(AND(ISNUMBER(K120),K120=T120),IF(L120="","(brand not stated)",L120),"")&amp;IF(AND(ISNUMBER(M120),M120=T120),IF(N120="","(brand not stated)",N120),"")&amp;IF(AND(ISNUMBER(O120),O120=T120),IF(P120="","(brand not stated)",P120),"")&amp;IF(AND(ISNUMBER(Q120),Q120=T120),IF(R120="","(brand not stated)",R120),"")))</f>
+        <v>Hochest</v>
+      </c>
     </row>
     <row r="121" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="5" t="n">
         <v>116</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F121" s="5" t="n">
         <v>20</v>
@@ -9123,7 +9590,7 @@
         <v>6324</v>
       </c>
       <c r="J121" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="6"/>
@@ -9150,22 +9617,26 @@
         <v>126480</v>
       </c>
       <c r="W121" s="6"/>
+      <c r="X121" s="9" t="str">
+        <f aca="false">IF(S121=0,"",IF(ISNUMBER(SEARCH(",",U121)),LEFT(IF(AND(ISNUMBER(G121),G121=T121),IF(H121="","(brand not stated)",H121)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I121),I121=T121),IF(J121="","(brand not stated)",J121)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K121),K121=T121),IF(L121="","(brand not stated)",L121)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M121),M121=T121),IF(N121="","(brand not stated)",N121)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O121),O121=T121),IF(P121="","(brand not stated)",P121)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q121),Q121=T121),IF(R121="","(brand not stated)",R121)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G121),G121=T121),IF(H121="","(brand not stated)",H121)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I121),I121=T121),IF(J121="","(brand not stated)",J121)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K121),K121=T121),IF(L121="","(brand not stated)",L121)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M121),M121=T121),IF(N121="","(brand not stated)",N121)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O121),O121=T121),IF(P121="","(brand not stated)",P121)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q121),Q121=T121),IF(R121="","(brand not stated)",R121)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G121),G121=T121),IF(H121="","(brand not stated)",H121),"")&amp;IF(AND(ISNUMBER(I121),I121=T121),IF(J121="","(brand not stated)",J121),"")&amp;IF(AND(ISNUMBER(K121),K121=T121),IF(L121="","(brand not stated)",L121),"")&amp;IF(AND(ISNUMBER(M121),M121=T121),IF(N121="","(brand not stated)",N121),"")&amp;IF(AND(ISNUMBER(O121),O121=T121),IF(P121="","(brand not stated)",P121),"")&amp;IF(AND(ISNUMBER(Q121),Q121=T121),IF(R121="","(brand not stated)",R121),"")))</f>
+        <v>Hochest</v>
+      </c>
     </row>
     <row r="122" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="5" t="n">
         <v>117</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F122" s="5" t="n">
         <v>2000</v>
@@ -9174,7 +9645,7 @@
         <v>187</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="I122" s="7"/>
       <c r="J122" s="6"/>
@@ -9184,13 +9655,13 @@
         <v>178.5</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="O122" s="7" t="n">
         <v>136</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="Q122" s="7"/>
       <c r="R122" s="6"/>
@@ -9211,22 +9682,26 @@
         <v>272000</v>
       </c>
       <c r="W122" s="6"/>
+      <c r="X122" s="9" t="str">
+        <f aca="false">IF(S122=0,"",IF(ISNUMBER(SEARCH(",",U122)),LEFT(IF(AND(ISNUMBER(G122),G122=T122),IF(H122="","(brand not stated)",H122)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I122),I122=T122),IF(J122="","(brand not stated)",J122)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K122),K122=T122),IF(L122="","(brand not stated)",L122)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M122),M122=T122),IF(N122="","(brand not stated)",N122)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O122),O122=T122),IF(P122="","(brand not stated)",P122)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q122),Q122=T122),IF(R122="","(brand not stated)",R122)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G122),G122=T122),IF(H122="","(brand not stated)",H122)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I122),I122=T122),IF(J122="","(brand not stated)",J122)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K122),K122=T122),IF(L122="","(brand not stated)",L122)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M122),M122=T122),IF(N122="","(brand not stated)",N122)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O122),O122=T122),IF(P122="","(brand not stated)",P122)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q122),Q122=T122),IF(R122="","(brand not stated)",R122)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G122),G122=T122),IF(H122="","(brand not stated)",H122),"")&amp;IF(AND(ISNUMBER(I122),I122=T122),IF(J122="","(brand not stated)",J122),"")&amp;IF(AND(ISNUMBER(K122),K122=T122),IF(L122="","(brand not stated)",L122),"")&amp;IF(AND(ISNUMBER(M122),M122=T122),IF(N122="","(brand not stated)",N122),"")&amp;IF(AND(ISNUMBER(O122),O122=T122),IF(P122="","(brand not stated)",P122),"")&amp;IF(AND(ISNUMBER(Q122),Q122=T122),IF(R122="","(brand not stated)",R122),"")))</f>
+        <v>D-ALL 200000 IU INJECTION</v>
+      </c>
     </row>
     <row r="123" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="5" t="n">
         <v>118</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C123" s="6" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F123" s="5" t="n">
         <v>100</v>
@@ -9235,7 +9710,7 @@
         <v>272</v>
       </c>
       <c r="H123" s="6" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="I123" s="7"/>
       <c r="J123" s="6"/>
@@ -9245,7 +9720,7 @@
         <v>1006.812</v>
       </c>
       <c r="N123" s="6" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O123" s="7"/>
       <c r="P123" s="6"/>
@@ -9268,22 +9743,26 @@
         <v>27200</v>
       </c>
       <c r="W123" s="6"/>
+      <c r="X123" s="9" t="str">
+        <f aca="false">IF(S123=0,"",IF(ISNUMBER(SEARCH(",",U123)),LEFT(IF(AND(ISNUMBER(G123),G123=T123),IF(H123="","(brand not stated)",H123)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I123),I123=T123),IF(J123="","(brand not stated)",J123)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K123),K123=T123),IF(L123="","(brand not stated)",L123)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M123),M123=T123),IF(N123="","(brand not stated)",N123)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O123),O123=T123),IF(P123="","(brand not stated)",P123)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q123),Q123=T123),IF(R123="","(brand not stated)",R123)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G123),G123=T123),IF(H123="","(brand not stated)",H123)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I123),I123=T123),IF(J123="","(brand not stated)",J123)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K123),K123=T123),IF(L123="","(brand not stated)",L123)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M123),M123=T123),IF(N123="","(brand not stated)",N123)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O123),O123=T123),IF(P123="","(brand not stated)",P123)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q123),Q123=T123),IF(R123="","(brand not stated)",R123)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G123),G123=T123),IF(H123="","(brand not stated)",H123),"")&amp;IF(AND(ISNUMBER(I123),I123=T123),IF(J123="","(brand not stated)",J123),"")&amp;IF(AND(ISNUMBER(K123),K123=T123),IF(L123="","(brand not stated)",L123),"")&amp;IF(AND(ISNUMBER(M123),M123=T123),IF(N123="","(brand not stated)",N123),"")&amp;IF(AND(ISNUMBER(O123),O123=T123),IF(P123="","(brand not stated)",P123),"")&amp;IF(AND(ISNUMBER(Q123),Q123=T123),IF(R123="","(brand not stated)",R123),"")))</f>
+        <v>NOVIDAT</v>
+      </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="5" t="n">
         <v>119</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D124" s="6" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="E124" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F124" s="5" t="n">
         <v>50</v>
@@ -9298,7 +9777,7 @@
         <v>677.88</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="O124" s="7"/>
       <c r="P124" s="6"/>
@@ -9321,22 +9800,26 @@
         <v>33894</v>
       </c>
       <c r="W124" s="6"/>
+      <c r="X124" s="9" t="str">
+        <f aca="false">IF(S124=0,"",IF(ISNUMBER(SEARCH(",",U124)),LEFT(IF(AND(ISNUMBER(G124),G124=T124),IF(H124="","(brand not stated)",H124)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I124),I124=T124),IF(J124="","(brand not stated)",J124)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K124),K124=T124),IF(L124="","(brand not stated)",L124)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M124),M124=T124),IF(N124="","(brand not stated)",N124)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O124),O124=T124),IF(P124="","(brand not stated)",P124)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q124),Q124=T124),IF(R124="","(brand not stated)",R124)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G124),G124=T124),IF(H124="","(brand not stated)",H124)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I124),I124=T124),IF(J124="","(brand not stated)",J124)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K124),K124=T124),IF(L124="","(brand not stated)",L124)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M124),M124=T124),IF(N124="","(brand not stated)",N124)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O124),O124=T124),IF(P124="","(brand not stated)",P124)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q124),Q124=T124),IF(R124="","(brand not stated)",R124)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G124),G124=T124),IF(H124="","(brand not stated)",H124),"")&amp;IF(AND(ISNUMBER(I124),I124=T124),IF(J124="","(brand not stated)",J124),"")&amp;IF(AND(ISNUMBER(K124),K124=T124),IF(L124="","(brand not stated)",L124),"")&amp;IF(AND(ISNUMBER(M124),M124=T124),IF(N124="","(brand not stated)",N124),"")&amp;IF(AND(ISNUMBER(O124),O124=T124),IF(P124="","(brand not stated)",P124),"")&amp;IF(AND(ISNUMBER(Q124),Q124=T124),IF(R124="","(brand not stated)",R124),"")))</f>
+        <v>SIBELIUM (ASPIN)</v>
+      </c>
     </row>
     <row r="125" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="5" t="n">
         <v>120</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F125" s="5" t="n">
         <v>100</v>
@@ -9349,7 +9832,7 @@
         <v>529.36</v>
       </c>
       <c r="L125" s="6" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="M125" s="7"/>
       <c r="N125" s="6"/>
@@ -9357,7 +9840,7 @@
         <v>252.45</v>
       </c>
       <c r="P125" s="6" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="Q125" s="7"/>
       <c r="R125" s="6"/>
@@ -9378,22 +9861,26 @@
         <v>25245</v>
       </c>
       <c r="W125" s="6"/>
+      <c r="X125" s="9" t="str">
+        <f aca="false">IF(S125=0,"",IF(ISNUMBER(SEARCH(",",U125)),LEFT(IF(AND(ISNUMBER(G125),G125=T125),IF(H125="","(brand not stated)",H125)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I125),I125=T125),IF(J125="","(brand not stated)",J125)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K125),K125=T125),IF(L125="","(brand not stated)",L125)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M125),M125=T125),IF(N125="","(brand not stated)",N125)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O125),O125=T125),IF(P125="","(brand not stated)",P125)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q125),Q125=T125),IF(R125="","(brand not stated)",R125)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G125),G125=T125),IF(H125="","(brand not stated)",H125)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I125),I125=T125),IF(J125="","(brand not stated)",J125)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K125),K125=T125),IF(L125="","(brand not stated)",L125)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M125),M125=T125),IF(N125="","(brand not stated)",N125)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O125),O125=T125),IF(P125="","(brand not stated)",P125)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q125),Q125=T125),IF(R125="","(brand not stated)",R125)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G125),G125=T125),IF(H125="","(brand not stated)",H125),"")&amp;IF(AND(ISNUMBER(I125),I125=T125),IF(J125="","(brand not stated)",J125),"")&amp;IF(AND(ISNUMBER(K125),K125=T125),IF(L125="","(brand not stated)",L125),"")&amp;IF(AND(ISNUMBER(M125),M125=T125),IF(N125="","(brand not stated)",N125),"")&amp;IF(AND(ISNUMBER(O125),O125=T125),IF(P125="","(brand not stated)",P125),"")&amp;IF(AND(ISNUMBER(Q125),Q125=T125),IF(R125="","(brand not stated)",R125),"")))</f>
+        <v>SANGOBION CAPSULE</v>
+      </c>
     </row>
     <row r="126" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="5" t="n">
         <v>121</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D126" s="6" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F126" s="5" t="n">
         <v>300</v>
@@ -9404,7 +9891,7 @@
         <v>1178.1</v>
       </c>
       <c r="J126" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K126" s="7"/>
       <c r="L126" s="6"/>
@@ -9416,7 +9903,7 @@
         <v>416.5</v>
       </c>
       <c r="R126" s="6" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="S126" s="5" t="n">
         <f aca="false">COUNT(G126,I126,K126,M126,O126,Q126)</f>
@@ -9435,22 +9922,26 @@
         <v>124950</v>
       </c>
       <c r="W126" s="6"/>
+      <c r="X126" s="9" t="str">
+        <f aca="false">IF(S126=0,"",IF(ISNUMBER(SEARCH(",",U126)),LEFT(IF(AND(ISNUMBER(G126),G126=T126),IF(H126="","(brand not stated)",H126)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I126),I126=T126),IF(J126="","(brand not stated)",J126)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K126),K126=T126),IF(L126="","(brand not stated)",L126)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M126),M126=T126),IF(N126="","(brand not stated)",N126)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O126),O126=T126),IF(P126="","(brand not stated)",P126)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q126),Q126=T126),IF(R126="","(brand not stated)",R126)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G126),G126=T126),IF(H126="","(brand not stated)",H126)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I126),I126=T126),IF(J126="","(brand not stated)",J126)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K126),K126=T126),IF(L126="","(brand not stated)",L126)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M126),M126=T126),IF(N126="","(brand not stated)",N126)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O126),O126=T126),IF(P126="","(brand not stated)",P126)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q126),Q126=T126),IF(R126="","(brand not stated)",R126)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G126),G126=T126),IF(H126="","(brand not stated)",H126),"")&amp;IF(AND(ISNUMBER(I126),I126=T126),IF(J126="","(brand not stated)",J126),"")&amp;IF(AND(ISNUMBER(K126),K126=T126),IF(L126="","(brand not stated)",L126),"")&amp;IF(AND(ISNUMBER(M126),M126=T126),IF(N126="","(brand not stated)",N126),"")&amp;IF(AND(ISNUMBER(O126),O126=T126),IF(P126="","(brand not stated)",P126),"")&amp;IF(AND(ISNUMBER(Q126),Q126=T126),IF(R126="","(brand not stated)",R126),"")))</f>
+        <v>Recline</v>
+      </c>
     </row>
     <row r="127" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="5" t="n">
         <v>122</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D127" s="6" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F127" s="5" t="n">
         <v>60</v>
@@ -9461,7 +9952,7 @@
         <v>106.85</v>
       </c>
       <c r="J127" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K127" s="7"/>
       <c r="L127" s="6"/>
@@ -9469,7 +9960,7 @@
         <v>331.91</v>
       </c>
       <c r="N127" s="6" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="O127" s="7"/>
       <c r="P127" s="6"/>
@@ -9492,22 +9983,26 @@
         <v>6411</v>
       </c>
       <c r="W127" s="6"/>
+      <c r="X127" s="9" t="str">
+        <f aca="false">IF(S127=0,"",IF(ISNUMBER(SEARCH(",",U127)),LEFT(IF(AND(ISNUMBER(G127),G127=T127),IF(H127="","(brand not stated)",H127)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I127),I127=T127),IF(J127="","(brand not stated)",J127)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K127),K127=T127),IF(L127="","(brand not stated)",L127)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M127),M127=T127),IF(N127="","(brand not stated)",N127)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O127),O127=T127),IF(P127="","(brand not stated)",P127)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q127),Q127=T127),IF(R127="","(brand not stated)",R127)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G127),G127=T127),IF(H127="","(brand not stated)",H127)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I127),I127=T127),IF(J127="","(brand not stated)",J127)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K127),K127=T127),IF(L127="","(brand not stated)",L127)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M127),M127=T127),IF(N127="","(brand not stated)",N127)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O127),O127=T127),IF(P127="","(brand not stated)",P127)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q127),Q127=T127),IF(R127="","(brand not stated)",R127)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G127),G127=T127),IF(H127="","(brand not stated)",H127),"")&amp;IF(AND(ISNUMBER(I127),I127=T127),IF(J127="","(brand not stated)",J127),"")&amp;IF(AND(ISNUMBER(K127),K127=T127),IF(L127="","(brand not stated)",L127),"")&amp;IF(AND(ISNUMBER(M127),M127=T127),IF(N127="","(brand not stated)",N127),"")&amp;IF(AND(ISNUMBER(O127),O127=T127),IF(P127="","(brand not stated)",P127),"")&amp;IF(AND(ISNUMBER(Q127),Q127=T127),IF(R127="","(brand not stated)",R127),"")))</f>
+        <v>Zafa</v>
+      </c>
     </row>
     <row r="128" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="5" t="n">
         <v>123</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F128" s="5" t="n">
         <v>100</v>
@@ -9516,7 +10011,7 @@
         <v>120.7</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="I128" s="7"/>
       <c r="J128" s="6"/>
@@ -9526,13 +10021,13 @@
         <v>323</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="O128" s="7" t="n">
         <v>127.5</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Q128" s="7"/>
       <c r="R128" s="6"/>
@@ -9553,22 +10048,26 @@
         <v>12070</v>
       </c>
       <c r="W128" s="6"/>
+      <c r="X128" s="9" t="str">
+        <f aca="false">IF(S128=0,"",IF(ISNUMBER(SEARCH(",",U128)),LEFT(IF(AND(ISNUMBER(G128),G128=T128),IF(H128="","(brand not stated)",H128)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I128),I128=T128),IF(J128="","(brand not stated)",J128)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K128),K128=T128),IF(L128="","(brand not stated)",L128)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M128),M128=T128),IF(N128="","(brand not stated)",N128)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O128),O128=T128),IF(P128="","(brand not stated)",P128)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q128),Q128=T128),IF(R128="","(brand not stated)",R128)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G128),G128=T128),IF(H128="","(brand not stated)",H128)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I128),I128=T128),IF(J128="","(brand not stated)",J128)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K128),K128=T128),IF(L128="","(brand not stated)",L128)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M128),M128=T128),IF(N128="","(brand not stated)",N128)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O128),O128=T128),IF(P128="","(brand not stated)",P128)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q128),Q128=T128),IF(R128="","(brand not stated)",R128)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G128),G128=T128),IF(H128="","(brand not stated)",H128),"")&amp;IF(AND(ISNUMBER(I128),I128=T128),IF(J128="","(brand not stated)",J128),"")&amp;IF(AND(ISNUMBER(K128),K128=T128),IF(L128="","(brand not stated)",L128),"")&amp;IF(AND(ISNUMBER(M128),M128=T128),IF(N128="","(brand not stated)",N128),"")&amp;IF(AND(ISNUMBER(O128),O128=T128),IF(P128="","(brand not stated)",P128),"")&amp;IF(AND(ISNUMBER(Q128),Q128=T128),IF(R128="","(brand not stated)",R128),"")))</f>
+        <v>FEROSOFT</v>
+      </c>
     </row>
     <row r="129" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="5" t="n">
         <v>124</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F129" s="5" t="n">
         <v>600</v>
@@ -9577,13 +10076,13 @@
         <v>450.5</v>
       </c>
       <c r="H129" s="6" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="I129" s="7" t="n">
         <v>188.7</v>
       </c>
       <c r="J129" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K129" s="7"/>
       <c r="L129" s="6"/>
@@ -9591,13 +10090,13 @@
         <v>695.3</v>
       </c>
       <c r="N129" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O129" s="7" t="n">
         <v>299.1525</v>
       </c>
       <c r="P129" s="6" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="Q129" s="7"/>
       <c r="R129" s="6"/>
@@ -9618,14 +10117,18 @@
         <v>113220</v>
       </c>
       <c r="W129" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
+      </c>
+      <c r="X129" s="9" t="str">
+        <f aca="false">IF(S129=0,"",IF(ISNUMBER(SEARCH(",",U129)),LEFT(IF(AND(ISNUMBER(G129),G129=T129),IF(H129="","(brand not stated)",H129)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I129),I129=T129),IF(J129="","(brand not stated)",J129)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K129),K129=T129),IF(L129="","(brand not stated)",L129)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M129),M129=T129),IF(N129="","(brand not stated)",N129)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O129),O129=T129),IF(P129="","(brand not stated)",P129)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q129),Q129=T129),IF(R129="","(brand not stated)",R129)&amp;" (Platinum); ",""),LEN(IF(AND(ISNUMBER(G129),G129=T129),IF(H129="","(brand not stated)",H129)&amp;" (Ahsan); ","")&amp;IF(AND(ISNUMBER(I129),I129=T129),IF(J129="","(brand not stated)",J129)&amp;" (Aslam); ","")&amp;IF(AND(ISNUMBER(K129),K129=T129),IF(L129="","(brand not stated)",L129)&amp;" (Jamil); ","")&amp;IF(AND(ISNUMBER(M129),M129=T129),IF(N129="","(brand not stated)",N129)&amp;" (Muller); ","")&amp;IF(AND(ISNUMBER(O129),O129=T129),IF(P129="","(brand not stated)",P129)&amp;" (NMMC); ","")&amp;IF(AND(ISNUMBER(Q129),Q129=T129),IF(R129="","(brand not stated)",R129)&amp;" (Platinum); ",""))-2),IF(AND(ISNUMBER(G129),G129=T129),IF(H129="","(brand not stated)",H129),"")&amp;IF(AND(ISNUMBER(I129),I129=T129),IF(J129="","(brand not stated)",J129),"")&amp;IF(AND(ISNUMBER(K129),K129=T129),IF(L129="","(brand not stated)",L129),"")&amp;IF(AND(ISNUMBER(M129),M129=T129),IF(N129="","(brand not stated)",N129),"")&amp;IF(AND(ISNUMBER(O129),O129=T129),IF(P129="","(brand not stated)",P129),"")&amp;IF(AND(ISNUMBER(Q129),Q129=T129),IF(R129="","(brand not stated)",R129),"")))</f>
+        <v>Bosch</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="11"/>
       <c r="B130" s="11"/>
       <c r="C130" s="12" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D130" s="11"/>
       <c r="E130" s="11"/>
@@ -9650,10 +10153,11 @@
         <v>8776293.9</v>
       </c>
       <c r="W130" s="11"/>
+      <c r="X130" s="11"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:W129"/>
-  <mergeCells count="17">
+  <autoFilter ref="A5:X129"/>
+  <mergeCells count="18">
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="C4:C5"/>
@@ -9671,6 +10175,7 @@
     <mergeCell ref="U4:U5"/>
     <mergeCell ref="V4:V5"/>
     <mergeCell ref="W4:W5"/>
+    <mergeCell ref="X4:X5"/>
   </mergeCells>
   <conditionalFormatting sqref="G6:H129">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
@@ -9731,21 +10236,21 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9852,7 +10357,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B10" s="16"/>
       <c r="C10" s="16" t="n">
@@ -9863,7 +10368,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B11" s="16"/>
       <c r="C11" s="16" t="n">
@@ -9874,37 +10379,37 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="17" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="18" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="18" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="18" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="18" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="18" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="18" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
   </sheetData>
